--- a/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-02-27.xlsx
+++ b/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-02-27.xlsx
@@ -720,12 +720,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -742,12 +742,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.142M</t>
+          <t>0.041M</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -764,22 +764,18 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -790,15 +786,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.416M</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>-0.1M</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
         <v>3</v>
@@ -812,22 +812,18 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.178M</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>-2.75M</t>
-        </is>
-      </c>
+          <t>0.099M</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -838,19 +834,15 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>6.406M</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>-0.1M</t>
-        </is>
-      </c>
+          <t>-0.416M</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
         <v>3</v>
@@ -864,18 +856,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>7.717M</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>0.7M</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -886,12 +882,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.041M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -908,18 +904,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.323M</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -974,12 +974,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/02</t>
+          <t>30-Year Mortgage RateJAN/02</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>6.13%</t>
+          <t>6.91%</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -996,12 +996,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/02</t>
+          <t>15-Year Mortgage RateJAN/02</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>6.91%</t>
+          <t>6.13%</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Fed Kugler Speech</t>
+          <t>Fed Daly Speech</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Fed Daly Speech</t>
+          <t>Fed Kugler Speech</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
@@ -1476,12 +1476,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>4.205%</t>
+          <t>4.110%</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -1498,12 +1498,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>4.110%</t>
+          <t>4.205%</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -1686,22 +1686,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>8.098M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>7.70M</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -1716,22 +1716,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -1746,18 +1746,18 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>3.065M</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -1772,18 +1772,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>3.065M</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
+          <t>64.4</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>57.5</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -1798,22 +1802,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -1828,22 +1832,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>8.098M</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>7.70M</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -1858,22 +1862,18 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>64.4</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>57.5</t>
-        </is>
-      </c>
+          <t>58.2</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2098,26 +2098,22 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/04</t>
+          <t>Jobless Claims 4-week AverageJAN/04</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>201K</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>218K</t>
-        </is>
-      </c>
+          <t>213K</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>213K</t>
+          <t>224K</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70">
@@ -2128,14 +2124,26 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Fed Waller Speech</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr"/>
-      <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr"/>
+          <t>Total Vehicle SalesDEC</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>16.8M</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>16.5M</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>16.3M</t>
+        </is>
+      </c>
       <c r="F70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71">
@@ -2146,26 +2154,14 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsDEC/28</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>1867K</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>1848K</t>
-        </is>
-      </c>
+          <t>Fed Waller Speech</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -2176,26 +2172,26 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Total Vehicle SalesDEC</t>
+          <t>Initial Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>16.8M</t>
+          <t>201K</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>16.5M</t>
+          <t>218K</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>16.3M</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -2206,18 +2202,22 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/04</t>
+          <t>Continuing Jobless ClaimsDEC/28</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>213K</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr"/>
+          <t>1867K</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>224K</t>
+          <t>1848K</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -2306,12 +2306,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>-0.081M</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -2328,22 +2328,18 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>-0.6M</t>
-        </is>
-      </c>
+          <t>0.045M</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79">
@@ -2354,12 +2350,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>-0.167M</t>
+          <t>-0.632M</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -2376,15 +2372,19 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Distillate Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>0.278M</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
+          <t>6.071M</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="n">
         <v>3</v>
@@ -2424,12 +2424,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>0.278M</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -2446,19 +2446,15 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>6.071M</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>1M</t>
-        </is>
-      </c>
+          <t>-0.167M</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="n">
         <v>3</v>
@@ -2472,18 +2468,22 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>-0.632M</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr"/>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>-0.6M</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
@@ -2494,12 +2494,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>0.045M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -2860,18 +2860,22 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>33K</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr"/>
+          <t>34.3</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F102" t="n">
@@ -2886,22 +2890,22 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
@@ -2912,26 +2916,26 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>135K</t>
+          <t>160K</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -2942,26 +2946,26 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -2972,22 +2976,22 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F106" t="n">
@@ -3002,22 +3006,22 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F107" t="n">
@@ -3032,26 +3036,26 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109">
@@ -3062,26 +3066,26 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>160K</t>
+          <t>135K</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110">
@@ -3092,22 +3096,22 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111">
@@ -3118,22 +3122,18 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>34.3</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
+          <t>33K</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F111" t="n">
@@ -3282,10 +3282,14 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>WASDE Report</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr"/>
+          <t>Quarterly Grain Stocks - CornDEC</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>12.074B</t>
+        </is>
+      </c>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="n">
@@ -3300,12 +3304,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - WheatDEC</t>
+          <t>Quarterly Grain Stocks - SoyDEC</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>1.57B</t>
+          <t>3.1B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -3322,14 +3326,10 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - SoyDEC</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>3.1B</t>
-        </is>
-      </c>
+          <t>WASDE Report</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="n">
@@ -3344,12 +3344,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - CornDEC</t>
+          <t>Quarterly Grain Stocks - WheatDEC</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>12.074B</t>
+          <t>1.57B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
@@ -3532,22 +3532,18 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>3.4%</t>
-        </is>
-      </c>
+          <t>146.842</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="F128" t="n">
@@ -3562,18 +3558,22 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr"/>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F129" t="n">
@@ -3588,22 +3588,26 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>146.842</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr"/>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="131">
@@ -3614,12 +3618,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -3629,11 +3633,11 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132">
@@ -3644,26 +3648,22 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="133">
@@ -3674,26 +3674,26 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="134">
@@ -3704,22 +3704,22 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F134" t="n">
@@ -4010,26 +4010,22 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYDEC</t>
+          <t>CPI s.aDEC</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+          <t>317.685</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>317.4</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="148">
@@ -4040,22 +4036,22 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMDEC</t>
+          <t>Core Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
           <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>0.4%</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -4070,26 +4066,26 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYDEC</t>
+          <t>NY Empire State Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>-12.60</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="150">
@@ -4130,26 +4126,26 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexJAN</t>
+          <t>Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>-12.60</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="152">
@@ -4160,22 +4156,22 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMDEC</t>
+          <t>Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F152" t="n">
@@ -4190,22 +4186,26 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>CPI s.aDEC</t>
+          <t>Core Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>317.685</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr"/>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>317.4</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154">
@@ -4252,22 +4252,22 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>3.077M</t>
+          <t>-1.961M</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>1.1M</t>
+          <t>-1.6M</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="157">
@@ -4278,18 +4278,22 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>-0.255M</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>2.60M</t>
+        </is>
+      </c>
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="158">
@@ -4300,12 +4304,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>0.765M</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
@@ -4322,12 +4326,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>-0.021M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
@@ -4344,12 +4348,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>-1.304M</t>
+          <t>0.646M</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
@@ -4366,12 +4370,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>0.765M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
@@ -4388,22 +4392,18 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>2.60M</t>
-        </is>
-      </c>
+          <t>-0.255M</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="163">
@@ -4414,22 +4414,22 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>-1.961M</t>
+          <t>3.077M</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>-1.6M</t>
+          <t>1.1M</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="164">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>0.646M</t>
+          <t>-0.021M</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
@@ -4556,26 +4556,26 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>1859K</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1870.0K</t>
         </is>
       </c>
       <c r="F170" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="171">
@@ -4586,22 +4586,22 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>217K</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>210K</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F171" t="n">
@@ -4616,26 +4616,26 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="173">
@@ -4646,26 +4646,22 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
+          <t>3.9%</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="174">
@@ -4676,16 +4672,24 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr"/>
-      <c r="E174" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>1.6%</t>
+        </is>
+      </c>
       <c r="F174" t="n">
         <v>3</v>
       </c>
@@ -4698,18 +4702,18 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>212.75K</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F175" t="n">
@@ -4724,18 +4728,26 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>46.3</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr"/>
-      <c r="E176" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F176" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="177">
@@ -4746,12 +4758,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>31.90</t>
+          <t>39.00</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
@@ -4768,12 +4780,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>39.00</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="D178" t="inlineStr"/>
@@ -4790,26 +4802,18 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>46.3</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr"/>
       <c r="F179" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="180">
@@ -4820,18 +4824,18 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>212.75K</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F180" t="n">
@@ -4846,22 +4850,26 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>3.9%</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F181" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="182">
@@ -4872,26 +4880,26 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="183">
@@ -4902,22 +4910,22 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>217K</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>210K</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>209.0K</t>
         </is>
       </c>
       <c r="F183" t="n">
@@ -4932,26 +4940,26 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="185">
@@ -4962,24 +4970,16 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>1.6%</t>
-        </is>
-      </c>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr"/>
+      <c r="E185" t="inlineStr"/>
       <c r="F185" t="n">
         <v>3</v>
       </c>
@@ -4992,12 +4992,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
@@ -5014,26 +5014,26 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>NAHB Housing Market IndexJAN</t>
+          <t>Retail Inventories Ex Autos MoMNOV</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F187" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="188">
@@ -5044,17 +5044,17 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoMNOV</t>
+          <t>Business Inventories MoMNOV</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -5063,7 +5063,7 @@
         </is>
       </c>
       <c r="F188" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="189">
@@ -5074,22 +5074,22 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Business Inventories MoMNOV</t>
+          <t>NAHB Housing Market IndexJAN</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F189" t="n">
@@ -5352,22 +5352,22 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMDEC</t>
+          <t>Capacity UtilizationDEC</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="F200" t="n">
@@ -5382,18 +5382,18 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Industrial Production YoYDEC</t>
+          <t>Manufacturing Production YoYDEC</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D201" t="inlineStr"/>
       <c r="E201" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F201" t="n">
@@ -5408,26 +5408,22 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Industrial Production MoMDEC</t>
+          <t>Industrial Production YoYDEC</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr"/>
       <c r="E202" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F202" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="203">
@@ -5438,18 +5434,22 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYDEC</t>
+          <t>Manufacturing Production MoMDEC</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr"/>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F203" t="n">
@@ -5464,26 +5464,26 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Capacity UtilizationDEC</t>
+          <t>Industrial Production MoMDEC</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F204" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="205">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>4.165%</t>
+          <t>4.215%</t>
         </is>
       </c>
       <c r="D211" t="inlineStr"/>
@@ -5648,12 +5648,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>4.215%</t>
+          <t>4.165%</t>
         </is>
       </c>
       <c r="D212" t="inlineStr"/>
@@ -5670,12 +5670,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>42-Day Bill Auction</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>4.025%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
@@ -5692,12 +5692,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>42-Day Bill Auction</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>4.025%</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
@@ -5942,22 +5942,18 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/11</t>
+          <t>Jobless Claims 4-week AverageJAN/18</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>1899K</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>1860K</t>
-        </is>
-      </c>
+          <t>213.5K</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr"/>
       <c r="E225" t="inlineStr">
         <is>
-          <t>1861K</t>
+          <t>213.0K</t>
         </is>
       </c>
       <c r="F225" t="n">
@@ -6002,18 +5998,22 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/18</t>
+          <t>Continuing Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>213.5K</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr"/>
+          <t>1899K</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>1860K</t>
+        </is>
+      </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>213.0K</t>
+          <t>1861K</t>
         </is>
       </c>
       <c r="F227" t="n">
@@ -6150,18 +6150,22 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>-0.148M</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E233" t="inlineStr"/>
       <c r="F233" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="234">
@@ -6172,12 +6176,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
@@ -6194,19 +6198,15 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>0.068M</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr"/>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="n">
         <v>3</v>
@@ -6220,18 +6220,22 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>6.96%</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E236" t="inlineStr"/>
       <c r="F236" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="237">
@@ -6242,12 +6246,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
@@ -6264,15 +6268,19 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>0.184M</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="n">
         <v>3</v>
@@ -6286,12 +6294,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
@@ -6308,22 +6316,18 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>6.96%</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr"/>
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="241">
@@ -6334,12 +6338,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D241" t="inlineStr"/>
@@ -6356,12 +6360,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -6378,22 +6382,18 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>-0.148M</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr"/>
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="244">
@@ -6534,26 +6534,26 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F249" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="250">
@@ -6564,26 +6564,26 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.24M</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.19M</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="F250" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="251">
@@ -6594,22 +6594,26 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr"/>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F251" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="252">
@@ -6620,22 +6624,22 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F252" t="n">
@@ -6650,26 +6654,22 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr"/>
       <c r="E253" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F253" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="254">
@@ -6680,26 +6680,26 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>4.24M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>4.19M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F254" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="255">
@@ -6710,26 +6710,26 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F255" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="256">
@@ -7040,26 +7040,22 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMDEC</t>
+          <t>Durable Goods Orders ex Defense MoMDEC</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D268" t="inlineStr">
+          <t>-2.4%</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr"/>
+      <c r="E268" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
-      <c r="E268" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
       <c r="F268" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="269">
@@ -7070,26 +7066,26 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirDEC</t>
+          <t>Durable Goods Orders MoMDEC</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
+          <t>-2.2%</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
           <t>0.5%</t>
         </is>
       </c>
-      <c r="D269" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E269" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
       <c r="F269" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="270">
@@ -7100,22 +7096,26 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMDEC</t>
+          <t>Durable Goods Orders Ex Transp MoMDEC</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>-2.4%</t>
-        </is>
-      </c>
-      <c r="D270" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E270" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
       <c r="F270" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="271">
@@ -7126,26 +7126,26 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMDEC</t>
+          <t>Non Defense Goods Orders Ex AirDEC</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F271" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="272">
@@ -7316,26 +7316,26 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexJAN</t>
+          <t>CB Consumer ConfidenceJAN</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>104.1</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>105.6</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F278" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="279">
@@ -7346,18 +7346,22 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexJAN</t>
+          <t>Richmond Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr"/>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>-8</t>
+        </is>
+      </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="F279" t="n">
@@ -7372,18 +7376,18 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
+          <t>Richmond Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D280" t="inlineStr"/>
       <c r="E280" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F280" t="n">
@@ -7398,26 +7402,22 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceJAN</t>
+          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>104.1</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr">
-        <is>
-          <t>105.6</t>
-        </is>
-      </c>
+          <t>-9</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr"/>
       <c r="E281" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="F281" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="282">
@@ -7428,18 +7428,18 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexJAN</t>
+          <t>Dallas Fed Services IndexJAN</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="D282" t="inlineStr"/>
       <c r="E282" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="F282" t="n">
@@ -7454,18 +7454,18 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexJAN</t>
+          <t>Dallas Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="D283" t="inlineStr"/>
       <c r="E283" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F283" t="n">
@@ -7704,18 +7704,22 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoM AdvDEC</t>
+          <t>Goods Trade Balance AdvDEC</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D294" t="inlineStr"/>
+          <t>$-122.11B</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>$-105.4B</t>
+        </is>
+      </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>$ -106B</t>
         </is>
       </c>
       <c r="F294" t="n">
@@ -7760,22 +7764,18 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvDEC</t>
+          <t>Retail Inventories Ex Autos MoM AdvDEC</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>$-122.11B</t>
-        </is>
-      </c>
-      <c r="D296" t="inlineStr">
-        <is>
-          <t>$-105.4B</t>
-        </is>
-      </c>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr"/>
       <c r="E296" t="inlineStr">
         <is>
-          <t>$ -106B</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F296" t="n">
@@ -8324,22 +8324,18 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Pending Home Sales MoMDEC</t>
+          <t>Pending Home Sales YoYDEC</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>-5.5%</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
+          <t>-5.0%</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr"/>
       <c r="E318" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F318" t="n">
@@ -8354,18 +8350,22 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Pending Home Sales YoYDEC</t>
+          <t>Pending Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>-5.0%</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr"/>
+          <t>-5.5%</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F319" t="n">
@@ -8516,20 +8516,12 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
-        </is>
-      </c>
-      <c r="C326" t="inlineStr">
-        <is>
-          <t>0.8%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr"/>
       <c r="D326" t="inlineStr"/>
-      <c r="E326" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+      <c r="E326" t="inlineStr"/>
       <c r="F326" t="n">
         <v>2</v>
       </c>
@@ -8542,26 +8534,26 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F327" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="328">
@@ -8572,18 +8564,22 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F328" t="n">
@@ -8598,26 +8594,26 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
+          <t>PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F329" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="330">
@@ -8628,26 +8624,26 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>Core PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F330" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="331">
@@ -8658,26 +8654,26 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F331" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="332">
@@ -8688,12 +8684,20 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C332" t="inlineStr"/>
+          <t>Employment Cost - Wages QoQQ4</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>0.9%</t>
+        </is>
+      </c>
       <c r="D332" t="inlineStr"/>
-      <c r="E332" t="inlineStr"/>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>0.7%</t>
+        </is>
+      </c>
       <c r="F332" t="n">
         <v>2</v>
       </c>
@@ -8706,26 +8710,26 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
+          <t>Personal Income MoMDEC</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F333" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="334">
@@ -8736,22 +8740,18 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
+          <t>Employment Cost - Benefits QoQQ4</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr"/>
       <c r="E334" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F334" t="n">
@@ -8766,26 +8766,26 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F335" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="336">
@@ -8904,18 +8904,22 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersJAN</t>
+          <t>Construction Spending MoMDEC</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>55.1</t>
-        </is>
-      </c>
-      <c r="D340" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F340" t="n">
@@ -8930,22 +8934,26 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentJAN</t>
+          <t>ISM Manufacturing PMIJAN</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>50.3</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr"/>
+          <t>50.9</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>49.8</t>
+        </is>
+      </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="F341" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="342">
@@ -8956,26 +8964,22 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesJAN</t>
+          <t>ISM Manufacturing EmploymentJAN</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>54.9</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
+          <t>50.3</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr"/>
       <c r="E342" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F342" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="343">
@@ -8986,22 +8990,18 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Construction Spending MoMDEC</t>
+          <t>ISM Manufacturing New OrdersJAN</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>55.1</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr"/>
       <c r="E343" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F343" t="n">
@@ -9016,26 +9016,26 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIJAN</t>
+          <t>ISM Manufacturing PricesJAN</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F344" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="345">
@@ -9206,26 +9206,26 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Factory Orders MoMDEC</t>
+          <t>JOLTs Job OpeningsDEC</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>7.6M</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>8M</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>7.8M</t>
         </is>
       </c>
       <c r="F353" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="354">
@@ -9236,18 +9236,18 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsDEC</t>
+          <t>Factory Orders ex TransportationDEC</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>3.197M</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D354" t="inlineStr"/>
       <c r="E354" t="inlineStr">
         <is>
-          <t>3.1M</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F354" t="n">
@@ -9262,22 +9262,26 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationDEC</t>
+          <t>Factory Orders MoMDEC</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr"/>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>-0.7%</t>
+        </is>
+      </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F355" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="356">
@@ -9288,26 +9292,22 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsDEC</t>
+          <t>JOLTs Job QuitsDEC</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>7.6M</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr">
-        <is>
-          <t>8M</t>
-        </is>
-      </c>
+          <t>3.197M</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr"/>
       <c r="E356" t="inlineStr">
         <is>
-          <t>7.8M</t>
+          <t>3.1M</t>
         </is>
       </c>
       <c r="F356" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="357">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/31</t>
+          <t>MBA Mortgage Refinance IndexJAN/31</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>224.8</t>
+          <t>584.3</t>
         </is>
       </c>
       <c r="D363" t="inlineStr"/>
@@ -9472,12 +9472,12 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/31</t>
+          <t>MBA Mortgage Market IndexJAN/31</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>584.3</t>
+          <t>224.8</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
@@ -9590,18 +9590,18 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>ImportsDEC</t>
+          <t>ExportsDEC</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>$364.9B</t>
+          <t>$266.5B</t>
         </is>
       </c>
       <c r="D369" t="inlineStr"/>
       <c r="E369" t="inlineStr">
         <is>
-          <t>$ 355.0B</t>
+          <t>$ 262B</t>
         </is>
       </c>
       <c r="F369" t="n">
@@ -9616,14 +9616,26 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Treasury Refunding Announcement</t>
-        </is>
-      </c>
-      <c r="C370" t="inlineStr"/>
-      <c r="D370" t="inlineStr"/>
-      <c r="E370" t="inlineStr"/>
+          <t>Balance of TradeDEC</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>$-98.4B</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>$-96.6B</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>$ -93.0B</t>
+        </is>
+      </c>
       <c r="F370" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="371">
@@ -9634,18 +9646,18 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>ExportsDEC</t>
+          <t>ImportsDEC</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>$266.5B</t>
+          <t>$364.9B</t>
         </is>
       </c>
       <c r="D371" t="inlineStr"/>
       <c r="E371" t="inlineStr">
         <is>
-          <t>$ 262B</t>
+          <t>$ 355.0B</t>
         </is>
       </c>
       <c r="F371" t="n">
@@ -9660,26 +9672,14 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Balance of TradeDEC</t>
-        </is>
-      </c>
-      <c r="C372" t="inlineStr">
-        <is>
-          <t>$-98.4B</t>
-        </is>
-      </c>
-      <c r="D372" t="inlineStr">
-        <is>
-          <t>$-96.6B</t>
-        </is>
-      </c>
-      <c r="E372" t="inlineStr">
-        <is>
-          <t>$ -93.0B</t>
-        </is>
-      </c>
+          <t>Treasury Refunding Announcement</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr"/>
+      <c r="D372" t="inlineStr"/>
+      <c r="E372" t="inlineStr"/>
       <c r="F372" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="373">
@@ -9768,18 +9768,18 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersJAN</t>
+          <t>ISM Services PricesJAN</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>60.4</t>
         </is>
       </c>
       <c r="D376" t="inlineStr"/>
       <c r="E376" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="F376" t="n">
@@ -9794,22 +9794,26 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentJAN</t>
+          <t>ISM Services PMIJAN</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>52.3</t>
-        </is>
-      </c>
-      <c r="D377" t="inlineStr"/>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>54.3</t>
+        </is>
+      </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F377" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="378">
@@ -9820,26 +9824,22 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>ISM Services PMIJAN</t>
+          <t>ISM Services Business ActivityJAN</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>52.8</t>
-        </is>
-      </c>
-      <c r="D378" t="inlineStr">
-        <is>
-          <t>54.3</t>
-        </is>
-      </c>
+          <t>54.5</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr"/>
       <c r="E378" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="F378" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="379">
@@ -9850,18 +9850,18 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityJAN</t>
+          <t>ISM Services EmploymentJAN</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="D379" t="inlineStr"/>
       <c r="E379" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F379" t="n">
@@ -9876,18 +9876,18 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>ISM Services PricesJAN</t>
+          <t>ISM Services New OrdersJAN</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="D380" t="inlineStr"/>
       <c r="E380" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F380" t="n">
@@ -9902,22 +9902,18 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>2.233M</t>
-        </is>
-      </c>
-      <c r="D381" t="inlineStr">
-        <is>
-          <t>1.2M</t>
-        </is>
-      </c>
+          <t>-0.027M</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr"/>
       <c r="E381" t="inlineStr"/>
       <c r="F381" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="382">
@@ -9928,15 +9924,19 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>-0.186M</t>
-        </is>
-      </c>
-      <c r="D382" t="inlineStr"/>
+          <t>-5.471M</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>-1.5M</t>
+        </is>
+      </c>
       <c r="E382" t="inlineStr"/>
       <c r="F382" t="n">
         <v>3</v>
@@ -9950,12 +9950,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>-0.178M</t>
+          <t>0.16M</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
@@ -9972,22 +9972,18 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>8.664M</t>
-        </is>
-      </c>
-      <c r="D384" t="inlineStr">
-        <is>
-          <t>2.6M</t>
-        </is>
-      </c>
+          <t>-0.034M</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr"/>
       <c r="E384" t="inlineStr"/>
       <c r="F384" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="385">
@@ -9998,12 +9994,12 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>-0.034M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="D385" t="inlineStr"/>
@@ -10020,12 +10016,12 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Crude Oil Imports ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>0.16M</t>
+          <t>-0.178M</t>
         </is>
       </c>
       <c r="D386" t="inlineStr"/>
@@ -10042,12 +10038,12 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>0.373M</t>
+          <t>-0.186M</t>
         </is>
       </c>
       <c r="D387" t="inlineStr"/>
@@ -10064,22 +10060,22 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>-5.471M</t>
+          <t>2.233M</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>-1.5M</t>
+          <t>1.2M</t>
         </is>
       </c>
       <c r="E388" t="inlineStr"/>
       <c r="F388" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="389">
@@ -10090,18 +10086,22 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>-0.027M</t>
-        </is>
-      </c>
-      <c r="D389" t="inlineStr"/>
+          <t>8.664M</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>2.6M</t>
+        </is>
+      </c>
       <c r="E389" t="inlineStr"/>
       <c r="F389" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="390">
@@ -10196,26 +10196,26 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Unit Labour Costs QoQ PrelQ4</t>
+          <t>Continuing Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>1886K</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>1855.0K</t>
         </is>
       </c>
       <c r="F394" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="395">
@@ -10226,26 +10226,22 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/01</t>
+          <t>Jobless Claims 4-week AverageFEB/01</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>219K</t>
-        </is>
-      </c>
-      <c r="D395" t="inlineStr">
-        <is>
-          <t>213K</t>
-        </is>
-      </c>
+          <t>216.75K</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr"/>
       <c r="E395" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>215.5K</t>
         </is>
       </c>
       <c r="F395" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="396">
@@ -10256,22 +10252,22 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Nonfarm Productivity QoQ PrelQ4</t>
+          <t>Initial Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F396" t="n">
@@ -10286,26 +10282,26 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/25</t>
+          <t>Unit Labour Costs QoQ PrelQ4</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>1886K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>1855.0K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F397" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="398">
@@ -10316,22 +10312,26 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/01</t>
+          <t>Nonfarm Productivity QoQ PrelQ4</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>216.75K</t>
-        </is>
-      </c>
-      <c r="D398" t="inlineStr"/>
+          <t>1.2%</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>1.4%</t>
+        </is>
+      </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>215.5K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F398" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="399">
@@ -10536,22 +10536,26 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Government PayrollsJAN</t>
+          <t>Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>32K</t>
-        </is>
-      </c>
-      <c r="D408" t="inlineStr"/>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>4.1%</t>
+        </is>
+      </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>25K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F408" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="409">
@@ -10562,18 +10566,22 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Participation RateJAN</t>
+          <t>Average Hourly Earnings YoYJAN</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>62.6%</t>
-        </is>
-      </c>
-      <c r="D409" t="inlineStr"/>
+          <t>4.1%</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="F409" t="n">
@@ -10588,26 +10596,26 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoYJAN</t>
+          <t>Manufacturing PayrollsJAN</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>3K</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>-2K</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>-5K</t>
         </is>
       </c>
       <c r="F410" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="411">
@@ -10618,26 +10626,22 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsJAN</t>
+          <t>U-6 Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>143K</t>
-        </is>
-      </c>
-      <c r="D411" t="inlineStr">
-        <is>
-          <t>170K</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr"/>
       <c r="E411" t="inlineStr">
         <is>
-          <t>205K</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="F411" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="412">
@@ -10648,22 +10652,22 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Average Weekly HoursJAN</t>
+          <t>Nonfarm Payrolls PrivateJAN</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>111K</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>141K</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>180K</t>
         </is>
       </c>
       <c r="F412" t="n">
@@ -10678,26 +10682,22 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMJAN</t>
+          <t>Government PayrollsJAN</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D413" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>32K</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr"/>
       <c r="E413" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>25K</t>
         </is>
       </c>
       <c r="F413" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="414">
@@ -10708,22 +10708,22 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateJAN</t>
+          <t>Average Weekly HoursJAN</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>111K</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>141K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>180K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F414" t="n">
@@ -10738,26 +10738,26 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsJAN</t>
+          <t>Non Farm PayrollsJAN</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>3K</t>
+          <t>143K</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>-2K</t>
+          <t>170K</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>-5K</t>
+          <t>205K</t>
         </is>
       </c>
       <c r="F415" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="416">
@@ -10768,26 +10768,22 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Unemployment RateJAN</t>
+          <t>Participation RateJAN</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>4%</t>
-        </is>
-      </c>
-      <c r="D416" t="inlineStr">
-        <is>
-          <t>4.1%</t>
-        </is>
-      </c>
+          <t>62.6%</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr"/>
       <c r="E416" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="F416" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="417">
@@ -10798,22 +10794,26 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>U-6 Unemployment RateJAN</t>
+          <t>Average Hourly Earnings MoMJAN</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D417" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F417" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="418">
@@ -10904,26 +10904,22 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelFEB</t>
+          <t>Michigan 5 Year Inflation Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>67.8</t>
-        </is>
-      </c>
-      <c r="D422" t="inlineStr">
-        <is>
-          <t>71.1</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr"/>
       <c r="E422" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F422" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="423">
@@ -10934,22 +10930,22 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelFEB</t>
+          <t>Michigan Consumer Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="F423" t="n">
@@ -10964,22 +10960,18 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoMDEC</t>
+          <t>Michigan Inflation Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
-      <c r="D424" t="inlineStr">
-        <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr"/>
       <c r="E424" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F424" t="n">
@@ -10994,22 +10986,22 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelFEB</t>
+          <t>Michigan Current Conditions PrelFEB</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>73</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="F425" t="n">
@@ -11024,22 +11016,26 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelFEB</t>
+          <t>Michigan Consumer Sentiment PrelFEB</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="D426" t="inlineStr"/>
+          <t>67.8</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>71.1</t>
+        </is>
+      </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F426" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="427">
@@ -11050,18 +11046,22 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelFEB</t>
+          <t>Wholesale Inventories MoMDEC</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D427" t="inlineStr"/>
+          <t>-0.5%</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>-0.5%</t>
+        </is>
+      </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F427" t="n">
@@ -11564,18 +11564,18 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C452" t="inlineStr"/>
       <c r="D452" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F452" t="n">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C453" t="inlineStr"/>
@@ -11601,7 +11601,7 @@
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F453" t="n">
@@ -11616,14 +11616,18 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>CPI s.aJAN</t>
+          <t>CPIJAN</t>
         </is>
       </c>
       <c r="C454" t="inlineStr"/>
-      <c r="D454" t="inlineStr"/>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>317.42</t>
+        </is>
+      </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>318.2</t>
+          <t>317.3</t>
         </is>
       </c>
       <c r="F454" t="n">
@@ -11638,22 +11642,22 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>CPIJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C455" t="inlineStr"/>
       <c r="D455" t="inlineStr">
         <is>
-          <t>317.42</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>317.3</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F455" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="456">
@@ -11664,7 +11668,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C456" t="inlineStr"/>
@@ -11675,7 +11679,7 @@
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F456" t="n">
@@ -11690,22 +11694,18 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>CPI s.aJAN</t>
         </is>
       </c>
       <c r="C457" t="inlineStr"/>
-      <c r="D457" t="inlineStr">
-        <is>
-          <t>2.9%</t>
-        </is>
-      </c>
+      <c r="D457" t="inlineStr"/>
       <c r="E457" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>318.2</t>
         </is>
       </c>
       <c r="F457" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="458">
@@ -11716,7 +11716,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C458" t="inlineStr"/>
@@ -11734,7 +11734,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C459" t="inlineStr"/>
@@ -11752,7 +11752,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C460" t="inlineStr"/>
@@ -11770,14 +11770,14 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C461" t="inlineStr"/>
       <c r="D461" t="inlineStr"/>
       <c r="E461" t="inlineStr"/>
       <c r="F461" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="462">
@@ -11788,14 +11788,14 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C462" t="inlineStr"/>
       <c r="D462" t="inlineStr"/>
       <c r="E462" t="inlineStr"/>
       <c r="F462" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="463">
@@ -11806,14 +11806,14 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C463" t="inlineStr"/>
       <c r="D463" t="inlineStr"/>
       <c r="E463" t="inlineStr"/>
       <c r="F463" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="464">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C464" t="inlineStr"/>
@@ -11842,7 +11842,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C465" t="inlineStr"/>
@@ -11860,14 +11860,14 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C466" t="inlineStr"/>
       <c r="D466" t="inlineStr"/>
       <c r="E466" t="inlineStr"/>
       <c r="F466" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="467">
@@ -11976,14 +11976,18 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C472" t="inlineStr"/>
-      <c r="D472" t="inlineStr"/>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F472" t="n">
@@ -11998,14 +12002,14 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C473" t="inlineStr"/>
       <c r="D473" t="inlineStr"/>
       <c r="E473" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="F473" t="n">
@@ -12020,18 +12024,22 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C474" t="inlineStr"/>
-      <c r="D474" t="inlineStr"/>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F474" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="475">
@@ -12042,22 +12050,22 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C475" t="inlineStr"/>
       <c r="D475" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F475" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="476">
@@ -12068,18 +12076,22 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C476" t="inlineStr"/>
-      <c r="D476" t="inlineStr"/>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F476" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="477">
@@ -12090,22 +12102,18 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C477" t="inlineStr"/>
-      <c r="D477" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D477" t="inlineStr"/>
       <c r="E477" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="F477" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="478">
@@ -12116,18 +12124,18 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C478" t="inlineStr"/>
       <c r="D478" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F478" t="n">
@@ -12142,22 +12150,18 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C479" t="inlineStr"/>
-      <c r="D479" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
+      <c r="D479" t="inlineStr"/>
       <c r="E479" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F479" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="480">
@@ -12168,22 +12172,18 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C480" t="inlineStr"/>
-      <c r="D480" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D480" t="inlineStr"/>
       <c r="E480" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="F480" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="481">
@@ -12194,14 +12194,14 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C481" t="inlineStr"/>
       <c r="D481" t="inlineStr"/>
       <c r="E481" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F481" t="n">
@@ -12574,18 +12574,14 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="C499" t="inlineStr"/>
-      <c r="D499" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+      <c r="D499" t="inlineStr"/>
       <c r="E499" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F499" t="n">
@@ -12600,14 +12596,18 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="C500" t="inlineStr"/>
-      <c r="D500" t="inlineStr"/>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>77.7%</t>
+        </is>
+      </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="F500" t="n">
@@ -12622,22 +12622,22 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="C501" t="inlineStr"/>
       <c r="D501" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F501" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="502">
@@ -12648,22 +12648,22 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Manufacturing Production MoMJAN</t>
         </is>
       </c>
       <c r="C502" t="inlineStr"/>
       <c r="D502" t="inlineStr">
         <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
           <t>0.2%</t>
         </is>
       </c>
-      <c r="E502" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
       <c r="F502" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="503">
@@ -12674,14 +12674,14 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="C503" t="inlineStr"/>
       <c r="D503" t="inlineStr"/>
       <c r="E503" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F503" t="n">
@@ -13248,14 +13248,18 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Net Long-term TIC FlowsDEC</t>
         </is>
       </c>
       <c r="C532" t="inlineStr"/>
-      <c r="D532" t="inlineStr"/>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>$149.1B</t>
+        </is>
+      </c>
       <c r="E532" t="inlineStr"/>
       <c r="F532" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="533">
@@ -13324,18 +13328,14 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsDEC</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="C536" t="inlineStr"/>
-      <c r="D536" t="inlineStr">
-        <is>
-          <t>$149.1B</t>
-        </is>
-      </c>
+      <c r="D536" t="inlineStr"/>
       <c r="E536" t="inlineStr"/>
       <c r="F536" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="537">
@@ -13552,18 +13552,18 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C548" t="inlineStr"/>
       <c r="D548" t="inlineStr">
         <is>
-          <t>1.45M</t>
+          <t>1.39M</t>
         </is>
       </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F548" t="n">
@@ -13648,22 +13648,18 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C552" t="inlineStr"/>
-      <c r="D552" t="inlineStr">
-        <is>
-          <t>1.39M</t>
-        </is>
-      </c>
+      <c r="D552" t="inlineStr"/>
       <c r="E552" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F552" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="553">
@@ -13674,14 +13670,14 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C553" t="inlineStr"/>
       <c r="D553" t="inlineStr"/>
       <c r="E553" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F553" t="n">
@@ -13696,18 +13692,22 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C554" t="inlineStr"/>
-      <c r="D554" t="inlineStr"/>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>1.45M</t>
+        </is>
+      </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F554" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="555">
@@ -14112,7 +14112,7 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C576" t="inlineStr"/>
@@ -14130,7 +14130,7 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C577" t="inlineStr"/>
@@ -14200,16 +14200,12 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C580" t="inlineStr"/>
       <c r="D580" t="inlineStr"/>
-      <c r="E580" t="inlineStr">
-        <is>
-          <t>1879.0K</t>
-        </is>
-      </c>
+      <c r="E580" t="inlineStr"/>
       <c r="F580" t="n">
         <v>3</v>
       </c>
@@ -14222,16 +14218,12 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C581" t="inlineStr"/>
       <c r="D581" t="inlineStr"/>
-      <c r="E581" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="E581" t="inlineStr"/>
       <c r="F581" t="n">
         <v>3</v>
       </c>
@@ -14244,7 +14236,7 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C582" t="inlineStr"/>
@@ -14262,12 +14254,16 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C583" t="inlineStr"/>
       <c r="D583" t="inlineStr"/>
-      <c r="E583" t="inlineStr"/>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="F583" t="n">
         <v>3</v>
       </c>
@@ -14280,12 +14276,16 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C584" t="inlineStr"/>
       <c r="D584" t="inlineStr"/>
-      <c r="E584" t="inlineStr"/>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="F584" t="n">
         <v>3</v>
       </c>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C597" t="inlineStr"/>
@@ -14672,7 +14672,7 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C604" t="inlineStr"/>
@@ -14708,7 +14708,7 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>Fed Musalem Speech</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C606" t="inlineStr"/>
@@ -14744,7 +14744,7 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>Fed Musalem Speech</t>
         </is>
       </c>
       <c r="C608" t="inlineStr"/>
@@ -14924,7 +14924,7 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C618" t="inlineStr"/>
@@ -14942,7 +14942,7 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C619" t="inlineStr"/>
@@ -15406,18 +15406,18 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C641" t="inlineStr"/>
       <c r="D641" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E641" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F641" t="n">
@@ -15484,22 +15484,18 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C644" t="inlineStr"/>
-      <c r="D644" t="inlineStr">
-        <is>
-          <t>67.3</t>
-        </is>
-      </c>
+      <c r="D644" t="inlineStr"/>
       <c r="E644" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F644" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="645">
@@ -15510,22 +15506,22 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C645" t="inlineStr"/>
       <c r="D645" t="inlineStr">
         <is>
-          <t>4.17M</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F645" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="646">
@@ -15536,18 +15532,22 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C646" t="inlineStr"/>
-      <c r="D646" t="inlineStr"/>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>4.17M</t>
+        </is>
+      </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F646" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="647">
@@ -15584,18 +15584,18 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C648" t="inlineStr"/>
       <c r="D648" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F648" t="n">
@@ -15610,18 +15610,18 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C649" t="inlineStr"/>
       <c r="D649" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F649" t="n">
@@ -16148,7 +16148,7 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C678" t="inlineStr"/>
@@ -16256,7 +16256,7 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C684" t="inlineStr"/>
@@ -16364,7 +16364,7 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>Money SupplyJAN</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C690" t="inlineStr"/>
@@ -16418,7 +16418,7 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>Money SupplyJAN</t>
         </is>
       </c>
       <c r="C693" t="inlineStr"/>
@@ -17210,7 +17210,7 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Fed Bostic Speech</t>
         </is>
       </c>
       <c r="C737" t="inlineStr"/>
@@ -17228,7 +17228,7 @@
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>Fed Bostic Speech</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C738" t="inlineStr"/>
@@ -17336,7 +17336,7 @@
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C744" t="inlineStr"/>
@@ -17354,7 +17354,7 @@
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>2-Year FRN Auction</t>
         </is>
       </c>
       <c r="C745" t="inlineStr"/>
@@ -17372,7 +17372,7 @@
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>2-Year FRN Auction</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C746" t="inlineStr"/>
@@ -17390,7 +17390,7 @@
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C747" t="inlineStr"/>

--- a/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-02-27.xlsx
+++ b/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-02-27.xlsx
@@ -720,18 +720,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.323M</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -742,12 +746,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.041M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -764,18 +768,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>7.717M</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0.7M</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -786,19 +794,15 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>6.406M</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>-0.1M</t>
-        </is>
-      </c>
+          <t>-0.416M</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
         <v>3</v>
@@ -812,12 +816,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -834,15 +838,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.416M</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>-0.1M</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
         <v>3</v>
@@ -856,22 +864,18 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -882,12 +886,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.142M</t>
+          <t>0.041M</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -904,22 +908,18 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.178M</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>-2.75M</t>
-        </is>
-      </c>
+          <t>0.099M</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -974,12 +974,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/02</t>
+          <t>15-Year Mortgage RateJAN/02</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>6.91%</t>
+          <t>6.13%</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -996,12 +996,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/02</t>
+          <t>30-Year Mortgage RateJAN/02</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>6.13%</t>
+          <t>6.91%</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Fed Daly Speech</t>
+          <t>Fed Kugler Speech</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Fed Kugler Speech</t>
+          <t>Fed Daly Speech</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
@@ -1476,12 +1476,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>4.110%</t>
+          <t>4.205%</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -1498,12 +1498,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>4.205%</t>
+          <t>4.110%</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -1686,22 +1686,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>8.098M</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>7.70M</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -1716,22 +1716,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -1746,18 +1746,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>3.065M</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
+          <t>64.4</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>57.5</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -1772,22 +1776,18 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>64.4</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>57.5</t>
-        </is>
-      </c>
+          <t>58.2</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -1802,22 +1802,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -1832,22 +1832,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>8.098M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>7.70M</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -1862,18 +1862,18 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>3.065M</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2098,18 +2098,22 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/04</t>
+          <t>Continuing Jobless ClaimsDEC/28</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>213K</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr"/>
+          <t>1867K</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>224K</t>
+          <t>1848K</t>
         </is>
       </c>
       <c r="F69" t="n">
@@ -2124,26 +2128,26 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Total Vehicle SalesDEC</t>
+          <t>Initial Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>16.8M</t>
+          <t>201K</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>16.5M</t>
+          <t>218K</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>16.3M</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -2154,14 +2158,26 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Fed Waller Speech</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr"/>
-      <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr"/>
+          <t>Total Vehicle SalesDEC</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>16.8M</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>16.5M</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>16.3M</t>
+        </is>
+      </c>
       <c r="F71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72">
@@ -2172,26 +2188,22 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/04</t>
+          <t>Jobless Claims 4-week AverageJAN/04</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>201K</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>218K</t>
-        </is>
-      </c>
+          <t>213K</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>213K</t>
+          <t>224K</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73">
@@ -2202,26 +2214,14 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsDEC/28</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>1867K</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>1848K</t>
-        </is>
-      </c>
+          <t>Fed Waller Speech</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -2306,12 +2306,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>0.278M</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -2328,12 +2328,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>0.045M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -2350,18 +2350,22 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>-0.632M</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>-0.6M</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
@@ -2372,19 +2376,15 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>6.071M</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>1M</t>
-        </is>
-      </c>
+          <t>-0.167M</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="n">
         <v>3</v>
@@ -2424,15 +2424,19 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Distillate Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>0.278M</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr"/>
+          <t>6.071M</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="n">
         <v>3</v>
@@ -2446,12 +2450,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>-0.167M</t>
+          <t>-0.632M</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -2468,22 +2472,18 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>-0.6M</t>
-        </is>
-      </c>
+          <t>0.045M</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85">
@@ -2494,12 +2494,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>-0.081M</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -2860,22 +2860,18 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>34.3</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
+          <t>33K</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F102" t="n">
@@ -2890,22 +2886,22 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
@@ -2916,26 +2912,26 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>160K</t>
+          <t>135K</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
@@ -2946,26 +2942,26 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106">
@@ -2976,22 +2972,22 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F106" t="n">
@@ -3006,22 +3002,22 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F107" t="n">
@@ -3036,26 +3032,26 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
@@ -3066,26 +3062,26 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>135K</t>
+          <t>160K</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
@@ -3096,22 +3092,22 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111">
@@ -3122,18 +3118,22 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>33K</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr"/>
+          <t>34.3</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F111" t="n">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - CornDEC</t>
+          <t>Quarterly Grain Stocks - WheatDEC</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>12.074B</t>
+          <t>1.57B</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
@@ -3304,14 +3304,10 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - SoyDEC</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>3.1B</t>
-        </is>
-      </c>
+          <t>WASDE Report</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="n">
@@ -3326,10 +3322,14 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>WASDE Report</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr"/>
+          <t>Quarterly Grain Stocks - CornDEC</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>12.074B</t>
+        </is>
+      </c>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="n">
@@ -3344,12 +3344,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - WheatDEC</t>
+          <t>Quarterly Grain Stocks - SoyDEC</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>1.57B</t>
+          <t>3.1B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
@@ -3532,22 +3532,26 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>146.842</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr"/>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="129">
@@ -3558,22 +3562,22 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F129" t="n">
@@ -3588,26 +3592,26 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="131">
@@ -3618,26 +3622,22 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="132">
@@ -3648,18 +3648,22 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr"/>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F132" t="n">
@@ -3674,22 +3678,18 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>3.4%</t>
-        </is>
-      </c>
+          <t>146.842</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="F133" t="n">
@@ -3704,12 +3704,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -3719,11 +3719,11 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135">
@@ -4010,22 +4010,26 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>CPI s.aDEC</t>
+          <t>Core Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>317.685</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr"/>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>317.4</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148">
@@ -4036,22 +4040,22 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMDEC</t>
+          <t>Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -4066,26 +4070,26 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexJAN</t>
+          <t>Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>-12.60</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150">
@@ -4126,26 +4130,26 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYDEC</t>
+          <t>NY Empire State Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>-12.60</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="152">
@@ -4156,22 +4160,22 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMDEC</t>
+          <t>Core Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
           <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>0.4%</t>
         </is>
       </c>
       <c r="F152" t="n">
@@ -4186,26 +4190,22 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYDEC</t>
+          <t>CPI s.aDEC</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+          <t>317.685</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>317.4</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="154">
@@ -4252,22 +4252,22 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>-1.961M</t>
+          <t>3.077M</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>-1.6M</t>
+          <t>1.1M</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="157">
@@ -4278,22 +4278,18 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>2.60M</t>
-        </is>
-      </c>
+          <t>-0.255M</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="158">
@@ -4304,12 +4300,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>0.765M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
@@ -4326,12 +4322,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>-1.304M</t>
+          <t>0.646M</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
@@ -4348,12 +4344,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>0.646M</t>
+          <t>-0.021M</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
@@ -4370,12 +4366,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>0.765M</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
@@ -4392,18 +4388,22 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>-0.255M</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>2.60M</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="163">
@@ -4414,22 +4414,22 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>3.077M</t>
+          <t>-1.961M</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>1.1M</t>
+          <t>-1.6M</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="164">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>-0.021M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
@@ -4556,26 +4556,26 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F170" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="171">
@@ -4586,22 +4586,22 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>217K</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>210K</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>209.0K</t>
         </is>
       </c>
       <c r="F171" t="n">
@@ -4616,26 +4616,26 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="173">
@@ -4646,22 +4646,26 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>3.9%</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="174">
@@ -4672,24 +4676,16 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>1.6%</t>
-        </is>
-      </c>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="inlineStr"/>
       <c r="F174" t="n">
         <v>3</v>
       </c>
@@ -4702,18 +4698,18 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>212.75K</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F175" t="n">
@@ -4728,26 +4724,18 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>46.3</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr"/>
       <c r="F176" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="177">
@@ -4758,12 +4746,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>39.00</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
@@ -4780,16 +4768,24 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr"/>
-      <c r="E178" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>1.6%</t>
+        </is>
+      </c>
       <c r="F178" t="n">
         <v>3</v>
       </c>
@@ -4802,18 +4798,26 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>46.3</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr"/>
-      <c r="E179" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F179" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="180">
@@ -4824,18 +4828,18 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>212.75K</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F180" t="n">
@@ -4850,26 +4854,22 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
+          <t>3.9%</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F181" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="182">
@@ -4880,26 +4880,26 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="183">
@@ -4910,22 +4910,22 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>217K</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>210K</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F183" t="n">
@@ -4940,26 +4940,26 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>1859K</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1870.0K</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="185">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
@@ -4992,12 +4992,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>31.90</t>
+          <t>39.00</t>
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
@@ -5014,17 +5014,17 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoMNOV</t>
+          <t>Business Inventories MoMNOV</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -5033,7 +5033,7 @@
         </is>
       </c>
       <c r="F187" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="188">
@@ -5044,22 +5044,22 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Business Inventories MoMNOV</t>
+          <t>NAHB Housing Market IndexJAN</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F188" t="n">
@@ -5074,26 +5074,26 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>NAHB Housing Market IndexJAN</t>
+          <t>Retail Inventories Ex Autos MoMNOV</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F189" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="190">
@@ -5352,26 +5352,26 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Capacity UtilizationDEC</t>
+          <t>Industrial Production MoMDEC</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F200" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="201">
@@ -5382,18 +5382,22 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYDEC</t>
+          <t>Manufacturing Production MoMDEC</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr"/>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F201" t="n">
@@ -5408,18 +5412,18 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Industrial Production YoYDEC</t>
+          <t>Manufacturing Production YoYDEC</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D202" t="inlineStr"/>
       <c r="E202" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F202" t="n">
@@ -5434,22 +5438,22 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMDEC</t>
+          <t>Capacity UtilizationDEC</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="F203" t="n">
@@ -5464,26 +5468,22 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Industrial Production MoMDEC</t>
+          <t>Industrial Production YoYDEC</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr"/>
       <c r="E204" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F204" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="205">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>4.215%</t>
+          <t>4.165%</t>
         </is>
       </c>
       <c r="D211" t="inlineStr"/>
@@ -5648,12 +5648,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>4.165%</t>
+          <t>4.215%</t>
         </is>
       </c>
       <c r="D212" t="inlineStr"/>
@@ -5670,12 +5670,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>42-Day Bill Auction</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>4.025%</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
@@ -5692,12 +5692,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>42-Day Bill Auction</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>4.025%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
@@ -5942,18 +5942,22 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/18</t>
+          <t>Continuing Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>213.5K</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr"/>
+          <t>1899K</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>1860K</t>
+        </is>
+      </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>213.0K</t>
+          <t>1861K</t>
         </is>
       </c>
       <c r="F225" t="n">
@@ -5998,22 +6002,18 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/11</t>
+          <t>Jobless Claims 4-week AverageJAN/18</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>1899K</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr">
-        <is>
-          <t>1860K</t>
-        </is>
-      </c>
+          <t>213.5K</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr"/>
       <c r="E227" t="inlineStr">
         <is>
-          <t>1861K</t>
+          <t>213.0K</t>
         </is>
       </c>
       <c r="F227" t="n">
@@ -6150,22 +6150,18 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>-0.148M</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr"/>
       <c r="E233" t="inlineStr"/>
       <c r="F233" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="234">
@@ -6176,12 +6172,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
@@ -6198,12 +6194,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D235" t="inlineStr"/>
@@ -6220,22 +6216,18 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>6.96%</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr"/>
       <c r="E236" t="inlineStr"/>
       <c r="F236" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="237">
@@ -6246,12 +6238,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
@@ -6268,19 +6260,15 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>0.068M</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr"/>
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="n">
         <v>3</v>
@@ -6294,12 +6282,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
@@ -6316,18 +6304,22 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>6.96%</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="241">
@@ -6338,15 +6330,19 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>0.184M</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="n">
         <v>3</v>
@@ -6360,12 +6356,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -6382,18 +6378,22 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>-0.148M</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="244">
@@ -6534,26 +6534,26 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F249" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="250">
@@ -6564,26 +6564,26 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>4.24M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>4.19M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F250" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="251">
@@ -6594,26 +6594,22 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr"/>
       <c r="E251" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F251" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="252">
@@ -6624,26 +6620,26 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F252" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="253">
@@ -6654,22 +6650,26 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr"/>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F253" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="254">
@@ -6680,26 +6680,26 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.24M</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.19M</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="F254" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="255">
@@ -6710,22 +6710,22 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F255" t="n">
@@ -7040,22 +7040,26 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMDEC</t>
+          <t>Durable Goods Orders Ex Transp MoMDEC</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>-2.4%</t>
-        </is>
-      </c>
-      <c r="D268" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E268" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
       <c r="F268" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="269">
@@ -7066,26 +7070,26 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMDEC</t>
+          <t>Non Defense Goods Orders Ex AirDEC</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F269" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="270">
@@ -7096,26 +7100,22 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMDEC</t>
+          <t>Durable Goods Orders ex Defense MoMDEC</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D270" t="inlineStr">
+          <t>-2.4%</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr"/>
+      <c r="E270" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
-      <c r="E270" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
       <c r="F270" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="271">
@@ -7126,26 +7126,26 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirDEC</t>
+          <t>Durable Goods Orders MoMDEC</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
+          <t>-2.2%</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
           <t>0.5%</t>
         </is>
       </c>
-      <c r="D271" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E271" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
       <c r="F271" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="272">
@@ -7316,26 +7316,22 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceJAN</t>
+          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>104.1</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr">
-        <is>
-          <t>105.6</t>
-        </is>
-      </c>
+          <t>-9</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr"/>
       <c r="E278" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="F278" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="279">
@@ -7346,26 +7342,26 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexJAN</t>
+          <t>CB Consumer ConfidenceJAN</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>104.1</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>105.6</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F279" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="280">
@@ -7376,18 +7372,22 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexJAN</t>
+          <t>Richmond Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr"/>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>-8</t>
+        </is>
+      </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="F280" t="n">
@@ -7402,18 +7402,18 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
+          <t>Richmond Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D281" t="inlineStr"/>
       <c r="E281" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F281" t="n">
@@ -7428,18 +7428,18 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexJAN</t>
+          <t>Dallas Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="D282" t="inlineStr"/>
       <c r="E282" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F282" t="n">
@@ -7454,18 +7454,18 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexJAN</t>
+          <t>Dallas Fed Services IndexJAN</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="D283" t="inlineStr"/>
       <c r="E283" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="F283" t="n">
@@ -7704,22 +7704,18 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvDEC</t>
+          <t>Retail Inventories Ex Autos MoM AdvDEC</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>$-122.11B</t>
-        </is>
-      </c>
-      <c r="D294" t="inlineStr">
-        <is>
-          <t>$-105.4B</t>
-        </is>
-      </c>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr"/>
       <c r="E294" t="inlineStr">
         <is>
-          <t>$ -106B</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F294" t="n">
@@ -7764,18 +7760,22 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoM AdvDEC</t>
+          <t>Goods Trade Balance AdvDEC</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D296" t="inlineStr"/>
+          <t>$-122.11B</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>$-105.4B</t>
+        </is>
+      </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>$ -106B</t>
         </is>
       </c>
       <c r="F296" t="n">
@@ -8324,18 +8324,22 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Pending Home Sales YoYDEC</t>
+          <t>Pending Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>-5.0%</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr"/>
+          <t>-5.5%</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F318" t="n">
@@ -8350,22 +8354,18 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Pending Home Sales MoMDEC</t>
+          <t>Pending Home Sales YoYDEC</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>-5.5%</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
+          <t>-5.0%</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr"/>
       <c r="E319" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F319" t="n">
@@ -8516,12 +8516,20 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C326" t="inlineStr"/>
+          <t>Employment Cost - Wages QoQQ4</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>0.9%</t>
+        </is>
+      </c>
       <c r="D326" t="inlineStr"/>
-      <c r="E326" t="inlineStr"/>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>0.7%</t>
+        </is>
+      </c>
       <c r="F326" t="n">
         <v>2</v>
       </c>
@@ -8534,26 +8542,26 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F327" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="328">
@@ -8564,22 +8572,18 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
+          <t>Employment Cost - Benefits QoQQ4</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr"/>
       <c r="E328" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F328" t="n">
@@ -8594,26 +8598,26 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
+          <t>Personal Income MoMDEC</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F329" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="330">
@@ -8624,26 +8628,26 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F330" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="331">
@@ -8654,26 +8658,26 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
+          <t>PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F331" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="332">
@@ -8684,18 +8688,22 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F332" t="n">
@@ -8710,26 +8718,26 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F333" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="334">
@@ -8740,20 +8748,12 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
-        </is>
-      </c>
-      <c r="C334" t="inlineStr">
-        <is>
-          <t>0.8%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr"/>
       <c r="D334" t="inlineStr"/>
-      <c r="E334" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+      <c r="E334" t="inlineStr"/>
       <c r="F334" t="n">
         <v>2</v>
       </c>
@@ -8766,26 +8766,26 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>Core PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F335" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="336">
@@ -8904,22 +8904,18 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Construction Spending MoMDEC</t>
+          <t>ISM Manufacturing New OrdersJAN</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D340" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>55.1</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr"/>
       <c r="E340" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F340" t="n">
@@ -8934,26 +8930,26 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIJAN</t>
+          <t>ISM Manufacturing PricesJAN</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F341" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="342">
@@ -8964,22 +8960,26 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentJAN</t>
+          <t>ISM Manufacturing PMIJAN</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>50.3</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr"/>
+          <t>50.9</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>49.8</t>
+        </is>
+      </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="F342" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="343">
@@ -8990,18 +8990,22 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersJAN</t>
+          <t>Construction Spending MoMDEC</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>55.1</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F343" t="n">
@@ -9016,26 +9020,22 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesJAN</t>
+          <t>ISM Manufacturing EmploymentJAN</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>54.9</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
+          <t>50.3</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr"/>
       <c r="E344" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F344" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="345">
@@ -9206,26 +9206,22 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsDEC</t>
+          <t>JOLTs Job QuitsDEC</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>7.6M</t>
-        </is>
-      </c>
-      <c r="D353" t="inlineStr">
-        <is>
-          <t>8M</t>
-        </is>
-      </c>
+          <t>3.197M</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr"/>
       <c r="E353" t="inlineStr">
         <is>
-          <t>7.8M</t>
+          <t>3.1M</t>
         </is>
       </c>
       <c r="F353" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="354">
@@ -9236,22 +9232,26 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationDEC</t>
+          <t>Factory Orders MoMDEC</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr"/>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>-0.7%</t>
+        </is>
+      </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F354" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="355">
@@ -9262,26 +9262,26 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Factory Orders MoMDEC</t>
+          <t>JOLTs Job OpeningsDEC</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>7.6M</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>8M</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>7.8M</t>
         </is>
       </c>
       <c r="F355" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="356">
@@ -9292,18 +9292,18 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsDEC</t>
+          <t>Factory Orders ex TransportationDEC</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>3.197M</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D356" t="inlineStr"/>
       <c r="E356" t="inlineStr">
         <is>
-          <t>3.1M</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F356" t="n">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/31</t>
+          <t>MBA Mortgage Market IndexJAN/31</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>584.3</t>
+          <t>224.8</t>
         </is>
       </c>
       <c r="D363" t="inlineStr"/>
@@ -9472,12 +9472,12 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/31</t>
+          <t>MBA Mortgage Refinance IndexJAN/31</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>224.8</t>
+          <t>584.3</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
@@ -9590,18 +9590,18 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>ExportsDEC</t>
+          <t>ImportsDEC</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>$266.5B</t>
+          <t>$364.9B</t>
         </is>
       </c>
       <c r="D369" t="inlineStr"/>
       <c r="E369" t="inlineStr">
         <is>
-          <t>$ 262B</t>
+          <t>$ 355.0B</t>
         </is>
       </c>
       <c r="F369" t="n">
@@ -9616,26 +9616,14 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Balance of TradeDEC</t>
-        </is>
-      </c>
-      <c r="C370" t="inlineStr">
-        <is>
-          <t>$-98.4B</t>
-        </is>
-      </c>
-      <c r="D370" t="inlineStr">
-        <is>
-          <t>$-96.6B</t>
-        </is>
-      </c>
-      <c r="E370" t="inlineStr">
-        <is>
-          <t>$ -93.0B</t>
-        </is>
-      </c>
+          <t>Treasury Refunding Announcement</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr"/>
+      <c r="D370" t="inlineStr"/>
+      <c r="E370" t="inlineStr"/>
       <c r="F370" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="371">
@@ -9646,18 +9634,18 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>ImportsDEC</t>
+          <t>ExportsDEC</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>$364.9B</t>
+          <t>$266.5B</t>
         </is>
       </c>
       <c r="D371" t="inlineStr"/>
       <c r="E371" t="inlineStr">
         <is>
-          <t>$ 355.0B</t>
+          <t>$ 262B</t>
         </is>
       </c>
       <c r="F371" t="n">
@@ -9672,14 +9660,26 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Treasury Refunding Announcement</t>
-        </is>
-      </c>
-      <c r="C372" t="inlineStr"/>
-      <c r="D372" t="inlineStr"/>
-      <c r="E372" t="inlineStr"/>
+          <t>Balance of TradeDEC</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>$-98.4B</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>$-96.6B</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>$ -93.0B</t>
+        </is>
+      </c>
       <c r="F372" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="373">
@@ -9768,18 +9768,18 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>ISM Services PricesJAN</t>
+          <t>ISM Services New OrdersJAN</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="D376" t="inlineStr"/>
       <c r="E376" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F376" t="n">
@@ -9794,26 +9794,22 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>ISM Services PMIJAN</t>
+          <t>ISM Services Business ActivityJAN</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>52.8</t>
-        </is>
-      </c>
-      <c r="D377" t="inlineStr">
-        <is>
-          <t>54.3</t>
-        </is>
-      </c>
+          <t>54.5</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr"/>
       <c r="E377" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="F377" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="378">
@@ -9824,18 +9820,18 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityJAN</t>
+          <t>ISM Services EmploymentJAN</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="D378" t="inlineStr"/>
       <c r="E378" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F378" t="n">
@@ -9850,22 +9846,26 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentJAN</t>
+          <t>ISM Services PMIJAN</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>52.3</t>
-        </is>
-      </c>
-      <c r="D379" t="inlineStr"/>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>54.3</t>
+        </is>
+      </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F379" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="380">
@@ -9876,18 +9876,18 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersJAN</t>
+          <t>ISM Services PricesJAN</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>60.4</t>
         </is>
       </c>
       <c r="D380" t="inlineStr"/>
       <c r="E380" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="F380" t="n">
@@ -9902,18 +9902,22 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>-0.027M</t>
-        </is>
-      </c>
-      <c r="D381" t="inlineStr"/>
+          <t>8.664M</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>2.6M</t>
+        </is>
+      </c>
       <c r="E381" t="inlineStr"/>
       <c r="F381" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="382">
@@ -9924,22 +9928,22 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>-5.471M</t>
+          <t>2.233M</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>-1.5M</t>
+          <t>1.2M</t>
         </is>
       </c>
       <c r="E382" t="inlineStr"/>
       <c r="F382" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="383">
@@ -9950,12 +9954,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Crude Oil Imports ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>0.16M</t>
+          <t>-0.178M</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
@@ -9972,12 +9976,12 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>-0.034M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="D384" t="inlineStr"/>
@@ -9994,12 +9998,12 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>0.373M</t>
+          <t>-0.186M</t>
         </is>
       </c>
       <c r="D385" t="inlineStr"/>
@@ -10016,12 +10020,12 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>-0.178M</t>
+          <t>0.16M</t>
         </is>
       </c>
       <c r="D386" t="inlineStr"/>
@@ -10038,15 +10042,19 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>-0.186M</t>
-        </is>
-      </c>
-      <c r="D387" t="inlineStr"/>
+          <t>-5.471M</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>-1.5M</t>
+        </is>
+      </c>
       <c r="E387" t="inlineStr"/>
       <c r="F387" t="n">
         <v>3</v>
@@ -10060,22 +10068,18 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>2.233M</t>
-        </is>
-      </c>
-      <c r="D388" t="inlineStr">
-        <is>
-          <t>1.2M</t>
-        </is>
-      </c>
+          <t>-0.027M</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr"/>
       <c r="E388" t="inlineStr"/>
       <c r="F388" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="389">
@@ -10086,22 +10090,18 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>8.664M</t>
-        </is>
-      </c>
-      <c r="D389" t="inlineStr">
-        <is>
-          <t>2.6M</t>
-        </is>
-      </c>
+          <t>-0.034M</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr"/>
       <c r="E389" t="inlineStr"/>
       <c r="F389" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="390">
@@ -10196,26 +10196,26 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/25</t>
+          <t>Unit Labour Costs QoQ PrelQ4</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>1886K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>1855.0K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F394" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="395">
@@ -10226,22 +10226,26 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/01</t>
+          <t>Nonfarm Productivity QoQ PrelQ4</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>216.75K</t>
-        </is>
-      </c>
-      <c r="D395" t="inlineStr"/>
+          <t>1.2%</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>1.4%</t>
+        </is>
+      </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>215.5K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F395" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="396">
@@ -10252,26 +10256,22 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/01</t>
+          <t>Jobless Claims 4-week AverageFEB/01</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>219K</t>
-        </is>
-      </c>
-      <c r="D396" t="inlineStr">
-        <is>
-          <t>213K</t>
-        </is>
-      </c>
+          <t>216.75K</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr"/>
       <c r="E396" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>215.5K</t>
         </is>
       </c>
       <c r="F396" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="397">
@@ -10282,26 +10282,26 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Unit Labour Costs QoQ PrelQ4</t>
+          <t>Continuing Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>1886K</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>1855.0K</t>
         </is>
       </c>
       <c r="F397" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="398">
@@ -10312,22 +10312,22 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Nonfarm Productivity QoQ PrelQ4</t>
+          <t>Initial Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F398" t="n">
@@ -10536,26 +10536,22 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Unemployment RateJAN</t>
+          <t>Participation RateJAN</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>4%</t>
-        </is>
-      </c>
-      <c r="D408" t="inlineStr">
-        <is>
-          <t>4.1%</t>
-        </is>
-      </c>
+          <t>62.6%</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr"/>
       <c r="E408" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="F408" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="409">
@@ -10566,26 +10562,26 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoYJAN</t>
+          <t>Manufacturing PayrollsJAN</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>3K</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>-2K</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>-5K</t>
         </is>
       </c>
       <c r="F409" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="410">
@@ -10596,26 +10592,26 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsJAN</t>
+          <t>Non Farm PayrollsJAN</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>3K</t>
+          <t>143K</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>-2K</t>
+          <t>170K</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>-5K</t>
+          <t>205K</t>
         </is>
       </c>
       <c r="F410" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="411">
@@ -10626,22 +10622,26 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>U-6 Unemployment RateJAN</t>
+          <t>Average Hourly Earnings MoMJAN</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D411" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F411" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="412">
@@ -10652,22 +10652,22 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateJAN</t>
+          <t>Average Weekly HoursJAN</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>111K</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>141K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>180K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F412" t="n">
@@ -10682,22 +10682,26 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Government PayrollsJAN</t>
+          <t>Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>32K</t>
-        </is>
-      </c>
-      <c r="D413" t="inlineStr"/>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>4.1%</t>
+        </is>
+      </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>25K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F413" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="414">
@@ -10708,22 +10712,22 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Average Weekly HoursJAN</t>
+          <t>Nonfarm Payrolls PrivateJAN</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>111K</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>141K</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>180K</t>
         </is>
       </c>
       <c r="F414" t="n">
@@ -10738,26 +10742,22 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsJAN</t>
+          <t>U-6 Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>143K</t>
-        </is>
-      </c>
-      <c r="D415" t="inlineStr">
-        <is>
-          <t>170K</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr"/>
       <c r="E415" t="inlineStr">
         <is>
-          <t>205K</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="F415" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="416">
@@ -10768,18 +10768,22 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Participation RateJAN</t>
+          <t>Average Hourly Earnings YoYJAN</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>62.6%</t>
-        </is>
-      </c>
-      <c r="D416" t="inlineStr"/>
+          <t>4.1%</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="F416" t="n">
@@ -10794,26 +10798,22 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMJAN</t>
+          <t>Government PayrollsJAN</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D417" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>32K</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr"/>
       <c r="E417" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>25K</t>
         </is>
       </c>
       <c r="F417" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="418">
@@ -10904,18 +10904,22 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelFEB</t>
+          <t>Wholesale Inventories MoMDEC</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D422" t="inlineStr"/>
+          <t>-0.5%</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>-0.5%</t>
+        </is>
+      </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F422" t="n">
@@ -10930,22 +10934,22 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelFEB</t>
+          <t>Michigan Current Conditions PrelFEB</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>73</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="F423" t="n">
@@ -10960,22 +10964,26 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelFEB</t>
+          <t>Michigan Consumer Sentiment PrelFEB</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="D424" t="inlineStr"/>
+          <t>67.8</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>71.1</t>
+        </is>
+      </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F424" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="425">
@@ -10986,22 +10994,22 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelFEB</t>
+          <t>Michigan Consumer Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="F425" t="n">
@@ -11016,26 +11024,22 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelFEB</t>
+          <t>Michigan 5 Year Inflation Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>67.8</t>
-        </is>
-      </c>
-      <c r="D426" t="inlineStr">
-        <is>
-          <t>71.1</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr"/>
       <c r="E426" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F426" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="427">
@@ -11046,22 +11050,18 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoMDEC</t>
+          <t>Michigan Inflation Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
-      <c r="D427" t="inlineStr">
-        <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr"/>
       <c r="E427" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F427" t="n">
@@ -11564,22 +11564,18 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>CPI s.aJAN</t>
         </is>
       </c>
       <c r="C452" t="inlineStr"/>
-      <c r="D452" t="inlineStr">
-        <is>
-          <t>2.9%</t>
-        </is>
-      </c>
+      <c r="D452" t="inlineStr"/>
       <c r="E452" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>318.2</t>
         </is>
       </c>
       <c r="F452" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="453">
@@ -11590,7 +11586,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C453" t="inlineStr"/>
@@ -11601,7 +11597,7 @@
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F453" t="n">
@@ -11616,22 +11612,22 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>CPIJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C454" t="inlineStr"/>
       <c r="D454" t="inlineStr">
         <is>
-          <t>317.42</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>317.3</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F454" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="455">
@@ -11642,18 +11638,18 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C455" t="inlineStr"/>
       <c r="D455" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F455" t="n">
@@ -11668,7 +11664,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C456" t="inlineStr"/>
@@ -11679,7 +11675,7 @@
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F456" t="n">
@@ -11694,14 +11690,18 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>CPI s.aJAN</t>
+          <t>CPIJAN</t>
         </is>
       </c>
       <c r="C457" t="inlineStr"/>
-      <c r="D457" t="inlineStr"/>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>317.42</t>
+        </is>
+      </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>318.2</t>
+          <t>317.3</t>
         </is>
       </c>
       <c r="F457" t="n">
@@ -11716,7 +11716,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C458" t="inlineStr"/>
@@ -11734,14 +11734,14 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C459" t="inlineStr"/>
       <c r="D459" t="inlineStr"/>
       <c r="E459" t="inlineStr"/>
       <c r="F459" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="460">
@@ -11752,7 +11752,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C460" t="inlineStr"/>
@@ -11770,14 +11770,14 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C461" t="inlineStr"/>
       <c r="D461" t="inlineStr"/>
       <c r="E461" t="inlineStr"/>
       <c r="F461" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="462">
@@ -11788,7 +11788,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C462" t="inlineStr"/>
@@ -11806,14 +11806,14 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C463" t="inlineStr"/>
       <c r="D463" t="inlineStr"/>
       <c r="E463" t="inlineStr"/>
       <c r="F463" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="464">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C464" t="inlineStr"/>
@@ -11842,7 +11842,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C465" t="inlineStr"/>
@@ -11860,14 +11860,14 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C466" t="inlineStr"/>
       <c r="D466" t="inlineStr"/>
       <c r="E466" t="inlineStr"/>
       <c r="F466" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="467">
@@ -11976,18 +11976,18 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C472" t="inlineStr"/>
       <c r="D472" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F472" t="n">
@@ -12002,14 +12002,14 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C473" t="inlineStr"/>
       <c r="D473" t="inlineStr"/>
       <c r="E473" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F473" t="n">
@@ -12024,22 +12024,18 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C474" t="inlineStr"/>
-      <c r="D474" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D474" t="inlineStr"/>
       <c r="E474" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="F474" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="475">
@@ -12050,22 +12046,18 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C475" t="inlineStr"/>
-      <c r="D475" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
+      <c r="D475" t="inlineStr"/>
       <c r="E475" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F475" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="476">
@@ -12076,22 +12068,18 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C476" t="inlineStr"/>
-      <c r="D476" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D476" t="inlineStr"/>
       <c r="E476" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="F476" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="477">
@@ -12102,14 +12090,18 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C477" t="inlineStr"/>
-      <c r="D477" t="inlineStr"/>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F477" t="n">
@@ -12124,22 +12116,22 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C478" t="inlineStr"/>
       <c r="D478" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F478" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="479">
@@ -12150,18 +12142,22 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C479" t="inlineStr"/>
-      <c r="D479" t="inlineStr"/>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F479" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="480">
@@ -12172,14 +12168,14 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C480" t="inlineStr"/>
       <c r="D480" t="inlineStr"/>
       <c r="E480" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="F480" t="n">
@@ -12194,18 +12190,22 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C481" t="inlineStr"/>
-      <c r="D481" t="inlineStr"/>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F481" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="482">
@@ -12574,14 +12574,14 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="C499" t="inlineStr"/>
       <c r="D499" t="inlineStr"/>
       <c r="E499" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F499" t="n">
@@ -12596,22 +12596,22 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="C500" t="inlineStr"/>
       <c r="D500" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F500" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="501">
@@ -12622,22 +12622,22 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Manufacturing Production MoMJAN</t>
         </is>
       </c>
       <c r="C501" t="inlineStr"/>
       <c r="D501" t="inlineStr">
         <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
           <t>0.2%</t>
         </is>
       </c>
-      <c r="E501" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
       <c r="F501" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="502">
@@ -12648,18 +12648,14 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="C502" t="inlineStr"/>
-      <c r="D502" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+      <c r="D502" t="inlineStr"/>
       <c r="E502" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F502" t="n">
@@ -12674,14 +12670,18 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="C503" t="inlineStr"/>
-      <c r="D503" t="inlineStr"/>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>77.7%</t>
+        </is>
+      </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="F503" t="n">
@@ -13248,18 +13248,14 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsDEC</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="C532" t="inlineStr"/>
-      <c r="D532" t="inlineStr">
-        <is>
-          <t>$149.1B</t>
-        </is>
-      </c>
+      <c r="D532" t="inlineStr"/>
       <c r="E532" t="inlineStr"/>
       <c r="F532" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="533">
@@ -13328,14 +13324,18 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Net Long-term TIC FlowsDEC</t>
         </is>
       </c>
       <c r="C536" t="inlineStr"/>
-      <c r="D536" t="inlineStr"/>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>$149.1B</t>
+        </is>
+      </c>
       <c r="E536" t="inlineStr"/>
       <c r="F536" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="537">
@@ -13552,22 +13552,18 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C548" t="inlineStr"/>
-      <c r="D548" t="inlineStr">
-        <is>
-          <t>1.39M</t>
-        </is>
-      </c>
+      <c r="D548" t="inlineStr"/>
       <c r="E548" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F548" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="549">
@@ -13648,14 +13644,14 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C552" t="inlineStr"/>
       <c r="D552" t="inlineStr"/>
       <c r="E552" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F552" t="n">
@@ -13670,18 +13666,22 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C553" t="inlineStr"/>
-      <c r="D553" t="inlineStr"/>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>1.45M</t>
+        </is>
+      </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F553" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="554">
@@ -13692,18 +13692,18 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C554" t="inlineStr"/>
       <c r="D554" t="inlineStr">
         <is>
-          <t>1.45M</t>
+          <t>1.39M</t>
         </is>
       </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F554" t="n">
@@ -14112,12 +14112,16 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C576" t="inlineStr"/>
       <c r="D576" t="inlineStr"/>
-      <c r="E576" t="inlineStr"/>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="F576" t="n">
         <v>3</v>
       </c>
@@ -14130,7 +14134,7 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C577" t="inlineStr"/>
@@ -14200,12 +14204,16 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C580" t="inlineStr"/>
       <c r="D580" t="inlineStr"/>
-      <c r="E580" t="inlineStr"/>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="F580" t="n">
         <v>3</v>
       </c>
@@ -14218,7 +14226,7 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C581" t="inlineStr"/>
@@ -14236,7 +14244,7 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C582" t="inlineStr"/>
@@ -14254,16 +14262,12 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C583" t="inlineStr"/>
       <c r="D583" t="inlineStr"/>
-      <c r="E583" t="inlineStr">
-        <is>
-          <t>1879.0K</t>
-        </is>
-      </c>
+      <c r="E583" t="inlineStr"/>
       <c r="F583" t="n">
         <v>3</v>
       </c>
@@ -14276,16 +14280,12 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C584" t="inlineStr"/>
       <c r="D584" t="inlineStr"/>
-      <c r="E584" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="E584" t="inlineStr"/>
       <c r="F584" t="n">
         <v>3</v>
       </c>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C597" t="inlineStr"/>
@@ -14672,7 +14672,7 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C604" t="inlineStr"/>
@@ -14708,7 +14708,7 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>Fed Musalem Speech</t>
         </is>
       </c>
       <c r="C606" t="inlineStr"/>
@@ -14744,7 +14744,7 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>Fed Musalem Speech</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C608" t="inlineStr"/>
@@ -14924,7 +14924,7 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C618" t="inlineStr"/>
@@ -14942,7 +14942,7 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C619" t="inlineStr"/>
@@ -15406,18 +15406,18 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C641" t="inlineStr"/>
       <c r="D641" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E641" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F641" t="n">
@@ -15484,18 +15484,22 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C644" t="inlineStr"/>
-      <c r="D644" t="inlineStr"/>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>4.17M</t>
+        </is>
+      </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F644" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="645">
@@ -15506,18 +15510,18 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C645" t="inlineStr"/>
       <c r="D645" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F645" t="n">
@@ -15532,22 +15536,22 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C646" t="inlineStr"/>
       <c r="D646" t="inlineStr">
         <is>
-          <t>4.17M</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F646" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="647">
@@ -15584,18 +15588,18 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C648" t="inlineStr"/>
       <c r="D648" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F648" t="n">
@@ -15610,22 +15614,18 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C649" t="inlineStr"/>
-      <c r="D649" t="inlineStr">
-        <is>
-          <t>67.3</t>
-        </is>
-      </c>
+      <c r="D649" t="inlineStr"/>
       <c r="E649" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F649" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="650">
@@ -16148,7 +16148,7 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C678" t="inlineStr"/>
@@ -16256,7 +16256,7 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C684" t="inlineStr"/>
@@ -16364,7 +16364,7 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>Money SupplyJAN</t>
         </is>
       </c>
       <c r="C690" t="inlineStr"/>
@@ -16418,7 +16418,7 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>Money SupplyJAN</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C693" t="inlineStr"/>
@@ -17210,7 +17210,7 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>Fed Bostic Speech</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C737" t="inlineStr"/>
@@ -17228,7 +17228,7 @@
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Fed Bostic Speech</t>
         </is>
       </c>
       <c r="C738" t="inlineStr"/>
@@ -17336,7 +17336,7 @@
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C744" t="inlineStr"/>
@@ -17354,7 +17354,7 @@
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>2-Year FRN Auction</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C745" t="inlineStr"/>
@@ -17372,7 +17372,7 @@
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>2-Year FRN Auction</t>
         </is>
       </c>
       <c r="C746" t="inlineStr"/>
@@ -17390,7 +17390,7 @@
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C747" t="inlineStr"/>

--- a/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-02-27.xlsx
+++ b/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-02-27.xlsx
@@ -720,22 +720,18 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.178M</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>-2.75M</t>
-        </is>
-      </c>
+          <t>0.099M</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -746,12 +742,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.142M</t>
+          <t>0.041M</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -768,22 +764,18 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -794,15 +786,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.416M</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>-0.1M</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
         <v>3</v>
@@ -816,18 +812,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.323M</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -838,19 +838,15 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>6.406M</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>-0.1M</t>
-        </is>
-      </c>
+          <t>-0.416M</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
         <v>3</v>
@@ -864,18 +860,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>7.717M</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>0.7M</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -886,12 +886,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.041M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -908,12 +908,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -974,12 +974,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/02</t>
+          <t>30-Year Mortgage RateJAN/02</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>6.13%</t>
+          <t>6.91%</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -996,12 +996,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/02</t>
+          <t>15-Year Mortgage RateJAN/02</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>6.91%</t>
+          <t>6.13%</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Fed Kugler Speech</t>
+          <t>Fed Daly Speech</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Fed Daly Speech</t>
+          <t>Fed Kugler Speech</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
@@ -1476,12 +1476,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>4.205%</t>
+          <t>4.110%</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -1498,12 +1498,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>4.110%</t>
+          <t>4.205%</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -1686,22 +1686,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>8.098M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>7.70M</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -1716,22 +1716,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -1746,22 +1746,18 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>64.4</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>57.5</t>
-        </is>
-      </c>
+          <t>58.2</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -1776,18 +1772,18 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>3.065M</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -1802,22 +1798,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -1832,22 +1828,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>8.098M</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>7.70M</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -1862,18 +1858,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>3.065M</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
+          <t>64.4</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>57.5</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2098,26 +2098,14 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsDEC/28</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>1867K</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>1848K</t>
-        </is>
-      </c>
+          <t>Fed Waller Speech</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
       <c r="F69" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -2128,26 +2116,22 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/04</t>
+          <t>Jobless Claims 4-week AverageJAN/04</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>201K</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>218K</t>
-        </is>
-      </c>
+          <t>213K</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>213K</t>
+          <t>224K</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71">
@@ -2158,26 +2142,26 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Total Vehicle SalesDEC</t>
+          <t>Initial Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>16.8M</t>
+          <t>201K</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>16.5M</t>
+          <t>218K</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>16.3M</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -2188,18 +2172,22 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/04</t>
+          <t>Continuing Jobless ClaimsDEC/28</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>213K</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr"/>
+          <t>1867K</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>224K</t>
+          <t>1848K</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -2214,14 +2202,26 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Fed Waller Speech</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr"/>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr"/>
+          <t>Total Vehicle SalesDEC</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>16.8M</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>16.5M</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>16.3M</t>
+        </is>
+      </c>
       <c r="F73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
@@ -2306,15 +2306,19 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Distillate Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>0.278M</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr"/>
+          <t>6.071M</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="n">
         <v>3</v>
@@ -2328,12 +2332,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>-0.081M</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -2350,22 +2354,18 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>-0.6M</t>
-        </is>
-      </c>
+          <t>0.045M</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>-0.167M</t>
+          <t>-0.632M</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -2424,19 +2424,15 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>6.071M</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>1M</t>
-        </is>
-      </c>
+          <t>-0.167M</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="n">
         <v>3</v>
@@ -2450,18 +2446,22 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>-0.632M</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr"/>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>-0.6M</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>0.045M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -2494,12 +2494,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>0.278M</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -2860,18 +2860,22 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>33K</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr"/>
+          <t>34.3</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F102" t="n">
@@ -2886,22 +2890,22 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
@@ -2912,26 +2916,26 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>135K</t>
+          <t>160K</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -2942,26 +2946,26 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -2972,22 +2976,22 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F106" t="n">
@@ -3002,22 +3006,22 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F107" t="n">
@@ -3032,26 +3036,26 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109">
@@ -3062,26 +3066,26 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>160K</t>
+          <t>135K</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110">
@@ -3092,22 +3096,22 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111">
@@ -3118,22 +3122,18 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>34.3</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
+          <t>33K</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F111" t="n">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - WheatDEC</t>
+          <t>Quarterly Grain Stocks - SoyDEC</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>1.57B</t>
+          <t>3.1B</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
@@ -3304,10 +3304,14 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>WASDE Report</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr"/>
+          <t>Quarterly Grain Stocks - CornDEC</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>12.074B</t>
+        </is>
+      </c>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="n">
@@ -3322,12 +3326,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - CornDEC</t>
+          <t>Quarterly Grain Stocks - WheatDEC</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>12.074B</t>
+          <t>1.57B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
@@ -3344,14 +3348,10 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - SoyDEC</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>3.1B</t>
-        </is>
-      </c>
+          <t>WASDE Report</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="n">
@@ -3532,26 +3532,26 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="129">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -3577,11 +3577,11 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130">
@@ -3592,22 +3592,18 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>3.4%</t>
-        </is>
-      </c>
+          <t>146.842</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -3622,18 +3618,22 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr"/>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F131" t="n">
@@ -3648,22 +3648,22 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F132" t="n">
@@ -3678,22 +3678,26 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>146.842</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr"/>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="134">
@@ -3704,26 +3708,22 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="135">
@@ -4010,26 +4010,22 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYDEC</t>
+          <t>CPI s.aDEC</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+          <t>317.685</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>317.4</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="148">
@@ -4040,22 +4036,22 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMDEC</t>
+          <t>Core Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
           <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>0.4%</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -4070,26 +4066,26 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYDEC</t>
+          <t>NY Empire State Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>-12.60</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="150">
@@ -4130,26 +4126,26 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexJAN</t>
+          <t>Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>-12.60</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="152">
@@ -4160,22 +4156,22 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMDEC</t>
+          <t>Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F152" t="n">
@@ -4190,22 +4186,26 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>CPI s.aDEC</t>
+          <t>Core Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>317.685</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr"/>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>317.4</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154">
@@ -4252,22 +4252,22 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>3.077M</t>
+          <t>-1.961M</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>1.1M</t>
+          <t>-1.6M</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="157">
@@ -4278,18 +4278,22 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>-0.255M</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>2.60M</t>
+        </is>
+      </c>
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="158">
@@ -4300,12 +4304,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>0.765M</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
@@ -4322,12 +4326,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>0.646M</t>
+          <t>-0.021M</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
@@ -4344,12 +4348,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>-0.021M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
@@ -4366,12 +4370,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>0.765M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
@@ -4388,22 +4392,18 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>2.60M</t>
-        </is>
-      </c>
+          <t>-0.255M</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="163">
@@ -4414,22 +4414,22 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>-1.961M</t>
+          <t>3.077M</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>-1.6M</t>
+          <t>1.1M</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="164">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>-1.304M</t>
+          <t>0.646M</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
@@ -4556,26 +4556,26 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>1859K</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1870.0K</t>
         </is>
       </c>
       <c r="F170" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="171">
@@ -4586,22 +4586,22 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>217K</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>210K</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F171" t="n">
@@ -4616,26 +4616,26 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="173">
@@ -4646,26 +4646,22 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
+          <t>3.9%</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="174">
@@ -4676,12 +4672,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
@@ -4698,18 +4694,18 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>212.75K</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F175" t="n">
@@ -4724,18 +4720,26 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>46.3</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr"/>
-      <c r="E176" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F176" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="177">
@@ -4746,16 +4750,24 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr"/>
-      <c r="E177" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>1.6%</t>
+        </is>
+      </c>
       <c r="F177" t="n">
         <v>3</v>
       </c>
@@ -4768,24 +4780,16 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>1.6%</t>
-        </is>
-      </c>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr"/>
       <c r="F178" t="n">
         <v>3</v>
       </c>
@@ -4798,26 +4802,18 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>46.3</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr"/>
       <c r="F179" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="180">
@@ -4828,18 +4824,18 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>212.75K</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F180" t="n">
@@ -4854,22 +4850,26 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>3.9%</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F181" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="182">
@@ -4880,26 +4880,26 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="183">
@@ -4910,22 +4910,22 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>217K</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>210K</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>209.0K</t>
         </is>
       </c>
       <c r="F183" t="n">
@@ -4940,26 +4940,26 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="185">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>31.90</t>
+          <t>39.00</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
@@ -4992,12 +4992,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>39.00</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
@@ -5014,22 +5014,22 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Business Inventories MoMNOV</t>
+          <t>NAHB Housing Market IndexJAN</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F187" t="n">
@@ -5044,26 +5044,26 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>NAHB Housing Market IndexJAN</t>
+          <t>Retail Inventories Ex Autos MoMNOV</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F188" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="189">
@@ -5074,17 +5074,17 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoMNOV</t>
+          <t>Business Inventories MoMNOV</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -5093,7 +5093,7 @@
         </is>
       </c>
       <c r="F189" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="190">
@@ -5352,26 +5352,22 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Industrial Production MoMDEC</t>
+          <t>Industrial Production YoYDEC</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F200" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="201">
@@ -5382,22 +5378,22 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMDEC</t>
+          <t>Capacity UtilizationDEC</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="F201" t="n">
@@ -5412,18 +5408,22 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYDEC</t>
+          <t>Manufacturing Production MoMDEC</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr"/>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F202" t="n">
@@ -5438,26 +5438,26 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Capacity UtilizationDEC</t>
+          <t>Industrial Production MoMDEC</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F203" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="204">
@@ -5468,18 +5468,18 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Industrial Production YoYDEC</t>
+          <t>Manufacturing Production YoYDEC</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D204" t="inlineStr"/>
       <c r="E204" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F204" t="n">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>4.165%</t>
+          <t>4.215%</t>
         </is>
       </c>
       <c r="D211" t="inlineStr"/>
@@ -5648,12 +5648,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>4.215%</t>
+          <t>4.165%</t>
         </is>
       </c>
       <c r="D212" t="inlineStr"/>
@@ -5670,12 +5670,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>42-Day Bill Auction</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>4.025%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
@@ -5692,12 +5692,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>42-Day Bill Auction</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>4.025%</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
@@ -5942,22 +5942,18 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/11</t>
+          <t>Jobless Claims 4-week AverageJAN/18</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>1899K</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>1860K</t>
-        </is>
-      </c>
+          <t>213.5K</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr"/>
       <c r="E225" t="inlineStr">
         <is>
-          <t>1861K</t>
+          <t>213.0K</t>
         </is>
       </c>
       <c r="F225" t="n">
@@ -6002,18 +5998,22 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/18</t>
+          <t>Continuing Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>213.5K</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr"/>
+          <t>1899K</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>1860K</t>
+        </is>
+      </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>213.0K</t>
+          <t>1861K</t>
         </is>
       </c>
       <c r="F227" t="n">
@@ -6150,18 +6150,22 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>-0.148M</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E233" t="inlineStr"/>
       <c r="F233" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="234">
@@ -6172,12 +6176,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
@@ -6194,15 +6198,19 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>0.184M</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="n">
         <v>3</v>
@@ -6216,18 +6224,22 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>6.96%</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E236" t="inlineStr"/>
       <c r="F236" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="237">
@@ -6238,12 +6250,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
@@ -6260,12 +6272,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -6282,12 +6294,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
@@ -6304,22 +6316,18 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>6.96%</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr"/>
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="241">
@@ -6330,19 +6338,15 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>0.068M</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr"/>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="n">
         <v>3</v>
@@ -6356,12 +6360,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -6378,22 +6382,18 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>-0.148M</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr"/>
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="244">
@@ -6534,22 +6534,22 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F249" t="n">
@@ -6564,26 +6564,26 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.24M</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.19M</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="F250" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="251">
@@ -6594,22 +6594,26 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr"/>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F251" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="252">
@@ -6620,26 +6624,26 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F252" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="253">
@@ -6650,26 +6654,22 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr"/>
       <c r="E253" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F253" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="254">
@@ -6680,26 +6680,26 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>4.24M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>4.19M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F254" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="255">
@@ -6710,26 +6710,26 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F255" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="256">
@@ -7040,26 +7040,22 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMDEC</t>
+          <t>Durable Goods Orders ex Defense MoMDEC</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D268" t="inlineStr">
+          <t>-2.4%</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr"/>
+      <c r="E268" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
-      <c r="E268" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
       <c r="F268" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="269">
@@ -7070,26 +7066,26 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirDEC</t>
+          <t>Durable Goods Orders MoMDEC</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
+          <t>-2.2%</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
           <t>0.5%</t>
         </is>
       </c>
-      <c r="D269" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E269" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
       <c r="F269" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="270">
@@ -7100,22 +7096,26 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMDEC</t>
+          <t>Durable Goods Orders Ex Transp MoMDEC</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>-2.4%</t>
-        </is>
-      </c>
-      <c r="D270" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E270" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
       <c r="F270" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="271">
@@ -7126,26 +7126,26 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMDEC</t>
+          <t>Non Defense Goods Orders Ex AirDEC</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F271" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="272">
@@ -7316,18 +7316,18 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
+          <t>Richmond Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D278" t="inlineStr"/>
       <c r="E278" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F278" t="n">
@@ -7342,26 +7342,22 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceJAN</t>
+          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>104.1</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr">
-        <is>
-          <t>105.6</t>
-        </is>
-      </c>
+          <t>-9</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr"/>
       <c r="E279" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="F279" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="280">
@@ -7372,26 +7368,26 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexJAN</t>
+          <t>CB Consumer ConfidenceJAN</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>104.1</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>105.6</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F280" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="281">
@@ -7402,18 +7398,22 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexJAN</t>
+          <t>Richmond Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr"/>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>-8</t>
+        </is>
+      </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="F281" t="n">
@@ -7428,18 +7428,18 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexJAN</t>
+          <t>Dallas Fed Services IndexJAN</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="D282" t="inlineStr"/>
       <c r="E282" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="F282" t="n">
@@ -7454,18 +7454,18 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexJAN</t>
+          <t>Dallas Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="D283" t="inlineStr"/>
       <c r="E283" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F283" t="n">
@@ -7704,18 +7704,22 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoM AdvDEC</t>
+          <t>Goods Trade Balance AdvDEC</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D294" t="inlineStr"/>
+          <t>$-122.11B</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>$-105.4B</t>
+        </is>
+      </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>$ -106B</t>
         </is>
       </c>
       <c r="F294" t="n">
@@ -7760,22 +7764,18 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvDEC</t>
+          <t>Retail Inventories Ex Autos MoM AdvDEC</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>$-122.11B</t>
-        </is>
-      </c>
-      <c r="D296" t="inlineStr">
-        <is>
-          <t>$-105.4B</t>
-        </is>
-      </c>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr"/>
       <c r="E296" t="inlineStr">
         <is>
-          <t>$ -106B</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F296" t="n">
@@ -8324,22 +8324,18 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Pending Home Sales MoMDEC</t>
+          <t>Pending Home Sales YoYDEC</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>-5.5%</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
+          <t>-5.0%</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr"/>
       <c r="E318" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F318" t="n">
@@ -8354,18 +8350,22 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Pending Home Sales YoYDEC</t>
+          <t>Pending Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>-5.0%</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr"/>
+          <t>-5.5%</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F319" t="n">
@@ -8516,18 +8516,22 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D326" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F326" t="n">
@@ -8542,26 +8546,26 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>Core PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F327" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="328">
@@ -8572,20 +8576,12 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
-        </is>
-      </c>
-      <c r="C328" t="inlineStr">
-        <is>
-          <t>0.8%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr"/>
       <c r="D328" t="inlineStr"/>
-      <c r="E328" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+      <c r="E328" t="inlineStr"/>
       <c r="F328" t="n">
         <v>2</v>
       </c>
@@ -8598,26 +8594,26 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F329" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="330">
@@ -8628,26 +8624,26 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
+          <t>PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F330" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="331">
@@ -8658,26 +8654,26 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
+          <t>Personal Income MoMDEC</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F331" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="332">
@@ -8688,22 +8684,18 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
+          <t>Employment Cost - Benefits QoQQ4</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr"/>
       <c r="E332" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F332" t="n">
@@ -8718,26 +8710,26 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F333" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="334">
@@ -8748,12 +8740,20 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C334" t="inlineStr"/>
+          <t>Employment Cost - Wages QoQQ4</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>0.9%</t>
+        </is>
+      </c>
       <c r="D334" t="inlineStr"/>
-      <c r="E334" t="inlineStr"/>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>0.7%</t>
+        </is>
+      </c>
       <c r="F334" t="n">
         <v>2</v>
       </c>
@@ -8766,26 +8766,26 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F335" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="336">
@@ -8904,18 +8904,22 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersJAN</t>
+          <t>Construction Spending MoMDEC</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>55.1</t>
-        </is>
-      </c>
-      <c r="D340" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F340" t="n">
@@ -8930,26 +8934,22 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesJAN</t>
+          <t>ISM Manufacturing EmploymentJAN</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>54.9</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
+          <t>50.3</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr"/>
       <c r="E341" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F341" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="342">
@@ -8960,26 +8960,26 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIJAN</t>
+          <t>ISM Manufacturing PricesJAN</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F342" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="343">
@@ -8990,22 +8990,18 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Construction Spending MoMDEC</t>
+          <t>ISM Manufacturing New OrdersJAN</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>55.1</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr"/>
       <c r="E343" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F343" t="n">
@@ -9020,22 +9016,26 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentJAN</t>
+          <t>ISM Manufacturing PMIJAN</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>50.3</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr"/>
+          <t>50.9</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>49.8</t>
+        </is>
+      </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="F344" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="345">
@@ -9206,18 +9206,18 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsDEC</t>
+          <t>Factory Orders ex TransportationDEC</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>3.197M</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D353" t="inlineStr"/>
       <c r="E353" t="inlineStr">
         <is>
-          <t>3.1M</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F353" t="n">
@@ -9232,26 +9232,26 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Factory Orders MoMDEC</t>
+          <t>JOLTs Job OpeningsDEC</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>7.6M</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>8M</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>7.8M</t>
         </is>
       </c>
       <c r="F354" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="355">
@@ -9262,26 +9262,22 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsDEC</t>
+          <t>JOLTs Job QuitsDEC</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>7.6M</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr">
-        <is>
-          <t>8M</t>
-        </is>
-      </c>
+          <t>3.197M</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr"/>
       <c r="E355" t="inlineStr">
         <is>
-          <t>7.8M</t>
+          <t>3.1M</t>
         </is>
       </c>
       <c r="F355" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="356">
@@ -9292,22 +9288,26 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationDEC</t>
+          <t>Factory Orders MoMDEC</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr"/>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>-0.7%</t>
+        </is>
+      </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F356" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="357">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/31</t>
+          <t>MBA Mortgage Refinance IndexJAN/31</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>224.8</t>
+          <t>584.3</t>
         </is>
       </c>
       <c r="D363" t="inlineStr"/>
@@ -9472,12 +9472,12 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/31</t>
+          <t>MBA Mortgage Market IndexJAN/31</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>584.3</t>
+          <t>224.8</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
@@ -9590,18 +9590,18 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>ImportsDEC</t>
+          <t>ExportsDEC</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>$364.9B</t>
+          <t>$266.5B</t>
         </is>
       </c>
       <c r="D369" t="inlineStr"/>
       <c r="E369" t="inlineStr">
         <is>
-          <t>$ 355.0B</t>
+          <t>$ 262B</t>
         </is>
       </c>
       <c r="F369" t="n">
@@ -9616,14 +9616,26 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Treasury Refunding Announcement</t>
-        </is>
-      </c>
-      <c r="C370" t="inlineStr"/>
-      <c r="D370" t="inlineStr"/>
-      <c r="E370" t="inlineStr"/>
+          <t>Balance of TradeDEC</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>$-98.4B</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>$-96.6B</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>$ -93.0B</t>
+        </is>
+      </c>
       <c r="F370" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="371">
@@ -9634,18 +9646,18 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>ExportsDEC</t>
+          <t>ImportsDEC</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>$266.5B</t>
+          <t>$364.9B</t>
         </is>
       </c>
       <c r="D371" t="inlineStr"/>
       <c r="E371" t="inlineStr">
         <is>
-          <t>$ 262B</t>
+          <t>$ 355.0B</t>
         </is>
       </c>
       <c r="F371" t="n">
@@ -9660,26 +9672,14 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Balance of TradeDEC</t>
-        </is>
-      </c>
-      <c r="C372" t="inlineStr">
-        <is>
-          <t>$-98.4B</t>
-        </is>
-      </c>
-      <c r="D372" t="inlineStr">
-        <is>
-          <t>$-96.6B</t>
-        </is>
-      </c>
-      <c r="E372" t="inlineStr">
-        <is>
-          <t>$ -93.0B</t>
-        </is>
-      </c>
+          <t>Treasury Refunding Announcement</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr"/>
+      <c r="D372" t="inlineStr"/>
+      <c r="E372" t="inlineStr"/>
       <c r="F372" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="373">
@@ -9768,18 +9768,18 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersJAN</t>
+          <t>ISM Services PricesJAN</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>60.4</t>
         </is>
       </c>
       <c r="D376" t="inlineStr"/>
       <c r="E376" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="F376" t="n">
@@ -9794,18 +9794,18 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityJAN</t>
+          <t>ISM Services EmploymentJAN</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="D377" t="inlineStr"/>
       <c r="E377" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F377" t="n">
@@ -9820,22 +9820,26 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentJAN</t>
+          <t>ISM Services PMIJAN</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>52.3</t>
-        </is>
-      </c>
-      <c r="D378" t="inlineStr"/>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>54.3</t>
+        </is>
+      </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F378" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="379">
@@ -9846,26 +9850,22 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>ISM Services PMIJAN</t>
+          <t>ISM Services Business ActivityJAN</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>52.8</t>
-        </is>
-      </c>
-      <c r="D379" t="inlineStr">
-        <is>
-          <t>54.3</t>
-        </is>
-      </c>
+          <t>54.5</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr"/>
       <c r="E379" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="F379" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="380">
@@ -9876,18 +9876,18 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>ISM Services PricesJAN</t>
+          <t>ISM Services New OrdersJAN</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="D380" t="inlineStr"/>
       <c r="E380" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F380" t="n">
@@ -9902,22 +9902,18 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>8.664M</t>
-        </is>
-      </c>
-      <c r="D381" t="inlineStr">
-        <is>
-          <t>2.6M</t>
-        </is>
-      </c>
+          <t>-0.034M</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr"/>
       <c r="E381" t="inlineStr"/>
       <c r="F381" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="382">
@@ -9928,22 +9924,18 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>2.233M</t>
-        </is>
-      </c>
-      <c r="D382" t="inlineStr">
-        <is>
-          <t>1.2M</t>
-        </is>
-      </c>
+          <t>-0.027M</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr"/>
       <c r="E382" t="inlineStr"/>
       <c r="F382" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="383">
@@ -9954,12 +9946,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>-0.178M</t>
+          <t>0.16M</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
@@ -9976,12 +9968,12 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>0.373M</t>
+          <t>-0.186M</t>
         </is>
       </c>
       <c r="D384" t="inlineStr"/>
@@ -9998,15 +9990,19 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>-0.186M</t>
-        </is>
-      </c>
-      <c r="D385" t="inlineStr"/>
+          <t>-5.471M</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>-1.5M</t>
+        </is>
+      </c>
       <c r="E385" t="inlineStr"/>
       <c r="F385" t="n">
         <v>3</v>
@@ -10020,12 +10016,12 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Crude Oil Imports ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>0.16M</t>
+          <t>-0.178M</t>
         </is>
       </c>
       <c r="D386" t="inlineStr"/>
@@ -10042,22 +10038,22 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>-5.471M</t>
+          <t>2.233M</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>-1.5M</t>
+          <t>1.2M</t>
         </is>
       </c>
       <c r="E387" t="inlineStr"/>
       <c r="F387" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="388">
@@ -10068,18 +10064,22 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>-0.027M</t>
-        </is>
-      </c>
-      <c r="D388" t="inlineStr"/>
+          <t>8.664M</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>2.6M</t>
+        </is>
+      </c>
       <c r="E388" t="inlineStr"/>
       <c r="F388" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="389">
@@ -10090,12 +10090,12 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>-0.034M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="D389" t="inlineStr"/>
@@ -10196,26 +10196,26 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Unit Labour Costs QoQ PrelQ4</t>
+          <t>Continuing Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>1886K</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>1855.0K</t>
         </is>
       </c>
       <c r="F394" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="395">
@@ -10226,22 +10226,22 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Nonfarm Productivity QoQ PrelQ4</t>
+          <t>Initial Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F395" t="n">
@@ -10256,22 +10256,26 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/01</t>
+          <t>Nonfarm Productivity QoQ PrelQ4</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>216.75K</t>
-        </is>
-      </c>
-      <c r="D396" t="inlineStr"/>
+          <t>1.2%</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>1.4%</t>
+        </is>
+      </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>215.5K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F396" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="397">
@@ -10282,26 +10286,26 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/25</t>
+          <t>Unit Labour Costs QoQ PrelQ4</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>1886K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>1855.0K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F397" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="398">
@@ -10312,26 +10316,22 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/01</t>
+          <t>Jobless Claims 4-week AverageFEB/01</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>219K</t>
-        </is>
-      </c>
-      <c r="D398" t="inlineStr">
-        <is>
-          <t>213K</t>
-        </is>
-      </c>
+          <t>216.75K</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr"/>
       <c r="E398" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>215.5K</t>
         </is>
       </c>
       <c r="F398" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="399">
@@ -10536,18 +10536,22 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Participation RateJAN</t>
+          <t>Average Hourly Earnings YoYJAN</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>62.6%</t>
-        </is>
-      </c>
-      <c r="D408" t="inlineStr"/>
+          <t>4.1%</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="F408" t="n">
@@ -10562,26 +10566,26 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsJAN</t>
+          <t>Non Farm PayrollsJAN</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>3K</t>
+          <t>143K</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>-2K</t>
+          <t>170K</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>-5K</t>
+          <t>205K</t>
         </is>
       </c>
       <c r="F409" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="410">
@@ -10592,26 +10596,22 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsJAN</t>
+          <t>U-6 Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>143K</t>
-        </is>
-      </c>
-      <c r="D410" t="inlineStr">
-        <is>
-          <t>170K</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr"/>
       <c r="E410" t="inlineStr">
         <is>
-          <t>205K</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="F410" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="411">
@@ -10622,26 +10622,22 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMJAN</t>
+          <t>Government PayrollsJAN</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D411" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>32K</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr"/>
       <c r="E411" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>25K</t>
         </is>
       </c>
       <c r="F411" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="412">
@@ -10652,22 +10648,22 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Average Weekly HoursJAN</t>
+          <t>Nonfarm Payrolls PrivateJAN</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>111K</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>141K</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>180K</t>
         </is>
       </c>
       <c r="F412" t="n">
@@ -10682,26 +10678,22 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Unemployment RateJAN</t>
+          <t>Participation RateJAN</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>4%</t>
-        </is>
-      </c>
-      <c r="D413" t="inlineStr">
-        <is>
-          <t>4.1%</t>
-        </is>
-      </c>
+          <t>62.6%</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr"/>
       <c r="E413" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="F413" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="414">
@@ -10712,22 +10704,22 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateJAN</t>
+          <t>Average Weekly HoursJAN</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>111K</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>141K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>180K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F414" t="n">
@@ -10742,22 +10734,26 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>U-6 Unemployment RateJAN</t>
+          <t>Average Hourly Earnings MoMJAN</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D415" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F415" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="416">
@@ -10768,26 +10764,26 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoYJAN</t>
+          <t>Manufacturing PayrollsJAN</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>3K</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>-2K</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>-5K</t>
         </is>
       </c>
       <c r="F416" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="417">
@@ -10798,22 +10794,26 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Government PayrollsJAN</t>
+          <t>Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>32K</t>
-        </is>
-      </c>
-      <c r="D417" t="inlineStr"/>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>4.1%</t>
+        </is>
+      </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>25K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F417" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="418">
@@ -10904,22 +10904,18 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoMDEC</t>
+          <t>Michigan Inflation Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
-      <c r="D422" t="inlineStr">
-        <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr"/>
       <c r="E422" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F422" t="n">
@@ -10934,22 +10930,22 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelFEB</t>
+          <t>Michigan Consumer Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="F423" t="n">
@@ -10964,26 +10960,22 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelFEB</t>
+          <t>Michigan 5 Year Inflation Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>67.8</t>
-        </is>
-      </c>
-      <c r="D424" t="inlineStr">
-        <is>
-          <t>71.1</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr"/>
       <c r="E424" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F424" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="425">
@@ -10994,22 +10986,22 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelFEB</t>
+          <t>Michigan Current Conditions PrelFEB</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>73</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="F425" t="n">
@@ -11024,18 +11016,22 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelFEB</t>
+          <t>Wholesale Inventories MoMDEC</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D426" t="inlineStr"/>
+          <t>-0.5%</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>-0.5%</t>
+        </is>
+      </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F426" t="n">
@@ -11050,22 +11046,26 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelFEB</t>
+          <t>Michigan Consumer Sentiment PrelFEB</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="D427" t="inlineStr"/>
+          <t>67.8</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>71.1</t>
+        </is>
+      </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F427" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="428">
@@ -11564,14 +11564,18 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>CPI s.aJAN</t>
+          <t>CPIJAN</t>
         </is>
       </c>
       <c r="C452" t="inlineStr"/>
-      <c r="D452" t="inlineStr"/>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>317.42</t>
+        </is>
+      </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>318.2</t>
+          <t>317.3</t>
         </is>
       </c>
       <c r="F452" t="n">
@@ -11586,7 +11590,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C453" t="inlineStr"/>
@@ -11597,7 +11601,7 @@
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F453" t="n">
@@ -11612,18 +11616,18 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C454" t="inlineStr"/>
       <c r="D454" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F454" t="n">
@@ -11638,22 +11642,18 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>CPI s.aJAN</t>
         </is>
       </c>
       <c r="C455" t="inlineStr"/>
-      <c r="D455" t="inlineStr">
-        <is>
-          <t>2.9%</t>
-        </is>
-      </c>
+      <c r="D455" t="inlineStr"/>
       <c r="E455" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>318.2</t>
         </is>
       </c>
       <c r="F455" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="456">
@@ -11664,7 +11664,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C456" t="inlineStr"/>
@@ -11675,7 +11675,7 @@
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F456" t="n">
@@ -11690,22 +11690,22 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>CPIJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C457" t="inlineStr"/>
       <c r="D457" t="inlineStr">
         <is>
-          <t>317.42</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>317.3</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F457" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="458">
@@ -11716,7 +11716,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C458" t="inlineStr"/>
@@ -11734,14 +11734,14 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C459" t="inlineStr"/>
       <c r="D459" t="inlineStr"/>
       <c r="E459" t="inlineStr"/>
       <c r="F459" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="460">
@@ -11752,7 +11752,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C460" t="inlineStr"/>
@@ -11770,14 +11770,14 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C461" t="inlineStr"/>
       <c r="D461" t="inlineStr"/>
       <c r="E461" t="inlineStr"/>
       <c r="F461" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="462">
@@ -11788,7 +11788,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C462" t="inlineStr"/>
@@ -11806,14 +11806,14 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C463" t="inlineStr"/>
       <c r="D463" t="inlineStr"/>
       <c r="E463" t="inlineStr"/>
       <c r="F463" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="464">
@@ -11824,14 +11824,14 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C464" t="inlineStr"/>
       <c r="D464" t="inlineStr"/>
       <c r="E464" t="inlineStr"/>
       <c r="F464" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="465">
@@ -11842,7 +11842,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C465" t="inlineStr"/>
@@ -11860,7 +11860,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C466" t="inlineStr"/>
@@ -11976,22 +11976,22 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C472" t="inlineStr"/>
       <c r="D472" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F472" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="473">
@@ -12002,18 +12002,22 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C473" t="inlineStr"/>
-      <c r="D473" t="inlineStr"/>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F473" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="474">
@@ -12024,14 +12028,14 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C474" t="inlineStr"/>
       <c r="D474" t="inlineStr"/>
       <c r="E474" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="F474" t="n">
@@ -12046,18 +12050,22 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C475" t="inlineStr"/>
-      <c r="D475" t="inlineStr"/>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F475" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="476">
@@ -12068,14 +12076,18 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C476" t="inlineStr"/>
-      <c r="D476" t="inlineStr"/>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F476" t="n">
@@ -12090,18 +12102,18 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C477" t="inlineStr"/>
       <c r="D477" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F477" t="n">
@@ -12116,22 +12128,18 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C478" t="inlineStr"/>
-      <c r="D478" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
+      <c r="D478" t="inlineStr"/>
       <c r="E478" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F478" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="479">
@@ -12142,22 +12150,18 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C479" t="inlineStr"/>
-      <c r="D479" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D479" t="inlineStr"/>
       <c r="E479" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="F479" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="480">
@@ -12168,14 +12172,14 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C480" t="inlineStr"/>
       <c r="D480" t="inlineStr"/>
       <c r="E480" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F480" t="n">
@@ -12190,22 +12194,18 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C481" t="inlineStr"/>
-      <c r="D481" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D481" t="inlineStr"/>
       <c r="E481" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="F481" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="482">
@@ -12574,14 +12574,18 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="C499" t="inlineStr"/>
-      <c r="D499" t="inlineStr"/>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>77.7%</t>
+        </is>
+      </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="F499" t="n">
@@ -12596,22 +12600,22 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Manufacturing Production MoMJAN</t>
         </is>
       </c>
       <c r="C500" t="inlineStr"/>
       <c r="D500" t="inlineStr">
         <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
           <t>0.2%</t>
         </is>
       </c>
-      <c r="E500" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
       <c r="F500" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="501">
@@ -12622,18 +12626,14 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="C501" t="inlineStr"/>
-      <c r="D501" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+      <c r="D501" t="inlineStr"/>
       <c r="E501" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F501" t="n">
@@ -12648,14 +12648,14 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="C502" t="inlineStr"/>
       <c r="D502" t="inlineStr"/>
       <c r="E502" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F502" t="n">
@@ -12670,22 +12670,22 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="C503" t="inlineStr"/>
       <c r="D503" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F503" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="504">
@@ -12898,7 +12898,7 @@
       <c r="C514" t="inlineStr"/>
       <c r="D514" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E514" t="inlineStr">
@@ -13248,14 +13248,18 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Net Long-term TIC FlowsDEC</t>
         </is>
       </c>
       <c r="C532" t="inlineStr"/>
-      <c r="D532" t="inlineStr"/>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>$149.1B</t>
+        </is>
+      </c>
       <c r="E532" t="inlineStr"/>
       <c r="F532" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="533">
@@ -13324,18 +13328,14 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsDEC</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="C536" t="inlineStr"/>
-      <c r="D536" t="inlineStr">
-        <is>
-          <t>$149.1B</t>
-        </is>
-      </c>
+      <c r="D536" t="inlineStr"/>
       <c r="E536" t="inlineStr"/>
       <c r="F536" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="537">
@@ -13532,7 +13532,7 @@
       <c r="C547" t="inlineStr"/>
       <c r="D547" t="inlineStr">
         <is>
-          <t>1.45M</t>
+          <t>1.46M</t>
         </is>
       </c>
       <c r="E547" t="inlineStr">
@@ -13552,14 +13552,14 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C548" t="inlineStr"/>
       <c r="D548" t="inlineStr"/>
       <c r="E548" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F548" t="n">
@@ -13580,7 +13580,7 @@
       <c r="C549" t="inlineStr"/>
       <c r="D549" t="inlineStr">
         <is>
-          <t>1.39M</t>
+          <t>1.4M</t>
         </is>
       </c>
       <c r="E549" t="inlineStr">
@@ -13644,18 +13644,22 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C552" t="inlineStr"/>
-      <c r="D552" t="inlineStr"/>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>1.45M</t>
+        </is>
+      </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F552" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="553">
@@ -13666,18 +13670,18 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C553" t="inlineStr"/>
       <c r="D553" t="inlineStr">
         <is>
-          <t>1.45M</t>
+          <t>1.39M</t>
         </is>
       </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F553" t="n">
@@ -13692,22 +13696,18 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C554" t="inlineStr"/>
-      <c r="D554" t="inlineStr">
-        <is>
-          <t>1.39M</t>
-        </is>
-      </c>
+      <c r="D554" t="inlineStr"/>
       <c r="E554" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F554" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="555">
@@ -13982,7 +13982,11 @@
         </is>
       </c>
       <c r="C569" t="inlineStr"/>
-      <c r="D569" t="inlineStr"/>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>1860K</t>
+        </is>
+      </c>
       <c r="E569" t="inlineStr">
         <is>
           <t>1879.0K</t>
@@ -14112,16 +14116,12 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C576" t="inlineStr"/>
       <c r="D576" t="inlineStr"/>
-      <c r="E576" t="inlineStr">
-        <is>
-          <t>1879.0K</t>
-        </is>
-      </c>
+      <c r="E576" t="inlineStr"/>
       <c r="F576" t="n">
         <v>3</v>
       </c>
@@ -14134,7 +14134,7 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C577" t="inlineStr"/>
@@ -14204,16 +14204,12 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C580" t="inlineStr"/>
       <c r="D580" t="inlineStr"/>
-      <c r="E580" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="E580" t="inlineStr"/>
       <c r="F580" t="n">
         <v>3</v>
       </c>
@@ -14226,12 +14222,16 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C581" t="inlineStr"/>
       <c r="D581" t="inlineStr"/>
-      <c r="E581" t="inlineStr"/>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="F581" t="n">
         <v>3</v>
       </c>
@@ -14244,7 +14244,7 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C582" t="inlineStr"/>
@@ -14262,12 +14262,16 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C583" t="inlineStr"/>
       <c r="D583" t="inlineStr"/>
-      <c r="E583" t="inlineStr"/>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="F583" t="n">
         <v>3</v>
       </c>
@@ -14280,7 +14284,7 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C584" t="inlineStr"/>
@@ -14304,7 +14308,7 @@
       <c r="C585" t="inlineStr"/>
       <c r="D585" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>16.3</t>
         </is>
       </c>
       <c r="E585" t="inlineStr">
@@ -14330,7 +14334,7 @@
       <c r="C586" t="inlineStr"/>
       <c r="D586" t="inlineStr">
         <is>
-          <t>216K</t>
+          <t>215K</t>
         </is>
       </c>
       <c r="E586" t="inlineStr">
@@ -14418,7 +14422,7 @@
       <c r="C590" t="inlineStr"/>
       <c r="D590" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E590" t="inlineStr">
@@ -14546,7 +14550,7 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C597" t="inlineStr"/>
@@ -14672,7 +14676,7 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C604" t="inlineStr"/>
@@ -14708,7 +14712,7 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>Fed Musalem Speech</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C606" t="inlineStr"/>
@@ -14744,7 +14748,7 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>Fed Musalem Speech</t>
         </is>
       </c>
       <c r="C608" t="inlineStr"/>
@@ -14924,7 +14928,7 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C618" t="inlineStr"/>
@@ -14942,7 +14946,7 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C619" t="inlineStr"/>
@@ -15210,7 +15214,11 @@
         </is>
       </c>
       <c r="C633" t="inlineStr"/>
-      <c r="D633" t="inlineStr"/>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>51.3</t>
+        </is>
+      </c>
       <c r="E633" t="inlineStr">
         <is>
           <t>51.3</t>
@@ -15234,7 +15242,7 @@
       <c r="C634" t="inlineStr"/>
       <c r="D634" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>53</t>
         </is>
       </c>
       <c r="E634" t="inlineStr">
@@ -15308,7 +15316,7 @@
       <c r="C637" t="inlineStr"/>
       <c r="D637" t="inlineStr">
         <is>
-          <t>4.17M</t>
+          <t>4.13M</t>
         </is>
       </c>
       <c r="E637" t="inlineStr">
@@ -15406,18 +15414,18 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C641" t="inlineStr"/>
       <c r="D641" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E641" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F641" t="n">
@@ -15484,22 +15492,22 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C644" t="inlineStr"/>
       <c r="D644" t="inlineStr">
         <is>
-          <t>4.17M</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F644" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="645">
@@ -15510,22 +15518,18 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C645" t="inlineStr"/>
-      <c r="D645" t="inlineStr">
-        <is>
-          <t>67.3</t>
-        </is>
-      </c>
+      <c r="D645" t="inlineStr"/>
       <c r="E645" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F645" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="646">
@@ -15536,18 +15540,18 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C646" t="inlineStr"/>
       <c r="D646" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F646" t="n">
@@ -15588,18 +15592,18 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C648" t="inlineStr"/>
       <c r="D648" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F648" t="n">
@@ -15614,18 +15618,22 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C649" t="inlineStr"/>
-      <c r="D649" t="inlineStr"/>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>4.17M</t>
+        </is>
+      </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F649" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="650">
@@ -16148,7 +16156,7 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C678" t="inlineStr"/>
@@ -16256,7 +16264,7 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C684" t="inlineStr"/>
@@ -16364,7 +16372,7 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>Money SupplyJAN</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C690" t="inlineStr"/>
@@ -16418,7 +16426,7 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>Money SupplyJAN</t>
         </is>
       </c>
       <c r="C693" t="inlineStr"/>
@@ -17210,7 +17218,7 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Fed Bostic Speech</t>
         </is>
       </c>
       <c r="C737" t="inlineStr"/>
@@ -17228,7 +17236,7 @@
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>Fed Bostic Speech</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C738" t="inlineStr"/>
@@ -17336,7 +17344,7 @@
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C744" t="inlineStr"/>
@@ -17354,7 +17362,7 @@
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>2-Year FRN Auction</t>
         </is>
       </c>
       <c r="C745" t="inlineStr"/>
@@ -17372,7 +17380,7 @@
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>2-Year FRN Auction</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C746" t="inlineStr"/>
@@ -17390,7 +17398,7 @@
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C747" t="inlineStr"/>

--- a/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-02-27.xlsx
+++ b/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-02-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F760"/>
+  <dimension ref="A1:F773"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -720,18 +720,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.323M</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -742,12 +746,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.142M</t>
+          <t>0.099M</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -764,22 +768,18 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -790,15 +790,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.416M</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>-0.1M</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
         <v>3</v>
@@ -812,12 +816,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.041M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -834,19 +838,15 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>6.406M</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>-0.1M</t>
-        </is>
-      </c>
+          <t>-0.416M</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
         <v>3</v>
@@ -860,18 +860,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>7.717M</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>0.7M</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -882,12 +886,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -904,22 +908,18 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.178M</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>-2.75M</t>
-        </is>
-      </c>
+          <t>0.041M</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -1582,18 +1582,22 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ImportsNOV</t>
+          <t>Balance of TradeNOV</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>$351.6B</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr"/>
+          <t>$-78.2B</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>$-78B</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>$334B</t>
+          <t>$-70B</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -1634,22 +1638,18 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Balance of TradeNOV</t>
+          <t>ImportsNOV</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>$-78.2B</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>$-78B</t>
-        </is>
-      </c>
+          <t>$351.6B</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>$-70B</t>
+          <t>$334B</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Used Car Prices YoYDEC</t>
+          <t>Used Car Prices MoMDEC</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -2254,12 +2254,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Used Car Prices MoMDEC</t>
+          <t>Used Car Prices YoYDEC</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -2860,18 +2860,22 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>33K</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr"/>
+          <t>34.3</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F102" t="n">
@@ -2886,26 +2890,22 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>223K</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>135K</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
@@ -2916,26 +2916,26 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>160K</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -2946,26 +2946,26 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -2976,22 +2976,26 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
@@ -3002,26 +3006,26 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108">
@@ -3032,26 +3036,26 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>160K</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109">
@@ -3062,22 +3066,26 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr"/>
+          <t>223K</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>135K</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110">
@@ -3088,22 +3096,18 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>34.3</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
+          <t>33K</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F110" t="n">
@@ -3118,26 +3122,22 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112">
@@ -3148,18 +3148,18 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelJAN</t>
+          <t>Michigan Consumer Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F112" t="n">
@@ -3174,22 +3174,26 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
+          <t>Michigan Consumer Sentiment PrelJAN</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr"/>
+          <t>73.2</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>73.8</t>
+        </is>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114">
@@ -3200,26 +3204,22 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelJAN</t>
+          <t>Michigan Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>73.2</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>73.8</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="115">
@@ -3230,18 +3230,18 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelJAN</t>
+          <t>Michigan Current Conditions PrelJAN</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F115" t="n">
@@ -3256,18 +3256,18 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelJAN</t>
+          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F116" t="n">
@@ -3366,12 +3366,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/10</t>
+          <t>Baker Hughes Oil Rig CountJAN/10</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>480</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
@@ -3388,12 +3388,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/10</t>
+          <t>Baker Hughes Total Rigs CountJAN/10</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>584</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
@@ -4010,22 +4010,26 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>CPI s.aDEC</t>
+          <t>Core Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>317.685</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr"/>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>317.4</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148">
@@ -4036,22 +4040,22 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMDEC</t>
+          <t>Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -4066,26 +4070,26 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexJAN</t>
+          <t>Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>-12.60</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150">
@@ -4096,26 +4100,26 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>CPIDEC</t>
+          <t>Core Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>315.6</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="151">
@@ -4126,26 +4130,26 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYDEC</t>
+          <t>NY Empire State Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>-12.60</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="152">
@@ -4156,26 +4160,26 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMDEC</t>
+          <t>CPIDEC</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>315.6</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="153">
@@ -4186,26 +4190,22 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYDEC</t>
+          <t>CPI s.aDEC</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+          <t>317.685</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>317.4</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="154">
@@ -4252,18 +4252,22 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>0.646M</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>2.60M</t>
+        </is>
+      </c>
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="157">
@@ -4274,19 +4278,15 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>3.077M</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>1.1M</t>
-        </is>
-      </c>
+          <t>0.765M</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="n">
         <v>3</v>
@@ -4300,12 +4300,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>-0.021M</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
@@ -4322,18 +4322,22 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>0.397M</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr"/>
+          <t>-1.961M</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>-1.6M</t>
+        </is>
+      </c>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="160">
@@ -4344,22 +4348,18 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>-1.961M</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>-1.6M</t>
-        </is>
-      </c>
+          <t>-1.304M</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="161">
@@ -4370,12 +4370,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>-0.021M</t>
+          <t>-0.255M</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
@@ -4392,15 +4392,19 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>0.765M</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr"/>
+          <t>3.077M</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>1.1M</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="n">
         <v>3</v>
@@ -4414,22 +4418,18 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>2.60M</t>
-        </is>
-      </c>
+          <t>0.646M</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="164">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>-1.304M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
@@ -4556,26 +4556,26 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F170" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="171">
@@ -4586,16 +4586,24 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr"/>
-      <c r="E171" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F171" t="n">
         <v>3</v>
       </c>
@@ -4608,16 +4616,20 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>39.00</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
-      <c r="E172" t="inlineStr"/>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>4.0%</t>
+        </is>
+      </c>
       <c r="F172" t="n">
         <v>3</v>
       </c>
@@ -4630,26 +4642,18 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
+          <t>31.90</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
+      <c r="E173" t="inlineStr"/>
       <c r="F173" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="174">
@@ -4660,26 +4664,18 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>217K</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>210K</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>209.0K</t>
-        </is>
-      </c>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="inlineStr"/>
       <c r="F174" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="175">
@@ -4690,26 +4686,22 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+          <t>212.75K</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F175" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="176">
@@ -4720,22 +4712,26 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>1.8%</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F176" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="177">
@@ -4746,16 +4742,24 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>46.3</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr"/>
-      <c r="E177" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>1.6%</t>
+        </is>
+      </c>
       <c r="F177" t="n">
         <v>3</v>
       </c>
@@ -4768,26 +4772,26 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>217K</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>210K</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>209.0K</t>
         </is>
       </c>
       <c r="F178" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="179">
@@ -4798,24 +4802,16 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>1.6%</t>
-        </is>
-      </c>
+          <t>46.3</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr"/>
       <c r="F179" t="n">
         <v>3</v>
       </c>
@@ -4828,26 +4824,22 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>1.8%</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F180" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="181">
@@ -4858,22 +4850,26 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>212.75K</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F181" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="182">
@@ -4884,18 +4880,26 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr"/>
-      <c r="E182" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
       <c r="F182" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="183">
@@ -4906,20 +4910,16 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>39.00</t>
         </is>
       </c>
       <c r="D183" t="inlineStr"/>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>4.0%</t>
-        </is>
-      </c>
+      <c r="E183" t="inlineStr"/>
       <c r="F183" t="n">
         <v>3</v>
       </c>
@@ -4932,24 +4932,16 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
+      <c r="E184" t="inlineStr"/>
       <c r="F184" t="n">
         <v>3</v>
       </c>
@@ -4962,26 +4954,26 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>1859K</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>1870.0K</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="186">
@@ -4992,18 +4984,26 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>11.9</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr"/>
-      <c r="E186" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
       <c r="F186" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="187">
@@ -5014,22 +5014,22 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>NAHB Housing Market IndexJAN</t>
+          <t>Business Inventories MoMNOV</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F187" t="n">
@@ -5074,22 +5074,22 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Business Inventories MoMNOV</t>
+          <t>NAHB Housing Market IndexJAN</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F189" t="n">
@@ -5240,26 +5240,22 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Housing StartsDEC</t>
+          <t>Housing Starts MoMDEC</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>1.499M</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>1.32M</t>
-        </is>
-      </c>
+          <t>15.8%</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr">
         <is>
-          <t>1.32M</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="F196" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="197">
@@ -5270,26 +5266,22 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Building Permits PrelDEC</t>
+          <t>Building Permits MoM PrelDEC</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>1.483M</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>1.46M</t>
-        </is>
-      </c>
+          <t>-0.7%</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr">
         <is>
-          <t>1.48M</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="F197" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="198">
@@ -5300,22 +5292,26 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelDEC</t>
+          <t>Housing StartsDEC</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr"/>
+          <t>1.499M</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>1.32M</t>
+        </is>
+      </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>1.32M</t>
         </is>
       </c>
       <c r="F198" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="199">
@@ -5326,22 +5322,26 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Housing Starts MoMDEC</t>
+          <t>Building Permits PrelDEC</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>15.8%</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr"/>
+          <t>1.483M</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>1.46M</t>
+        </is>
+      </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>1.48M</t>
         </is>
       </c>
       <c r="F199" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="200">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>6.96%</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D233" t="inlineStr"/>
@@ -6172,15 +6172,19 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>-0.473M</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="n">
         <v>3</v>
@@ -6194,12 +6198,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D235" t="inlineStr"/>
@@ -6216,18 +6220,22 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>0.068M</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E236" t="inlineStr"/>
       <c r="F236" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="237">
@@ -6238,18 +6246,22 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>0.184M</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E237" t="inlineStr"/>
       <c r="F237" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="238">
@@ -6260,12 +6272,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -6282,22 +6294,18 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>0.184M</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr"/>
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="240">
@@ -6308,22 +6316,18 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.068M</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr"/>
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="241">
@@ -6334,12 +6338,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="D241" t="inlineStr"/>
@@ -6356,19 +6360,15 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>6.96%</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr"/>
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="n">
         <v>3</v>
@@ -6382,12 +6382,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
@@ -6448,22 +6448,18 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashJAN</t>
+          <t>S&amp;P Global Composite PMI FlashJAN</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>50.1</t>
-        </is>
-      </c>
-      <c r="D246" t="inlineStr">
-        <is>
-          <t>49.7</t>
-        </is>
-      </c>
+          <t>52.4</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr"/>
       <c r="E246" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="F246" t="n">
@@ -6508,18 +6504,22 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashJAN</t>
+          <t>S&amp;P Global Manufacturing PMI FlashJAN</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>52.4</t>
-        </is>
-      </c>
-      <c r="D248" t="inlineStr"/>
+          <t>50.1</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="F248" t="n">
@@ -6784,22 +6784,22 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalDEC</t>
+          <t>Building Permits FinalDEC</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.482M</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.483M</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.6M</t>
         </is>
       </c>
       <c r="F258" t="n">
@@ -6814,22 +6814,22 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Building Permits FinalDEC</t>
+          <t>Building Permits MoM FinalDEC</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>1.482M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>1.483M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>1.6M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F259" t="n">
@@ -7040,22 +7040,26 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMDEC</t>
+          <t>Durable Goods Orders Ex Transp MoMDEC</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>-2.4%</t>
-        </is>
-      </c>
-      <c r="D268" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E268" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
       <c r="F268" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="269">
@@ -7066,26 +7070,26 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMDEC</t>
+          <t>Non Defense Goods Orders Ex AirDEC</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F269" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="270">
@@ -7096,26 +7100,22 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMDEC</t>
+          <t>Durable Goods Orders ex Defense MoMDEC</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D270" t="inlineStr">
+          <t>-2.4%</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr"/>
+      <c r="E270" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
-      <c r="E270" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
       <c r="F270" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="271">
@@ -7126,26 +7126,26 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirDEC</t>
+          <t>Durable Goods Orders MoMDEC</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
+          <t>-2.2%</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
           <t>0.5%</t>
         </is>
       </c>
-      <c r="D271" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E271" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
       <c r="F271" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="272">
@@ -7428,18 +7428,18 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexJAN</t>
+          <t>Dallas Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="D282" t="inlineStr"/>
       <c r="E282" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F282" t="n">
@@ -7454,18 +7454,18 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexJAN</t>
+          <t>Dallas Fed Services IndexJAN</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="D283" t="inlineStr"/>
       <c r="E283" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="F283" t="n">
@@ -7704,22 +7704,18 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvDEC</t>
+          <t>Retail Inventories Ex Autos MoM AdvDEC</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>$-122.11B</t>
-        </is>
-      </c>
-      <c r="D294" t="inlineStr">
-        <is>
-          <t>$-105.4B</t>
-        </is>
-      </c>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr"/>
       <c r="E294" t="inlineStr">
         <is>
-          <t>$ -106B</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F294" t="n">
@@ -7764,18 +7760,22 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoM AdvDEC</t>
+          <t>Goods Trade Balance AdvDEC</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D296" t="inlineStr"/>
+          <t>$-122.11B</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>$-105.4B</t>
+        </is>
+      </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>$ -106B</t>
         </is>
       </c>
       <c r="F296" t="n">
@@ -8324,18 +8324,22 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Pending Home Sales YoYDEC</t>
+          <t>Pending Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>-5.0%</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr"/>
+          <t>-5.5%</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F318" t="n">
@@ -8350,22 +8354,18 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Pending Home Sales MoMDEC</t>
+          <t>Pending Home Sales YoYDEC</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>-5.5%</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
+          <t>-5.0%</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr"/>
       <c r="E319" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F319" t="n">
@@ -8516,22 +8516,26 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D326" t="inlineStr"/>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F326" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="327">
@@ -8542,26 +8546,26 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F327" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="328">
@@ -8572,18 +8576,22 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F328" t="n">
@@ -8598,26 +8606,26 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>Core PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F329" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="330">
@@ -8628,26 +8636,14 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
-        </is>
-      </c>
-      <c r="C330" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D330" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E330" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr"/>
+      <c r="D330" t="inlineStr"/>
+      <c r="E330" t="inlineStr"/>
       <c r="F330" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="331">
@@ -8658,26 +8654,26 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>Personal Income MoMDEC</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F331" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="332">
@@ -8688,12 +8684,20 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C332" t="inlineStr"/>
+          <t>Employment Cost - Benefits QoQQ4</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>0.8%</t>
+        </is>
+      </c>
       <c r="D332" t="inlineStr"/>
-      <c r="E332" t="inlineStr"/>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>0.7%</t>
+        </is>
+      </c>
       <c r="F332" t="n">
         <v>2</v>
       </c>
@@ -8706,26 +8710,26 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F333" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="334">
@@ -8736,22 +8740,18 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
+          <t>Employment Cost - Wages QoQQ4</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr"/>
       <c r="E334" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F334" t="n">
@@ -8766,22 +8766,22 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F335" t="n">
@@ -8826,15 +8826,19 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/31</t>
+          <t>Baker Hughes Oil Rig CountJAN/31</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>582</t>
-        </is>
-      </c>
-      <c r="D337" t="inlineStr"/>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>468</t>
+        </is>
+      </c>
       <c r="E337" t="inlineStr"/>
       <c r="F337" t="n">
         <v>3</v>
@@ -8848,19 +8852,15 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/31</t>
+          <t>Baker Hughes Total Rigs CountJAN/31</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>479</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr">
-        <is>
-          <t>468</t>
-        </is>
-      </c>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr"/>
       <c r="E338" t="inlineStr"/>
       <c r="F338" t="n">
         <v>3</v>
@@ -8904,26 +8904,26 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Construction Spending MoMDEC</t>
+          <t>ISM Manufacturing PMIJAN</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="F340" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="341">
@@ -8934,22 +8934,26 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentJAN</t>
+          <t>ISM Manufacturing PricesJAN</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>50.3</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr"/>
+          <t>54.9</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>52.6</t>
+        </is>
+      </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F341" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="342">
@@ -8960,22 +8964,18 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesJAN</t>
+          <t>ISM Manufacturing New OrdersJAN</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>54.9</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
+          <t>55.1</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr"/>
       <c r="E342" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F342" t="n">
@@ -8990,22 +8990,22 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersJAN</t>
+          <t>ISM Manufacturing EmploymentJAN</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="D343" t="inlineStr"/>
       <c r="E343" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F343" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="344">
@@ -9016,26 +9016,26 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIJAN</t>
+          <t>Construction Spending MoMDEC</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F344" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="345">
@@ -9206,22 +9206,26 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationDEC</t>
+          <t>Factory Orders MoMDEC</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D353" t="inlineStr"/>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>-0.7%</t>
+        </is>
+      </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F353" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="354">
@@ -9232,26 +9236,22 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsDEC</t>
+          <t>JOLTs Job QuitsDEC</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>7.6M</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr">
-        <is>
-          <t>8M</t>
-        </is>
-      </c>
+          <t>3.197M</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr"/>
       <c r="E354" t="inlineStr">
         <is>
-          <t>7.8M</t>
+          <t>3.1M</t>
         </is>
       </c>
       <c r="F354" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="355">
@@ -9262,18 +9262,18 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsDEC</t>
+          <t>Factory Orders ex TransportationDEC</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>3.197M</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D355" t="inlineStr"/>
       <c r="E355" t="inlineStr">
         <is>
-          <t>3.1M</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F355" t="n">
@@ -9288,26 +9288,26 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Factory Orders MoMDEC</t>
+          <t>JOLTs Job OpeningsDEC</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>7.6M</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>8M</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>7.8M</t>
         </is>
       </c>
       <c r="F356" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="357">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/31</t>
+          <t>MBA Purchase IndexJAN/31</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>584.3</t>
+          <t>156.7</t>
         </is>
       </c>
       <c r="D363" t="inlineStr"/>
@@ -9472,18 +9472,18 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/31</t>
+          <t>MBA 30-Year Mortgage RateJAN/31</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>224.8</t>
+          <t>6.97%</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
       <c r="E364" t="inlineStr"/>
       <c r="F364" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="365">
@@ -9494,12 +9494,12 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/31</t>
+          <t>MBA Mortgage Refinance IndexJAN/31</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>584.3</t>
         </is>
       </c>
       <c r="D365" t="inlineStr"/>
@@ -9516,18 +9516,18 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/31</t>
+          <t>MBA Mortgage Market IndexJAN/31</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>6.97%</t>
+          <t>224.8</t>
         </is>
       </c>
       <c r="D366" t="inlineStr"/>
       <c r="E366" t="inlineStr"/>
       <c r="F366" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="367">
@@ -9538,12 +9538,12 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/31</t>
+          <t>MBA Mortgage ApplicationsJAN/31</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>156.7</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
@@ -9708,22 +9708,22 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FinalJAN</t>
+          <t>S&amp;P Global Services PMI FinalJAN</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F374" t="n">
@@ -9738,22 +9738,22 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FinalJAN</t>
+          <t>S&amp;P Global Composite PMI FinalJAN</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="F375" t="n">
@@ -9902,22 +9902,18 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>8.664M</t>
-        </is>
-      </c>
-      <c r="D381" t="inlineStr">
-        <is>
-          <t>2.6M</t>
-        </is>
-      </c>
+          <t>0.16M</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr"/>
       <c r="E381" t="inlineStr"/>
       <c r="F381" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="382">
@@ -9928,22 +9924,18 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>2.233M</t>
-        </is>
-      </c>
-      <c r="D382" t="inlineStr">
-        <is>
-          <t>1.2M</t>
-        </is>
-      </c>
+          <t>-0.186M</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr"/>
       <c r="E382" t="inlineStr"/>
       <c r="F382" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="383">
@@ -9954,15 +9946,19 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>0.373M</t>
-        </is>
-      </c>
-      <c r="D383" t="inlineStr"/>
+          <t>-5.471M</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>-1.5M</t>
+        </is>
+      </c>
       <c r="E383" t="inlineStr"/>
       <c r="F383" t="n">
         <v>3</v>
@@ -9976,12 +9972,12 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>-0.178M</t>
+          <t>-0.027M</t>
         </is>
       </c>
       <c r="D384" t="inlineStr"/>
@@ -9998,19 +9994,15 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>-5.471M</t>
-        </is>
-      </c>
-      <c r="D385" t="inlineStr">
-        <is>
-          <t>-1.5M</t>
-        </is>
-      </c>
+          <t>0.373M</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr"/>
       <c r="E385" t="inlineStr"/>
       <c r="F385" t="n">
         <v>3</v>
@@ -10024,18 +10016,22 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Gasoline Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>-0.186M</t>
-        </is>
-      </c>
-      <c r="D386" t="inlineStr"/>
+          <t>2.233M</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>1.2M</t>
+        </is>
+      </c>
       <c r="E386" t="inlineStr"/>
       <c r="F386" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="387">
@@ -10046,18 +10042,22 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>0.16M</t>
-        </is>
-      </c>
-      <c r="D387" t="inlineStr"/>
+          <t>8.664M</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>2.6M</t>
+        </is>
+      </c>
       <c r="E387" t="inlineStr"/>
       <c r="F387" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="388">
@@ -10068,12 +10068,12 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Crude Oil Imports ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>-0.027M</t>
+          <t>-0.178M</t>
         </is>
       </c>
       <c r="D388" t="inlineStr"/>
@@ -10390,12 +10390,12 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="D401" t="inlineStr"/>
@@ -10412,12 +10412,12 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D402" t="inlineStr"/>
@@ -10536,26 +10536,22 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Unemployment RateJAN</t>
+          <t>Government PayrollsJAN</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>4%</t>
-        </is>
-      </c>
-      <c r="D408" t="inlineStr">
-        <is>
-          <t>4.1%</t>
-        </is>
-      </c>
+          <t>32K</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr"/>
       <c r="E408" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>25K</t>
         </is>
       </c>
       <c r="F408" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="409">
@@ -10566,22 +10562,22 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsJAN</t>
+          <t>Nonfarm Payrolls PrivateJAN</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>3K</t>
+          <t>111K</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>-2K</t>
+          <t>141K</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>-5K</t>
+          <t>180K</t>
         </is>
       </c>
       <c r="F409" t="n">
@@ -10596,22 +10592,22 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMJAN</t>
+          <t>Average Hourly Earnings YoYJAN</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="F410" t="n">
@@ -10626,26 +10622,26 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Average Weekly HoursJAN</t>
+          <t>Non Farm PayrollsJAN</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>143K</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>170K</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>205K</t>
         </is>
       </c>
       <c r="F411" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="412">
@@ -10656,22 +10652,22 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Participation RateJAN</t>
+          <t>U-6 Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="D412" t="inlineStr"/>
       <c r="E412" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="F412" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="413">
@@ -10682,18 +10678,22 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>U-6 Unemployment RateJAN</t>
+          <t>Average Weekly HoursJAN</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D413" t="inlineStr"/>
+          <t>34.1</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F413" t="n">
@@ -10708,22 +10708,26 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Government PayrollsJAN</t>
+          <t>Average Hourly Earnings MoMJAN</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>32K</t>
-        </is>
-      </c>
-      <c r="D414" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>25K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F414" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="415">
@@ -10734,26 +10738,26 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsJAN</t>
+          <t>Manufacturing PayrollsJAN</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>143K</t>
+          <t>3K</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>170K</t>
+          <t>-2K</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>205K</t>
+          <t>-5K</t>
         </is>
       </c>
       <c r="F415" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="416">
@@ -10764,26 +10768,26 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoYJAN</t>
+          <t>Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
           <t>4.1%</t>
         </is>
       </c>
-      <c r="D416" t="inlineStr">
-        <is>
-          <t>3.8%</t>
-        </is>
-      </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F416" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="417">
@@ -10794,26 +10798,22 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateJAN</t>
+          <t>Participation RateJAN</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>111K</t>
-        </is>
-      </c>
-      <c r="D417" t="inlineStr">
-        <is>
-          <t>141K</t>
-        </is>
-      </c>
+          <t>62.6%</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr"/>
       <c r="E417" t="inlineStr">
         <is>
-          <t>180K</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="F417" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="418">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/07</t>
+          <t>Baker Hughes Total Rigs CountFEB/07</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>586</t>
         </is>
       </c>
       <c r="D430" t="inlineStr"/>
@@ -11134,12 +11134,12 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/07</t>
+          <t>Baker Hughes Oil Rig CountFEB/07</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>480</t>
         </is>
       </c>
       <c r="D431" t="inlineStr"/>
@@ -11474,14 +11474,14 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/07</t>
+          <t>MBA 30-Year Mortgage RateFEB/07</t>
         </is>
       </c>
       <c r="C447" t="inlineStr"/>
       <c r="D447" t="inlineStr"/>
       <c r="E447" t="inlineStr"/>
       <c r="F447" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="448">
@@ -11492,7 +11492,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/07</t>
+          <t>MBA Mortgage ApplicationsFEB/07</t>
         </is>
       </c>
       <c r="C448" t="inlineStr"/>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/07</t>
+          <t>MBA Mortgage Market IndexFEB/07</t>
         </is>
       </c>
       <c r="C450" t="inlineStr"/>
@@ -11546,14 +11546,14 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/07</t>
+          <t>MBA Mortgage Refinance IndexFEB/07</t>
         </is>
       </c>
       <c r="C451" t="inlineStr"/>
       <c r="D451" t="inlineStr"/>
       <c r="E451" t="inlineStr"/>
       <c r="F451" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="452">
@@ -11716,7 +11716,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C458" t="inlineStr"/>
@@ -11734,14 +11734,14 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C459" t="inlineStr"/>
       <c r="D459" t="inlineStr"/>
       <c r="E459" t="inlineStr"/>
       <c r="F459" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="460">
@@ -11752,14 +11752,14 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C460" t="inlineStr"/>
       <c r="D460" t="inlineStr"/>
       <c r="E460" t="inlineStr"/>
       <c r="F460" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="461">
@@ -11770,7 +11770,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C461" t="inlineStr"/>
@@ -11788,7 +11788,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C462" t="inlineStr"/>
@@ -11806,7 +11806,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C463" t="inlineStr"/>
@@ -11824,14 +11824,14 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C464" t="inlineStr"/>
       <c r="D464" t="inlineStr"/>
       <c r="E464" t="inlineStr"/>
       <c r="F464" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="465">
@@ -11842,14 +11842,14 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C465" t="inlineStr"/>
       <c r="D465" t="inlineStr"/>
       <c r="E465" t="inlineStr"/>
       <c r="F465" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="466">
@@ -11860,7 +11860,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C466" t="inlineStr"/>
@@ -11998,14 +11998,18 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C473" t="inlineStr"/>
-      <c r="D473" t="inlineStr"/>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F473" t="n">
@@ -12020,18 +12024,22 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C474" t="inlineStr"/>
-      <c r="D474" t="inlineStr"/>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F474" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="475">
@@ -12042,18 +12050,14 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C475" t="inlineStr"/>
-      <c r="D475" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+      <c r="D475" t="inlineStr"/>
       <c r="E475" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="F475" t="n">
@@ -12068,18 +12072,22 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C476" t="inlineStr"/>
-      <c r="D476" t="inlineStr"/>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F476" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="477">
@@ -12090,18 +12098,18 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C477" t="inlineStr"/>
       <c r="D477" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F477" t="n">
@@ -12116,14 +12124,18 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C478" t="inlineStr"/>
-      <c r="D478" t="inlineStr"/>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F478" t="n">
@@ -12138,22 +12150,18 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C479" t="inlineStr"/>
-      <c r="D479" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D479" t="inlineStr"/>
       <c r="E479" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F479" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="480">
@@ -12164,22 +12172,18 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C480" t="inlineStr"/>
-      <c r="D480" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
+      <c r="D480" t="inlineStr"/>
       <c r="E480" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="F480" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="481">
@@ -12190,18 +12194,14 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C481" t="inlineStr"/>
-      <c r="D481" t="inlineStr">
-        <is>
-          <t>3.2%</t>
-        </is>
-      </c>
+      <c r="D481" t="inlineStr"/>
       <c r="E481" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="F481" t="n">
@@ -12288,7 +12288,7 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/13</t>
+          <t>30-Year Mortgage RateFEB/13</t>
         </is>
       </c>
       <c r="C486" t="inlineStr"/>
@@ -12306,7 +12306,7 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/13</t>
+          <t>15-Year Mortgage RateFEB/13</t>
         </is>
       </c>
       <c r="C487" t="inlineStr"/>
@@ -12386,14 +12386,14 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="C491" t="inlineStr"/>
       <c r="D491" t="inlineStr"/>
       <c r="E491" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F491" t="n">
@@ -12408,18 +12408,22 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="C492" t="inlineStr"/>
-      <c r="D492" t="inlineStr"/>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F492" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="493">
@@ -12430,22 +12434,22 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="C493" t="inlineStr"/>
       <c r="D493" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="F493" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="494">
@@ -12456,18 +12460,18 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="C494" t="inlineStr"/>
       <c r="D494" t="inlineStr"/>
       <c r="E494" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F494" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="495">
@@ -12478,22 +12482,22 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="C495" t="inlineStr"/>
       <c r="D495" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F495" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="496">
@@ -12504,22 +12508,18 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="C496" t="inlineStr"/>
-      <c r="D496" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D496" t="inlineStr"/>
       <c r="E496" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F496" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="497">
@@ -12530,14 +12530,14 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="C497" t="inlineStr"/>
       <c r="D497" t="inlineStr"/>
       <c r="E497" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F497" t="n">
@@ -12552,18 +12552,18 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="C498" t="inlineStr"/>
       <c r="D498" t="inlineStr"/>
       <c r="E498" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F498" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="499">
@@ -12898,7 +12898,7 @@
       <c r="C514" t="inlineStr"/>
       <c r="D514" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E514" t="inlineStr">
@@ -13086,7 +13086,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C523" t="inlineStr"/>
@@ -13104,7 +13104,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C524" t="inlineStr"/>
@@ -13158,14 +13158,14 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="C527" t="inlineStr"/>
       <c r="D527" t="inlineStr"/>
       <c r="E527" t="inlineStr"/>
       <c r="F527" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="528">
@@ -13176,14 +13176,14 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C528" t="inlineStr"/>
       <c r="D528" t="inlineStr"/>
       <c r="E528" t="inlineStr"/>
       <c r="F528" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="529">
@@ -13194,14 +13194,14 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="C529" t="inlineStr"/>
       <c r="D529" t="inlineStr"/>
       <c r="E529" t="inlineStr"/>
       <c r="F529" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="530">
@@ -13212,14 +13212,14 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C530" t="inlineStr"/>
       <c r="D530" t="inlineStr"/>
       <c r="E530" t="inlineStr"/>
       <c r="F530" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="531">
@@ -13230,14 +13230,18 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Net Long-term TIC FlowsDEC</t>
         </is>
       </c>
       <c r="C531" t="inlineStr"/>
-      <c r="D531" t="inlineStr"/>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>$149.1B</t>
+        </is>
+      </c>
       <c r="E531" t="inlineStr"/>
       <c r="F531" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="532">
@@ -13284,18 +13288,14 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsDEC</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C534" t="inlineStr"/>
-      <c r="D534" t="inlineStr">
-        <is>
-          <t>$149.1B</t>
-        </is>
-      </c>
+      <c r="D534" t="inlineStr"/>
       <c r="E534" t="inlineStr"/>
       <c r="F534" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="535">
@@ -13306,18 +13306,14 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsDEC</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="C535" t="inlineStr"/>
-      <c r="D535" t="inlineStr">
-        <is>
-          <t>$149.1B</t>
-        </is>
-      </c>
+      <c r="D535" t="inlineStr"/>
       <c r="E535" t="inlineStr"/>
       <c r="F535" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="536">
@@ -13328,14 +13324,18 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Net Long-term TIC FlowsDEC</t>
         </is>
       </c>
       <c r="C536" t="inlineStr"/>
-      <c r="D536" t="inlineStr"/>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>$149.1B</t>
+        </is>
+      </c>
       <c r="E536" t="inlineStr"/>
       <c r="F536" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="537">
@@ -13346,7 +13346,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C537" t="inlineStr"/>
@@ -13364,14 +13364,14 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C538" t="inlineStr"/>
       <c r="D538" t="inlineStr"/>
       <c r="E538" t="inlineStr"/>
       <c r="F538" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="539">
@@ -13382,7 +13382,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C539" t="inlineStr"/>
@@ -13400,7 +13400,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C540" t="inlineStr"/>
@@ -13418,14 +13418,14 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C541" t="inlineStr"/>
       <c r="D541" t="inlineStr"/>
       <c r="E541" t="inlineStr"/>
       <c r="F541" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="542">
@@ -13436,7 +13436,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C542" t="inlineStr"/>
@@ -13454,7 +13454,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C543" t="inlineStr"/>
@@ -13472,7 +13472,7 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C544" t="inlineStr"/>
@@ -13490,7 +13490,7 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C545" t="inlineStr"/>
@@ -13526,18 +13526,22 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C547" t="inlineStr"/>
-      <c r="D547" t="inlineStr"/>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>1.4M</t>
+        </is>
+      </c>
       <c r="E547" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F547" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="548">
@@ -13548,18 +13552,18 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C548" t="inlineStr"/>
       <c r="D548" t="inlineStr">
         <is>
-          <t>1.39M</t>
+          <t>1.46M</t>
         </is>
       </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F548" t="n">
@@ -13574,18 +13578,18 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C549" t="inlineStr"/>
       <c r="D549" t="inlineStr">
         <is>
-          <t>1.45M</t>
+          <t>1.4M</t>
         </is>
       </c>
       <c r="E549" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F549" t="n">
@@ -13600,14 +13604,14 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C550" t="inlineStr"/>
       <c r="D550" t="inlineStr"/>
       <c r="E550" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F550" t="n">
@@ -13692,22 +13696,18 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C554" t="inlineStr"/>
-      <c r="D554" t="inlineStr">
-        <is>
-          <t>1.4M</t>
-        </is>
-      </c>
+      <c r="D554" t="inlineStr"/>
       <c r="E554" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F554" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="555">
@@ -13978,18 +13978,22 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C569" t="inlineStr"/>
-      <c r="D569" t="inlineStr"/>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>16.3</t>
+        </is>
+      </c>
       <c r="E569" t="inlineStr">
         <is>
-          <t>1879.0K</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F569" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="570">
@@ -14000,22 +14004,18 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C570" t="inlineStr"/>
-      <c r="D570" t="inlineStr">
-        <is>
-          <t>215K</t>
-        </is>
-      </c>
+      <c r="D570" t="inlineStr"/>
       <c r="E570" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>219.0K</t>
         </is>
       </c>
       <c r="F570" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="571">
@@ -14026,20 +14026,12 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C571" t="inlineStr"/>
-      <c r="D571" t="inlineStr">
-        <is>
-          <t>1860K</t>
-        </is>
-      </c>
-      <c r="E571" t="inlineStr">
-        <is>
-          <t>1879.0K</t>
-        </is>
-      </c>
+      <c r="D571" t="inlineStr"/>
+      <c r="E571" t="inlineStr"/>
       <c r="F571" t="n">
         <v>3</v>
       </c>
@@ -14052,16 +14044,12 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C572" t="inlineStr"/>
       <c r="D572" t="inlineStr"/>
-      <c r="E572" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="E572" t="inlineStr"/>
       <c r="F572" t="n">
         <v>3</v>
       </c>
@@ -14074,14 +14062,22 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C573" t="inlineStr"/>
-      <c r="D573" t="inlineStr"/>
-      <c r="E573" t="inlineStr"/>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>215K</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>220.0K</t>
+        </is>
+      </c>
       <c r="F573" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="574">
@@ -14092,12 +14088,20 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C574" t="inlineStr"/>
-      <c r="D574" t="inlineStr"/>
-      <c r="E574" t="inlineStr"/>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>1860K</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="F574" t="n">
         <v>3</v>
       </c>
@@ -14110,14 +14114,22 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C575" t="inlineStr"/>
-      <c r="D575" t="inlineStr"/>
-      <c r="E575" t="inlineStr"/>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>215K</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>220.0K</t>
+        </is>
+      </c>
       <c r="F575" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="576">
@@ -14128,7 +14140,7 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C576" t="inlineStr"/>
@@ -14146,14 +14158,22 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C577" t="inlineStr"/>
-      <c r="D577" t="inlineStr"/>
-      <c r="E577" t="inlineStr"/>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>16.3</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="F577" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="578">
@@ -14164,7 +14184,7 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C578" t="inlineStr"/>
@@ -14182,22 +14202,14 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C579" t="inlineStr"/>
-      <c r="D579" t="inlineStr">
-        <is>
-          <t>16.3</t>
-        </is>
-      </c>
-      <c r="E579" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="D579" t="inlineStr"/>
+      <c r="E579" t="inlineStr"/>
       <c r="F579" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="580">
@@ -14208,16 +14220,12 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C580" t="inlineStr"/>
       <c r="D580" t="inlineStr"/>
-      <c r="E580" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="E580" t="inlineStr"/>
       <c r="F580" t="n">
         <v>3</v>
       </c>
@@ -14248,12 +14256,16 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C582" t="inlineStr"/>
       <c r="D582" t="inlineStr"/>
-      <c r="E582" t="inlineStr"/>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="F582" t="n">
         <v>3</v>
       </c>
@@ -14266,7 +14278,7 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C583" t="inlineStr"/>
@@ -14284,22 +14296,22 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C584" t="inlineStr"/>
       <c r="D584" t="inlineStr">
         <is>
-          <t>215K</t>
+          <t>1860K</t>
         </is>
       </c>
       <c r="E584" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>1879.0K</t>
         </is>
       </c>
       <c r="F584" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="585">
@@ -14310,22 +14322,14 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C585" t="inlineStr"/>
-      <c r="D585" t="inlineStr">
-        <is>
-          <t>16.3</t>
-        </is>
-      </c>
-      <c r="E585" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="D585" t="inlineStr"/>
+      <c r="E585" t="inlineStr"/>
       <c r="F585" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="586">
@@ -14336,7 +14340,7 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C586" t="inlineStr"/>
@@ -14550,7 +14554,7 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C597" t="inlineStr"/>
@@ -14568,14 +14572,14 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C598" t="inlineStr"/>
       <c r="D598" t="inlineStr"/>
       <c r="E598" t="inlineStr"/>
       <c r="F598" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="599">
@@ -14586,14 +14590,14 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C599" t="inlineStr"/>
       <c r="D599" t="inlineStr"/>
       <c r="E599" t="inlineStr"/>
       <c r="F599" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="600">
@@ -14604,14 +14608,14 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C600" t="inlineStr"/>
       <c r="D600" t="inlineStr"/>
       <c r="E600" t="inlineStr"/>
       <c r="F600" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="601">
@@ -14622,14 +14626,14 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C601" t="inlineStr"/>
       <c r="D601" t="inlineStr"/>
       <c r="E601" t="inlineStr"/>
       <c r="F601" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="602">
@@ -14640,7 +14644,7 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C602" t="inlineStr"/>
@@ -14658,7 +14662,7 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C603" t="inlineStr"/>
@@ -14676,7 +14680,7 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C604" t="inlineStr"/>
@@ -14694,7 +14698,7 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C605" t="inlineStr"/>
@@ -14712,7 +14716,7 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C606" t="inlineStr"/>
@@ -14730,7 +14734,7 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C607" t="inlineStr"/>
@@ -14748,7 +14752,7 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C608" t="inlineStr"/>
@@ -14766,14 +14770,14 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>Fed Musalem Speech</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C609" t="inlineStr"/>
       <c r="D609" t="inlineStr"/>
       <c r="E609" t="inlineStr"/>
       <c r="F609" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="610">
@@ -14784,14 +14788,14 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C610" t="inlineStr"/>
       <c r="D610" t="inlineStr"/>
       <c r="E610" t="inlineStr"/>
       <c r="F610" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="611">
@@ -14802,7 +14806,7 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C611" t="inlineStr"/>
@@ -14820,7 +14824,7 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C612" t="inlineStr"/>
@@ -14838,14 +14842,14 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C613" t="inlineStr"/>
       <c r="D613" t="inlineStr"/>
       <c r="E613" t="inlineStr"/>
       <c r="F613" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="614">
@@ -14856,7 +14860,7 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C614" t="inlineStr"/>
@@ -14874,7 +14878,7 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C615" t="inlineStr"/>
@@ -14892,14 +14896,14 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C616" t="inlineStr"/>
       <c r="D616" t="inlineStr"/>
       <c r="E616" t="inlineStr"/>
       <c r="F616" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="617">
@@ -14910,14 +14914,14 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>Fed Musalem Speech</t>
         </is>
       </c>
       <c r="C617" t="inlineStr"/>
       <c r="D617" t="inlineStr"/>
       <c r="E617" t="inlineStr"/>
       <c r="F617" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="618">
@@ -14928,7 +14932,7 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C618" t="inlineStr"/>
@@ -14946,14 +14950,14 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C619" t="inlineStr"/>
       <c r="D619" t="inlineStr"/>
       <c r="E619" t="inlineStr"/>
       <c r="F619" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="620">
@@ -15198,7 +15202,7 @@
       <c r="C632" t="inlineStr"/>
       <c r="D632" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>53</t>
         </is>
       </c>
       <c r="E632" t="inlineStr">
@@ -15292,14 +15296,18 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C636" t="inlineStr"/>
-      <c r="D636" t="inlineStr"/>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>67.8</t>
+        </is>
+      </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F636" t="n">
@@ -15314,22 +15322,22 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C637" t="inlineStr"/>
       <c r="D637" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E637" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F637" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="638">
@@ -15340,18 +15348,18 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C638" t="inlineStr"/>
       <c r="D638" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="E638" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F638" t="n">
@@ -15366,22 +15374,18 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C639" t="inlineStr"/>
-      <c r="D639" t="inlineStr">
-        <is>
-          <t>67.3</t>
-        </is>
-      </c>
+      <c r="D639" t="inlineStr"/>
       <c r="E639" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F639" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="640">
@@ -15392,18 +15396,18 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C640" t="inlineStr"/>
       <c r="D640" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="E640" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F640" t="n">
@@ -15418,22 +15422,22 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C641" t="inlineStr"/>
       <c r="D641" t="inlineStr">
         <is>
-          <t>4.13M</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E641" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F641" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="642">
@@ -15444,18 +15448,18 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C642" t="inlineStr"/>
       <c r="D642" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="E642" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F642" t="n">
@@ -15470,22 +15474,22 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C643" t="inlineStr"/>
       <c r="D643" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.13M</t>
         </is>
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F643" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="644">
@@ -15496,22 +15500,18 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C644" t="inlineStr"/>
-      <c r="D644" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+      <c r="D644" t="inlineStr"/>
       <c r="E644" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F644" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="645">
@@ -15522,18 +15522,18 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C645" t="inlineStr"/>
       <c r="D645" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F645" t="n">
@@ -15548,18 +15548,22 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C646" t="inlineStr"/>
-      <c r="D646" t="inlineStr"/>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F646" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="647">
@@ -15570,22 +15574,22 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C647" t="inlineStr"/>
       <c r="D647" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F647" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="648">
@@ -15596,22 +15600,22 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C648" t="inlineStr"/>
       <c r="D648" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>4.17M</t>
         </is>
       </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F648" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="649">
@@ -15622,22 +15626,22 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C649" t="inlineStr"/>
       <c r="D649" t="inlineStr">
         <is>
-          <t>4.17M</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F649" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="650">
@@ -15720,7 +15724,7 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/21</t>
+          <t>Baker Hughes Oil Rig CountFEB/21</t>
         </is>
       </c>
       <c r="C654" t="inlineStr"/>
@@ -15738,7 +15742,7 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/21</t>
+          <t>Baker Hughes Total Rigs CountFEB/21</t>
         </is>
       </c>
       <c r="C655" t="inlineStr"/>
@@ -15828,7 +15832,7 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C660" t="inlineStr"/>
@@ -15846,7 +15850,7 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C661" t="inlineStr"/>
@@ -15864,7 +15868,7 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C662" t="inlineStr"/>
@@ -15882,7 +15886,7 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C663" t="inlineStr"/>
@@ -15990,7 +15994,7 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C669" t="inlineStr"/>
@@ -16048,7 +16052,7 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C672" t="inlineStr"/>
@@ -16066,7 +16070,7 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C673" t="inlineStr"/>
@@ -16084,14 +16088,18 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C674" t="inlineStr"/>
       <c r="D674" t="inlineStr"/>
-      <c r="E674" t="inlineStr"/>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="F674" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="675">
@@ -16102,7 +16110,7 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C675" t="inlineStr"/>
@@ -16120,18 +16128,14 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C676" t="inlineStr"/>
       <c r="D676" t="inlineStr"/>
-      <c r="E676" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="E676" t="inlineStr"/>
       <c r="F676" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="677">
@@ -16142,7 +16146,7 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C677" t="inlineStr"/>
@@ -16232,14 +16236,14 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C682" t="inlineStr"/>
       <c r="D682" t="inlineStr"/>
       <c r="E682" t="inlineStr"/>
       <c r="F682" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="683">
@@ -16250,14 +16254,14 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C683" t="inlineStr"/>
       <c r="D683" t="inlineStr"/>
       <c r="E683" t="inlineStr"/>
       <c r="F683" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="684">
@@ -16340,7 +16344,7 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexFEB</t>
+          <t>Dallas Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C688" t="inlineStr"/>
@@ -16358,7 +16362,7 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexFEB</t>
+          <t>Dallas Fed Services IndexFEB</t>
         </is>
       </c>
       <c r="C689" t="inlineStr"/>
@@ -16376,7 +16380,7 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>Money SupplyJAN</t>
         </is>
       </c>
       <c r="C690" t="inlineStr"/>
@@ -16394,7 +16398,7 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>Money SupplyJAN</t>
         </is>
       </c>
       <c r="C691" t="inlineStr"/>
@@ -16412,7 +16416,7 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>Money SupplyJAN</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C692" t="inlineStr"/>
@@ -16430,7 +16434,7 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>Money SupplyJAN</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C693" t="inlineStr"/>
@@ -16484,7 +16488,7 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/21</t>
+          <t>MBA Mortgage ApplicationsFEB/21</t>
         </is>
       </c>
       <c r="C696" t="inlineStr"/>
@@ -16502,7 +16506,7 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/21</t>
+          <t>MBA Purchase IndexFEB/21</t>
         </is>
       </c>
       <c r="C697" t="inlineStr"/>
@@ -16520,14 +16524,14 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
+          <t>MBA Mortgage Market IndexFEB/21</t>
         </is>
       </c>
       <c r="C698" t="inlineStr"/>
       <c r="D698" t="inlineStr"/>
       <c r="E698" t="inlineStr"/>
       <c r="F698" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="699">
@@ -16538,7 +16542,7 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/21</t>
+          <t>MBA Mortgage ApplicationsFEB/21</t>
         </is>
       </c>
       <c r="C699" t="inlineStr"/>
@@ -16556,7 +16560,7 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C700" t="inlineStr"/>
@@ -16574,7 +16578,7 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/21</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C701" t="inlineStr"/>
@@ -16592,7 +16596,7 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>MBA Mortgage Market IndexFEB/21</t>
         </is>
       </c>
       <c r="C702" t="inlineStr"/>
@@ -16610,14 +16614,14 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
         </is>
       </c>
       <c r="C703" t="inlineStr"/>
       <c r="D703" t="inlineStr"/>
       <c r="E703" t="inlineStr"/>
       <c r="F703" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="704">
@@ -16628,7 +16632,7 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/21</t>
+          <t>MBA Mortgage Refinance IndexFEB/21</t>
         </is>
       </c>
       <c r="C704" t="inlineStr"/>
@@ -16700,7 +16704,7 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>New Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C708" t="inlineStr"/>
@@ -16718,7 +16722,7 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>New Home Sales MoMJAN</t>
+          <t>New Home SalesJAN</t>
         </is>
       </c>
       <c r="C709" t="inlineStr"/>
@@ -16736,7 +16740,7 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>New Home Sales MoMJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C710" t="inlineStr"/>
@@ -16772,7 +16776,7 @@
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>New Home SalesJAN</t>
+          <t>New Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C712" t="inlineStr"/>
@@ -16790,7 +16794,7 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C713" t="inlineStr"/>
@@ -16808,14 +16812,14 @@
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C714" t="inlineStr"/>
       <c r="D714" t="inlineStr"/>
       <c r="E714" t="inlineStr"/>
       <c r="F714" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="715">
@@ -16844,7 +16848,7 @@
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C716" t="inlineStr"/>
@@ -16880,14 +16884,14 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
       <c r="C718" t="inlineStr"/>
       <c r="D718" t="inlineStr"/>
       <c r="E718" t="inlineStr"/>
       <c r="F718" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="719">
@@ -16898,14 +16902,14 @@
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C719" t="inlineStr"/>
       <c r="D719" t="inlineStr"/>
       <c r="E719" t="inlineStr"/>
       <c r="F719" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="720">
@@ -16916,7 +16920,7 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C720" t="inlineStr"/>
@@ -16952,14 +16956,14 @@
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C722" t="inlineStr"/>
       <c r="D722" t="inlineStr"/>
       <c r="E722" t="inlineStr"/>
       <c r="F722" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="723">
@@ -16970,7 +16974,7 @@
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C723" t="inlineStr"/>
@@ -16988,7 +16992,7 @@
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/21</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C724" t="inlineStr"/>
@@ -17006,7 +17010,7 @@
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/21</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C725" t="inlineStr"/>
@@ -17024,7 +17028,7 @@
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
+          <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C726" t="inlineStr"/>
@@ -17042,7 +17046,7 @@
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+          <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C727" t="inlineStr"/>
@@ -17060,14 +17064,14 @@
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C728" t="inlineStr"/>
       <c r="D728" t="inlineStr"/>
       <c r="E728" t="inlineStr"/>
       <c r="F728" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="729">
@@ -17078,14 +17082,14 @@
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C729" t="inlineStr"/>
       <c r="D729" t="inlineStr"/>
       <c r="E729" t="inlineStr"/>
       <c r="F729" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="730">
@@ -17096,7 +17100,7 @@
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
+          <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C730" t="inlineStr"/>
@@ -17132,7 +17136,7 @@
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>17-Week Bill Auction</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C732" t="inlineStr"/>
@@ -17168,7 +17172,7 @@
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>17-Week Bill Auction</t>
         </is>
       </c>
       <c r="C734" t="inlineStr"/>
@@ -17204,7 +17208,7 @@
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Fed Bostic Speech</t>
         </is>
       </c>
       <c r="C736" t="inlineStr"/>
@@ -17240,7 +17244,7 @@
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>Fed Bostic Speech</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C738" t="inlineStr"/>
@@ -17276,7 +17280,7 @@
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C740" t="inlineStr"/>
@@ -17294,7 +17298,7 @@
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>2-Year FRN Auction</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C741" t="inlineStr"/>
@@ -17312,7 +17316,7 @@
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>2-Year FRN Auction</t>
         </is>
       </c>
       <c r="C742" t="inlineStr"/>
@@ -17348,7 +17352,7 @@
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C744" t="inlineStr"/>
@@ -17366,7 +17370,7 @@
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C745" t="inlineStr"/>
@@ -17384,7 +17388,7 @@
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>2-Year FRN Auction</t>
         </is>
       </c>
       <c r="C746" t="inlineStr"/>
@@ -17402,7 +17406,7 @@
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>2-Year FRN Auction</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C747" t="inlineStr"/>
@@ -17420,14 +17424,14 @@
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirJAN</t>
+          <t>Durable Goods Orders MoMJAN</t>
         </is>
       </c>
       <c r="C748" t="inlineStr"/>
       <c r="D748" t="inlineStr"/>
       <c r="E748" t="inlineStr"/>
       <c r="F748" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="749">
@@ -17438,7 +17442,7 @@
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/22</t>
+          <t>Non Defense Goods Orders Ex AirJAN</t>
         </is>
       </c>
       <c r="C749" t="inlineStr"/>
@@ -17456,18 +17460,22 @@
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ 2nd EstQ4</t>
+          <t>GDP Price Index QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C750" t="inlineStr"/>
-      <c r="D750" t="inlineStr"/>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>2.2%</t>
+        </is>
+      </c>
       <c r="E750" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="F750" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="751">
@@ -17478,14 +17486,14 @@
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMJAN</t>
+          <t>Initial Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C751" t="inlineStr"/>
       <c r="D751" t="inlineStr"/>
       <c r="E751" t="inlineStr"/>
       <c r="F751" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="752">
@@ -17496,20 +17504,12 @@
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ 2nd EstQ4</t>
+          <t>Continuing Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C752" t="inlineStr"/>
-      <c r="D752" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
-      <c r="E752" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+      <c r="D752" t="inlineStr"/>
+      <c r="E752" t="inlineStr"/>
       <c r="F752" t="n">
         <v>3</v>
       </c>
@@ -17522,12 +17522,20 @@
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/15</t>
+          <t>Core PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C753" t="inlineStr"/>
-      <c r="D753" t="inlineStr"/>
-      <c r="E753" t="inlineStr"/>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="E753" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="F753" t="n">
         <v>3</v>
       </c>
@@ -17540,22 +17548,14 @@
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ 2nd EstQ4</t>
+          <t>Durable Goods Orders ex Defense MoMJAN</t>
         </is>
       </c>
       <c r="C754" t="inlineStr"/>
-      <c r="D754" t="inlineStr">
-        <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="E754" t="inlineStr">
-        <is>
-          <t>2.2%</t>
-        </is>
-      </c>
+      <c r="D754" t="inlineStr"/>
+      <c r="E754" t="inlineStr"/>
       <c r="F754" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="755">
@@ -17566,14 +17566,18 @@
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMJAN</t>
+          <t>GDP Sales QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C755" t="inlineStr"/>
       <c r="D755" t="inlineStr"/>
-      <c r="E755" t="inlineStr"/>
+      <c r="E755" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="F755" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="756">
@@ -17584,22 +17588,14 @@
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
+          <t>Jobless Claims 4-week AverageFEB/22</t>
         </is>
       </c>
       <c r="C756" t="inlineStr"/>
-      <c r="D756" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
-      <c r="E756" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
+      <c r="D756" t="inlineStr"/>
+      <c r="E756" t="inlineStr"/>
       <c r="F756" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="757">
@@ -17610,14 +17606,14 @@
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMJAN</t>
+          <t>Durable Goods Orders Ex Transp MoMJAN</t>
         </is>
       </c>
       <c r="C757" t="inlineStr"/>
       <c r="D757" t="inlineStr"/>
       <c r="E757" t="inlineStr"/>
       <c r="F757" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="758">
@@ -17628,7 +17624,7 @@
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ 2nd EstQ4</t>
+          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C758" t="inlineStr"/>
@@ -17643,7 +17639,7 @@
         </is>
       </c>
       <c r="F758" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="759">
@@ -17686,6 +17682,288 @@
         <v>3</v>
       </c>
     </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>2025-02-27 08:30:00-05:00</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>Non Defense Goods Orders Ex AirJAN</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr"/>
+      <c r="D761" t="inlineStr"/>
+      <c r="E761" t="inlineStr"/>
+      <c r="F761" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>2025-02-27 08:30:00-05:00</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>Jobless Claims 4-week AverageFEB/22</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr"/>
+      <c r="D762" t="inlineStr"/>
+      <c r="E762" t="inlineStr"/>
+      <c r="F762" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>2025-02-27 08:30:00-05:00</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>GDP Sales QoQ 2nd EstQ4</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr"/>
+      <c r="D763" t="inlineStr"/>
+      <c r="E763" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="F763" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>2025-02-27 08:30:00-05:00</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>Durable Goods Orders ex Defense MoMJAN</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr"/>
+      <c r="D764" t="inlineStr"/>
+      <c r="E764" t="inlineStr"/>
+      <c r="F764" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>2025-02-27 08:30:00-05:00</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>Core PCE Prices QoQ 2nd EstQ4</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr"/>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="E765" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="F765" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>2025-02-27 08:30:00-05:00</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>Continuing Jobless ClaimsFEB/15</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr"/>
+      <c r="D766" t="inlineStr"/>
+      <c r="E766" t="inlineStr"/>
+      <c r="F766" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>2025-02-27 08:30:00-05:00</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>GDP Price Index QoQ 2nd EstQ4</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr"/>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="E767" t="inlineStr">
+        <is>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="F767" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>2025-02-27 08:30:00-05:00</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>Durable Goods Orders Ex Transp MoMJAN</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr"/>
+      <c r="D768" t="inlineStr"/>
+      <c r="E768" t="inlineStr"/>
+      <c r="F768" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>2025-02-27 08:30:00-05:00</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr"/>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="E769" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="F769" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>2025-02-27 08:30:00-05:00</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>Durable Goods Orders MoMJAN</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr"/>
+      <c r="D770" t="inlineStr"/>
+      <c r="E770" t="inlineStr"/>
+      <c r="F770" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>2025-02-27 08:30:00-05:00</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>PCE Prices QoQ 2nd EstQ4</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr"/>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="E771" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="F771" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>2025-02-27 08:30:00-05:00</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>PCE Prices QoQ 2nd EstQ4</t>
+        </is>
+      </c>
+      <c r="C772" t="inlineStr"/>
+      <c r="D772" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="E772" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="F772" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>2025-02-27 08:30:00-05:00</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
+        </is>
+      </c>
+      <c r="C773" t="inlineStr"/>
+      <c r="D773" t="inlineStr"/>
+      <c r="E773" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="F773" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-02-27.xlsx
+++ b/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-02-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F773"/>
+  <dimension ref="A1:F777"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -720,22 +720,18 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.178M</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>-2.75M</t>
-        </is>
-      </c>
+          <t>0.041M</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -746,12 +742,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -768,18 +764,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>7.717M</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0.7M</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -790,19 +790,15 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>6.406M</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>-0.1M</t>
-        </is>
-      </c>
+          <t>-0.416M</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
         <v>3</v>
@@ -816,12 +812,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.142M</t>
+          <t>0.099M</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -838,15 +834,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.416M</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>-0.1M</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
         <v>3</v>
@@ -860,22 +860,18 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -886,18 +882,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.323M</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -908,12 +908,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.041M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1582,22 +1582,18 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Balance of TradeNOV</t>
+          <t>ImportsNOV</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>$-78.2B</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>$-78B</t>
-        </is>
-      </c>
+          <t>$351.6B</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>$-70B</t>
+          <t>$334B</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -1638,18 +1634,22 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ImportsNOV</t>
+          <t>Balance of TradeNOV</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>$351.6B</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
+          <t>$-78.2B</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>$-78B</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>$334B</t>
+          <t>$-70B</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Used Car Prices MoMDEC</t>
+          <t>Used Car Prices YoYDEC</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -2254,12 +2254,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Used Car Prices YoYDEC</t>
+          <t>Used Car Prices MoMDEC</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -2860,22 +2860,18 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>34.3</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
+          <t>33K</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F102" t="n">
@@ -2890,22 +2886,26 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr"/>
+          <t>223K</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>135K</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
@@ -2916,26 +2916,26 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>160K</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
@@ -2946,26 +2946,26 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106">
@@ -2976,26 +2976,22 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107">
@@ -3006,26 +3002,26 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
@@ -3036,26 +3032,26 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>160K</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
@@ -3066,26 +3062,22 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>223K</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>135K</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="110">
@@ -3096,18 +3088,22 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>33K</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr"/>
+          <t>34.3</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F110" t="n">
@@ -3122,22 +3118,26 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="112">
@@ -3148,18 +3148,18 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelJAN</t>
+          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F112" t="n">
@@ -3174,26 +3174,22 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelJAN</t>
+          <t>Michigan Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>73.2</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>73.8</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="114">
@@ -3204,18 +3200,18 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelJAN</t>
+          <t>Michigan Current Conditions PrelJAN</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F114" t="n">
@@ -3230,18 +3226,18 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelJAN</t>
+          <t>Michigan Consumer Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F115" t="n">
@@ -3256,22 +3252,26 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
+          <t>Michigan Consumer Sentiment PrelJAN</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr"/>
+          <t>73.2</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>73.8</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117">
@@ -3366,12 +3366,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/10</t>
+          <t>Baker Hughes Total Rigs CountJAN/10</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>584</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
@@ -3388,12 +3388,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/10</t>
+          <t>Baker Hughes Oil Rig CountJAN/10</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>480</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
@@ -4010,26 +4010,22 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYDEC</t>
+          <t>CPI s.aDEC</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+          <t>317.685</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>317.4</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="148">
@@ -4040,26 +4036,26 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMDEC</t>
+          <t>CPIDEC</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>315.6</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="149">
@@ -4070,26 +4066,26 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYDEC</t>
+          <t>NY Empire State Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>-12.60</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="150">
@@ -4100,22 +4096,22 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMDEC</t>
+          <t>Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F150" t="n">
@@ -4130,26 +4126,26 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexJAN</t>
+          <t>Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>-12.60</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="152">
@@ -4160,26 +4156,26 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>CPIDEC</t>
+          <t>Core Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>315.6</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153">
@@ -4190,22 +4186,26 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>CPI s.aDEC</t>
+          <t>Core Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>317.685</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr"/>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>317.4</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154">
@@ -4252,22 +4252,18 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>2.60M</t>
-        </is>
-      </c>
+          <t>0.646M</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="157">
@@ -4278,15 +4274,19 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>0.765M</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr"/>
+          <t>3.077M</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>1.1M</t>
+        </is>
+      </c>
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="n">
         <v>3</v>
@@ -4300,12 +4300,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>-0.021M</t>
+          <t>-0.255M</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
@@ -4322,22 +4322,18 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>-1.961M</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>-1.6M</t>
-        </is>
-      </c>
+          <t>-1.304M</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="160">
@@ -4348,12 +4344,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>-1.304M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
@@ -4370,12 +4366,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>-0.021M</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
@@ -4392,19 +4388,15 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>3.077M</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>1.1M</t>
-        </is>
-      </c>
+          <t>0.765M</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="n">
         <v>3</v>
@@ -4418,18 +4410,22 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>0.646M</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>2.60M</t>
+        </is>
+      </c>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="164">
@@ -4440,18 +4436,22 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>0.397M</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr"/>
+          <t>-1.961M</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>-1.6M</t>
+        </is>
+      </c>
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="165">
@@ -4556,26 +4556,26 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>1859K</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>1870.0K</t>
         </is>
       </c>
       <c r="F170" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="171">
@@ -4586,24 +4586,16 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr"/>
       <c r="F171" t="n">
         <v>3</v>
       </c>
@@ -4616,20 +4608,16 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>39.00</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>4.0%</t>
-        </is>
-      </c>
+      <c r="E172" t="inlineStr"/>
       <c r="F172" t="n">
         <v>3</v>
       </c>
@@ -4642,18 +4630,26 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr"/>
-      <c r="E173" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
       <c r="F173" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="174">
@@ -4664,18 +4660,26 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>11.9</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr"/>
-      <c r="E174" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
       <c r="F174" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="175">
@@ -4686,22 +4690,26 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>212.75K</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F175" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="176">
@@ -4712,26 +4720,22 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>1.8%</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F176" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="177">
@@ -4742,24 +4746,16 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>1.6%</t>
-        </is>
-      </c>
+          <t>46.3</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" t="inlineStr"/>
       <c r="F177" t="n">
         <v>3</v>
       </c>
@@ -4772,26 +4768,18 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>217K</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>210K</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>209.0K</t>
-        </is>
-      </c>
+          <t>31.90</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr"/>
       <c r="F178" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="179">
@@ -4802,16 +4790,24 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>46.3</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr"/>
-      <c r="E179" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>1.6%</t>
+        </is>
+      </c>
       <c r="F179" t="n">
         <v>3</v>
       </c>
@@ -4824,22 +4820,26 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>1.8%</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F180" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="181">
@@ -4850,26 +4850,22 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+          <t>212.75K</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F181" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="182">
@@ -4880,26 +4876,18 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr"/>
+      <c r="E182" t="inlineStr"/>
       <c r="F182" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="183">
@@ -4910,16 +4898,20 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>39.00</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D183" t="inlineStr"/>
-      <c r="E183" t="inlineStr"/>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>4.0%</t>
+        </is>
+      </c>
       <c r="F183" t="n">
         <v>3</v>
       </c>
@@ -4932,16 +4924,24 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr"/>
-      <c r="E184" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F184" t="n">
         <v>3</v>
       </c>
@@ -4954,26 +4954,26 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="186">
@@ -4984,26 +4984,26 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>217K</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>210K</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>209.0K</t>
         </is>
       </c>
       <c r="F186" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="187">
@@ -5014,22 +5014,22 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Business Inventories MoMNOV</t>
+          <t>NAHB Housing Market IndexJAN</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F187" t="n">
@@ -5044,17 +5044,17 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoMNOV</t>
+          <t>Business Inventories MoMNOV</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -5063,7 +5063,7 @@
         </is>
       </c>
       <c r="F188" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="189">
@@ -5074,26 +5074,26 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>NAHB Housing Market IndexJAN</t>
+          <t>Retail Inventories Ex Autos MoMNOV</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F189" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="190">
@@ -5240,22 +5240,26 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Housing Starts MoMDEC</t>
+          <t>Building Permits PrelDEC</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>15.8%</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr"/>
+          <t>1.483M</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>1.46M</t>
+        </is>
+      </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>1.48M</t>
         </is>
       </c>
       <c r="F196" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="197">
@@ -5266,22 +5270,26 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelDEC</t>
+          <t>Housing StartsDEC</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr"/>
+          <t>1.499M</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>1.32M</t>
+        </is>
+      </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>1.32M</t>
         </is>
       </c>
       <c r="F197" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="198">
@@ -5292,26 +5300,22 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Housing StartsDEC</t>
+          <t>Building Permits MoM PrelDEC</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>1.499M</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>1.32M</t>
-        </is>
-      </c>
+          <t>-0.7%</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr">
         <is>
-          <t>1.32M</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="F198" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="199">
@@ -5322,26 +5326,22 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Building Permits PrelDEC</t>
+          <t>Housing Starts MoMDEC</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>1.483M</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>1.46M</t>
-        </is>
-      </c>
+          <t>15.8%</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr"/>
       <c r="E199" t="inlineStr">
         <is>
-          <t>1.48M</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="F199" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="200">
@@ -5538,22 +5538,18 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsNOV</t>
+          <t>Overall Net Capital FlowsNOV</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>$79B</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr">
-        <is>
           <t>$159.9B</t>
         </is>
       </c>
+      <c r="D207" t="inlineStr"/>
       <c r="E207" t="inlineStr"/>
       <c r="F207" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="208">
@@ -5564,12 +5560,12 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsNOV</t>
+          <t>Foreign Bond InvestmentNOV</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>$159.9B</t>
+          <t>$-15.8B</t>
         </is>
       </c>
       <c r="D208" t="inlineStr"/>
@@ -5586,18 +5582,22 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentNOV</t>
+          <t>Net Long-term TIC FlowsNOV</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>$-15.8B</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr"/>
+          <t>$79B</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>$159.9B</t>
+        </is>
+      </c>
       <c r="E209" t="inlineStr"/>
       <c r="F209" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="210">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D233" t="inlineStr"/>
@@ -6172,19 +6172,15 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>6.96%</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr"/>
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="n">
         <v>3</v>
@@ -6198,12 +6194,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="D235" t="inlineStr"/>
@@ -6220,22 +6216,18 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.068M</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr"/>
       <c r="E236" t="inlineStr"/>
       <c r="F236" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="237">
@@ -6246,22 +6238,18 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>0.184M</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr"/>
       <c r="E237" t="inlineStr"/>
       <c r="F237" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="238">
@@ -6272,15 +6260,19 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>-0.473M</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="n">
         <v>3</v>
@@ -6294,18 +6286,22 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>0.184M</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="240">
@@ -6316,18 +6312,22 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>0.068M</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="241">
@@ -6338,12 +6338,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D241" t="inlineStr"/>
@@ -6360,12 +6360,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>6.96%</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -6382,12 +6382,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
@@ -6448,18 +6448,22 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashJAN</t>
+          <t>S&amp;P Global Manufacturing PMI FlashJAN</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>52.4</t>
-        </is>
-      </c>
-      <c r="D246" t="inlineStr"/>
+          <t>50.1</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="F246" t="n">
@@ -6474,22 +6478,18 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashJAN</t>
+          <t>S&amp;P Global Composite PMI FlashJAN</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>52.8</t>
-        </is>
-      </c>
-      <c r="D247" t="inlineStr">
-        <is>
-          <t>56.5</t>
-        </is>
-      </c>
+          <t>52.4</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr"/>
       <c r="E247" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="F247" t="n">
@@ -6504,22 +6504,22 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashJAN</t>
+          <t>S&amp;P Global Services PMI FlashJAN</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="F248" t="n">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/24</t>
+          <t>Baker Hughes Total Rigs CountJAN/24</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>576</t>
         </is>
       </c>
       <c r="D256" t="inlineStr"/>
@@ -6762,12 +6762,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/24</t>
+          <t>Baker Hughes Oil Rig CountJAN/24</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>472</t>
         </is>
       </c>
       <c r="D257" t="inlineStr"/>
@@ -6784,22 +6784,22 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Building Permits FinalDEC</t>
+          <t>Building Permits MoM FinalDEC</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>1.482M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>1.483M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>1.6M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F258" t="n">
@@ -6814,22 +6814,22 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalDEC</t>
+          <t>Building Permits FinalDEC</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.482M</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.483M</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.6M</t>
         </is>
       </c>
       <c r="F259" t="n">
@@ -7040,26 +7040,26 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMDEC</t>
+          <t>Durable Goods Orders MoMDEC</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F268" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="269">
@@ -7070,22 +7070,18 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirDEC</t>
+          <t>Durable Goods Orders ex Defense MoMDEC</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D269" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>-2.4%</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr"/>
       <c r="E269" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F269" t="n">
@@ -7100,18 +7096,22 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMDEC</t>
+          <t>Non Defense Goods Orders Ex AirDEC</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>-2.4%</t>
-        </is>
-      </c>
-      <c r="D270" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F270" t="n">
@@ -7126,26 +7126,26 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMDEC</t>
+          <t>Durable Goods Orders Ex Transp MoMDEC</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F271" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="272">
@@ -7316,22 +7316,18 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexJAN</t>
+          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>-4</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr">
-        <is>
-          <t>-8</t>
-        </is>
-      </c>
+          <t>-9</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr"/>
       <c r="E278" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="F278" t="n">
@@ -7346,26 +7342,22 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceJAN</t>
+          <t>Richmond Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>104.1</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr">
-        <is>
-          <t>105.6</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr"/>
       <c r="E279" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F279" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="280">
@@ -7376,18 +7368,22 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexJAN</t>
+          <t>Richmond Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr"/>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>-8</t>
+        </is>
+      </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="F280" t="n">
@@ -7402,22 +7398,26 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
+          <t>CB Consumer ConfidenceJAN</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>-9</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr"/>
+          <t>104.1</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>105.6</t>
+        </is>
+      </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F281" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="282">
@@ -7594,18 +7594,18 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/24</t>
+          <t>MBA Mortgage ApplicationsJAN/24</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="D289" t="inlineStr"/>
       <c r="E289" t="inlineStr"/>
       <c r="F289" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="290">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/24</t>
+          <t>MBA Purchase IndexJAN/24</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>162.4</t>
         </is>
       </c>
       <c r="D290" t="inlineStr"/>
@@ -7638,12 +7638,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/24</t>
+          <t>MBA Mortgage Refinance IndexJAN/24</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>162.4</t>
+          <t>520.9</t>
         </is>
       </c>
       <c r="D291" t="inlineStr"/>
@@ -7660,18 +7660,18 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/24</t>
+          <t>MBA 30-Year Mortgage RateJAN/24</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="D292" t="inlineStr"/>
       <c r="E292" t="inlineStr"/>
       <c r="F292" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="293">
@@ -7682,12 +7682,12 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/24</t>
+          <t>MBA Mortgage Market IndexJAN/24</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>520.9</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="D293" t="inlineStr"/>
@@ -7704,18 +7704,22 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoM AdvDEC</t>
+          <t>Goods Trade Balance AdvDEC</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D294" t="inlineStr"/>
+          <t>$-122.11B</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>$-105.4B</t>
+        </is>
+      </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>$ -106B</t>
         </is>
       </c>
       <c r="F294" t="n">
@@ -7760,22 +7764,18 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvDEC</t>
+          <t>Retail Inventories Ex Autos MoM AdvDEC</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>$-122.11B</t>
-        </is>
-      </c>
-      <c r="D296" t="inlineStr">
-        <is>
-          <t>$-105.4B</t>
-        </is>
-      </c>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr"/>
       <c r="E296" t="inlineStr">
         <is>
-          <t>$ -106B</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F296" t="n">
@@ -8324,22 +8324,18 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Pending Home Sales MoMDEC</t>
+          <t>Pending Home Sales YoYDEC</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>-5.5%</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
+          <t>-5.0%</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr"/>
       <c r="E318" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F318" t="n">
@@ -8354,18 +8350,22 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Pending Home Sales YoYDEC</t>
+          <t>Pending Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>-5.0%</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr"/>
+          <t>-5.5%</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F319" t="n">
@@ -8516,26 +8516,26 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F326" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="327">
@@ -8546,22 +8546,18 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
+          <t>Employment Cost - Wages QoQQ4</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="D327" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr"/>
       <c r="E327" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F327" t="n">
@@ -8576,26 +8572,26 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F328" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="329">
@@ -8606,26 +8602,22 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>Employment Cost - Benefits QoQQ4</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>2.8%</t>
-        </is>
-      </c>
-      <c r="D329" t="inlineStr">
-        <is>
-          <t>2.8%</t>
-        </is>
-      </c>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr"/>
       <c r="E329" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F329" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="330">
@@ -8636,14 +8628,26 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C330" t="inlineStr"/>
-      <c r="D330" t="inlineStr"/>
-      <c r="E330" t="inlineStr"/>
+          <t>Personal Income MoMDEC</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F330" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="331">
@@ -8654,26 +8658,14 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
-        </is>
-      </c>
-      <c r="C331" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D331" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E331" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr"/>
+      <c r="D331" t="inlineStr"/>
+      <c r="E331" t="inlineStr"/>
       <c r="F331" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="332">
@@ -8684,22 +8676,26 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
+          <t>Core PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr"/>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F332" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="333">
@@ -8710,26 +8706,26 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F333" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="334">
@@ -8740,18 +8736,22 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr"/>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F334" t="n">
@@ -8766,26 +8766,26 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F335" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="336">
@@ -8904,26 +8904,22 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIJAN</t>
+          <t>ISM Manufacturing EmploymentJAN</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>50.9</t>
-        </is>
-      </c>
-      <c r="D340" t="inlineStr">
-        <is>
-          <t>49.8</t>
-        </is>
-      </c>
+          <t>50.3</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr"/>
       <c r="E340" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F340" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="341">
@@ -8934,22 +8930,18 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesJAN</t>
+          <t>ISM Manufacturing New OrdersJAN</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>54.9</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
+          <t>55.1</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr"/>
       <c r="E341" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F341" t="n">
@@ -8964,18 +8956,22 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersJAN</t>
+          <t>Construction Spending MoMDEC</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>55.1</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F342" t="n">
@@ -8990,22 +8986,26 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentJAN</t>
+          <t>ISM Manufacturing PMIJAN</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>50.3</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr"/>
+          <t>50.9</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>49.8</t>
+        </is>
+      </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="F343" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="344">
@@ -9016,22 +9016,22 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Construction Spending MoMDEC</t>
+          <t>ISM Manufacturing PricesJAN</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F344" t="n">
@@ -9206,26 +9206,26 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Factory Orders MoMDEC</t>
+          <t>JOLTs Job OpeningsDEC</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>7.6M</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>8M</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>7.8M</t>
         </is>
       </c>
       <c r="F353" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="354">
@@ -9236,18 +9236,18 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsDEC</t>
+          <t>Factory Orders ex TransportationDEC</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>3.197M</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D354" t="inlineStr"/>
       <c r="E354" t="inlineStr">
         <is>
-          <t>3.1M</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F354" t="n">
@@ -9262,22 +9262,26 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationDEC</t>
+          <t>Factory Orders MoMDEC</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr"/>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>-0.7%</t>
+        </is>
+      </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F355" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="356">
@@ -9288,26 +9292,22 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsDEC</t>
+          <t>JOLTs Job QuitsDEC</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>7.6M</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr">
-        <is>
-          <t>8M</t>
-        </is>
-      </c>
+          <t>3.197M</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr"/>
       <c r="E356" t="inlineStr">
         <is>
-          <t>7.8M</t>
+          <t>3.1M</t>
         </is>
       </c>
       <c r="F356" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="357">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/31</t>
+          <t>MBA Mortgage Market IndexJAN/31</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>156.7</t>
+          <t>224.8</t>
         </is>
       </c>
       <c r="D363" t="inlineStr"/>
@@ -9472,18 +9472,18 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/31</t>
+          <t>MBA Purchase IndexJAN/31</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>6.97%</t>
+          <t>156.7</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
       <c r="E364" t="inlineStr"/>
       <c r="F364" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="365">
@@ -9494,18 +9494,18 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/31</t>
+          <t>MBA 30-Year Mortgage RateJAN/31</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>584.3</t>
+          <t>6.97%</t>
         </is>
       </c>
       <c r="D365" t="inlineStr"/>
       <c r="E365" t="inlineStr"/>
       <c r="F365" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="366">
@@ -9516,12 +9516,12 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/31</t>
+          <t>MBA Mortgage Refinance IndexJAN/31</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>224.8</t>
+          <t>584.3</t>
         </is>
       </c>
       <c r="D366" t="inlineStr"/>
@@ -9902,12 +9902,12 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>0.16M</t>
+          <t>-0.034M</t>
         </is>
       </c>
       <c r="D381" t="inlineStr"/>
@@ -9924,12 +9924,12 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Crude Oil Imports ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>-0.186M</t>
+          <t>-0.178M</t>
         </is>
       </c>
       <c r="D382" t="inlineStr"/>
@@ -9946,22 +9946,22 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>-5.471M</t>
+          <t>8.664M</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>-1.5M</t>
+          <t>2.6M</t>
         </is>
       </c>
       <c r="E383" t="inlineStr"/>
       <c r="F383" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="384">
@@ -9972,18 +9972,22 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Gasoline Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>-0.027M</t>
-        </is>
-      </c>
-      <c r="D384" t="inlineStr"/>
+          <t>2.233M</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>1.2M</t>
+        </is>
+      </c>
       <c r="E384" t="inlineStr"/>
       <c r="F384" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="385">
@@ -9994,12 +9998,12 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>0.373M</t>
+          <t>0.16M</t>
         </is>
       </c>
       <c r="D385" t="inlineStr"/>
@@ -10016,22 +10020,18 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>2.233M</t>
-        </is>
-      </c>
-      <c r="D386" t="inlineStr">
-        <is>
-          <t>1.2M</t>
-        </is>
-      </c>
+          <t>-0.027M</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr"/>
       <c r="E386" t="inlineStr"/>
       <c r="F386" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="387">
@@ -10042,22 +10042,22 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>8.664M</t>
+          <t>-5.471M</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>2.6M</t>
+          <t>-1.5M</t>
         </is>
       </c>
       <c r="E387" t="inlineStr"/>
       <c r="F387" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="388">
@@ -10068,12 +10068,12 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>-0.178M</t>
+          <t>-0.186M</t>
         </is>
       </c>
       <c r="D388" t="inlineStr"/>
@@ -10090,12 +10090,12 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>-0.034M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="D389" t="inlineStr"/>
@@ -10196,22 +10196,18 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/25</t>
+          <t>Jobless Claims 4-week AverageFEB/01</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>1886K</t>
-        </is>
-      </c>
-      <c r="D394" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
+          <t>216.75K</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr"/>
       <c r="E394" t="inlineStr">
         <is>
-          <t>1855.0K</t>
+          <t>215.5K</t>
         </is>
       </c>
       <c r="F394" t="n">
@@ -10226,22 +10222,22 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/01</t>
+          <t>Unit Labour Costs QoQ PrelQ4</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>213K</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F395" t="n">
@@ -10256,26 +10252,26 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Nonfarm Productivity QoQ PrelQ4</t>
+          <t>Continuing Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>1886K</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>1855.0K</t>
         </is>
       </c>
       <c r="F396" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="397">
@@ -10286,22 +10282,22 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Unit Labour Costs QoQ PrelQ4</t>
+          <t>Initial Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F397" t="n">
@@ -10316,22 +10312,26 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/01</t>
+          <t>Nonfarm Productivity QoQ PrelQ4</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>216.75K</t>
-        </is>
-      </c>
-      <c r="D398" t="inlineStr"/>
+          <t>1.2%</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>1.4%</t>
+        </is>
+      </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>215.5K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F398" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="399">
@@ -10536,22 +10536,22 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Government PayrollsJAN</t>
+          <t>Participation RateJAN</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>32K</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="D408" t="inlineStr"/>
       <c r="E408" t="inlineStr">
         <is>
-          <t>25K</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="F408" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="409">
@@ -10562,26 +10562,26 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateJAN</t>
+          <t>Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>111K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>141K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>180K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F409" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="410">
@@ -10592,26 +10592,26 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoYJAN</t>
+          <t>Manufacturing PayrollsJAN</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>3K</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>-2K</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>-5K</t>
         </is>
       </c>
       <c r="F410" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="411">
@@ -10622,26 +10622,26 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsJAN</t>
+          <t>Average Hourly Earnings MoMJAN</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>143K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>170K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>205K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F411" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="412">
@@ -10652,18 +10652,22 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>U-6 Unemployment RateJAN</t>
+          <t>Average Weekly HoursJAN</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D412" t="inlineStr"/>
+          <t>34.1</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F412" t="n">
@@ -10678,22 +10682,22 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Average Weekly HoursJAN</t>
+          <t>Nonfarm Payrolls PrivateJAN</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>111K</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>141K</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>180K</t>
         </is>
       </c>
       <c r="F413" t="n">
@@ -10708,26 +10712,26 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMJAN</t>
+          <t>Non Farm PayrollsJAN</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>143K</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>170K</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>205K</t>
         </is>
       </c>
       <c r="F414" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="415">
@@ -10738,26 +10742,26 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsJAN</t>
+          <t>Average Hourly Earnings YoYJAN</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>3K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>-2K</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>-5K</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="F415" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="416">
@@ -10768,26 +10772,22 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Unemployment RateJAN</t>
+          <t>Government PayrollsJAN</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>4%</t>
-        </is>
-      </c>
-      <c r="D416" t="inlineStr">
-        <is>
-          <t>4.1%</t>
-        </is>
-      </c>
+          <t>32K</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr"/>
       <c r="E416" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>25K</t>
         </is>
       </c>
       <c r="F416" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="417">
@@ -10798,22 +10798,22 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Participation RateJAN</t>
+          <t>U-6 Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="D417" t="inlineStr"/>
       <c r="E417" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="F417" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="418">
@@ -10842,12 +10842,12 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Used Car Prices MoMJAN</t>
+          <t>Used Car Prices YoYJAN</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="D419" t="inlineStr"/>
@@ -10864,12 +10864,12 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Used Car Prices YoYJAN</t>
+          <t>Used Car Prices MoMJAN</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D420" t="inlineStr"/>
@@ -11112,12 +11112,12 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/07</t>
+          <t>Baker Hughes Oil Rig CountFEB/07</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>480</t>
         </is>
       </c>
       <c r="D430" t="inlineStr"/>
@@ -11134,12 +11134,12 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/07</t>
+          <t>Baker Hughes Total Rigs CountFEB/07</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>586</t>
         </is>
       </c>
       <c r="D431" t="inlineStr"/>
@@ -11474,14 +11474,14 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/07</t>
+          <t>MBA Mortgage Market IndexFEB/07</t>
         </is>
       </c>
       <c r="C447" t="inlineStr"/>
       <c r="D447" t="inlineStr"/>
       <c r="E447" t="inlineStr"/>
       <c r="F447" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="448">
@@ -11492,7 +11492,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/07</t>
+          <t>MBA Purchase IndexFEB/07</t>
         </is>
       </c>
       <c r="C448" t="inlineStr"/>
@@ -11510,7 +11510,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/07</t>
+          <t>MBA Mortgage Refinance IndexFEB/07</t>
         </is>
       </c>
       <c r="C449" t="inlineStr"/>
@@ -11528,14 +11528,14 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/07</t>
+          <t>MBA 30-Year Mortgage RateFEB/07</t>
         </is>
       </c>
       <c r="C450" t="inlineStr"/>
       <c r="D450" t="inlineStr"/>
       <c r="E450" t="inlineStr"/>
       <c r="F450" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="451">
@@ -11546,7 +11546,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/07</t>
+          <t>MBA Mortgage ApplicationsFEB/07</t>
         </is>
       </c>
       <c r="C451" t="inlineStr"/>
@@ -11716,7 +11716,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C458" t="inlineStr"/>
@@ -11734,14 +11734,14 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C459" t="inlineStr"/>
       <c r="D459" t="inlineStr"/>
       <c r="E459" t="inlineStr"/>
       <c r="F459" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="460">
@@ -11752,14 +11752,14 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C460" t="inlineStr"/>
       <c r="D460" t="inlineStr"/>
       <c r="E460" t="inlineStr"/>
       <c r="F460" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="461">
@@ -11770,7 +11770,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C461" t="inlineStr"/>
@@ -11788,7 +11788,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C462" t="inlineStr"/>
@@ -11806,14 +11806,14 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C463" t="inlineStr"/>
       <c r="D463" t="inlineStr"/>
       <c r="E463" t="inlineStr"/>
       <c r="F463" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="464">
@@ -11824,14 +11824,14 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C464" t="inlineStr"/>
       <c r="D464" t="inlineStr"/>
       <c r="E464" t="inlineStr"/>
       <c r="F464" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="465">
@@ -11842,7 +11842,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C465" t="inlineStr"/>
@@ -11860,7 +11860,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C466" t="inlineStr"/>
@@ -11976,14 +11976,14 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C472" t="inlineStr"/>
       <c r="D472" t="inlineStr"/>
       <c r="E472" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="F472" t="n">
@@ -11998,18 +11998,14 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C473" t="inlineStr"/>
-      <c r="D473" t="inlineStr">
-        <is>
-          <t>3.2%</t>
-        </is>
-      </c>
+      <c r="D473" t="inlineStr"/>
       <c r="E473" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F473" t="n">
@@ -12024,22 +12020,22 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C474" t="inlineStr"/>
       <c r="D474" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F474" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="475">
@@ -12050,18 +12046,22 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C475" t="inlineStr"/>
-      <c r="D475" t="inlineStr"/>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F475" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="476">
@@ -12072,22 +12072,18 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C476" t="inlineStr"/>
-      <c r="D476" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D476" t="inlineStr"/>
       <c r="E476" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F476" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="477">
@@ -12098,22 +12094,18 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C477" t="inlineStr"/>
-      <c r="D477" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
+      <c r="D477" t="inlineStr"/>
       <c r="E477" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="F477" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="478">
@@ -12124,22 +12116,22 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C478" t="inlineStr"/>
       <c r="D478" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F478" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="479">
@@ -12150,14 +12142,18 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C479" t="inlineStr"/>
-      <c r="D479" t="inlineStr"/>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F479" t="n">
@@ -12172,18 +12168,22 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C480" t="inlineStr"/>
-      <c r="D480" t="inlineStr"/>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F480" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="481">
@@ -12360,22 +12360,18 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="C490" t="inlineStr"/>
-      <c r="D490" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D490" t="inlineStr"/>
       <c r="E490" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F490" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="491">
@@ -12386,14 +12382,14 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="C491" t="inlineStr"/>
       <c r="D491" t="inlineStr"/>
       <c r="E491" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F491" t="n">
@@ -12408,22 +12404,18 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="C492" t="inlineStr"/>
-      <c r="D492" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D492" t="inlineStr"/>
       <c r="E492" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F492" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="493">
@@ -12434,22 +12426,22 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="C493" t="inlineStr"/>
       <c r="D493" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F493" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="494">
@@ -12460,18 +12452,18 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="C494" t="inlineStr"/>
       <c r="D494" t="inlineStr"/>
       <c r="E494" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F494" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="495">
@@ -12482,22 +12474,22 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="C495" t="inlineStr"/>
       <c r="D495" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="F495" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="496">
@@ -12508,18 +12500,22 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="C496" t="inlineStr"/>
-      <c r="D496" t="inlineStr"/>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F496" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="497">
@@ -12530,18 +12526,22 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="C497" t="inlineStr"/>
-      <c r="D497" t="inlineStr"/>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E497" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F497" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="498">
@@ -12552,18 +12552,18 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="C498" t="inlineStr"/>
       <c r="D498" t="inlineStr"/>
       <c r="E498" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F498" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="499">
@@ -12574,22 +12574,22 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="C499" t="inlineStr"/>
       <c r="D499" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F499" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="500">
@@ -12600,18 +12600,14 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="C500" t="inlineStr"/>
-      <c r="D500" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+      <c r="D500" t="inlineStr"/>
       <c r="E500" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F500" t="n">
@@ -12626,14 +12622,18 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="C501" t="inlineStr"/>
-      <c r="D501" t="inlineStr"/>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>77.7%</t>
+        </is>
+      </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="F501" t="n">
@@ -12648,14 +12648,18 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Manufacturing Production MoMJAN</t>
         </is>
       </c>
       <c r="C502" t="inlineStr"/>
-      <c r="D502" t="inlineStr"/>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F502" t="n">
@@ -12670,22 +12674,18 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="C503" t="inlineStr"/>
-      <c r="D503" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="D503" t="inlineStr"/>
       <c r="E503" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F503" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="504">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C520" t="inlineStr"/>
@@ -13050,7 +13050,7 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C521" t="inlineStr"/>
@@ -13068,7 +13068,7 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C522" t="inlineStr"/>
@@ -13104,7 +13104,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C524" t="inlineStr"/>
@@ -13158,14 +13158,14 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C527" t="inlineStr"/>
       <c r="D527" t="inlineStr"/>
       <c r="E527" t="inlineStr"/>
       <c r="F527" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="528">
@@ -13176,14 +13176,14 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="C528" t="inlineStr"/>
       <c r="D528" t="inlineStr"/>
       <c r="E528" t="inlineStr"/>
       <c r="F528" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="529">
@@ -13288,14 +13288,18 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Net Long-term TIC FlowsDEC</t>
         </is>
       </c>
       <c r="C534" t="inlineStr"/>
-      <c r="D534" t="inlineStr"/>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>$149.1B</t>
+        </is>
+      </c>
       <c r="E534" t="inlineStr"/>
       <c r="F534" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="535">
@@ -13324,18 +13328,14 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsDEC</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C536" t="inlineStr"/>
-      <c r="D536" t="inlineStr">
-        <is>
-          <t>$149.1B</t>
-        </is>
-      </c>
+      <c r="D536" t="inlineStr"/>
       <c r="E536" t="inlineStr"/>
       <c r="F536" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="537">
@@ -13346,14 +13346,14 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C537" t="inlineStr"/>
       <c r="D537" t="inlineStr"/>
       <c r="E537" t="inlineStr"/>
       <c r="F537" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="538">
@@ -13400,7 +13400,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C540" t="inlineStr"/>
@@ -13418,14 +13418,14 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C541" t="inlineStr"/>
       <c r="D541" t="inlineStr"/>
       <c r="E541" t="inlineStr"/>
       <c r="F541" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="542">
@@ -13436,7 +13436,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C542" t="inlineStr"/>
@@ -13454,7 +13454,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C543" t="inlineStr"/>
@@ -13472,7 +13472,7 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C544" t="inlineStr"/>
@@ -13578,22 +13578,18 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C549" t="inlineStr"/>
-      <c r="D549" t="inlineStr">
-        <is>
-          <t>1.4M</t>
-        </is>
-      </c>
+      <c r="D549" t="inlineStr"/>
       <c r="E549" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F549" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="550">
@@ -13604,18 +13600,22 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C550" t="inlineStr"/>
-      <c r="D550" t="inlineStr"/>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>1.4M</t>
+        </is>
+      </c>
       <c r="E550" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F550" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="551">
@@ -13674,14 +13674,14 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C553" t="inlineStr"/>
       <c r="D553" t="inlineStr"/>
       <c r="E553" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F553" t="n">
@@ -13696,14 +13696,14 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C554" t="inlineStr"/>
       <c r="D554" t="inlineStr"/>
       <c r="E554" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F554" t="n">
@@ -13978,22 +13978,14 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C569" t="inlineStr"/>
-      <c r="D569" t="inlineStr">
-        <is>
-          <t>16.3</t>
-        </is>
-      </c>
-      <c r="E569" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="D569" t="inlineStr"/>
+      <c r="E569" t="inlineStr"/>
       <c r="F569" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="570">
@@ -14004,16 +13996,12 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C570" t="inlineStr"/>
       <c r="D570" t="inlineStr"/>
-      <c r="E570" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="E570" t="inlineStr"/>
       <c r="F570" t="n">
         <v>3</v>
       </c>
@@ -14026,12 +14014,20 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C571" t="inlineStr"/>
-      <c r="D571" t="inlineStr"/>
-      <c r="E571" t="inlineStr"/>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>1860K</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="F571" t="n">
         <v>3</v>
       </c>
@@ -14044,14 +14040,22 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C572" t="inlineStr"/>
-      <c r="D572" t="inlineStr"/>
-      <c r="E572" t="inlineStr"/>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>16.3</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="F572" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="573">
@@ -14088,20 +14092,12 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C574" t="inlineStr"/>
-      <c r="D574" t="inlineStr">
-        <is>
-          <t>1860K</t>
-        </is>
-      </c>
-      <c r="E574" t="inlineStr">
-        <is>
-          <t>1879.0K</t>
-        </is>
-      </c>
+      <c r="D574" t="inlineStr"/>
+      <c r="E574" t="inlineStr"/>
       <c r="F574" t="n">
         <v>3</v>
       </c>
@@ -14114,22 +14110,14 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C575" t="inlineStr"/>
-      <c r="D575" t="inlineStr">
-        <is>
-          <t>215K</t>
-        </is>
-      </c>
-      <c r="E575" t="inlineStr">
-        <is>
-          <t>220.0K</t>
-        </is>
-      </c>
+      <c r="D575" t="inlineStr"/>
+      <c r="E575" t="inlineStr"/>
       <c r="F575" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="576">
@@ -14140,7 +14128,7 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C576" t="inlineStr"/>
@@ -14158,22 +14146,22 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C577" t="inlineStr"/>
       <c r="D577" t="inlineStr">
         <is>
-          <t>16.3</t>
+          <t>1860K</t>
         </is>
       </c>
       <c r="E577" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>1879.0K</t>
         </is>
       </c>
       <c r="F577" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="578">
@@ -14184,12 +14172,16 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C578" t="inlineStr"/>
       <c r="D578" t="inlineStr"/>
-      <c r="E578" t="inlineStr"/>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="F578" t="n">
         <v>3</v>
       </c>
@@ -14202,7 +14194,7 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C579" t="inlineStr"/>
@@ -14220,12 +14212,16 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C580" t="inlineStr"/>
       <c r="D580" t="inlineStr"/>
-      <c r="E580" t="inlineStr"/>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="F580" t="n">
         <v>3</v>
       </c>
@@ -14238,7 +14234,7 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C581" t="inlineStr"/>
@@ -14256,18 +14252,22 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C582" t="inlineStr"/>
-      <c r="D582" t="inlineStr"/>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>16.3</t>
+        </is>
+      </c>
       <c r="E582" t="inlineStr">
         <is>
-          <t>219.0K</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F582" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="583">
@@ -14278,7 +14278,7 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C583" t="inlineStr"/>
@@ -14296,22 +14296,22 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C584" t="inlineStr"/>
       <c r="D584" t="inlineStr">
         <is>
-          <t>1860K</t>
+          <t>215K</t>
         </is>
       </c>
       <c r="E584" t="inlineStr">
         <is>
-          <t>1879.0K</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="F584" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="585">
@@ -14340,7 +14340,7 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C586" t="inlineStr"/>
@@ -14482,7 +14482,7 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C593" t="inlineStr"/>
@@ -14500,7 +14500,7 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C594" t="inlineStr"/>
@@ -14554,7 +14554,7 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C597" t="inlineStr"/>
@@ -14572,14 +14572,14 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C598" t="inlineStr"/>
       <c r="D598" t="inlineStr"/>
       <c r="E598" t="inlineStr"/>
       <c r="F598" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="599">
@@ -14590,14 +14590,14 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C599" t="inlineStr"/>
       <c r="D599" t="inlineStr"/>
       <c r="E599" t="inlineStr"/>
       <c r="F599" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="600">
@@ -14608,14 +14608,14 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C600" t="inlineStr"/>
       <c r="D600" t="inlineStr"/>
       <c r="E600" t="inlineStr"/>
       <c r="F600" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="601">
@@ -14626,7 +14626,7 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C601" t="inlineStr"/>
@@ -14644,7 +14644,7 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C602" t="inlineStr"/>
@@ -14680,14 +14680,14 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C604" t="inlineStr"/>
       <c r="D604" t="inlineStr"/>
       <c r="E604" t="inlineStr"/>
       <c r="F604" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="605">
@@ -14716,7 +14716,7 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C606" t="inlineStr"/>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C607" t="inlineStr"/>
@@ -14752,7 +14752,7 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C608" t="inlineStr"/>
@@ -14770,7 +14770,7 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C609" t="inlineStr"/>
@@ -14788,14 +14788,14 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>Fed Musalem Speech</t>
         </is>
       </c>
       <c r="C610" t="inlineStr"/>
       <c r="D610" t="inlineStr"/>
       <c r="E610" t="inlineStr"/>
       <c r="F610" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="611">
@@ -14806,14 +14806,14 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C611" t="inlineStr"/>
       <c r="D611" t="inlineStr"/>
       <c r="E611" t="inlineStr"/>
       <c r="F611" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="612">
@@ -14824,7 +14824,7 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C612" t="inlineStr"/>
@@ -14842,14 +14842,14 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C613" t="inlineStr"/>
       <c r="D613" t="inlineStr"/>
       <c r="E613" t="inlineStr"/>
       <c r="F613" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="614">
@@ -14860,14 +14860,14 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C614" t="inlineStr"/>
       <c r="D614" t="inlineStr"/>
       <c r="E614" t="inlineStr"/>
       <c r="F614" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="615">
@@ -14878,7 +14878,7 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C615" t="inlineStr"/>
@@ -14896,14 +14896,14 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C616" t="inlineStr"/>
       <c r="D616" t="inlineStr"/>
       <c r="E616" t="inlineStr"/>
       <c r="F616" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="617">
@@ -14914,14 +14914,14 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>Fed Musalem Speech</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C617" t="inlineStr"/>
       <c r="D617" t="inlineStr"/>
       <c r="E617" t="inlineStr"/>
       <c r="F617" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="618">
@@ -14932,7 +14932,7 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C618" t="inlineStr"/>
@@ -14950,7 +14950,7 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C619" t="inlineStr"/>
@@ -15148,14 +15148,18 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C630" t="inlineStr"/>
-      <c r="D630" t="inlineStr"/>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>51.3</t>
+        </is>
+      </c>
       <c r="E630" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F630" t="n">
@@ -15170,18 +15174,18 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="C631" t="inlineStr"/>
       <c r="D631" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>53</t>
         </is>
       </c>
       <c r="E631" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="F631" t="n">
@@ -15222,14 +15226,18 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C633" t="inlineStr"/>
-      <c r="D633" t="inlineStr"/>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>51.3</t>
+        </is>
+      </c>
       <c r="E633" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F633" t="n">
@@ -15244,18 +15252,14 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C634" t="inlineStr"/>
-      <c r="D634" t="inlineStr">
-        <is>
-          <t>51.3</t>
-        </is>
-      </c>
+      <c r="D634" t="inlineStr"/>
       <c r="E634" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="F634" t="n">
@@ -15270,15 +15274,11 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C635" t="inlineStr"/>
-      <c r="D635" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
+      <c r="D635" t="inlineStr"/>
       <c r="E635" t="inlineStr">
         <is>
           <t>52.7</t>
@@ -15296,22 +15296,22 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C636" t="inlineStr"/>
       <c r="D636" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F636" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="637">
@@ -15322,22 +15322,18 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C637" t="inlineStr"/>
-      <c r="D637" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+      <c r="D637" t="inlineStr"/>
       <c r="E637" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F637" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="638">
@@ -15374,18 +15370,22 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C639" t="inlineStr"/>
-      <c r="D639" t="inlineStr"/>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>67.3</t>
+        </is>
+      </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F639" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="640">
@@ -15396,22 +15396,22 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C640" t="inlineStr"/>
       <c r="D640" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>4.17M</t>
         </is>
       </c>
       <c r="E640" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F640" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="641">
@@ -15448,18 +15448,18 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C642" t="inlineStr"/>
       <c r="D642" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="E642" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F642" t="n">
@@ -15474,22 +15474,22 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C643" t="inlineStr"/>
       <c r="D643" t="inlineStr">
         <is>
-          <t>4.13M</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F643" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="644">
@@ -15500,18 +15500,22 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C644" t="inlineStr"/>
-      <c r="D644" t="inlineStr"/>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F644" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="645">
@@ -15522,22 +15526,22 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C645" t="inlineStr"/>
       <c r="D645" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F645" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="646">
@@ -15548,22 +15552,18 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C646" t="inlineStr"/>
-      <c r="D646" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+      <c r="D646" t="inlineStr"/>
       <c r="E646" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F646" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="647">
@@ -15574,22 +15574,22 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C647" t="inlineStr"/>
       <c r="D647" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.13M</t>
         </is>
       </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F647" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="648">
@@ -15600,22 +15600,22 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C648" t="inlineStr"/>
       <c r="D648" t="inlineStr">
         <is>
-          <t>4.17M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F648" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="649">
@@ -15626,22 +15626,22 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C649" t="inlineStr"/>
       <c r="D649" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F649" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="650">
@@ -15688,7 +15688,7 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/21</t>
+          <t>Baker Hughes Total Rigs CountFEB/21</t>
         </is>
       </c>
       <c r="C652" t="inlineStr"/>
@@ -15706,7 +15706,7 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/21</t>
+          <t>Baker Hughes Oil Rig CountFEB/21</t>
         </is>
       </c>
       <c r="C653" t="inlineStr"/>
@@ -15832,7 +15832,7 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C660" t="inlineStr"/>
@@ -15850,7 +15850,7 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C661" t="inlineStr"/>
@@ -15976,14 +15976,18 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C668" t="inlineStr"/>
       <c r="D668" t="inlineStr"/>
-      <c r="E668" t="inlineStr"/>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="F668" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="669">
@@ -15994,7 +15998,7 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C669" t="inlineStr"/>
@@ -16012,18 +16016,14 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C670" t="inlineStr"/>
       <c r="D670" t="inlineStr"/>
-      <c r="E670" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="E670" t="inlineStr"/>
       <c r="F670" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="671">
@@ -16034,7 +16034,7 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C671" t="inlineStr"/>
@@ -16052,7 +16052,7 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C672" t="inlineStr"/>
@@ -16070,7 +16070,7 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C673" t="inlineStr"/>
@@ -16088,18 +16088,14 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C674" t="inlineStr"/>
       <c r="D674" t="inlineStr"/>
-      <c r="E674" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="E674" t="inlineStr"/>
       <c r="F674" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="675">
@@ -16110,7 +16106,7 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C675" t="inlineStr"/>
@@ -16128,14 +16124,18 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C676" t="inlineStr"/>
       <c r="D676" t="inlineStr"/>
-      <c r="E676" t="inlineStr"/>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="F676" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="677">
@@ -16146,7 +16146,7 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C677" t="inlineStr"/>
@@ -16182,14 +16182,14 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
       <c r="C679" t="inlineStr"/>
       <c r="D679" t="inlineStr"/>
       <c r="E679" t="inlineStr"/>
       <c r="F679" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="680">
@@ -16218,14 +16218,14 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C681" t="inlineStr"/>
       <c r="D681" t="inlineStr"/>
       <c r="E681" t="inlineStr"/>
       <c r="F681" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="682">
@@ -16326,7 +16326,7 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexFEB</t>
+          <t>Dallas Fed Services IndexFEB</t>
         </is>
       </c>
       <c r="C687" t="inlineStr"/>
@@ -16362,7 +16362,7 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexFEB</t>
+          <t>Dallas Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C689" t="inlineStr"/>
@@ -16380,7 +16380,7 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>Money SupplyJAN</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C690" t="inlineStr"/>
@@ -16434,7 +16434,7 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>Money SupplyJAN</t>
         </is>
       </c>
       <c r="C693" t="inlineStr"/>
@@ -16524,7 +16524,7 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/21</t>
+          <t>MBA Mortgage Refinance IndexFEB/21</t>
         </is>
       </c>
       <c r="C698" t="inlineStr"/>
@@ -16542,14 +16542,14 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/21</t>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
         </is>
       </c>
       <c r="C699" t="inlineStr"/>
       <c r="D699" t="inlineStr"/>
       <c r="E699" t="inlineStr"/>
       <c r="F699" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="700">
@@ -16560,7 +16560,7 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>MBA Mortgage Market IndexFEB/21</t>
         </is>
       </c>
       <c r="C700" t="inlineStr"/>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>MBA Mortgage ApplicationsFEB/21</t>
         </is>
       </c>
       <c r="C701" t="inlineStr"/>
@@ -16596,7 +16596,7 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C702" t="inlineStr"/>
@@ -16614,14 +16614,14 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
+          <t>MBA Mortgage Market IndexFEB/21</t>
         </is>
       </c>
       <c r="C703" t="inlineStr"/>
       <c r="D703" t="inlineStr"/>
       <c r="E703" t="inlineStr"/>
       <c r="F703" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="704">
@@ -16632,7 +16632,7 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/21</t>
+          <t>MBA Purchase IndexFEB/21</t>
         </is>
       </c>
       <c r="C704" t="inlineStr"/>
@@ -16650,7 +16650,7 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/21</t>
+          <t>MBA Mortgage Refinance IndexFEB/21</t>
         </is>
       </c>
       <c r="C705" t="inlineStr"/>
@@ -16668,14 +16668,14 @@
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/21</t>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
         </is>
       </c>
       <c r="C706" t="inlineStr"/>
       <c r="D706" t="inlineStr"/>
       <c r="E706" t="inlineStr"/>
       <c r="F706" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="707">
@@ -16686,14 +16686,14 @@
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C707" t="inlineStr"/>
       <c r="D707" t="inlineStr"/>
       <c r="E707" t="inlineStr"/>
       <c r="F707" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="708">
@@ -16704,7 +16704,7 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>New Home Sales MoMJAN</t>
+          <t>New Home SalesJAN</t>
         </is>
       </c>
       <c r="C708" t="inlineStr"/>
@@ -16722,7 +16722,7 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>New Home SalesJAN</t>
+          <t>New Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C709" t="inlineStr"/>
@@ -16740,7 +16740,7 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C710" t="inlineStr"/>
@@ -16758,7 +16758,7 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>New Home SalesJAN</t>
+          <t>New Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C711" t="inlineStr"/>
@@ -16776,7 +16776,7 @@
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>New Home Sales MoMJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C712" t="inlineStr"/>
@@ -16794,7 +16794,7 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>New Home SalesJAN</t>
         </is>
       </c>
       <c r="C713" t="inlineStr"/>
@@ -16812,14 +16812,14 @@
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C714" t="inlineStr"/>
       <c r="D714" t="inlineStr"/>
       <c r="E714" t="inlineStr"/>
       <c r="F714" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="715">
@@ -16830,14 +16830,14 @@
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+          <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C715" t="inlineStr"/>
       <c r="D715" t="inlineStr"/>
       <c r="E715" t="inlineStr"/>
       <c r="F715" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="716">
@@ -16848,14 +16848,14 @@
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C716" t="inlineStr"/>
       <c r="D716" t="inlineStr"/>
       <c r="E716" t="inlineStr"/>
       <c r="F716" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="717">
@@ -16866,7 +16866,7 @@
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C717" t="inlineStr"/>
@@ -16884,7 +16884,7 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C718" t="inlineStr"/>
@@ -16902,7 +16902,7 @@
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
       <c r="C719" t="inlineStr"/>
@@ -16920,14 +16920,14 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C720" t="inlineStr"/>
       <c r="D720" t="inlineStr"/>
       <c r="E720" t="inlineStr"/>
       <c r="F720" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="721">
@@ -16938,7 +16938,7 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/21</t>
+          <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C721" t="inlineStr"/>
@@ -16956,14 +16956,14 @@
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C722" t="inlineStr"/>
       <c r="D722" t="inlineStr"/>
       <c r="E722" t="inlineStr"/>
       <c r="F722" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="723">
@@ -16974,14 +16974,14 @@
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C723" t="inlineStr"/>
       <c r="D723" t="inlineStr"/>
       <c r="E723" t="inlineStr"/>
       <c r="F723" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="724">
@@ -16992,7 +16992,7 @@
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C724" t="inlineStr"/>
@@ -17028,7 +17028,7 @@
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/21</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C726" t="inlineStr"/>
@@ -17046,7 +17046,7 @@
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/21</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C727" t="inlineStr"/>
@@ -17064,14 +17064,14 @@
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C728" t="inlineStr"/>
       <c r="D728" t="inlineStr"/>
       <c r="E728" t="inlineStr"/>
       <c r="F728" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="729">
@@ -17082,14 +17082,14 @@
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C729" t="inlineStr"/>
       <c r="D729" t="inlineStr"/>
       <c r="E729" t="inlineStr"/>
       <c r="F729" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="730">
@@ -17100,7 +17100,7 @@
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/21</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
       <c r="C730" t="inlineStr"/>
@@ -17118,7 +17118,7 @@
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C731" t="inlineStr"/>
@@ -17172,7 +17172,7 @@
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>17-Week Bill Auction</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C734" t="inlineStr"/>
@@ -17190,7 +17190,7 @@
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>17-Week Bill Auction</t>
         </is>
       </c>
       <c r="C735" t="inlineStr"/>
@@ -17226,7 +17226,7 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Fed Bostic Speech</t>
         </is>
       </c>
       <c r="C737" t="inlineStr"/>
@@ -17262,7 +17262,7 @@
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>Fed Bostic Speech</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C739" t="inlineStr"/>
@@ -17280,7 +17280,7 @@
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>2-Year FRN Auction</t>
         </is>
       </c>
       <c r="C740" t="inlineStr"/>
@@ -17316,7 +17316,7 @@
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>2-Year FRN Auction</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C742" t="inlineStr"/>
@@ -17334,7 +17334,7 @@
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C743" t="inlineStr"/>
@@ -17352,7 +17352,7 @@
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C744" t="inlineStr"/>
@@ -17424,14 +17424,18 @@
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMJAN</t>
+          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C748" t="inlineStr"/>
       <c r="D748" t="inlineStr"/>
-      <c r="E748" t="inlineStr"/>
+      <c r="E748" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="F748" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="749">
@@ -17442,14 +17446,14 @@
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirJAN</t>
+          <t>Durable Goods Orders Ex Transp MoMJAN</t>
         </is>
       </c>
       <c r="C749" t="inlineStr"/>
       <c r="D749" t="inlineStr"/>
       <c r="E749" t="inlineStr"/>
       <c r="F749" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="750">
@@ -17460,22 +17464,22 @@
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ 2nd EstQ4</t>
+          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C750" t="inlineStr"/>
       <c r="D750" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="E750" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F750" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="751">
@@ -17606,14 +17610,14 @@
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMJAN</t>
+          <t>Non Defense Goods Orders Ex AirJAN</t>
         </is>
       </c>
       <c r="C757" t="inlineStr"/>
       <c r="D757" t="inlineStr"/>
       <c r="E757" t="inlineStr"/>
       <c r="F757" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="758">
@@ -17624,7 +17628,7 @@
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
+          <t>PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C758" t="inlineStr"/>
@@ -17639,7 +17643,7 @@
         </is>
       </c>
       <c r="F758" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="759">
@@ -17650,14 +17654,14 @@
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/22</t>
+          <t>Durable Goods Orders MoMJAN</t>
         </is>
       </c>
       <c r="C759" t="inlineStr"/>
       <c r="D759" t="inlineStr"/>
       <c r="E759" t="inlineStr"/>
       <c r="F759" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="760">
@@ -17668,18 +17672,22 @@
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
+          <t>GDP Price Index QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C760" t="inlineStr"/>
-      <c r="D760" t="inlineStr"/>
+      <c r="D760" t="inlineStr">
+        <is>
+          <t>2.2%</t>
+        </is>
+      </c>
       <c r="E760" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="F760" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="761">
@@ -17690,12 +17698,20 @@
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirJAN</t>
+          <t>PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C761" t="inlineStr"/>
-      <c r="D761" t="inlineStr"/>
-      <c r="E761" t="inlineStr"/>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="E761" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
       <c r="F761" t="n">
         <v>3</v>
       </c>
@@ -17708,7 +17724,7 @@
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/22</t>
+          <t>Continuing Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C762" t="inlineStr"/>
@@ -17726,14 +17742,14 @@
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ 2nd EstQ4</t>
+          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C763" t="inlineStr"/>
       <c r="D763" t="inlineStr"/>
       <c r="E763" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F763" t="n">
@@ -17748,14 +17764,14 @@
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMJAN</t>
+          <t>Initial Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C764" t="inlineStr"/>
       <c r="D764" t="inlineStr"/>
       <c r="E764" t="inlineStr"/>
       <c r="F764" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="765">
@@ -17766,20 +17782,12 @@
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ 2nd EstQ4</t>
+          <t>Non Defense Goods Orders Ex AirJAN</t>
         </is>
       </c>
       <c r="C765" t="inlineStr"/>
-      <c r="D765" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
-      <c r="E765" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+      <c r="D765" t="inlineStr"/>
+      <c r="E765" t="inlineStr"/>
       <c r="F765" t="n">
         <v>3</v>
       </c>
@@ -17792,7 +17800,7 @@
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/15</t>
+          <t>Jobless Claims 4-week AverageFEB/22</t>
         </is>
       </c>
       <c r="C766" t="inlineStr"/>
@@ -17810,22 +17818,18 @@
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ 2nd EstQ4</t>
+          <t>GDP Sales QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C767" t="inlineStr"/>
-      <c r="D767" t="inlineStr">
-        <is>
-          <t>2.2%</t>
-        </is>
-      </c>
+      <c r="D767" t="inlineStr"/>
       <c r="E767" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F767" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="768">
@@ -17836,14 +17840,14 @@
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMJAN</t>
+          <t>Durable Goods Orders ex Defense MoMJAN</t>
         </is>
       </c>
       <c r="C768" t="inlineStr"/>
       <c r="D768" t="inlineStr"/>
       <c r="E768" t="inlineStr"/>
       <c r="F768" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="769">
@@ -17854,22 +17858,22 @@
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
+          <t>Core PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C769" t="inlineStr"/>
       <c r="D769" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="E769" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F769" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="770">
@@ -17880,14 +17884,22 @@
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMJAN</t>
+          <t>GDP Price Index QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C770" t="inlineStr"/>
-      <c r="D770" t="inlineStr"/>
-      <c r="E770" t="inlineStr"/>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="E770" t="inlineStr">
+        <is>
+          <t>2.2%</t>
+        </is>
+      </c>
       <c r="F770" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="771">
@@ -17898,22 +17910,14 @@
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ 2nd EstQ4</t>
+          <t>Durable Goods Orders Ex Transp MoMJAN</t>
         </is>
       </c>
       <c r="C771" t="inlineStr"/>
-      <c r="D771" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
-      <c r="E771" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
+      <c r="D771" t="inlineStr"/>
+      <c r="E771" t="inlineStr"/>
       <c r="F771" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="772">
@@ -17924,7 +17928,7 @@
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ 2nd EstQ4</t>
+          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C772" t="inlineStr"/>
@@ -17939,7 +17943,7 @@
         </is>
       </c>
       <c r="F772" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="773">
@@ -17950,17 +17954,89 @@
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
+          <t>Durable Goods Orders MoMJAN</t>
         </is>
       </c>
       <c r="C773" t="inlineStr"/>
       <c r="D773" t="inlineStr"/>
-      <c r="E773" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="E773" t="inlineStr"/>
       <c r="F773" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>2025-02-27 10:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>Pending Home Sales YoYJAN</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr"/>
+      <c r="D774" t="inlineStr"/>
+      <c r="E774" t="inlineStr"/>
+      <c r="F774" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>2025-02-27 10:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>Pending Home Sales MoMJAN</t>
+        </is>
+      </c>
+      <c r="C775" t="inlineStr"/>
+      <c r="D775" t="inlineStr"/>
+      <c r="E775" t="inlineStr"/>
+      <c r="F775" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>2025-02-27 10:30:00-05:00</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>EIA Natural Gas Stocks ChangeFEB/21</t>
+        </is>
+      </c>
+      <c r="C776" t="inlineStr"/>
+      <c r="D776" t="inlineStr"/>
+      <c r="E776" t="inlineStr"/>
+      <c r="F776" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>2025-02-27 10:30:00-05:00</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>NY Fed Treasury Purchases 4 to 6 yrs</t>
+        </is>
+      </c>
+      <c r="C777" t="inlineStr"/>
+      <c r="D777" t="inlineStr">
+        <is>
+          <t>$50 million</t>
+        </is>
+      </c>
+      <c r="E777" t="inlineStr"/>
+      <c r="F777" t="n">
         <v>3</v>
       </c>
     </row>

--- a/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-02-27.xlsx
+++ b/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-02-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F785"/>
+  <dimension ref="A1:F791"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -720,12 +720,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.142M</t>
+          <t>0.099M</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -742,22 +742,18 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-1.178M</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>-2.75M</t>
-        </is>
-      </c>
+          <t>0.041M</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -768,18 +764,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>7.717M</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0.7M</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -790,19 +790,15 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>6.406M</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>-0.1M</t>
-        </is>
-      </c>
+          <t>-0.416M</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
         <v>3</v>
@@ -816,18 +812,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.323M</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -838,15 +838,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.416M</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>-0.1M</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
         <v>3</v>
@@ -860,22 +864,18 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -886,12 +886,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.041M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -908,12 +908,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1582,22 +1582,18 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Balance of TradeNOV</t>
+          <t>ExportsNOV</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>$-78.2B</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>$-78B</t>
-        </is>
-      </c>
+          <t>$273.4B</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>$-70B</t>
+          <t>$264B</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -1612,18 +1608,18 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ExportsNOV</t>
+          <t>ImportsNOV</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>$273.4B</t>
+          <t>$351.6B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>$264B</t>
+          <t>$334B</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -1638,18 +1634,22 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ImportsNOV</t>
+          <t>Balance of TradeNOV</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>$351.6B</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
+          <t>$-78.2B</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>$-78B</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>$334B</t>
+          <t>$-70B</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Used Car Prices MoMDEC</t>
+          <t>Used Car Prices YoYDEC</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -2254,12 +2254,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Used Car Prices YoYDEC</t>
+          <t>Used Car Prices MoMDEC</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -3148,26 +3148,22 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelJAN</t>
+          <t>Michigan Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>73.2</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>73.8</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113">
@@ -3178,18 +3174,18 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelJAN</t>
+          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F113" t="n">
@@ -3204,18 +3200,18 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelJAN</t>
+          <t>Michigan Current Conditions PrelJAN</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F114" t="n">
@@ -3230,22 +3226,26 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
+          <t>Michigan Consumer Sentiment PrelJAN</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr"/>
+          <t>73.2</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>73.8</t>
+        </is>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116">
@@ -3256,18 +3256,18 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelJAN</t>
+          <t>Michigan Consumer Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F116" t="n">
@@ -3458,12 +3458,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>4.180%</t>
+          <t>4.225%</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
@@ -3480,12 +3480,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>4.225%</t>
+          <t>4.180%</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
@@ -4010,26 +4010,22 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYDEC</t>
+          <t>CPI s.aDEC</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+          <t>317.685</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>317.4</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="148">
@@ -4040,22 +4036,22 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMDEC</t>
+          <t>Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -4070,26 +4066,26 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYDEC</t>
+          <t>CPIDEC</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>315.6</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="150">
@@ -4100,22 +4096,22 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>CPIDEC</t>
+          <t>NY Empire State Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>-12.60</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>315.6</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="F150" t="n">
@@ -4130,26 +4126,26 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexJAN</t>
+          <t>Core Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>-12.60</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="152">
@@ -4160,22 +4156,22 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMDEC</t>
+          <t>Core Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F152" t="n">
@@ -4190,22 +4186,26 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>CPI s.aDEC</t>
+          <t>Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>317.685</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr"/>
+          <t>2.9%</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>2.9%</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>317.4</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154">
@@ -4252,22 +4252,18 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>2.60M</t>
-        </is>
-      </c>
+          <t>-1.304M</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="157">
@@ -4278,12 +4274,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>0.765M</t>
+          <t>0.646M</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
@@ -4300,15 +4296,19 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>-0.021M</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr"/>
+          <t>3.077M</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>1.1M</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="n">
         <v>3</v>
@@ -4322,18 +4322,22 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>0.397M</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr"/>
+          <t>-1.961M</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>-1.6M</t>
+        </is>
+      </c>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="160">
@@ -4344,22 +4348,18 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>-1.961M</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>-1.6M</t>
-        </is>
-      </c>
+          <t>-0.255M</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="161">
@@ -4370,12 +4370,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>-0.021M</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
@@ -4392,19 +4392,15 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>3.077M</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>1.1M</t>
-        </is>
-      </c>
+          <t>0.765M</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="n">
         <v>3</v>
@@ -4418,18 +4414,22 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>0.646M</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>2.60M</t>
+        </is>
+      </c>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="164">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>-1.304M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
@@ -4556,22 +4556,22 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F170" t="n">
@@ -4586,26 +4586,26 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F171" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="172">
@@ -4616,20 +4616,16 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>39.00</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>4.0%</t>
-        </is>
-      </c>
+      <c r="E172" t="inlineStr"/>
       <c r="F172" t="n">
         <v>3</v>
       </c>
@@ -4642,22 +4638,22 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>217K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>210K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F173" t="n">
@@ -4672,16 +4668,24 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>11.9</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr"/>
-      <c r="E174" t="inlineStr"/>
+          <t>1859K</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>1870.0K</t>
+        </is>
+      </c>
       <c r="F174" t="n">
         <v>3</v>
       </c>
@@ -4694,20 +4698,16 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>212.75K</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>215.0K</t>
-        </is>
-      </c>
+      <c r="E175" t="inlineStr"/>
       <c r="F175" t="n">
         <v>3</v>
       </c>
@@ -4720,26 +4720,22 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>1.8%</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F176" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="177">
@@ -4750,24 +4746,16 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>1.6%</t>
-        </is>
-      </c>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" t="inlineStr"/>
       <c r="F177" t="n">
         <v>3</v>
       </c>
@@ -4780,26 +4768,18 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
+          <t>46.3</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr"/>
       <c r="F178" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="179">
@@ -4810,16 +4790,20 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>212.75K</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
-      <c r="E179" t="inlineStr"/>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>215.0K</t>
+        </is>
+      </c>
       <c r="F179" t="n">
         <v>3</v>
       </c>
@@ -4832,18 +4816,22 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>1.8%</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="F180" t="n">
@@ -4858,26 +4846,26 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F181" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="182">
@@ -4888,26 +4876,18 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr"/>
+      <c r="E182" t="inlineStr"/>
       <c r="F182" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="183">
@@ -4918,18 +4898,26 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>39.00</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr"/>
-      <c r="E183" t="inlineStr"/>
+          <t>217K</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>210K</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>209.0K</t>
+        </is>
+      </c>
       <c r="F183" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="184">
@@ -4940,16 +4928,20 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D184" t="inlineStr"/>
-      <c r="E184" t="inlineStr"/>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>4.0%</t>
+        </is>
+      </c>
       <c r="F184" t="n">
         <v>3</v>
       </c>
@@ -4962,22 +4954,22 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F185" t="n">
@@ -4992,18 +4984,26 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr"/>
-      <c r="E186" t="inlineStr"/>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>-10</t>
+        </is>
+      </c>
       <c r="F186" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="187">
@@ -5014,26 +5014,26 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoMNOV</t>
+          <t>NAHB Housing Market IndexJAN</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F187" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="188">
@@ -5044,22 +5044,22 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>NAHB Housing Market IndexJAN</t>
+          <t>Business Inventories MoMNOV</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F188" t="n">
@@ -5074,17 +5074,17 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Business Inventories MoMNOV</t>
+          <t>Retail Inventories Ex Autos MoMNOV</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -5093,7 +5093,7 @@
         </is>
       </c>
       <c r="F189" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="190">
@@ -5240,22 +5240,26 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Housing Starts MoMDEC</t>
+          <t>Housing StartsDEC</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>15.8%</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr"/>
+          <t>1.499M</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>1.32M</t>
+        </is>
+      </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>1.32M</t>
         </is>
       </c>
       <c r="F196" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="197">
@@ -5266,18 +5270,18 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelDEC</t>
+          <t>Housing Starts MoMDEC</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>15.8%</t>
         </is>
       </c>
       <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="F197" t="n">
@@ -5292,26 +5296,22 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Housing StartsDEC</t>
+          <t>Building Permits MoM PrelDEC</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>1.499M</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>1.32M</t>
-        </is>
-      </c>
+          <t>-0.7%</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr">
         <is>
-          <t>1.32M</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="F198" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="199">
@@ -5352,18 +5352,18 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Industrial Production YoYDEC</t>
+          <t>Manufacturing Production YoYDEC</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F200" t="n">
@@ -5378,26 +5378,26 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Capacity UtilizationDEC</t>
+          <t>Industrial Production MoMDEC</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F201" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="202">
@@ -5408,22 +5408,22 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMDEC</t>
+          <t>Capacity UtilizationDEC</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="F202" t="n">
@@ -5438,26 +5438,26 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Industrial Production MoMDEC</t>
+          <t>Manufacturing Production MoMDEC</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F203" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="204">
@@ -5468,18 +5468,18 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYDEC</t>
+          <t>Industrial Production YoYDEC</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D204" t="inlineStr"/>
       <c r="E204" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F204" t="n">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>42-Day Bill Auction</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>4.025%</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
@@ -5692,12 +5692,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>42-Day Bill Auction</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>4.025%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
@@ -5942,22 +5942,18 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/11</t>
+          <t>Jobless Claims 4-week AverageJAN/18</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>1899K</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>1860K</t>
-        </is>
-      </c>
+          <t>213.5K</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr"/>
       <c r="E225" t="inlineStr">
         <is>
-          <t>1861K</t>
+          <t>213.0K</t>
         </is>
       </c>
       <c r="F225" t="n">
@@ -5972,22 +5968,26 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/18</t>
+          <t>Initial Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>213.5K</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr"/>
+          <t>223K</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>220K</t>
+        </is>
+      </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>213.0K</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="F226" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="227">
@@ -5998,26 +5998,26 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/18</t>
+          <t>Continuing Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>1899K</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>220K</t>
+          <t>1860K</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>1861K</t>
         </is>
       </c>
       <c r="F227" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="228">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D233" t="inlineStr"/>
@@ -6172,15 +6172,19 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>-1.125M</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="n">
         <v>3</v>
@@ -6194,12 +6198,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D235" t="inlineStr"/>
@@ -6216,22 +6220,18 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>-0.148M</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr"/>
       <c r="E236" t="inlineStr"/>
       <c r="F236" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="237">
@@ -6242,22 +6242,18 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>0.068M</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr"/>
       <c r="E237" t="inlineStr"/>
       <c r="F237" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="238">
@@ -6268,18 +6264,22 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>6.96%</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="239">
@@ -6290,18 +6290,22 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>0.184M</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="240">
@@ -6312,12 +6316,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
@@ -6334,12 +6338,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D241" t="inlineStr"/>
@@ -6356,12 +6360,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -6378,19 +6382,15 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>6.96%</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr"/>
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="n">
         <v>3</v>
@@ -6448,22 +6448,22 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashJAN</t>
+          <t>S&amp;P Global Manufacturing PMI FlashJAN</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="F246" t="n">
@@ -6478,22 +6478,22 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashJAN</t>
+          <t>S&amp;P Global Services PMI FlashJAN</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="F247" t="n">
@@ -6534,22 +6534,26 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr"/>
+          <t>69.3</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>70.2</t>
+        </is>
+      </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F249" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="250">
@@ -6560,26 +6564,26 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F250" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="251">
@@ -6590,26 +6594,26 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.24M</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.19M</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="F251" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="252">
@@ -6620,12 +6624,12 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -6650,26 +6654,26 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>4.24M</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>4.19M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F253" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="254">
@@ -6680,26 +6684,26 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F254" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="255">
@@ -6710,26 +6714,22 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr">
-        <is>
-          <t>77.9</t>
-        </is>
-      </c>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr"/>
       <c r="E255" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F255" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="256">
@@ -7178,18 +7178,18 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>House Price Index YoYNOV</t>
+          <t>House Price IndexNOV</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>433.4</t>
         </is>
       </c>
       <c r="D273" t="inlineStr"/>
       <c r="E273" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>433</t>
         </is>
       </c>
       <c r="F273" t="n">
@@ -7204,22 +7204,26 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYNOV</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr"/>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>4.3%</t>
+        </is>
+      </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F274" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="275">
@@ -7260,26 +7264,22 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYNOV</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr">
-        <is>
-          <t>4.3%</t>
-        </is>
-      </c>
+          <t>-0.1%</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr"/>
       <c r="E276" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F276" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="277">
@@ -7290,18 +7290,18 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>House Price IndexNOV</t>
+          <t>House Price Index YoYNOV</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>433.4</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="D277" t="inlineStr"/>
       <c r="E277" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F277" t="n">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Money SupplyDEC</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>$21.53T</t>
+          <t>4.457%</t>
         </is>
       </c>
       <c r="D286" t="inlineStr"/>
@@ -7546,12 +7546,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>Money SupplyDEC</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>4.457%</t>
+          <t>$21.53T</t>
         </is>
       </c>
       <c r="D287" t="inlineStr"/>
@@ -7790,19 +7790,15 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>-4.994M</t>
-        </is>
-      </c>
-      <c r="D297" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.532M</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr"/>
       <c r="E297" t="inlineStr"/>
       <c r="F297" t="n">
         <v>3</v>
@@ -7816,12 +7812,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>-0.333M</t>
+          <t>0.128M</t>
         </is>
       </c>
       <c r="D298" t="inlineStr"/>
@@ -7838,22 +7834,18 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>2.957M</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>0.326M</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr"/>
       <c r="E299" t="inlineStr"/>
       <c r="F299" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="300">
@@ -7864,18 +7856,22 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>0.028M</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr"/>
+          <t>3.463M</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>3.2M</t>
+        </is>
+      </c>
       <c r="E300" t="inlineStr"/>
       <c r="F300" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="301">
@@ -7908,22 +7904,18 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>3.463M</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr">
-        <is>
-          <t>3.2M</t>
-        </is>
-      </c>
+          <t>0.028M</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr"/>
       <c r="E302" t="inlineStr"/>
       <c r="F302" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="303">
@@ -7934,18 +7926,22 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>0.128M</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr"/>
+          <t>2.957M</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E303" t="inlineStr"/>
       <c r="F303" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="304">
@@ -7956,12 +7952,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>0.532M</t>
+          <t>-0.333M</t>
         </is>
       </c>
       <c r="D304" t="inlineStr"/>
@@ -7978,15 +7974,19 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>0.326M</t>
-        </is>
-      </c>
-      <c r="D305" t="inlineStr"/>
+          <t>-4.994M</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E305" t="inlineStr"/>
       <c r="F305" t="n">
         <v>3</v>
@@ -8070,18 +8070,22 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ AdvQ4</t>
+          <t>Core PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="D309" t="inlineStr"/>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F309" t="n">
@@ -8096,22 +8100,26 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/25</t>
+          <t>GDP Price Index QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>212.5K</t>
-        </is>
-      </c>
-      <c r="D310" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>214.0K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F310" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="311">
@@ -8122,18 +8130,22 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ AdvQ4</t>
+          <t>Continuing Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D311" t="inlineStr"/>
+          <t>1858K</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>1890K</t>
+        </is>
+      </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>1885.0K</t>
         </is>
       </c>
       <c r="F311" t="n">
@@ -8148,7 +8160,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ AdvQ4</t>
+          <t>GDP Growth Rate QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -8156,14 +8168,18 @@
           <t>2.3%</t>
         </is>
       </c>
-      <c r="D312" t="inlineStr"/>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F312" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="313">
@@ -8204,7 +8220,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ AdvQ4</t>
+          <t>PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -8212,18 +8228,14 @@
           <t>2.3%</t>
         </is>
       </c>
-      <c r="D314" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+      <c r="D314" t="inlineStr"/>
       <c r="E314" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="F314" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="315">
@@ -8234,22 +8246,18 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/18</t>
+          <t>GDP Sales QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>1858K</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr">
-        <is>
-          <t>1890K</t>
-        </is>
-      </c>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr"/>
       <c r="E315" t="inlineStr">
         <is>
-          <t>1885.0K</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F315" t="n">
@@ -8264,26 +8272,22 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ AdvQ4</t>
+          <t>Jobless Claims 4-week AverageJAN/25</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D316" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>212.5K</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr"/>
       <c r="E316" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>214.0K</t>
         </is>
       </c>
       <c r="F316" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="317">
@@ -8294,22 +8298,18 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ AdvQ4</t>
+          <t>Real Consumer Spending QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>2.5%</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr"/>
       <c r="E317" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F317" t="n">
@@ -8826,19 +8826,15 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/31</t>
+          <t>Baker Hughes Total Rigs CountJAN/31</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>479</t>
-        </is>
-      </c>
-      <c r="D337" t="inlineStr">
-        <is>
-          <t>468</t>
-        </is>
-      </c>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr"/>
       <c r="E337" t="inlineStr"/>
       <c r="F337" t="n">
         <v>3</v>
@@ -8852,15 +8848,19 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/31</t>
+          <t>Baker Hughes Oil Rig CountJAN/31</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>582</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr"/>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>468</t>
+        </is>
+      </c>
       <c r="E338" t="inlineStr"/>
       <c r="F338" t="n">
         <v>3</v>
@@ -9708,22 +9708,22 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FinalJAN</t>
+          <t>S&amp;P Global Composite PMI FinalJAN</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="F374" t="n">
@@ -9738,22 +9738,22 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FinalJAN</t>
+          <t>S&amp;P Global Services PMI FinalJAN</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F375" t="n">
@@ -9902,18 +9902,22 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>0.373M</t>
-        </is>
-      </c>
-      <c r="D381" t="inlineStr"/>
+          <t>8.664M</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>2.6M</t>
+        </is>
+      </c>
       <c r="E381" t="inlineStr"/>
       <c r="F381" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="382">
@@ -9924,12 +9928,12 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>-0.186M</t>
+          <t>0.16M</t>
         </is>
       </c>
       <c r="D382" t="inlineStr"/>
@@ -9946,19 +9950,15 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Crude Oil Imports ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>-5.471M</t>
-        </is>
-      </c>
-      <c r="D383" t="inlineStr">
-        <is>
-          <t>-1.5M</t>
-        </is>
-      </c>
+          <t>-0.178M</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr"/>
       <c r="E383" t="inlineStr"/>
       <c r="F383" t="n">
         <v>3</v>
@@ -9972,18 +9972,22 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Gasoline Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>-0.027M</t>
-        </is>
-      </c>
-      <c r="D384" t="inlineStr"/>
+          <t>2.233M</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>1.2M</t>
+        </is>
+      </c>
       <c r="E384" t="inlineStr"/>
       <c r="F384" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="385">
@@ -10016,22 +10020,18 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>2.233M</t>
-        </is>
-      </c>
-      <c r="D386" t="inlineStr">
-        <is>
-          <t>1.2M</t>
-        </is>
-      </c>
+          <t>-0.027M</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr"/>
       <c r="E386" t="inlineStr"/>
       <c r="F386" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="387">
@@ -10042,22 +10042,22 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>8.664M</t>
+          <t>-5.471M</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>2.6M</t>
+          <t>-1.5M</t>
         </is>
       </c>
       <c r="E387" t="inlineStr"/>
       <c r="F387" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="388">
@@ -10068,12 +10068,12 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>-0.178M</t>
+          <t>-0.186M</t>
         </is>
       </c>
       <c r="D388" t="inlineStr"/>
@@ -10090,12 +10090,12 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>0.16M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="D389" t="inlineStr"/>
@@ -10196,26 +10196,22 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/01</t>
+          <t>Jobless Claims 4-week AverageFEB/01</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>219K</t>
-        </is>
-      </c>
-      <c r="D394" t="inlineStr">
-        <is>
-          <t>213K</t>
-        </is>
-      </c>
+          <t>216.75K</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr"/>
       <c r="E394" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>215.5K</t>
         </is>
       </c>
       <c r="F394" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="395">
@@ -10226,26 +10222,26 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/25</t>
+          <t>Nonfarm Productivity QoQ PrelQ4</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>1886K</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>1855.0K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F395" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="396">
@@ -10256,22 +10252,22 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Nonfarm Productivity QoQ PrelQ4</t>
+          <t>Unit Labour Costs QoQ PrelQ4</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F396" t="n">
@@ -10286,22 +10282,26 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/01</t>
+          <t>Initial Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>216.75K</t>
-        </is>
-      </c>
-      <c r="D397" t="inlineStr"/>
+          <t>219K</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>213K</t>
+        </is>
+      </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>215.5K</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F397" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="398">
@@ -10312,26 +10312,26 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Unit Labour Costs QoQ PrelQ4</t>
+          <t>Continuing Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>1886K</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>1855.0K</t>
         </is>
       </c>
       <c r="F398" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="399">
@@ -10390,12 +10390,12 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D401" t="inlineStr"/>
@@ -10412,12 +10412,12 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="D402" t="inlineStr"/>
@@ -10536,18 +10536,22 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Government PayrollsJAN</t>
+          <t>Average Weekly HoursJAN</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>32K</t>
-        </is>
-      </c>
-      <c r="D408" t="inlineStr"/>
+          <t>34.1</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>25K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F408" t="n">
@@ -10562,26 +10566,22 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoYJAN</t>
+          <t>U-6 Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>4.1%</t>
-        </is>
-      </c>
-      <c r="D409" t="inlineStr">
-        <is>
-          <t>3.8%</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr"/>
       <c r="E409" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="F409" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="410">
@@ -10592,22 +10592,22 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsJAN</t>
+          <t>Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>143K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>170K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>205K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F410" t="n">
@@ -10622,22 +10622,22 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateJAN</t>
+          <t>Manufacturing PayrollsJAN</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>111K</t>
+          <t>3K</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>141K</t>
+          <t>-2K</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>180K</t>
+          <t>-5K</t>
         </is>
       </c>
       <c r="F411" t="n">
@@ -10652,18 +10652,22 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Participation RateJAN</t>
+          <t>Average Hourly Earnings MoMJAN</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>62.6%</t>
-        </is>
-      </c>
-      <c r="D412" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F412" t="n">
@@ -10678,26 +10682,26 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMJAN</t>
+          <t>Nonfarm Payrolls PrivateJAN</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>111K</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>141K</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>180K</t>
         </is>
       </c>
       <c r="F413" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="414">
@@ -10708,26 +10712,26 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsJAN</t>
+          <t>Non Farm PayrollsJAN</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>3K</t>
+          <t>143K</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>-2K</t>
+          <t>170K</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>-5K</t>
+          <t>205K</t>
         </is>
       </c>
       <c r="F414" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="415">
@@ -10738,26 +10742,26 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Unemployment RateJAN</t>
+          <t>Average Hourly Earnings YoYJAN</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="F415" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="416">
@@ -10768,18 +10772,18 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>U-6 Unemployment RateJAN</t>
+          <t>Government PayrollsJAN</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>32K</t>
         </is>
       </c>
       <c r="D416" t="inlineStr"/>
       <c r="E416" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>25K</t>
         </is>
       </c>
       <c r="F416" t="n">
@@ -10794,26 +10798,22 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Average Weekly HoursJAN</t>
+          <t>Participation RateJAN</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>34.1</t>
-        </is>
-      </c>
-      <c r="D417" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
+          <t>62.6%</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr"/>
       <c r="E417" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="F417" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="418">
@@ -10904,22 +10904,26 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelFEB</t>
+          <t>Michigan Consumer Sentiment PrelFEB</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="D422" t="inlineStr"/>
+          <t>67.8</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>71.1</t>
+        </is>
+      </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F422" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="423">
@@ -10930,22 +10934,22 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelFEB</t>
+          <t>Wholesale Inventories MoMDEC</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F423" t="n">
@@ -10960,18 +10964,22 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelFEB</t>
+          <t>Michigan Current Conditions PrelFEB</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D424" t="inlineStr"/>
+          <t>68.7</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="F424" t="n">
@@ -10986,22 +10994,22 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelFEB</t>
+          <t>Michigan Consumer Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="F425" t="n">
@@ -11016,22 +11024,18 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoMDEC</t>
+          <t>Michigan Inflation Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
-      <c r="D426" t="inlineStr">
-        <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr"/>
       <c r="E426" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F426" t="n">
@@ -11046,26 +11050,22 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelFEB</t>
+          <t>Michigan 5 Year Inflation Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>67.8</t>
-        </is>
-      </c>
-      <c r="D427" t="inlineStr">
-        <is>
-          <t>71.1</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr"/>
       <c r="E427" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F427" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="428">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>4.225%</t>
+          <t>4.185%</t>
         </is>
       </c>
       <c r="D434" t="inlineStr"/>
@@ -11234,12 +11234,12 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>4.185%</t>
+          <t>4.225%</t>
         </is>
       </c>
       <c r="D435" t="inlineStr"/>
@@ -11474,7 +11474,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/07</t>
+          <t>MBA Mortgage ApplicationsFEB/07</t>
         </is>
       </c>
       <c r="C447" t="inlineStr"/>
@@ -11492,14 +11492,14 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/07</t>
+          <t>MBA 30-Year Mortgage RateFEB/07</t>
         </is>
       </c>
       <c r="C448" t="inlineStr"/>
       <c r="D448" t="inlineStr"/>
       <c r="E448" t="inlineStr"/>
       <c r="F448" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="449">
@@ -11510,7 +11510,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/07</t>
+          <t>MBA Purchase IndexFEB/07</t>
         </is>
       </c>
       <c r="C449" t="inlineStr"/>
@@ -11528,14 +11528,14 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/07</t>
+          <t>MBA Mortgage Refinance IndexFEB/07</t>
         </is>
       </c>
       <c r="C450" t="inlineStr"/>
       <c r="D450" t="inlineStr"/>
       <c r="E450" t="inlineStr"/>
       <c r="F450" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="451">
@@ -11546,7 +11546,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/07</t>
+          <t>MBA Mortgage Market IndexFEB/07</t>
         </is>
       </c>
       <c r="C451" t="inlineStr"/>
@@ -11716,14 +11716,14 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C458" t="inlineStr"/>
       <c r="D458" t="inlineStr"/>
       <c r="E458" t="inlineStr"/>
       <c r="F458" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="459">
@@ -11734,7 +11734,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C459" t="inlineStr"/>
@@ -11752,7 +11752,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C460" t="inlineStr"/>
@@ -11770,7 +11770,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C461" t="inlineStr"/>
@@ -11788,14 +11788,14 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C462" t="inlineStr"/>
       <c r="D462" t="inlineStr"/>
       <c r="E462" t="inlineStr"/>
       <c r="F462" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="463">
@@ -11806,7 +11806,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C463" t="inlineStr"/>
@@ -11824,7 +11824,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C464" t="inlineStr"/>
@@ -11842,14 +11842,14 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C465" t="inlineStr"/>
       <c r="D465" t="inlineStr"/>
       <c r="E465" t="inlineStr"/>
       <c r="F465" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="466">
@@ -11860,14 +11860,14 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C466" t="inlineStr"/>
       <c r="D466" t="inlineStr"/>
       <c r="E466" t="inlineStr"/>
       <c r="F466" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="467">
@@ -11998,22 +11998,18 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C473" t="inlineStr"/>
-      <c r="D473" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D473" t="inlineStr"/>
       <c r="E473" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="F473" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="474">
@@ -12024,18 +12020,14 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C474" t="inlineStr"/>
-      <c r="D474" t="inlineStr">
-        <is>
-          <t>3.2%</t>
-        </is>
-      </c>
+      <c r="D474" t="inlineStr"/>
       <c r="E474" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F474" t="n">
@@ -12050,22 +12042,22 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C475" t="inlineStr"/>
       <c r="D475" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F475" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="476">
@@ -12076,14 +12068,18 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C476" t="inlineStr"/>
-      <c r="D476" t="inlineStr"/>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F476" t="n">
@@ -12098,18 +12094,14 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C477" t="inlineStr"/>
-      <c r="D477" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+      <c r="D477" t="inlineStr"/>
       <c r="E477" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F477" t="n">
@@ -12124,22 +12116,22 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C478" t="inlineStr"/>
       <c r="D478" t="inlineStr">
         <is>
-          <t>216K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F478" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="479">
@@ -12150,14 +12142,18 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C479" t="inlineStr"/>
-      <c r="D479" t="inlineStr"/>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F479" t="n">
@@ -12172,18 +12168,22 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C480" t="inlineStr"/>
-      <c r="D480" t="inlineStr"/>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F480" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="481">
@@ -12194,14 +12194,14 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C481" t="inlineStr"/>
       <c r="D481" t="inlineStr"/>
       <c r="E481" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="F481" t="n">
@@ -12360,22 +12360,18 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="C490" t="inlineStr"/>
-      <c r="D490" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D490" t="inlineStr"/>
       <c r="E490" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F490" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="491">
@@ -12386,22 +12382,18 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="C491" t="inlineStr"/>
-      <c r="D491" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D491" t="inlineStr"/>
       <c r="E491" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F491" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="492">
@@ -12412,22 +12404,22 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="C492" t="inlineStr"/>
       <c r="D492" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F492" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="493">
@@ -12438,18 +12430,18 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="C493" t="inlineStr"/>
       <c r="D493" t="inlineStr"/>
       <c r="E493" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F493" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="494">
@@ -12460,18 +12452,18 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="C494" t="inlineStr"/>
       <c r="D494" t="inlineStr"/>
       <c r="E494" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F494" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="495">
@@ -12482,18 +12474,22 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="C495" t="inlineStr"/>
-      <c r="D495" t="inlineStr"/>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="F495" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="496">
@@ -12504,18 +12500,22 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="C496" t="inlineStr"/>
-      <c r="D496" t="inlineStr"/>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F496" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="497">
@@ -12526,14 +12526,14 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="C497" t="inlineStr"/>
       <c r="D497" t="inlineStr"/>
       <c r="E497" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F497" t="n">
@@ -12548,13 +12548,13 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="C498" t="inlineStr"/>
       <c r="D498" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E498" t="inlineStr">
@@ -13068,7 +13068,7 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C522" t="inlineStr"/>
@@ -13086,7 +13086,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C523" t="inlineStr"/>
@@ -13158,14 +13158,14 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C527" t="inlineStr"/>
       <c r="D527" t="inlineStr"/>
       <c r="E527" t="inlineStr"/>
       <c r="F527" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="528">
@@ -13176,14 +13176,14 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="C528" t="inlineStr"/>
       <c r="D528" t="inlineStr"/>
       <c r="E528" t="inlineStr"/>
       <c r="F528" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="529">
@@ -13194,14 +13194,14 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C529" t="inlineStr"/>
       <c r="D529" t="inlineStr"/>
       <c r="E529" t="inlineStr"/>
       <c r="F529" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="530">
@@ -13212,14 +13212,14 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="C530" t="inlineStr"/>
       <c r="D530" t="inlineStr"/>
       <c r="E530" t="inlineStr"/>
       <c r="F530" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="531">
@@ -13230,7 +13230,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C531" t="inlineStr"/>
@@ -13248,7 +13248,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="C532" t="inlineStr"/>
@@ -13306,18 +13306,14 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsDEC</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C535" t="inlineStr"/>
-      <c r="D535" t="inlineStr">
-        <is>
-          <t>$149.1B</t>
-        </is>
-      </c>
+      <c r="D535" t="inlineStr"/>
       <c r="E535" t="inlineStr"/>
       <c r="F535" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="536">
@@ -13328,14 +13324,18 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Net Long-term TIC FlowsDEC</t>
         </is>
       </c>
       <c r="C536" t="inlineStr"/>
-      <c r="D536" t="inlineStr"/>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>$149.1B</t>
+        </is>
+      </c>
       <c r="E536" t="inlineStr"/>
       <c r="F536" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="537">
@@ -13346,7 +13346,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C537" t="inlineStr"/>
@@ -13364,7 +13364,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C538" t="inlineStr"/>
@@ -13382,14 +13382,14 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C539" t="inlineStr"/>
       <c r="D539" t="inlineStr"/>
       <c r="E539" t="inlineStr"/>
       <c r="F539" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="540">
@@ -13400,7 +13400,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C540" t="inlineStr"/>
@@ -13418,14 +13418,14 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C541" t="inlineStr"/>
       <c r="D541" t="inlineStr"/>
       <c r="E541" t="inlineStr"/>
       <c r="F541" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="542">
@@ -13436,7 +13436,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C542" t="inlineStr"/>
@@ -13472,14 +13472,14 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C544" t="inlineStr"/>
       <c r="D544" t="inlineStr"/>
       <c r="E544" t="inlineStr"/>
       <c r="F544" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="545">
@@ -13508,14 +13508,14 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C546" t="inlineStr"/>
       <c r="D546" t="inlineStr"/>
       <c r="E546" t="inlineStr"/>
       <c r="F546" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="547">
@@ -13548,18 +13548,18 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C548" t="inlineStr"/>
       <c r="D548" t="inlineStr">
         <is>
-          <t>1.4M</t>
+          <t>1.46M</t>
         </is>
       </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F548" t="n">
@@ -13574,18 +13574,22 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C549" t="inlineStr"/>
-      <c r="D549" t="inlineStr"/>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>1.4M</t>
+        </is>
+      </c>
       <c r="E549" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F549" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="550">
@@ -13596,18 +13600,22 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C550" t="inlineStr"/>
-      <c r="D550" t="inlineStr"/>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>1.4M</t>
+        </is>
+      </c>
       <c r="E550" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F550" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="551">
@@ -13618,18 +13626,18 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C551" t="inlineStr"/>
       <c r="D551" t="inlineStr">
         <is>
-          <t>1.4M</t>
+          <t>1.46M</t>
         </is>
       </c>
       <c r="E551" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F551" t="n">
@@ -13644,22 +13652,18 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C552" t="inlineStr"/>
-      <c r="D552" t="inlineStr">
-        <is>
-          <t>1.46M</t>
-        </is>
-      </c>
+      <c r="D552" t="inlineStr"/>
       <c r="E552" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F552" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="553">
@@ -13670,22 +13674,18 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C553" t="inlineStr"/>
-      <c r="D553" t="inlineStr">
-        <is>
-          <t>1.46M</t>
-        </is>
-      </c>
+      <c r="D553" t="inlineStr"/>
       <c r="E553" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F553" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="554">
@@ -13696,14 +13696,14 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C554" t="inlineStr"/>
       <c r="D554" t="inlineStr"/>
       <c r="E554" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F554" t="n">
@@ -13978,22 +13978,14 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C569" t="inlineStr"/>
-      <c r="D569" t="inlineStr">
-        <is>
-          <t>16.3</t>
-        </is>
-      </c>
-      <c r="E569" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="D569" t="inlineStr"/>
+      <c r="E569" t="inlineStr"/>
       <c r="F569" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="570">
@@ -14004,18 +13996,18 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C570" t="inlineStr"/>
       <c r="D570" t="inlineStr">
         <is>
-          <t>215K</t>
+          <t>16.3</t>
         </is>
       </c>
       <c r="E570" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F570" t="n">
@@ -14030,22 +14022,22 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C571" t="inlineStr"/>
       <c r="D571" t="inlineStr">
         <is>
-          <t>1860K</t>
+          <t>16.3</t>
         </is>
       </c>
       <c r="E571" t="inlineStr">
         <is>
-          <t>1879.0K</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F571" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="572">
@@ -14056,14 +14048,22 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C572" t="inlineStr"/>
-      <c r="D572" t="inlineStr"/>
-      <c r="E572" t="inlineStr"/>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>215K</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>220.0K</t>
+        </is>
+      </c>
       <c r="F572" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="573">
@@ -14074,7 +14074,7 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C573" t="inlineStr"/>
@@ -14092,7 +14092,7 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C574" t="inlineStr"/>
@@ -14110,14 +14110,22 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C575" t="inlineStr"/>
-      <c r="D575" t="inlineStr"/>
-      <c r="E575" t="inlineStr"/>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>215K</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>220.0K</t>
+        </is>
+      </c>
       <c r="F575" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="576">
@@ -14128,14 +14136,18 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C576" t="inlineStr"/>
-      <c r="D576" t="inlineStr"/>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>1860K</t>
+        </is>
+      </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t>219.0K</t>
+          <t>1879.0K</t>
         </is>
       </c>
       <c r="F576" t="n">
@@ -14150,12 +14162,16 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C577" t="inlineStr"/>
       <c r="D577" t="inlineStr"/>
-      <c r="E577" t="inlineStr"/>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="F577" t="n">
         <v>3</v>
       </c>
@@ -14186,20 +14202,12 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C579" t="inlineStr"/>
-      <c r="D579" t="inlineStr">
-        <is>
-          <t>1860K</t>
-        </is>
-      </c>
-      <c r="E579" t="inlineStr">
-        <is>
-          <t>1879.0K</t>
-        </is>
-      </c>
+      <c r="D579" t="inlineStr"/>
+      <c r="E579" t="inlineStr"/>
       <c r="F579" t="n">
         <v>3</v>
       </c>
@@ -14212,7 +14220,7 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C580" t="inlineStr"/>
@@ -14230,16 +14238,12 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C581" t="inlineStr"/>
       <c r="D581" t="inlineStr"/>
-      <c r="E581" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="E581" t="inlineStr"/>
       <c r="F581" t="n">
         <v>3</v>
       </c>
@@ -14252,7 +14256,7 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C582" t="inlineStr"/>
@@ -14270,22 +14274,18 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C583" t="inlineStr"/>
-      <c r="D583" t="inlineStr">
-        <is>
-          <t>16.3</t>
-        </is>
-      </c>
+      <c r="D583" t="inlineStr"/>
       <c r="E583" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>219.0K</t>
         </is>
       </c>
       <c r="F583" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="584">
@@ -14296,22 +14296,22 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C584" t="inlineStr"/>
       <c r="D584" t="inlineStr">
         <is>
-          <t>215K</t>
+          <t>1860K</t>
         </is>
       </c>
       <c r="E584" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>1879.0K</t>
         </is>
       </c>
       <c r="F584" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="585">
@@ -14340,7 +14340,7 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C586" t="inlineStr"/>
@@ -14518,7 +14518,7 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C595" t="inlineStr"/>
@@ -14536,7 +14536,7 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C596" t="inlineStr"/>
@@ -14554,7 +14554,7 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C597" t="inlineStr"/>
@@ -14572,7 +14572,7 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C598" t="inlineStr"/>
@@ -14590,14 +14590,14 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C599" t="inlineStr"/>
       <c r="D599" t="inlineStr"/>
       <c r="E599" t="inlineStr"/>
       <c r="F599" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="600">
@@ -14608,14 +14608,14 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C600" t="inlineStr"/>
       <c r="D600" t="inlineStr"/>
       <c r="E600" t="inlineStr"/>
       <c r="F600" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="601">
@@ -14626,7 +14626,7 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C601" t="inlineStr"/>
@@ -14644,7 +14644,7 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C602" t="inlineStr"/>
@@ -14662,14 +14662,14 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C603" t="inlineStr"/>
       <c r="D603" t="inlineStr"/>
       <c r="E603" t="inlineStr"/>
       <c r="F603" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="604">
@@ -14680,14 +14680,14 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C604" t="inlineStr"/>
       <c r="D604" t="inlineStr"/>
       <c r="E604" t="inlineStr"/>
       <c r="F604" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="605">
@@ -14698,7 +14698,7 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C605" t="inlineStr"/>
@@ -14716,7 +14716,7 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C606" t="inlineStr"/>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C607" t="inlineStr"/>
@@ -14752,7 +14752,7 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C608" t="inlineStr"/>
@@ -14770,7 +14770,7 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C609" t="inlineStr"/>
@@ -14788,7 +14788,7 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>Fed Musalem Speech</t>
         </is>
       </c>
       <c r="C610" t="inlineStr"/>
@@ -14806,14 +14806,14 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C611" t="inlineStr"/>
       <c r="D611" t="inlineStr"/>
       <c r="E611" t="inlineStr"/>
       <c r="F611" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="612">
@@ -14824,7 +14824,7 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C612" t="inlineStr"/>
@@ -14842,7 +14842,7 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C613" t="inlineStr"/>
@@ -14860,14 +14860,14 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>Fed Musalem Speech</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C614" t="inlineStr"/>
       <c r="D614" t="inlineStr"/>
       <c r="E614" t="inlineStr"/>
       <c r="F614" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="615">
@@ -14878,7 +14878,7 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C615" t="inlineStr"/>
@@ -14896,7 +14896,7 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C616" t="inlineStr"/>
@@ -14914,7 +14914,7 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C617" t="inlineStr"/>
@@ -14950,7 +14950,7 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C619" t="inlineStr"/>
@@ -15148,15 +15148,11 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C630" t="inlineStr"/>
-      <c r="D630" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
+      <c r="D630" t="inlineStr"/>
       <c r="E630" t="inlineStr">
         <is>
           <t>52.7</t>
@@ -15200,18 +15196,18 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="C632" t="inlineStr"/>
       <c r="D632" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>53</t>
         </is>
       </c>
       <c r="E632" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="F632" t="n">
@@ -15226,14 +15222,18 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C633" t="inlineStr"/>
-      <c r="D633" t="inlineStr"/>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>51.3</t>
+        </is>
+      </c>
       <c r="E633" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F633" t="n">
@@ -15248,18 +15248,14 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C634" t="inlineStr"/>
-      <c r="D634" t="inlineStr">
-        <is>
-          <t>51.3</t>
-        </is>
-      </c>
+      <c r="D634" t="inlineStr"/>
       <c r="E634" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="F634" t="n">
@@ -15274,14 +15270,18 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C635" t="inlineStr"/>
-      <c r="D635" t="inlineStr"/>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>51.3</t>
+        </is>
+      </c>
       <c r="E635" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F635" t="n">
@@ -15296,22 +15296,22 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C636" t="inlineStr"/>
       <c r="D636" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.13M</t>
         </is>
       </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F636" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="637">
@@ -15322,22 +15322,22 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C637" t="inlineStr"/>
       <c r="D637" t="inlineStr">
         <is>
-          <t>4.13M</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="E637" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F637" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="638">
@@ -15348,22 +15348,18 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C638" t="inlineStr"/>
-      <c r="D638" t="inlineStr">
-        <is>
-          <t>4.3%</t>
-        </is>
-      </c>
+      <c r="D638" t="inlineStr"/>
       <c r="E638" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F638" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="639">
@@ -15374,22 +15370,22 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C639" t="inlineStr"/>
       <c r="D639" t="inlineStr">
         <is>
-          <t>4.13M</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F639" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="640">
@@ -15400,18 +15396,22 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C640" t="inlineStr"/>
-      <c r="D640" t="inlineStr"/>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>68.7</t>
+        </is>
+      </c>
       <c r="E640" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F640" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="641">
@@ -15422,22 +15422,22 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C641" t="inlineStr"/>
       <c r="D641" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E641" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F641" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="642">
@@ -15448,18 +15448,22 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C642" t="inlineStr"/>
-      <c r="D642" t="inlineStr"/>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>4.13M</t>
+        </is>
+      </c>
       <c r="E642" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F642" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="643">
@@ -15470,22 +15474,18 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C643" t="inlineStr"/>
-      <c r="D643" t="inlineStr">
-        <is>
-          <t>67.3</t>
-        </is>
-      </c>
+      <c r="D643" t="inlineStr"/>
       <c r="E643" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F643" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="644">
@@ -15496,22 +15496,22 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C644" t="inlineStr"/>
       <c r="D644" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F644" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="645">
@@ -15522,18 +15522,18 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C645" t="inlineStr"/>
       <c r="D645" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F645" t="n">
@@ -15548,18 +15548,18 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C646" t="inlineStr"/>
       <c r="D646" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F646" t="n">
@@ -15574,18 +15574,18 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C647" t="inlineStr"/>
       <c r="D647" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F647" t="n">
@@ -15600,18 +15600,18 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C648" t="inlineStr"/>
       <c r="D648" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F648" t="n">
@@ -15706,7 +15706,7 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/21</t>
+          <t>Baker Hughes Total Rigs CountFEB/21</t>
         </is>
       </c>
       <c r="C653" t="inlineStr"/>
@@ -15724,7 +15724,7 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/21</t>
+          <t>Baker Hughes Oil Rig CountFEB/21</t>
         </is>
       </c>
       <c r="C654" t="inlineStr"/>
@@ -15832,7 +15832,7 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C660" t="inlineStr"/>
@@ -15886,7 +15886,7 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C663" t="inlineStr"/>
@@ -15976,18 +15976,14 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C668" t="inlineStr"/>
       <c r="D668" t="inlineStr"/>
-      <c r="E668" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="E668" t="inlineStr"/>
       <c r="F668" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="669">
@@ -16016,7 +16012,7 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C670" t="inlineStr"/>
@@ -16034,7 +16030,7 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C671" t="inlineStr"/>
@@ -16052,7 +16048,7 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C672" t="inlineStr"/>
@@ -16088,14 +16084,18 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C674" t="inlineStr"/>
       <c r="D674" t="inlineStr"/>
-      <c r="E674" t="inlineStr"/>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="F674" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="675">
@@ -16106,18 +16106,14 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C675" t="inlineStr"/>
       <c r="D675" t="inlineStr"/>
-      <c r="E675" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="E675" t="inlineStr"/>
       <c r="F675" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="676">
@@ -16128,14 +16124,18 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C676" t="inlineStr"/>
       <c r="D676" t="inlineStr"/>
-      <c r="E676" t="inlineStr"/>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="F676" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="677">
@@ -16146,7 +16146,7 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C677" t="inlineStr"/>
@@ -16182,7 +16182,7 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C679" t="inlineStr"/>
@@ -16200,14 +16200,14 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C680" t="inlineStr"/>
       <c r="D680" t="inlineStr"/>
       <c r="E680" t="inlineStr"/>
       <c r="F680" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="681">
@@ -16236,14 +16236,14 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C682" t="inlineStr"/>
       <c r="D682" t="inlineStr"/>
       <c r="E682" t="inlineStr"/>
       <c r="F682" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="683">
@@ -16254,14 +16254,14 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C683" t="inlineStr"/>
       <c r="D683" t="inlineStr"/>
       <c r="E683" t="inlineStr"/>
       <c r="F683" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="684">
@@ -16272,7 +16272,7 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
       <c r="C684" t="inlineStr"/>
@@ -16290,14 +16290,14 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C685" t="inlineStr"/>
       <c r="D685" t="inlineStr"/>
       <c r="E685" t="inlineStr"/>
       <c r="F685" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="686">
@@ -16308,7 +16308,7 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexFEB</t>
+          <t>Dallas Fed Services IndexFEB</t>
         </is>
       </c>
       <c r="C686" t="inlineStr"/>
@@ -16326,7 +16326,7 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexFEB</t>
+          <t>Dallas Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C687" t="inlineStr"/>
@@ -16344,7 +16344,7 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexFEB</t>
+          <t>Dallas Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C688" t="inlineStr"/>
@@ -16362,7 +16362,7 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexFEB</t>
+          <t>Dallas Fed Services IndexFEB</t>
         </is>
       </c>
       <c r="C689" t="inlineStr"/>
@@ -16380,7 +16380,7 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>Money SupplyJAN</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C690" t="inlineStr"/>
@@ -16398,7 +16398,7 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>Money SupplyJAN</t>
         </is>
       </c>
       <c r="C691" t="inlineStr"/>
@@ -16416,7 +16416,7 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>Money SupplyJAN</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C692" t="inlineStr"/>
@@ -16434,7 +16434,7 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>Money SupplyJAN</t>
         </is>
       </c>
       <c r="C693" t="inlineStr"/>
@@ -16488,7 +16488,7 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/21</t>
+          <t>MBA Purchase IndexFEB/21</t>
         </is>
       </c>
       <c r="C696" t="inlineStr"/>
@@ -16506,14 +16506,14 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
+          <t>MBA Mortgage Refinance IndexFEB/21</t>
         </is>
       </c>
       <c r="C697" t="inlineStr"/>
       <c r="D697" t="inlineStr"/>
       <c r="E697" t="inlineStr"/>
       <c r="F697" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="698">
@@ -16524,7 +16524,7 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/21</t>
+          <t>MBA Mortgage Market IndexFEB/21</t>
         </is>
       </c>
       <c r="C698" t="inlineStr"/>
@@ -16542,7 +16542,7 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/21</t>
+          <t>MBA Mortgage ApplicationsFEB/21</t>
         </is>
       </c>
       <c r="C699" t="inlineStr"/>
@@ -16560,14 +16560,14 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
         </is>
       </c>
       <c r="C700" t="inlineStr"/>
       <c r="D700" t="inlineStr"/>
       <c r="E700" t="inlineStr"/>
       <c r="F700" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="701">
@@ -16578,7 +16578,7 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C701" t="inlineStr"/>
@@ -16614,7 +16614,7 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/21</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C703" t="inlineStr"/>
@@ -16632,7 +16632,7 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>MBA Mortgage Refinance IndexFEB/21</t>
         </is>
       </c>
       <c r="C704" t="inlineStr"/>
@@ -16650,7 +16650,7 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/21</t>
+          <t>MBA Purchase IndexFEB/21</t>
         </is>
       </c>
       <c r="C705" t="inlineStr"/>
@@ -16668,7 +16668,7 @@
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/21</t>
+          <t>MBA Mortgage Market IndexFEB/21</t>
         </is>
       </c>
       <c r="C706" t="inlineStr"/>
@@ -16686,7 +16686,7 @@
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/21</t>
+          <t>MBA Mortgage ApplicationsFEB/21</t>
         </is>
       </c>
       <c r="C707" t="inlineStr"/>
@@ -16704,7 +16704,7 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>New Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C708" t="inlineStr"/>
@@ -16722,7 +16722,7 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>New Home Sales MoMJAN</t>
+          <t>New Home SalesJAN</t>
         </is>
       </c>
       <c r="C709" t="inlineStr"/>
@@ -16740,7 +16740,7 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>New Home SalesJAN</t>
         </is>
       </c>
       <c r="C710" t="inlineStr"/>
@@ -16758,7 +16758,7 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>New Home SalesJAN</t>
+          <t>New Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C711" t="inlineStr"/>
@@ -16776,7 +16776,7 @@
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>New Home Sales MoMJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C712" t="inlineStr"/>
@@ -16794,7 +16794,7 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>New Home SalesJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C713" t="inlineStr"/>
@@ -16812,7 +16812,7 @@
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C714" t="inlineStr"/>
@@ -16830,7 +16830,7 @@
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C715" t="inlineStr"/>
@@ -16848,14 +16848,14 @@
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C716" t="inlineStr"/>
       <c r="D716" t="inlineStr"/>
       <c r="E716" t="inlineStr"/>
       <c r="F716" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="717">
@@ -16866,14 +16866,14 @@
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
       <c r="C717" t="inlineStr"/>
       <c r="D717" t="inlineStr"/>
       <c r="E717" t="inlineStr"/>
       <c r="F717" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="718">
@@ -16884,7 +16884,7 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+          <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C718" t="inlineStr"/>
@@ -16902,7 +16902,7 @@
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
+          <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C719" t="inlineStr"/>
@@ -16920,7 +16920,7 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C720" t="inlineStr"/>
@@ -16938,7 +16938,7 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/21</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C721" t="inlineStr"/>
@@ -16956,7 +16956,7 @@
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C722" t="inlineStr"/>
@@ -16992,14 +16992,14 @@
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C724" t="inlineStr"/>
       <c r="D724" t="inlineStr"/>
       <c r="E724" t="inlineStr"/>
       <c r="F724" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="725">
@@ -17010,7 +17010,7 @@
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/21</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C725" t="inlineStr"/>
@@ -17028,7 +17028,7 @@
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C726" t="inlineStr"/>
@@ -17046,14 +17046,14 @@
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C727" t="inlineStr"/>
       <c r="D727" t="inlineStr"/>
       <c r="E727" t="inlineStr"/>
       <c r="F727" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="728">
@@ -17064,7 +17064,7 @@
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C728" t="inlineStr"/>
@@ -17082,14 +17082,14 @@
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C729" t="inlineStr"/>
       <c r="D729" t="inlineStr"/>
       <c r="E729" t="inlineStr"/>
       <c r="F729" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="730">
@@ -17100,14 +17100,14 @@
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C730" t="inlineStr"/>
       <c r="D730" t="inlineStr"/>
       <c r="E730" t="inlineStr"/>
       <c r="F730" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="731">
@@ -17118,7 +17118,7 @@
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/21</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
       <c r="C731" t="inlineStr"/>
@@ -17136,7 +17136,7 @@
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>17-Week Bill Auction</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C732" t="inlineStr"/>
@@ -17154,7 +17154,7 @@
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>17-Week Bill Auction</t>
         </is>
       </c>
       <c r="C733" t="inlineStr"/>
@@ -17172,7 +17172,7 @@
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>17-Week Bill Auction</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C734" t="inlineStr"/>
@@ -17190,7 +17190,7 @@
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>17-Week Bill Auction</t>
         </is>
       </c>
       <c r="C735" t="inlineStr"/>
@@ -17208,7 +17208,7 @@
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Fed Bostic Speech</t>
         </is>
       </c>
       <c r="C736" t="inlineStr"/>
@@ -17262,7 +17262,7 @@
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>Fed Bostic Speech</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C739" t="inlineStr"/>
@@ -17280,7 +17280,7 @@
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C740" t="inlineStr"/>
@@ -17298,7 +17298,7 @@
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>2-Year FRN Auction</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C741" t="inlineStr"/>
@@ -17316,7 +17316,7 @@
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C742" t="inlineStr"/>
@@ -17334,7 +17334,7 @@
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>2-Year FRN Auction</t>
         </is>
       </c>
       <c r="C743" t="inlineStr"/>
@@ -17352,7 +17352,7 @@
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C744" t="inlineStr"/>
@@ -17388,7 +17388,7 @@
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C746" t="inlineStr"/>
@@ -17406,7 +17406,7 @@
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C747" t="inlineStr"/>
@@ -17424,14 +17424,22 @@
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMJAN</t>
+          <t>Core PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C748" t="inlineStr"/>
-      <c r="D748" t="inlineStr"/>
-      <c r="E748" t="inlineStr"/>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="E748" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="F748" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="749">
@@ -17460,18 +17468,22 @@
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ 2nd EstQ4</t>
+          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C750" t="inlineStr"/>
-      <c r="D750" t="inlineStr"/>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
       <c r="E750" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F750" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="751">
@@ -17482,20 +17494,12 @@
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ 2nd EstQ4</t>
+          <t>Durable Goods Orders Ex Transp MoMJAN</t>
         </is>
       </c>
       <c r="C751" t="inlineStr"/>
-      <c r="D751" t="inlineStr">
-        <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="E751" t="inlineStr">
-        <is>
-          <t>2.2%</t>
-        </is>
-      </c>
+      <c r="D751" t="inlineStr"/>
+      <c r="E751" t="inlineStr"/>
       <c r="F751" t="n">
         <v>2</v>
       </c>
@@ -17508,12 +17512,20 @@
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/22</t>
+          <t>GDP Price Index QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C752" t="inlineStr"/>
-      <c r="D752" t="inlineStr"/>
-      <c r="E752" t="inlineStr"/>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="E752" t="inlineStr">
+        <is>
+          <t>2.2%</t>
+        </is>
+      </c>
       <c r="F752" t="n">
         <v>2</v>
       </c>
@@ -17526,12 +17538,16 @@
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/15</t>
+          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C753" t="inlineStr"/>
       <c r="D753" t="inlineStr"/>
-      <c r="E753" t="inlineStr"/>
+      <c r="E753" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="F753" t="n">
         <v>3</v>
       </c>
@@ -17544,22 +17560,22 @@
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
+          <t>Core PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C754" t="inlineStr"/>
       <c r="D754" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="E754" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F754" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="755">
@@ -17570,14 +17586,18 @@
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/22</t>
+          <t>GDP Sales QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C755" t="inlineStr"/>
       <c r="D755" t="inlineStr"/>
-      <c r="E755" t="inlineStr"/>
+      <c r="E755" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="F755" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="756">
@@ -17588,18 +17608,14 @@
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ 2nd EstQ4</t>
+          <t>GDP Sales QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C756" t="inlineStr"/>
-      <c r="D756" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
+      <c r="D756" t="inlineStr"/>
       <c r="E756" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F756" t="n">
@@ -17614,12 +17630,20 @@
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirJAN</t>
+          <t>PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C757" t="inlineStr"/>
-      <c r="D757" t="inlineStr"/>
-      <c r="E757" t="inlineStr"/>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="E757" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
       <c r="F757" t="n">
         <v>3</v>
       </c>
@@ -17632,16 +17656,12 @@
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
+          <t>Continuing Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C758" t="inlineStr"/>
       <c r="D758" t="inlineStr"/>
-      <c r="E758" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="E758" t="inlineStr"/>
       <c r="F758" t="n">
         <v>3</v>
       </c>
@@ -17654,14 +17674,14 @@
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/15</t>
+          <t>Initial Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C759" t="inlineStr"/>
       <c r="D759" t="inlineStr"/>
       <c r="E759" t="inlineStr"/>
       <c r="F759" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="760">
@@ -17672,22 +17692,22 @@
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ 2nd EstQ4</t>
+          <t>GDP Price Index QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C760" t="inlineStr"/>
       <c r="D760" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="E760" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="F760" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="761">
@@ -17698,14 +17718,14 @@
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/22</t>
+          <t>Durable Goods Orders Ex Transp MoMJAN</t>
         </is>
       </c>
       <c r="C761" t="inlineStr"/>
       <c r="D761" t="inlineStr"/>
       <c r="E761" t="inlineStr"/>
       <c r="F761" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="762">
@@ -17716,16 +17736,12 @@
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ 2nd EstQ4</t>
+          <t>Non Defense Goods Orders Ex AirJAN</t>
         </is>
       </c>
       <c r="C762" t="inlineStr"/>
       <c r="D762" t="inlineStr"/>
-      <c r="E762" t="inlineStr">
-        <is>
-          <t>3.2%</t>
-        </is>
-      </c>
+      <c r="E762" t="inlineStr"/>
       <c r="F762" t="n">
         <v>3</v>
       </c>
@@ -17738,18 +17754,22 @@
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
+          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C763" t="inlineStr"/>
-      <c r="D763" t="inlineStr"/>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
       <c r="E763" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F763" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="764">
@@ -17760,7 +17780,7 @@
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/22</t>
+          <t>Durable Goods Orders ex Defense MoMJAN</t>
         </is>
       </c>
       <c r="C764" t="inlineStr"/>
@@ -17778,7 +17798,7 @@
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMJAN</t>
+          <t>Continuing Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C765" t="inlineStr"/>
@@ -17796,22 +17816,14 @@
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ 2nd EstQ4</t>
+          <t>Initial Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C766" t="inlineStr"/>
-      <c r="D766" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
-      <c r="E766" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+      <c r="D766" t="inlineStr"/>
+      <c r="E766" t="inlineStr"/>
       <c r="F766" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="767">
@@ -17822,22 +17834,18 @@
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ 2nd EstQ4</t>
+          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C767" t="inlineStr"/>
-      <c r="D767" t="inlineStr">
-        <is>
-          <t>2.2%</t>
-        </is>
-      </c>
+      <c r="D767" t="inlineStr"/>
       <c r="E767" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F767" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="768">
@@ -17848,14 +17856,14 @@
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMJAN</t>
+          <t>Durable Goods Orders ex Defense MoMJAN</t>
         </is>
       </c>
       <c r="C768" t="inlineStr"/>
       <c r="D768" t="inlineStr"/>
       <c r="E768" t="inlineStr"/>
       <c r="F768" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="769">
@@ -17866,12 +17874,20 @@
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirJAN</t>
+          <t>PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C769" t="inlineStr"/>
-      <c r="D769" t="inlineStr"/>
-      <c r="E769" t="inlineStr"/>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="E769" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
       <c r="F769" t="n">
         <v>3</v>
       </c>
@@ -17884,22 +17900,14 @@
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
+          <t>Jobless Claims 4-week AverageFEB/22</t>
         </is>
       </c>
       <c r="C770" t="inlineStr"/>
-      <c r="D770" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
-      <c r="E770" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
+      <c r="D770" t="inlineStr"/>
+      <c r="E770" t="inlineStr"/>
       <c r="F770" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="771">
@@ -17910,14 +17918,14 @@
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMJAN</t>
+          <t>Non Defense Goods Orders Ex AirJAN</t>
         </is>
       </c>
       <c r="C771" t="inlineStr"/>
       <c r="D771" t="inlineStr"/>
       <c r="E771" t="inlineStr"/>
       <c r="F771" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="772">
@@ -17928,20 +17936,12 @@
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ 2nd EstQ4</t>
+          <t>Jobless Claims 4-week AverageFEB/22</t>
         </is>
       </c>
       <c r="C772" t="inlineStr"/>
-      <c r="D772" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
-      <c r="E772" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+      <c r="D772" t="inlineStr"/>
+      <c r="E772" t="inlineStr"/>
       <c r="F772" t="n">
         <v>3</v>
       </c>
@@ -17954,14 +17954,14 @@
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMJAN</t>
+          <t>Durable Goods Orders MoMJAN</t>
         </is>
       </c>
       <c r="C773" t="inlineStr"/>
       <c r="D773" t="inlineStr"/>
       <c r="E773" t="inlineStr"/>
       <c r="F773" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="774">
@@ -17990,7 +17990,7 @@
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>Pending Home Sales MoMJAN</t>
+          <t>Pending Home Sales YoYJAN</t>
         </is>
       </c>
       <c r="C775" t="inlineStr"/>
@@ -18026,7 +18026,7 @@
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>Pending Home Sales YoYJAN</t>
+          <t>Pending Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C777" t="inlineStr"/>
@@ -18084,11 +18084,15 @@
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>EIA Natural Gas Stocks ChangeFEB/21</t>
+          <t>NY Fed Treasury Purchases 4 to 6 yrs</t>
         </is>
       </c>
       <c r="C780" t="inlineStr"/>
-      <c r="D780" t="inlineStr"/>
+      <c r="D780" t="inlineStr">
+        <is>
+          <t>$50 million</t>
+        </is>
+      </c>
       <c r="E780" t="inlineStr"/>
       <c r="F780" t="n">
         <v>3</v>
@@ -18102,15 +18106,11 @@
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>NY Fed Treasury Purchases 4 to 6 yrs</t>
+          <t>EIA Natural Gas Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C781" t="inlineStr"/>
-      <c r="D781" t="inlineStr">
-        <is>
-          <t>$50 million</t>
-        </is>
-      </c>
+      <c r="D781" t="inlineStr"/>
       <c r="E781" t="inlineStr"/>
       <c r="F781" t="n">
         <v>3</v>
@@ -18124,7 +18124,7 @@
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>Kansas Fed Composite IndexFEB</t>
+          <t>Kansas Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C782" t="inlineStr"/>
@@ -18142,7 +18142,7 @@
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>Kansas Fed Manufacturing IndexFEB</t>
+          <t>Kansas Fed Composite IndexFEB</t>
         </is>
       </c>
       <c r="C783" t="inlineStr"/>
@@ -18155,12 +18155,12 @@
     <row r="784">
       <c r="A784" t="inlineStr">
         <is>
-          <t>2025-02-27 11:30:00-05:00</t>
+          <t>2025-02-27 11:00:00-05:00</t>
         </is>
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>Kansas Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C784" t="inlineStr"/>
@@ -18173,12 +18173,12 @@
     <row r="785">
       <c r="A785" t="inlineStr">
         <is>
-          <t>2025-02-27 11:30:00-05:00</t>
+          <t>2025-02-27 11:00:00-05:00</t>
         </is>
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>Kansas Fed Composite IndexFEB</t>
         </is>
       </c>
       <c r="C785" t="inlineStr"/>
@@ -18188,6 +18188,114 @@
         <v>3</v>
       </c>
     </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>2025-02-27 11:30:00-05:00</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>4-Week Bill Auction</t>
+        </is>
+      </c>
+      <c r="C786" t="inlineStr"/>
+      <c r="D786" t="inlineStr"/>
+      <c r="E786" t="inlineStr"/>
+      <c r="F786" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>2025-02-27 11:30:00-05:00</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>8-Week Bill Auction</t>
+        </is>
+      </c>
+      <c r="C787" t="inlineStr"/>
+      <c r="D787" t="inlineStr"/>
+      <c r="E787" t="inlineStr"/>
+      <c r="F787" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>2025-02-27 11:30:00-05:00</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>4-Week Bill Auction</t>
+        </is>
+      </c>
+      <c r="C788" t="inlineStr"/>
+      <c r="D788" t="inlineStr"/>
+      <c r="E788" t="inlineStr"/>
+      <c r="F788" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>2025-02-27 11:30:00-05:00</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>8-Week Bill Auction</t>
+        </is>
+      </c>
+      <c r="C789" t="inlineStr"/>
+      <c r="D789" t="inlineStr"/>
+      <c r="E789" t="inlineStr"/>
+      <c r="F789" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>2025-02-27 12:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>15-Year Mortgage RateFEB/27</t>
+        </is>
+      </c>
+      <c r="C790" t="inlineStr"/>
+      <c r="D790" t="inlineStr"/>
+      <c r="E790" t="inlineStr"/>
+      <c r="F790" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>2025-02-27 12:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>30-Year Mortgage RateFEB/27</t>
+        </is>
+      </c>
+      <c r="C791" t="inlineStr"/>
+      <c r="D791" t="inlineStr"/>
+      <c r="E791" t="inlineStr"/>
+      <c r="F791" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-02-27.xlsx
+++ b/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-02-27.xlsx
@@ -720,18 +720,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.323M</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -742,12 +746,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.142M</t>
+          <t>0.099M</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -764,18 +768,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>7.717M</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0.7M</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -786,19 +794,15 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>6.406M</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>-0.1M</t>
-        </is>
-      </c>
+          <t>-0.416M</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
         <v>3</v>
@@ -812,12 +816,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.041M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -834,15 +838,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.416M</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>-0.1M</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
         <v>3</v>
@@ -856,22 +864,18 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -882,12 +886,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -904,22 +908,18 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.178M</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>-2.75M</t>
-        </is>
-      </c>
+          <t>0.041M</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -1582,18 +1582,22 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ImportsNOV</t>
+          <t>Balance of TradeNOV</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>$351.6B</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr"/>
+          <t>$-78.2B</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>$-78B</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>$334B</t>
+          <t>$-70B</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -1608,22 +1612,18 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Balance of TradeNOV</t>
+          <t>ExportsNOV</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>$-78.2B</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>$-78B</t>
-        </is>
-      </c>
+          <t>$273.4B</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>$-70B</t>
+          <t>$264B</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -1638,18 +1638,18 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ExportsNOV</t>
+          <t>ImportsNOV</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>$273.4B</t>
+          <t>$351.6B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>$264B</t>
+          <t>$334B</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Used Car Prices MoMDEC</t>
+          <t>Used Car Prices YoYDEC</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -2254,12 +2254,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Used Car Prices YoYDEC</t>
+          <t>Used Car Prices MoMDEC</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -3148,18 +3148,18 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelJAN</t>
+          <t>Michigan Current Conditions PrelJAN</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F112" t="n">
@@ -3174,26 +3174,22 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelJAN</t>
+          <t>Michigan Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>73.2</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>73.8</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="114">
@@ -3204,22 +3200,26 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
+          <t>Michigan Consumer Sentiment PrelJAN</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr"/>
+          <t>73.2</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>73.8</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115">
@@ -3230,18 +3230,18 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelJAN</t>
+          <t>Michigan Consumer Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F115" t="n">
@@ -3256,18 +3256,18 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelJAN</t>
+          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F116" t="n">
@@ -3458,12 +3458,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>4.180%</t>
+          <t>4.225%</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
@@ -3480,12 +3480,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>4.225%</t>
+          <t>4.180%</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
@@ -4010,26 +4010,26 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYDEC</t>
+          <t>CPIDEC</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>315.6</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="148">
@@ -4040,26 +4040,22 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYDEC</t>
+          <t>CPI s.aDEC</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+          <t>317.685</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>317.4</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="149">
@@ -4070,26 +4066,26 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexJAN</t>
+          <t>Core Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>-12.60</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150">
@@ -4100,22 +4096,22 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMDEC</t>
+          <t>Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F150" t="n">
@@ -4130,22 +4126,22 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMDEC</t>
+          <t>Core Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F151" t="n">
@@ -4160,22 +4156,26 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>CPI s.aDEC</t>
+          <t>Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>317.685</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr"/>
+          <t>2.9%</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>2.9%</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>317.4</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153">
@@ -4186,22 +4186,22 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>CPIDEC</t>
+          <t>NY Empire State Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>-12.60</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>315.6</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="F153" t="n">
@@ -4252,18 +4252,22 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>0.397M</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr"/>
+          <t>-1.961M</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>-1.6M</t>
+        </is>
+      </c>
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="157">
@@ -4274,22 +4278,18 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>2.60M</t>
-        </is>
-      </c>
+          <t>-1.304M</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="158">
@@ -4300,12 +4300,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>0.765M</t>
+          <t>0.646M</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>-0.021M</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
@@ -4344,15 +4344,19 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>-0.021M</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr"/>
+          <t>3.077M</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>1.1M</t>
+        </is>
+      </c>
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="n">
         <v>3</v>
@@ -4366,19 +4370,15 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>3.077M</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>1.1M</t>
-        </is>
-      </c>
+          <t>0.765M</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="n">
         <v>3</v>
@@ -4392,18 +4392,22 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>0.646M</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>2.60M</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="163">
@@ -4414,12 +4418,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>-1.304M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
@@ -4436,22 +4440,18 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>-1.961M</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>-1.6M</t>
-        </is>
-      </c>
+          <t>-0.255M</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="165">
@@ -4556,16 +4556,24 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>11.9</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr"/>
-      <c r="E170" t="inlineStr"/>
+          <t>1859K</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>1870.0K</t>
+        </is>
+      </c>
       <c r="F170" t="n">
         <v>3</v>
       </c>
@@ -4578,26 +4586,18 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
+          <t>46.3</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr"/>
       <c r="F171" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="172">
@@ -4608,22 +4608,22 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>217K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>210K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F172" t="n">
@@ -4638,18 +4638,22 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>1.8%</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="F173" t="n">
@@ -4664,26 +4668,26 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="175">
@@ -4694,22 +4698,22 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F175" t="n">
@@ -4724,24 +4728,16 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>1.6%</t>
-        </is>
-      </c>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr"/>
       <c r="F176" t="n">
         <v>3</v>
       </c>
@@ -4754,20 +4750,16 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>39.00</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>4.0%</t>
-        </is>
-      </c>
+      <c r="E177" t="inlineStr"/>
       <c r="F177" t="n">
         <v>3</v>
       </c>
@@ -4780,20 +4772,16 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>212.75K</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="D178" t="inlineStr"/>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>215.0K</t>
-        </is>
-      </c>
+      <c r="E178" t="inlineStr"/>
       <c r="F178" t="n">
         <v>3</v>
       </c>
@@ -4806,18 +4794,26 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr"/>
-      <c r="E179" t="inlineStr"/>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>-10</t>
+        </is>
+      </c>
       <c r="F179" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="180">
@@ -4828,16 +4824,20 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
-      <c r="E180" t="inlineStr"/>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>4.0%</t>
+        </is>
+      </c>
       <c r="F180" t="n">
         <v>3</v>
       </c>
@@ -4850,16 +4850,20 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>212.75K</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
-      <c r="E181" t="inlineStr"/>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>215.0K</t>
+        </is>
+      </c>
       <c r="F181" t="n">
         <v>3</v>
       </c>
@@ -4872,22 +4876,22 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F182" t="n">
@@ -4902,26 +4906,22 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>1.8%</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="184">
@@ -4932,18 +4932,26 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>39.00</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr"/>
-      <c r="E184" t="inlineStr"/>
+          <t>217K</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>210K</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>209.0K</t>
+        </is>
+      </c>
       <c r="F184" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="185">
@@ -4954,26 +4962,26 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="186">
@@ -4984,26 +4992,18 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr"/>
       <c r="F186" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="187">
@@ -5014,17 +5014,17 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Business Inventories MoMNOV</t>
+          <t>Retail Inventories Ex Autos MoMNOV</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -5033,7 +5033,7 @@
         </is>
       </c>
       <c r="F187" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="188">
@@ -5044,26 +5044,26 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoMNOV</t>
+          <t>NAHB Housing Market IndexJAN</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F188" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="189">
@@ -5074,22 +5074,22 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>NAHB Housing Market IndexJAN</t>
+          <t>Business Inventories MoMNOV</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F189" t="n">
@@ -5240,18 +5240,18 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelDEC</t>
+          <t>Housing Starts MoMDEC</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>15.8%</t>
         </is>
       </c>
       <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="F196" t="n">
@@ -5266,26 +5266,22 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Housing StartsDEC</t>
+          <t>Building Permits MoM PrelDEC</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>1.499M</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>1.32M</t>
-        </is>
-      </c>
+          <t>-0.7%</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr">
         <is>
-          <t>1.32M</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="F197" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="198">
@@ -5296,22 +5292,26 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Housing Starts MoMDEC</t>
+          <t>Housing StartsDEC</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>15.8%</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr"/>
+          <t>1.499M</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>1.32M</t>
+        </is>
+      </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>1.32M</t>
         </is>
       </c>
       <c r="F198" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="199">
@@ -5352,18 +5352,18 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Industrial Production YoYDEC</t>
+          <t>Manufacturing Production YoYDEC</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F200" t="n">
@@ -5378,22 +5378,22 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMDEC</t>
+          <t>Capacity UtilizationDEC</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="F201" t="n">
@@ -5408,26 +5408,26 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Industrial Production MoMDEC</t>
+          <t>Manufacturing Production MoMDEC</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F202" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="203">
@@ -5438,26 +5438,26 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Capacity UtilizationDEC</t>
+          <t>Industrial Production MoMDEC</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F203" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="204">
@@ -5468,18 +5468,18 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYDEC</t>
+          <t>Industrial Production YoYDEC</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D204" t="inlineStr"/>
       <c r="E204" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F204" t="n">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>42-Day Bill Auction</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>4.025%</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
@@ -5692,12 +5692,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>42-Day Bill Auction</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>4.025%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
@@ -5942,26 +5942,26 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/18</t>
+          <t>Continuing Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>1899K</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>220K</t>
+          <t>1860K</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>1861K</t>
         </is>
       </c>
       <c r="F225" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="226">
@@ -5972,22 +5972,18 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/11</t>
+          <t>Jobless Claims 4-week AverageJAN/18</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>1899K</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr">
-        <is>
-          <t>1860K</t>
-        </is>
-      </c>
+          <t>213.5K</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr"/>
       <c r="E226" t="inlineStr">
         <is>
-          <t>1861K</t>
+          <t>213.0K</t>
         </is>
       </c>
       <c r="F226" t="n">
@@ -6002,22 +5998,26 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/18</t>
+          <t>Initial Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>213.5K</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr"/>
+          <t>223K</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>220K</t>
+        </is>
+      </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>213.0K</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="F227" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="228">
@@ -6150,22 +6150,18 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>-0.148M</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr"/>
       <c r="E233" t="inlineStr"/>
       <c r="F233" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="234">
@@ -6176,18 +6172,22 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>6.96%</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="235">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D235" t="inlineStr"/>
@@ -6220,15 +6220,19 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>-1.125M</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="E236" t="inlineStr"/>
       <c r="F236" t="n">
         <v>3</v>
@@ -6242,12 +6246,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
@@ -6264,12 +6268,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -6286,12 +6290,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
@@ -6308,12 +6312,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
@@ -6330,19 +6334,15 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>6.96%</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr"/>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="n">
         <v>3</v>
@@ -6356,18 +6356,22 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>0.184M</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="243">
@@ -6378,22 +6382,18 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>0.068M</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr"/>
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="244">
@@ -6448,22 +6448,22 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashJAN</t>
+          <t>S&amp;P Global Manufacturing PMI FlashJAN</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="F246" t="n">
@@ -6478,22 +6478,22 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashJAN</t>
+          <t>S&amp;P Global Services PMI FlashJAN</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="F247" t="n">
@@ -6534,26 +6534,26 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F249" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="250">
@@ -6564,22 +6564,26 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr"/>
+          <t>69.3</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>70.2</t>
+        </is>
+      </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F250" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="251">
@@ -6590,26 +6594,26 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>4.24M</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.19M</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="F251" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="252">
@@ -6650,26 +6654,26 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>4.24M</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>4.19M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F253" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="254">
@@ -6680,26 +6684,22 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="D254" t="inlineStr">
-        <is>
-          <t>77.9</t>
-        </is>
-      </c>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr"/>
       <c r="E254" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F254" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="255">
@@ -6710,26 +6710,26 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F255" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="256">
@@ -7178,18 +7178,18 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
+          <t>House Price IndexNOV</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>433.4</t>
         </is>
       </c>
       <c r="D273" t="inlineStr"/>
       <c r="E273" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>433</t>
         </is>
       </c>
       <c r="F273" t="n">
@@ -7204,22 +7204,18 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>House Price Index MoMNOV</t>
+          <t>House Price Index YoYNOV</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr"/>
       <c r="E274" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F274" t="n">
@@ -7234,22 +7230,26 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>House Price Index YoYNOV</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYNOV</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="D275" t="inlineStr"/>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>4.3%</t>
+        </is>
+      </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F275" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="276">
@@ -7260,18 +7260,18 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>House Price IndexNOV</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>433.4</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="D276" t="inlineStr"/>
       <c r="E276" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F276" t="n">
@@ -7286,26 +7286,26 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYNOV</t>
+          <t>House Price Index MoMNOV</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F277" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="278">
@@ -7790,19 +7790,15 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>-4.994M</t>
-        </is>
-      </c>
-      <c r="D297" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.532M</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr"/>
       <c r="E297" t="inlineStr"/>
       <c r="F297" t="n">
         <v>3</v>
@@ -7816,12 +7812,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>-0.333M</t>
+          <t>0.128M</t>
         </is>
       </c>
       <c r="D298" t="inlineStr"/>
@@ -7838,22 +7834,18 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>2.957M</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>0.326M</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr"/>
       <c r="E299" t="inlineStr"/>
       <c r="F299" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="300">
@@ -7864,18 +7856,22 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>0.028M</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr"/>
+          <t>3.463M</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>3.2M</t>
+        </is>
+      </c>
       <c r="E300" t="inlineStr"/>
       <c r="F300" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="301">
@@ -7908,22 +7904,18 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>3.463M</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr">
-        <is>
-          <t>3.2M</t>
-        </is>
-      </c>
+          <t>0.028M</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr"/>
       <c r="E302" t="inlineStr"/>
       <c r="F302" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="303">
@@ -7934,18 +7926,22 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>0.326M</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr"/>
+          <t>2.957M</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E303" t="inlineStr"/>
       <c r="F303" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="304">
@@ -7956,12 +7952,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>0.128M</t>
+          <t>-0.333M</t>
         </is>
       </c>
       <c r="D304" t="inlineStr"/>
@@ -7978,15 +7974,19 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>0.532M</t>
-        </is>
-      </c>
-      <c r="D305" t="inlineStr"/>
+          <t>-4.994M</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E305" t="inlineStr"/>
       <c r="F305" t="n">
         <v>3</v>
@@ -8070,18 +8070,22 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ AdvQ4</t>
+          <t>Core PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="D309" t="inlineStr"/>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F309" t="n">
@@ -8096,22 +8100,26 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ AdvQ4</t>
+          <t>GDP Price Index QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D310" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F310" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="311">
@@ -8122,18 +8130,22 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ AdvQ4</t>
+          <t>Continuing Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>2.3%</t>
-        </is>
-      </c>
-      <c r="D311" t="inlineStr"/>
+          <t>1858K</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>1890K</t>
+        </is>
+      </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>1885.0K</t>
         </is>
       </c>
       <c r="F311" t="n">
@@ -8148,26 +8160,22 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/25</t>
+          <t>Jobless Claims 4-week AverageJAN/25</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>207K</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+          <t>212.5K</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr"/>
       <c r="E312" t="inlineStr">
         <is>
-          <t>228.0K</t>
+          <t>214.0K</t>
         </is>
       </c>
       <c r="F312" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="313">
@@ -8178,22 +8186,26 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/25</t>
+          <t>GDP Growth Rate QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>212.5K</t>
-        </is>
-      </c>
-      <c r="D313" t="inlineStr"/>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>214.0K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F313" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="314">
@@ -8204,22 +8216,18 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/18</t>
+          <t>PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>1858K</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr">
-        <is>
-          <t>1890K</t>
-        </is>
-      </c>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr"/>
       <c r="E314" t="inlineStr">
         <is>
-          <t>1885.0K</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="F314" t="n">
@@ -8234,26 +8242,22 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ AdvQ4</t>
+          <t>GDP Sales QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr"/>
       <c r="E315" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F315" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="316">
@@ -8264,26 +8268,26 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ AdvQ4</t>
+          <t>Initial Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>207K</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>228.0K</t>
         </is>
       </c>
       <c r="F316" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="317">
@@ -8294,22 +8298,18 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ AdvQ4</t>
+          <t>Real Consumer Spending QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>2.5%</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr"/>
       <c r="E317" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F317" t="n">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D321" t="inlineStr"/>
@@ -8428,12 +8428,12 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="D322" t="inlineStr"/>
@@ -8516,22 +8516,26 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
+          <t>Core PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="D326" t="inlineStr"/>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F326" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="327">
@@ -8542,24 +8546,12 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
-        </is>
-      </c>
-      <c r="C327" t="inlineStr">
-        <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D327" t="inlineStr">
-        <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="E327" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr"/>
+      <c r="D327" t="inlineStr"/>
+      <c r="E327" t="inlineStr"/>
       <c r="F327" t="n">
         <v>2</v>
       </c>
@@ -8572,18 +8564,22 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr"/>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F328" t="n">
@@ -8598,26 +8594,26 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F329" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="330">
@@ -8628,22 +8624,22 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F330" t="n">
@@ -8658,26 +8654,22 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
+          <t>Employment Cost - Benefits QoQQ4</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D331" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr"/>
       <c r="E331" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F331" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="332">
@@ -8688,26 +8680,26 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F332" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="333">
@@ -8718,22 +8710,18 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
+          <t>Employment Cost - Wages QoQQ4</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr"/>
       <c r="E333" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F333" t="n">
@@ -8748,22 +8736,22 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F334" t="n">
@@ -8778,14 +8766,26 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C335" t="inlineStr"/>
-      <c r="D335" t="inlineStr"/>
-      <c r="E335" t="inlineStr"/>
+          <t>Personal Income MoMDEC</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F335" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="336">
@@ -8904,18 +8904,22 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersJAN</t>
+          <t>ISM Manufacturing PricesJAN</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>55.1</t>
-        </is>
-      </c>
-      <c r="D340" t="inlineStr"/>
+          <t>54.9</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>52.6</t>
+        </is>
+      </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F340" t="n">
@@ -8930,22 +8934,26 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentJAN</t>
+          <t>Construction Spending MoMDEC</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>50.3</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F341" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="342">
@@ -8956,26 +8964,22 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIJAN</t>
+          <t>ISM Manufacturing New OrdersJAN</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>50.9</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr">
-        <is>
-          <t>49.8</t>
-        </is>
-      </c>
+          <t>55.1</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr"/>
       <c r="E342" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F342" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="343">
@@ -8986,26 +8990,22 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Construction Spending MoMDEC</t>
+          <t>ISM Manufacturing EmploymentJAN</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>50.3</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr"/>
       <c r="E343" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F343" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="344">
@@ -9016,26 +9016,26 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesJAN</t>
+          <t>ISM Manufacturing PMIJAN</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="F344" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="345">
@@ -9708,22 +9708,22 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FinalJAN</t>
+          <t>S&amp;P Global Composite PMI FinalJAN</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="F374" t="n">
@@ -9738,22 +9738,22 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FinalJAN</t>
+          <t>S&amp;P Global Services PMI FinalJAN</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F375" t="n">
@@ -9902,18 +9902,22 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>0.373M</t>
-        </is>
-      </c>
-      <c r="D381" t="inlineStr"/>
+          <t>2.233M</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>1.2M</t>
+        </is>
+      </c>
       <c r="E381" t="inlineStr"/>
       <c r="F381" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="382">
@@ -9924,18 +9928,22 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>-0.186M</t>
-        </is>
-      </c>
-      <c r="D382" t="inlineStr"/>
+          <t>8.664M</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>2.6M</t>
+        </is>
+      </c>
       <c r="E382" t="inlineStr"/>
       <c r="F382" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="383">
@@ -9946,12 +9954,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Crude Oil Imports ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>-0.027M</t>
+          <t>-0.178M</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
@@ -9968,15 +9976,19 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>-0.034M</t>
-        </is>
-      </c>
-      <c r="D384" t="inlineStr"/>
+          <t>-5.471M</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>-1.5M</t>
+        </is>
+      </c>
       <c r="E384" t="inlineStr"/>
       <c r="F384" t="n">
         <v>3</v>
@@ -9990,19 +10002,15 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>-5.471M</t>
-        </is>
-      </c>
-      <c r="D385" t="inlineStr">
-        <is>
-          <t>-1.5M</t>
-        </is>
-      </c>
+          <t>0.16M</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr"/>
       <c r="E385" t="inlineStr"/>
       <c r="F385" t="n">
         <v>3</v>
@@ -10016,12 +10024,12 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>-0.178M</t>
+          <t>-0.027M</t>
         </is>
       </c>
       <c r="D386" t="inlineStr"/>
@@ -10038,12 +10046,12 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>0.16M</t>
+          <t>-0.186M</t>
         </is>
       </c>
       <c r="D387" t="inlineStr"/>
@@ -10060,22 +10068,18 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>8.664M</t>
-        </is>
-      </c>
-      <c r="D388" t="inlineStr">
-        <is>
-          <t>2.6M</t>
-        </is>
-      </c>
+          <t>0.373M</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr"/>
       <c r="E388" t="inlineStr"/>
       <c r="F388" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="389">
@@ -10086,22 +10090,18 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>2.233M</t>
-        </is>
-      </c>
-      <c r="D389" t="inlineStr">
-        <is>
-          <t>1.2M</t>
-        </is>
-      </c>
+          <t>-0.034M</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr"/>
       <c r="E389" t="inlineStr"/>
       <c r="F389" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="390">
@@ -10196,22 +10196,22 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/01</t>
+          <t>Unit Labour Costs QoQ PrelQ4</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>213K</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F394" t="n">
@@ -10226,22 +10226,26 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/01</t>
+          <t>Initial Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>216.75K</t>
-        </is>
-      </c>
-      <c r="D395" t="inlineStr"/>
+          <t>219K</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>213K</t>
+        </is>
+      </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>215.5K</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F395" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="396">
@@ -10252,26 +10256,22 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Nonfarm Productivity QoQ PrelQ4</t>
+          <t>Jobless Claims 4-week AverageFEB/01</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>1.2%</t>
-        </is>
-      </c>
-      <c r="D396" t="inlineStr">
-        <is>
-          <t>1.4%</t>
-        </is>
-      </c>
+          <t>216.75K</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr"/>
       <c r="E396" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>215.5K</t>
         </is>
       </c>
       <c r="F396" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="397">
@@ -10282,22 +10282,22 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Unit Labour Costs QoQ PrelQ4</t>
+          <t>Nonfarm Productivity QoQ PrelQ4</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F397" t="n">
@@ -10390,12 +10390,12 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D401" t="inlineStr"/>
@@ -10412,12 +10412,12 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="D402" t="inlineStr"/>
@@ -10536,22 +10536,26 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Participation RateJAN</t>
+          <t>Average Weekly HoursJAN</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>62.6%</t>
-        </is>
-      </c>
-      <c r="D408" t="inlineStr"/>
+          <t>34.1</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F408" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="409">
@@ -10562,18 +10566,18 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Government PayrollsJAN</t>
+          <t>U-6 Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>32K</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="D409" t="inlineStr"/>
       <c r="E409" t="inlineStr">
         <is>
-          <t>25K</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="F409" t="n">
@@ -10588,26 +10592,26 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoYJAN</t>
+          <t>Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
           <t>4.1%</t>
         </is>
       </c>
-      <c r="D410" t="inlineStr">
-        <is>
-          <t>3.8%</t>
-        </is>
-      </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F410" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="411">
@@ -10618,26 +10622,26 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsJAN</t>
+          <t>Manufacturing PayrollsJAN</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>143K</t>
+          <t>3K</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>170K</t>
+          <t>-2K</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>205K</t>
+          <t>-5K</t>
         </is>
       </c>
       <c r="F411" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="412">
@@ -10648,26 +10652,26 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateJAN</t>
+          <t>Average Hourly Earnings MoMJAN</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>111K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>141K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>180K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F412" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="413">
@@ -10678,26 +10682,26 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMJAN</t>
+          <t>Nonfarm Payrolls PrivateJAN</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>111K</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>141K</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>180K</t>
         </is>
       </c>
       <c r="F413" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="414">
@@ -10708,26 +10712,26 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsJAN</t>
+          <t>Non Farm PayrollsJAN</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>3K</t>
+          <t>143K</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>-2K</t>
+          <t>170K</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>-5K</t>
+          <t>205K</t>
         </is>
       </c>
       <c r="F414" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="415">
@@ -10738,26 +10742,26 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Unemployment RateJAN</t>
+          <t>Average Hourly Earnings YoYJAN</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="F415" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="416">
@@ -10768,18 +10772,18 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>U-6 Unemployment RateJAN</t>
+          <t>Government PayrollsJAN</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>32K</t>
         </is>
       </c>
       <c r="D416" t="inlineStr"/>
       <c r="E416" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>25K</t>
         </is>
       </c>
       <c r="F416" t="n">
@@ -10794,26 +10798,22 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Average Weekly HoursJAN</t>
+          <t>Participation RateJAN</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>34.1</t>
-        </is>
-      </c>
-      <c r="D417" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
+          <t>62.6%</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr"/>
       <c r="E417" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="F417" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="418">
@@ -10904,18 +10904,22 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelFEB</t>
+          <t>Michigan Current Conditions PrelFEB</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D422" t="inlineStr"/>
+          <t>68.7</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="F422" t="n">
@@ -10930,22 +10934,26 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelFEB</t>
+          <t>Michigan Consumer Sentiment PrelFEB</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="D423" t="inlineStr"/>
+          <t>67.8</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>71.1</t>
+        </is>
+      </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F423" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="424">
@@ -10956,22 +10964,22 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelFEB</t>
+          <t>Wholesale Inventories MoMDEC</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F424" t="n">
@@ -10986,22 +10994,18 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoMDEC</t>
+          <t>Michigan Inflation Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
-      <c r="D425" t="inlineStr">
-        <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr"/>
       <c r="E425" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F425" t="n">
@@ -11016,26 +11020,22 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelFEB</t>
+          <t>Michigan 5 Year Inflation Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>67.8</t>
-        </is>
-      </c>
-      <c r="D426" t="inlineStr">
-        <is>
-          <t>71.1</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr"/>
       <c r="E426" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F426" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="427">
@@ -11046,22 +11046,22 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelFEB</t>
+          <t>Michigan Consumer Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="F427" t="n">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>4.225%</t>
+          <t>4.185%</t>
         </is>
       </c>
       <c r="D434" t="inlineStr"/>
@@ -11234,12 +11234,12 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>4.185%</t>
+          <t>4.225%</t>
         </is>
       </c>
       <c r="D435" t="inlineStr"/>
@@ -11474,7 +11474,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/07</t>
+          <t>MBA Mortgage ApplicationsFEB/07</t>
         </is>
       </c>
       <c r="C447" t="inlineStr"/>
@@ -11492,7 +11492,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/07</t>
+          <t>MBA Mortgage Market IndexFEB/07</t>
         </is>
       </c>
       <c r="C448" t="inlineStr"/>
@@ -11510,14 +11510,14 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/07</t>
+          <t>MBA 30-Year Mortgage RateFEB/07</t>
         </is>
       </c>
       <c r="C449" t="inlineStr"/>
       <c r="D449" t="inlineStr"/>
       <c r="E449" t="inlineStr"/>
       <c r="F449" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="450">
@@ -11528,7 +11528,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/07</t>
+          <t>MBA Mortgage Refinance IndexFEB/07</t>
         </is>
       </c>
       <c r="C450" t="inlineStr"/>
@@ -11546,14 +11546,14 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/07</t>
+          <t>MBA Purchase IndexFEB/07</t>
         </is>
       </c>
       <c r="C451" t="inlineStr"/>
       <c r="D451" t="inlineStr"/>
       <c r="E451" t="inlineStr"/>
       <c r="F451" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="452">
@@ -11716,14 +11716,14 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C458" t="inlineStr"/>
       <c r="D458" t="inlineStr"/>
       <c r="E458" t="inlineStr"/>
       <c r="F458" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="459">
@@ -11734,14 +11734,14 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C459" t="inlineStr"/>
       <c r="D459" t="inlineStr"/>
       <c r="E459" t="inlineStr"/>
       <c r="F459" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="460">
@@ -11752,7 +11752,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C460" t="inlineStr"/>
@@ -11770,7 +11770,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C461" t="inlineStr"/>
@@ -11788,7 +11788,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C462" t="inlineStr"/>
@@ -11806,7 +11806,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C463" t="inlineStr"/>
@@ -11824,14 +11824,14 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C464" t="inlineStr"/>
       <c r="D464" t="inlineStr"/>
       <c r="E464" t="inlineStr"/>
       <c r="F464" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="465">
@@ -11842,14 +11842,14 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C465" t="inlineStr"/>
       <c r="D465" t="inlineStr"/>
       <c r="E465" t="inlineStr"/>
       <c r="F465" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="466">
@@ -11860,7 +11860,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C466" t="inlineStr"/>
@@ -11976,14 +11976,18 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C472" t="inlineStr"/>
-      <c r="D472" t="inlineStr"/>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F472" t="n">
@@ -11998,22 +12002,18 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C473" t="inlineStr"/>
-      <c r="D473" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D473" t="inlineStr"/>
       <c r="E473" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="F473" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="474">
@@ -12024,18 +12024,14 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C474" t="inlineStr"/>
-      <c r="D474" t="inlineStr">
-        <is>
-          <t>3.2%</t>
-        </is>
-      </c>
+      <c r="D474" t="inlineStr"/>
       <c r="E474" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="F474" t="n">
@@ -12050,22 +12046,18 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C475" t="inlineStr"/>
-      <c r="D475" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D475" t="inlineStr"/>
       <c r="E475" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F475" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="476">
@@ -12076,18 +12068,22 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C476" t="inlineStr"/>
-      <c r="D476" t="inlineStr"/>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F476" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="477">
@@ -12098,22 +12094,22 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C477" t="inlineStr"/>
       <c r="D477" t="inlineStr">
         <is>
-          <t>216K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F477" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="478">
@@ -12124,14 +12120,18 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C478" t="inlineStr"/>
-      <c r="D478" t="inlineStr"/>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F478" t="n">
@@ -12146,18 +12146,22 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C479" t="inlineStr"/>
-      <c r="D479" t="inlineStr"/>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F479" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="480">
@@ -12168,14 +12172,14 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C480" t="inlineStr"/>
       <c r="D480" t="inlineStr"/>
       <c r="E480" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="F480" t="n">
@@ -12190,18 +12194,14 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C481" t="inlineStr"/>
-      <c r="D481" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+      <c r="D481" t="inlineStr"/>
       <c r="E481" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F481" t="n">
@@ -12574,22 +12574,22 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Manufacturing Production MoMJAN</t>
         </is>
       </c>
       <c r="C499" t="inlineStr"/>
       <c r="D499" t="inlineStr">
         <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
           <t>0.2%</t>
         </is>
       </c>
-      <c r="E499" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
       <c r="F499" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="500">
@@ -12600,14 +12600,18 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="C500" t="inlineStr"/>
-      <c r="D500" t="inlineStr"/>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>77.7%</t>
+        </is>
+      </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="F500" t="n">
@@ -12622,18 +12626,22 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="C501" t="inlineStr"/>
-      <c r="D501" t="inlineStr"/>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F501" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="502">
@@ -12644,18 +12652,14 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="C502" t="inlineStr"/>
-      <c r="D502" t="inlineStr">
-        <is>
-          <t>77.7%</t>
-        </is>
-      </c>
+      <c r="D502" t="inlineStr"/>
       <c r="E502" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F502" t="n">
@@ -12670,18 +12674,14 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="C503" t="inlineStr"/>
-      <c r="D503" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+      <c r="D503" t="inlineStr"/>
       <c r="E503" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F503" t="n">
@@ -13158,14 +13158,14 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C527" t="inlineStr"/>
       <c r="D527" t="inlineStr"/>
       <c r="E527" t="inlineStr"/>
       <c r="F527" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="528">
@@ -13212,14 +13212,14 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="C530" t="inlineStr"/>
       <c r="D530" t="inlineStr"/>
       <c r="E530" t="inlineStr"/>
       <c r="F530" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="531">
@@ -13364,7 +13364,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C538" t="inlineStr"/>
@@ -13382,7 +13382,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C539" t="inlineStr"/>
@@ -13418,14 +13418,14 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C541" t="inlineStr"/>
       <c r="D541" t="inlineStr"/>
       <c r="E541" t="inlineStr"/>
       <c r="F541" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="542">
@@ -13436,14 +13436,14 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C542" t="inlineStr"/>
       <c r="D542" t="inlineStr"/>
       <c r="E542" t="inlineStr"/>
       <c r="F542" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="543">
@@ -13578,14 +13578,14 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C549" t="inlineStr"/>
       <c r="D549" t="inlineStr"/>
       <c r="E549" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F549" t="n">
@@ -13622,18 +13622,22 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C551" t="inlineStr"/>
-      <c r="D551" t="inlineStr"/>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>1.4M</t>
+        </is>
+      </c>
       <c r="E551" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F551" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="552">
@@ -13670,22 +13674,18 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C553" t="inlineStr"/>
-      <c r="D553" t="inlineStr">
-        <is>
-          <t>1.4M</t>
-        </is>
-      </c>
+      <c r="D553" t="inlineStr"/>
       <c r="E553" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F553" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="554">
@@ -14004,18 +14004,18 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C570" t="inlineStr"/>
       <c r="D570" t="inlineStr">
         <is>
-          <t>16.3</t>
+          <t>215K</t>
         </is>
       </c>
       <c r="E570" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="F570" t="n">
@@ -14030,22 +14030,14 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C571" t="inlineStr"/>
-      <c r="D571" t="inlineStr">
-        <is>
-          <t>215K</t>
-        </is>
-      </c>
-      <c r="E571" t="inlineStr">
-        <is>
-          <t>220.0K</t>
-        </is>
-      </c>
+      <c r="D571" t="inlineStr"/>
+      <c r="E571" t="inlineStr"/>
       <c r="F571" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="572">
@@ -14110,16 +14102,12 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C575" t="inlineStr"/>
       <c r="D575" t="inlineStr"/>
-      <c r="E575" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="E575" t="inlineStr"/>
       <c r="F575" t="n">
         <v>3</v>
       </c>
@@ -14132,18 +14120,14 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C576" t="inlineStr"/>
-      <c r="D576" t="inlineStr">
-        <is>
-          <t>1860K</t>
-        </is>
-      </c>
+      <c r="D576" t="inlineStr"/>
       <c r="E576" t="inlineStr">
         <is>
-          <t>1879.0K</t>
+          <t>219.0K</t>
         </is>
       </c>
       <c r="F576" t="n">
@@ -14158,14 +14142,22 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C577" t="inlineStr"/>
-      <c r="D577" t="inlineStr"/>
-      <c r="E577" t="inlineStr"/>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>16.3</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="F577" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="578">
@@ -14176,12 +14168,20 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C578" t="inlineStr"/>
-      <c r="D578" t="inlineStr"/>
-      <c r="E578" t="inlineStr"/>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>1860K</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="F578" t="n">
         <v>3</v>
       </c>
@@ -14572,14 +14572,14 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>Fed Musalem Speech</t>
         </is>
       </c>
       <c r="C598" t="inlineStr"/>
       <c r="D598" t="inlineStr"/>
       <c r="E598" t="inlineStr"/>
       <c r="F598" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="599">
@@ -14590,14 +14590,14 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C599" t="inlineStr"/>
       <c r="D599" t="inlineStr"/>
       <c r="E599" t="inlineStr"/>
       <c r="F599" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="600">
@@ -14608,7 +14608,7 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C600" t="inlineStr"/>
@@ -14788,7 +14788,7 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C610" t="inlineStr"/>
@@ -14806,14 +14806,14 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C611" t="inlineStr"/>
       <c r="D611" t="inlineStr"/>
       <c r="E611" t="inlineStr"/>
       <c r="F611" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="612">
@@ -14842,14 +14842,14 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C613" t="inlineStr"/>
       <c r="D613" t="inlineStr"/>
       <c r="E613" t="inlineStr"/>
       <c r="F613" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="614">
@@ -14860,7 +14860,7 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C614" t="inlineStr"/>
@@ -14878,7 +14878,7 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C615" t="inlineStr"/>
@@ -14896,7 +14896,7 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C616" t="inlineStr"/>
@@ -14914,14 +14914,14 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>Fed Musalem Speech</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C617" t="inlineStr"/>
       <c r="D617" t="inlineStr"/>
       <c r="E617" t="inlineStr"/>
       <c r="F617" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="618">
@@ -14932,14 +14932,14 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C618" t="inlineStr"/>
       <c r="D618" t="inlineStr"/>
       <c r="E618" t="inlineStr"/>
       <c r="F618" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="619">
@@ -14950,7 +14950,7 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C619" t="inlineStr"/>
@@ -15370,18 +15370,18 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C639" t="inlineStr"/>
       <c r="D639" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F639" t="n">
@@ -15396,18 +15396,18 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C640" t="inlineStr"/>
       <c r="D640" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="E640" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F640" t="n">
@@ -15422,18 +15422,18 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C641" t="inlineStr"/>
       <c r="D641" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="E641" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F641" t="n">
@@ -15448,18 +15448,18 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C642" t="inlineStr"/>
       <c r="D642" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E642" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F642" t="n">
@@ -15706,7 +15706,7 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/21</t>
+          <t>Baker Hughes Oil Rig CountFEB/21</t>
         </is>
       </c>
       <c r="C653" t="inlineStr"/>
@@ -15724,7 +15724,7 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/21</t>
+          <t>Baker Hughes Total Rigs CountFEB/21</t>
         </is>
       </c>
       <c r="C654" t="inlineStr"/>
@@ -15832,7 +15832,7 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C660" t="inlineStr"/>
@@ -15850,7 +15850,7 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C661" t="inlineStr"/>
@@ -16016,14 +16016,18 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C670" t="inlineStr"/>
       <c r="D670" t="inlineStr"/>
-      <c r="E670" t="inlineStr"/>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="F670" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="671">
@@ -16034,7 +16038,7 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C671" t="inlineStr"/>
@@ -16052,18 +16056,14 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C672" t="inlineStr"/>
       <c r="D672" t="inlineStr"/>
-      <c r="E672" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="E672" t="inlineStr"/>
       <c r="F672" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="673">
@@ -16074,7 +16074,7 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C673" t="inlineStr"/>
@@ -16146,7 +16146,7 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C677" t="inlineStr"/>
@@ -16164,7 +16164,7 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
       <c r="C678" t="inlineStr"/>
@@ -16200,14 +16200,14 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C680" t="inlineStr"/>
       <c r="D680" t="inlineStr"/>
       <c r="E680" t="inlineStr"/>
       <c r="F680" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="681">
@@ -16254,14 +16254,14 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C683" t="inlineStr"/>
       <c r="D683" t="inlineStr"/>
       <c r="E683" t="inlineStr"/>
       <c r="F683" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="684">
@@ -16290,7 +16290,7 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C685" t="inlineStr"/>
@@ -16416,7 +16416,7 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>Money SupplyJAN</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C692" t="inlineStr"/>
@@ -16434,7 +16434,7 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>Money SupplyJAN</t>
         </is>
       </c>
       <c r="C693" t="inlineStr"/>
@@ -16488,7 +16488,7 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/21</t>
+          <t>MBA Mortgage Refinance IndexFEB/21</t>
         </is>
       </c>
       <c r="C696" t="inlineStr"/>
@@ -16524,7 +16524,7 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/21</t>
+          <t>MBA Purchase IndexFEB/21</t>
         </is>
       </c>
       <c r="C698" t="inlineStr"/>
@@ -16542,7 +16542,7 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/21</t>
+          <t>MBA Mortgage Market IndexFEB/21</t>
         </is>
       </c>
       <c r="C699" t="inlineStr"/>
@@ -16560,7 +16560,7 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C700" t="inlineStr"/>
@@ -16614,7 +16614,7 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C703" t="inlineStr"/>
@@ -16704,7 +16704,7 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C708" t="inlineStr"/>
@@ -16758,7 +16758,7 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>New Home SalesJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C711" t="inlineStr"/>
@@ -16776,7 +16776,7 @@
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>New Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C712" t="inlineStr"/>
@@ -16794,7 +16794,7 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>New Home Sales MoMJAN</t>
+          <t>New Home SalesJAN</t>
         </is>
       </c>
       <c r="C713" t="inlineStr"/>
@@ -17028,14 +17028,14 @@
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C726" t="inlineStr"/>
       <c r="D726" t="inlineStr"/>
       <c r="E726" t="inlineStr"/>
       <c r="F726" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="727">
@@ -17046,14 +17046,14 @@
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C727" t="inlineStr"/>
       <c r="D727" t="inlineStr"/>
       <c r="E727" t="inlineStr"/>
       <c r="F727" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="728">
@@ -17064,7 +17064,7 @@
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C728" t="inlineStr"/>
@@ -17100,7 +17100,7 @@
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+          <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C730" t="inlineStr"/>
@@ -17118,7 +17118,7 @@
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/21</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
       <c r="C731" t="inlineStr"/>
@@ -17208,7 +17208,7 @@
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>Fed Bostic Speech</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C736" t="inlineStr"/>
@@ -17226,7 +17226,7 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C737" t="inlineStr"/>
@@ -17244,7 +17244,7 @@
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Fed Bostic Speech</t>
         </is>
       </c>
       <c r="C738" t="inlineStr"/>
@@ -17298,7 +17298,7 @@
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>2-Year FRN Auction</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C741" t="inlineStr"/>
@@ -17316,7 +17316,7 @@
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C742" t="inlineStr"/>
@@ -17334,7 +17334,7 @@
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>2-Year FRN Auction</t>
         </is>
       </c>
       <c r="C743" t="inlineStr"/>
@@ -17610,14 +17610,14 @@
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMJAN</t>
+          <t>Continuing Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C757" t="inlineStr"/>
       <c r="D757" t="inlineStr"/>
       <c r="E757" t="inlineStr"/>
       <c r="F757" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="758">
@@ -17672,22 +17672,22 @@
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ 2nd EstQ4</t>
+          <t>Core PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C760" t="inlineStr"/>
       <c r="D760" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="E760" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F760" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="761">
@@ -17720,18 +17720,22 @@
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ 2nd EstQ4</t>
+          <t>GDP Price Index QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C762" t="inlineStr"/>
-      <c r="D762" t="inlineStr"/>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>2.2%</t>
+        </is>
+      </c>
       <c r="E762" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="F762" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="763">
@@ -17742,22 +17746,14 @@
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ 2nd EstQ4</t>
+          <t>Durable Goods Orders Ex Transp MoMJAN</t>
         </is>
       </c>
       <c r="C763" t="inlineStr"/>
-      <c r="D763" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
-      <c r="E763" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+      <c r="D763" t="inlineStr"/>
+      <c r="E763" t="inlineStr"/>
       <c r="F763" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="764">
@@ -17768,14 +17764,14 @@
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/15</t>
+          <t>Initial Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C764" t="inlineStr"/>
       <c r="D764" t="inlineStr"/>
       <c r="E764" t="inlineStr"/>
       <c r="F764" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="765">
@@ -17812,14 +17808,14 @@
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/22</t>
+          <t>Durable Goods Orders MoMJAN</t>
         </is>
       </c>
       <c r="C766" t="inlineStr"/>
       <c r="D766" t="inlineStr"/>
       <c r="E766" t="inlineStr"/>
       <c r="F766" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="767">
@@ -17830,14 +17826,18 @@
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMJAN</t>
+          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C767" t="inlineStr"/>
       <c r="D767" t="inlineStr"/>
-      <c r="E767" t="inlineStr"/>
+      <c r="E767" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="F767" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="768">
@@ -17848,7 +17848,7 @@
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/22</t>
+          <t>Durable Goods Orders ex Defense MoMJAN</t>
         </is>
       </c>
       <c r="C768" t="inlineStr"/>
@@ -17866,12 +17866,20 @@
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirJAN</t>
+          <t>PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C769" t="inlineStr"/>
-      <c r="D769" t="inlineStr"/>
-      <c r="E769" t="inlineStr"/>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="E769" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
       <c r="F769" t="n">
         <v>3</v>
       </c>
@@ -17906,18 +17914,14 @@
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ 2nd EstQ4</t>
+          <t>GDP Sales QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C771" t="inlineStr"/>
-      <c r="D771" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
+      <c r="D771" t="inlineStr"/>
       <c r="E771" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F771" t="n">
@@ -17932,7 +17936,7 @@
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMJAN</t>
+          <t>Non Defense Goods Orders Ex AirJAN</t>
         </is>
       </c>
       <c r="C772" t="inlineStr"/>
@@ -17950,16 +17954,12 @@
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
+          <t>Jobless Claims 4-week AverageFEB/22</t>
         </is>
       </c>
       <c r="C773" t="inlineStr"/>
       <c r="D773" t="inlineStr"/>
-      <c r="E773" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="E773" t="inlineStr"/>
       <c r="F773" t="n">
         <v>3</v>
       </c>
@@ -18044,15 +18044,11 @@
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>NY Fed Treasury Purchases 4 to 6 yrs</t>
+          <t>EIA Natural Gas Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C778" t="inlineStr"/>
-      <c r="D778" t="inlineStr">
-        <is>
-          <t>$50 million</t>
-        </is>
-      </c>
+      <c r="D778" t="inlineStr"/>
       <c r="E778" t="inlineStr"/>
       <c r="F778" t="n">
         <v>3</v>
@@ -18066,11 +18062,15 @@
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>EIA Natural Gas Stocks ChangeFEB/21</t>
+          <t>NY Fed Treasury Purchases 4 to 6 yrs</t>
         </is>
       </c>
       <c r="C779" t="inlineStr"/>
-      <c r="D779" t="inlineStr"/>
+      <c r="D779" t="inlineStr">
+        <is>
+          <t>$50 million</t>
+        </is>
+      </c>
       <c r="E779" t="inlineStr"/>
       <c r="F779" t="n">
         <v>3</v>
@@ -18142,7 +18142,7 @@
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>Kansas Fed Manufacturing IndexFEB</t>
+          <t>Kansas Fed Composite IndexFEB</t>
         </is>
       </c>
       <c r="C783" t="inlineStr"/>
@@ -18160,7 +18160,7 @@
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>Kansas Fed Composite IndexFEB</t>
+          <t>Kansas Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C784" t="inlineStr"/>

--- a/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-02-27.xlsx
+++ b/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-02-27.xlsx
@@ -720,12 +720,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.041M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -742,18 +742,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.323M</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -764,18 +768,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>7.717M</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0.7M</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -786,19 +794,15 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>6.406M</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>-0.1M</t>
-        </is>
-      </c>
+          <t>-0.416M</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
         <v>3</v>
@@ -812,12 +816,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -834,15 +838,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.416M</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>-0.1M</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
         <v>3</v>
@@ -856,22 +864,18 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -882,22 +886,18 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-1.178M</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>-2.75M</t>
-        </is>
-      </c>
+          <t>0.041M</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -908,12 +908,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.142M</t>
+          <t>0.099M</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1582,18 +1582,18 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ExportsNOV</t>
+          <t>ImportsNOV</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>$273.4B</t>
+          <t>$351.6B</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>$264B</t>
+          <t>$334B</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -1608,18 +1608,22 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ImportsNOV</t>
+          <t>Balance of TradeNOV</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>$351.6B</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
+          <t>$-78.2B</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>$-78B</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>$334B</t>
+          <t>$-70B</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -1634,22 +1638,18 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Balance of TradeNOV</t>
+          <t>ExportsNOV</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>$-78.2B</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>$-78B</t>
-        </is>
-      </c>
+          <t>$273.4B</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>$-70B</t>
+          <t>$264B</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Used Car Prices MoMDEC</t>
+          <t>Used Car Prices YoYDEC</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -2254,12 +2254,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Used Car Prices YoYDEC</t>
+          <t>Used Car Prices MoMDEC</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -3148,22 +3148,26 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
+          <t>Michigan Consumer Sentiment PrelJAN</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr"/>
+          <t>73.2</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>73.8</t>
+        </is>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
@@ -3174,18 +3178,18 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelJAN</t>
+          <t>Michigan Current Conditions PrelJAN</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F113" t="n">
@@ -3200,18 +3204,18 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelJAN</t>
+          <t>Michigan Consumer Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F114" t="n">
@@ -3226,18 +3230,18 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelJAN</t>
+          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F115" t="n">
@@ -3252,26 +3256,22 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelJAN</t>
+          <t>Michigan Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>73.2</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>73.8</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="117">
@@ -3458,12 +3458,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>4.180%</t>
+          <t>4.225%</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
@@ -3480,12 +3480,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>4.225%</t>
+          <t>4.180%</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
@@ -4010,26 +4010,26 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexJAN</t>
+          <t>Core Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>-12.60</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148">
@@ -4040,26 +4040,26 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYDEC</t>
+          <t>CPIDEC</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>315.6</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="149">
@@ -4070,22 +4070,22 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMDEC</t>
+          <t>Core Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F149" t="n">
@@ -4100,26 +4100,22 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYDEC</t>
+          <t>CPI s.aDEC</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+          <t>317.685</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>317.4</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="151">
@@ -4130,22 +4126,26 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>CPI s.aDEC</t>
+          <t>Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>317.685</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr"/>
+          <t>2.9%</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>2.9%</t>
+        </is>
+      </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>317.4</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="152">
@@ -4156,22 +4156,22 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>CPIDEC</t>
+          <t>NY Empire State Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>-12.60</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>315.6</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="F152" t="n">
@@ -4186,22 +4186,22 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMDEC</t>
+          <t>Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F153" t="n">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>-0.021M</t>
         </is>
       </c>
       <c r="D156" t="inlineStr"/>
@@ -4274,18 +4274,22 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>0.397M</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr"/>
+          <t>-1.961M</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>-1.6M</t>
+        </is>
+      </c>
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="158">
@@ -4296,22 +4300,18 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>2.60M</t>
-        </is>
-      </c>
+          <t>-1.304M</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="159">
@@ -4322,19 +4322,15 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>3.077M</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>1.1M</t>
-        </is>
-      </c>
+          <t>0.765M</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="n">
         <v>3</v>
@@ -4348,12 +4344,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>0.765M</t>
+          <t>0.646M</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
@@ -4370,18 +4366,22 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>0.646M</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>2.60M</t>
+        </is>
+      </c>
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="162">
@@ -4392,12 +4392,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>-1.304M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
@@ -4414,22 +4414,18 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>-1.961M</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>-1.6M</t>
-        </is>
-      </c>
+          <t>-0.255M</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="164">
@@ -4440,15 +4436,19 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>-0.021M</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr"/>
+          <t>3.077M</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>1.1M</t>
+        </is>
+      </c>
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="n">
         <v>3</v>
@@ -4556,26 +4556,26 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F170" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="171">
@@ -4586,20 +4586,16 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>212.75K</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>215.0K</t>
-        </is>
-      </c>
+      <c r="E171" t="inlineStr"/>
       <c r="F171" t="n">
         <v>3</v>
       </c>
@@ -4612,18 +4608,22 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>1.8%</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="F172" t="n">
@@ -4638,16 +4638,20 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D173" t="inlineStr"/>
-      <c r="E173" t="inlineStr"/>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>4.0%</t>
+        </is>
+      </c>
       <c r="F173" t="n">
         <v>3</v>
       </c>
@@ -4660,26 +4664,18 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
+          <t>46.3</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="inlineStr"/>
       <c r="F174" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="175">
@@ -4690,16 +4686,24 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>11.9</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr"/>
-      <c r="E175" t="inlineStr"/>
+          <t>1859K</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>1870.0K</t>
+        </is>
+      </c>
       <c r="F175" t="n">
         <v>3</v>
       </c>
@@ -4712,20 +4716,16 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>39.00</t>
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>4.0%</t>
-        </is>
-      </c>
+      <c r="E176" t="inlineStr"/>
       <c r="F176" t="n">
         <v>3</v>
       </c>
@@ -4738,22 +4738,22 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>217K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>210K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F177" t="n">
@@ -4768,22 +4768,22 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F178" t="n">
@@ -4798,26 +4798,18 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr"/>
       <c r="F179" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="180">
@@ -4828,18 +4820,26 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>39.00</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr"/>
-      <c r="E180" t="inlineStr"/>
+          <t>217K</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>210K</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>209.0K</t>
+        </is>
+      </c>
       <c r="F180" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="181">
@@ -4850,18 +4850,26 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr"/>
-      <c r="E181" t="inlineStr"/>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>-10</t>
+        </is>
+      </c>
       <c r="F181" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="182">
@@ -4872,26 +4880,26 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="183">
@@ -4902,24 +4910,16 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>1.6%</t>
-        </is>
-      </c>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr"/>
+      <c r="E183" t="inlineStr"/>
       <c r="F183" t="n">
         <v>3</v>
       </c>
@@ -4932,26 +4932,22 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>1.8%</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="185">
@@ -4962,16 +4958,20 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>212.75K</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
-      <c r="E185" t="inlineStr"/>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>215.0K</t>
+        </is>
+      </c>
       <c r="F185" t="n">
         <v>3</v>
       </c>
@@ -4984,22 +4984,22 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F186" t="n">
@@ -5014,22 +5014,22 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>NAHB Housing Market IndexJAN</t>
+          <t>Business Inventories MoMNOV</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F187" t="n">
@@ -5044,17 +5044,17 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Business Inventories MoMNOV</t>
+          <t>Retail Inventories Ex Autos MoMNOV</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -5063,7 +5063,7 @@
         </is>
       </c>
       <c r="F188" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="189">
@@ -5074,26 +5074,26 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoMNOV</t>
+          <t>NAHB Housing Market IndexJAN</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F189" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="190">
@@ -5240,26 +5240,22 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Housing StartsDEC</t>
+          <t>Building Permits MoM PrelDEC</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>1.499M</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>1.32M</t>
-        </is>
-      </c>
+          <t>-0.7%</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr">
         <is>
-          <t>1.32M</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="F196" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="197">
@@ -5270,22 +5266,26 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Housing Starts MoMDEC</t>
+          <t>Housing StartsDEC</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>15.8%</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr"/>
+          <t>1.499M</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>1.32M</t>
+        </is>
+      </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>1.32M</t>
         </is>
       </c>
       <c r="F197" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="198">
@@ -5296,18 +5296,18 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelDEC</t>
+          <t>Housing Starts MoMDEC</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>15.8%</t>
         </is>
       </c>
       <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="F198" t="n">
@@ -5352,18 +5352,18 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Industrial Production YoYDEC</t>
+          <t>Manufacturing Production YoYDEC</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F200" t="n">
@@ -5378,26 +5378,26 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Industrial Production MoMDEC</t>
+          <t>Manufacturing Production MoMDEC</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F201" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="202">
@@ -5408,26 +5408,26 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Capacity UtilizationDEC</t>
+          <t>Industrial Production MoMDEC</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F202" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="203">
@@ -5438,22 +5438,22 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMDEC</t>
+          <t>Capacity UtilizationDEC</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="F203" t="n">
@@ -5468,18 +5468,18 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYDEC</t>
+          <t>Industrial Production YoYDEC</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D204" t="inlineStr"/>
       <c r="E204" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F204" t="n">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>42-Day Bill Auction</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>4.025%</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
@@ -5692,12 +5692,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>42-Day Bill Auction</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>4.025%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
@@ -5942,22 +5942,26 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/18</t>
+          <t>Initial Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>213.5K</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr"/>
+          <t>223K</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>220K</t>
+        </is>
+      </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>213.0K</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="F225" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="226">
@@ -5968,26 +5972,26 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/18</t>
+          <t>Continuing Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>1899K</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>220K</t>
+          <t>1860K</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>1861K</t>
         </is>
       </c>
       <c r="F226" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="227">
@@ -5998,22 +6002,18 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/11</t>
+          <t>Jobless Claims 4-week AverageJAN/18</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>1899K</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr">
-        <is>
-          <t>1860K</t>
-        </is>
-      </c>
+          <t>213.5K</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr"/>
       <c r="E227" t="inlineStr">
         <is>
-          <t>1861K</t>
+          <t>213.0K</t>
         </is>
       </c>
       <c r="F227" t="n">
@@ -6150,15 +6150,19 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>-1.125M</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="E233" t="inlineStr"/>
       <c r="F233" t="n">
         <v>3</v>
@@ -6172,12 +6176,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
@@ -6194,22 +6198,18 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>-0.148M</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr"/>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="236">
@@ -6220,18 +6220,22 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>6.96%</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E236" t="inlineStr"/>
       <c r="F236" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="237">
@@ -6242,12 +6246,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
@@ -6264,12 +6268,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -6286,19 +6290,15 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>6.96%</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr"/>
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="n">
         <v>3</v>
@@ -6312,18 +6312,22 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>0.184M</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="241">
@@ -6334,22 +6338,18 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>0.068M</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr"/>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="242">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -6382,12 +6382,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
@@ -6448,22 +6448,22 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashJAN</t>
+          <t>S&amp;P Global Manufacturing PMI FlashJAN</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="F246" t="n">
@@ -6478,22 +6478,22 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashJAN</t>
+          <t>S&amp;P Global Services PMI FlashJAN</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="F247" t="n">
@@ -6534,22 +6534,26 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr"/>
+          <t>69.3</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>70.2</t>
+        </is>
+      </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F249" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="250">
@@ -6560,26 +6564,26 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F250" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="251">
@@ -6590,26 +6594,26 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>4.24M</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.19M</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="F251" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="252">
@@ -6650,26 +6654,26 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>4.24M</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>4.19M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F253" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="254">
@@ -6680,26 +6684,26 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F254" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="255">
@@ -6710,26 +6714,22 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr">
-        <is>
-          <t>77.9</t>
-        </is>
-      </c>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr"/>
       <c r="E255" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F255" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="256">
@@ -7178,18 +7178,18 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
+          <t>House Price IndexNOV</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>433.4</t>
         </is>
       </c>
       <c r="D273" t="inlineStr"/>
       <c r="E273" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>433</t>
         </is>
       </c>
       <c r="F273" t="n">
@@ -7204,26 +7204,26 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYNOV</t>
+          <t>House Price Index MoMNOV</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F274" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="275">
@@ -7234,22 +7234,18 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>House Price Index MoMNOV</t>
+          <t>House Price Index YoYNOV</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D275" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr"/>
       <c r="E275" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F275" t="n">
@@ -7264,18 +7260,18 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>House Price IndexNOV</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>433.4</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="D276" t="inlineStr"/>
       <c r="E276" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F276" t="n">
@@ -7290,22 +7286,26 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>House Price Index YoYNOV</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYNOV</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="D277" t="inlineStr"/>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>4.3%</t>
+        </is>
+      </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F277" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="278">
@@ -7790,19 +7790,15 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>-4.994M</t>
-        </is>
-      </c>
-      <c r="D297" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.532M</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr"/>
       <c r="E297" t="inlineStr"/>
       <c r="F297" t="n">
         <v>3</v>
@@ -7816,12 +7812,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>-0.333M</t>
+          <t>0.128M</t>
         </is>
       </c>
       <c r="D298" t="inlineStr"/>
@@ -7838,22 +7834,18 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>2.957M</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>0.326M</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr"/>
       <c r="E299" t="inlineStr"/>
       <c r="F299" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="300">
@@ -7864,18 +7856,22 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>0.028M</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr"/>
+          <t>3.463M</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>3.2M</t>
+        </is>
+      </c>
       <c r="E300" t="inlineStr"/>
       <c r="F300" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="301">
@@ -7908,22 +7904,18 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>3.463M</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr">
-        <is>
-          <t>3.2M</t>
-        </is>
-      </c>
+          <t>0.028M</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr"/>
       <c r="E302" t="inlineStr"/>
       <c r="F302" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="303">
@@ -7934,18 +7926,22 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>0.326M</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr"/>
+          <t>2.957M</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E303" t="inlineStr"/>
       <c r="F303" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="304">
@@ -7956,12 +7952,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>0.128M</t>
+          <t>-0.333M</t>
         </is>
       </c>
       <c r="D304" t="inlineStr"/>
@@ -7978,15 +7974,19 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>0.532M</t>
-        </is>
-      </c>
-      <c r="D305" t="inlineStr"/>
+          <t>-4.994M</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E305" t="inlineStr"/>
       <c r="F305" t="n">
         <v>3</v>
@@ -8070,18 +8070,22 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ AdvQ4</t>
+          <t>Core PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="D309" t="inlineStr"/>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F309" t="n">
@@ -8096,22 +8100,26 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ AdvQ4</t>
+          <t>GDP Price Index QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D310" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F310" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="311">
@@ -8122,18 +8130,22 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ AdvQ4</t>
+          <t>Continuing Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>2.3%</t>
-        </is>
-      </c>
-      <c r="D311" t="inlineStr"/>
+          <t>1858K</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>1890K</t>
+        </is>
+      </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>1885.0K</t>
         </is>
       </c>
       <c r="F311" t="n">
@@ -8148,26 +8160,26 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ AdvQ4</t>
+          <t>Initial Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>207K</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>228.0K</t>
         </is>
       </c>
       <c r="F312" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="313">
@@ -8178,26 +8190,22 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/25</t>
+          <t>Jobless Claims 4-week AverageJAN/25</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>207K</t>
-        </is>
-      </c>
-      <c r="D313" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+          <t>212.5K</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr"/>
       <c r="E313" t="inlineStr">
         <is>
-          <t>228.0K</t>
+          <t>214.0K</t>
         </is>
       </c>
       <c r="F313" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="314">
@@ -8208,22 +8216,18 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/18</t>
+          <t>PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>1858K</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr">
-        <is>
-          <t>1890K</t>
-        </is>
-      </c>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr"/>
       <c r="E314" t="inlineStr">
         <is>
-          <t>1885.0K</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="F314" t="n">
@@ -8238,26 +8242,22 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ AdvQ4</t>
+          <t>GDP Sales QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr"/>
       <c r="E315" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F315" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="316">
@@ -8268,22 +8268,26 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/25</t>
+          <t>GDP Growth Rate QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>212.5K</t>
-        </is>
-      </c>
-      <c r="D316" t="inlineStr"/>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>214.0K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F316" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="317">
@@ -8294,22 +8298,18 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ AdvQ4</t>
+          <t>Real Consumer Spending QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>2.5%</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr"/>
       <c r="E317" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F317" t="n">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D321" t="inlineStr"/>
@@ -8428,12 +8428,12 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="D322" t="inlineStr"/>
@@ -8516,26 +8516,26 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F326" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="327">
@@ -8546,22 +8546,22 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F327" t="n">
@@ -8576,24 +8576,12 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
-        </is>
-      </c>
-      <c r="C328" t="inlineStr">
-        <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr">
-        <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="E328" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr"/>
+      <c r="D328" t="inlineStr"/>
+      <c r="E328" t="inlineStr"/>
       <c r="F328" t="n">
         <v>2</v>
       </c>
@@ -8606,18 +8594,22 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D329" t="inlineStr"/>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F329" t="n">
@@ -8632,22 +8624,26 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
+          <t>Core PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="D330" t="inlineStr"/>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F330" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="331">
@@ -8658,26 +8654,26 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F331" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="332">
@@ -8688,22 +8684,18 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
+          <t>Employment Cost - Wages QoQQ4</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr"/>
       <c r="E332" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F332" t="n">
@@ -8718,22 +8710,22 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F333" t="n">
@@ -8748,14 +8740,26 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C334" t="inlineStr"/>
-      <c r="D334" t="inlineStr"/>
-      <c r="E334" t="inlineStr"/>
+          <t>Personal Income MoMDEC</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F334" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="335">
@@ -8766,26 +8770,22 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
+          <t>Employment Cost - Benefits QoQQ4</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D335" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr"/>
       <c r="E335" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F335" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="336">
@@ -8904,26 +8904,22 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIJAN</t>
+          <t>ISM Manufacturing New OrdersJAN</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>50.9</t>
-        </is>
-      </c>
-      <c r="D340" t="inlineStr">
-        <is>
-          <t>49.8</t>
-        </is>
-      </c>
+          <t>55.1</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr"/>
       <c r="E340" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F340" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="341">
@@ -8934,22 +8930,26 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentJAN</t>
+          <t>Construction Spending MoMDEC</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>50.3</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F341" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="342">
@@ -8960,26 +8960,26 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesJAN</t>
+          <t>ISM Manufacturing PMIJAN</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="F342" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="343">
@@ -8990,26 +8990,22 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Construction Spending MoMDEC</t>
+          <t>ISM Manufacturing EmploymentJAN</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>50.3</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr"/>
       <c r="E343" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F343" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="344">
@@ -9020,18 +9016,22 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersJAN</t>
+          <t>ISM Manufacturing PricesJAN</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>55.1</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr"/>
+          <t>54.9</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>52.6</t>
+        </is>
+      </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F344" t="n">
@@ -9708,22 +9708,22 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FinalJAN</t>
+          <t>S&amp;P Global Composite PMI FinalJAN</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="F374" t="n">
@@ -9738,22 +9738,22 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FinalJAN</t>
+          <t>S&amp;P Global Services PMI FinalJAN</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F375" t="n">
@@ -9902,15 +9902,19 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>-0.034M</t>
-        </is>
-      </c>
-      <c r="D381" t="inlineStr"/>
+          <t>-5.471M</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>-1.5M</t>
+        </is>
+      </c>
       <c r="E381" t="inlineStr"/>
       <c r="F381" t="n">
         <v>3</v>
@@ -9924,18 +9928,22 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>0.373M</t>
-        </is>
-      </c>
-      <c r="D382" t="inlineStr"/>
+          <t>2.233M</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>1.2M</t>
+        </is>
+      </c>
       <c r="E382" t="inlineStr"/>
       <c r="F382" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="383">
@@ -9946,12 +9954,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Crude Oil Imports ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>-0.027M</t>
+          <t>-0.178M</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
@@ -9968,12 +9976,12 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>0.16M</t>
+          <t>-0.186M</t>
         </is>
       </c>
       <c r="D384" t="inlineStr"/>
@@ -9990,18 +9998,22 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>-0.186M</t>
-        </is>
-      </c>
-      <c r="D385" t="inlineStr"/>
+          <t>8.664M</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>2.6M</t>
+        </is>
+      </c>
       <c r="E385" t="inlineStr"/>
       <c r="F385" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="386">
@@ -10012,12 +10024,12 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>-0.178M</t>
+          <t>-0.027M</t>
         </is>
       </c>
       <c r="D386" t="inlineStr"/>
@@ -10034,22 +10046,18 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>8.664M</t>
-        </is>
-      </c>
-      <c r="D387" t="inlineStr">
-        <is>
-          <t>2.6M</t>
-        </is>
-      </c>
+          <t>0.373M</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr"/>
       <c r="E387" t="inlineStr"/>
       <c r="F387" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="388">
@@ -10060,22 +10068,18 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>2.233M</t>
-        </is>
-      </c>
-      <c r="D388" t="inlineStr">
-        <is>
-          <t>1.2M</t>
-        </is>
-      </c>
+          <t>-0.034M</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr"/>
       <c r="E388" t="inlineStr"/>
       <c r="F388" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="389">
@@ -10086,19 +10090,15 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>-5.471M</t>
-        </is>
-      </c>
-      <c r="D389" t="inlineStr">
-        <is>
-          <t>-1.5M</t>
-        </is>
-      </c>
+          <t>0.16M</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr"/>
       <c r="E389" t="inlineStr"/>
       <c r="F389" t="n">
         <v>3</v>
@@ -10196,26 +10196,22 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Nonfarm Productivity QoQ PrelQ4</t>
+          <t>Jobless Claims 4-week AverageFEB/01</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>1.2%</t>
-        </is>
-      </c>
-      <c r="D394" t="inlineStr">
-        <is>
-          <t>1.4%</t>
-        </is>
-      </c>
+          <t>216.75K</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr"/>
       <c r="E394" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>215.5K</t>
         </is>
       </c>
       <c r="F394" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="395">
@@ -10226,22 +10222,22 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Unit Labour Costs QoQ PrelQ4</t>
+          <t>Nonfarm Productivity QoQ PrelQ4</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F395" t="n">
@@ -10256,22 +10252,22 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/01</t>
+          <t>Unit Labour Costs QoQ PrelQ4</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>213K</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F396" t="n">
@@ -10286,22 +10282,26 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/01</t>
+          <t>Initial Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>216.75K</t>
-        </is>
-      </c>
-      <c r="D397" t="inlineStr"/>
+          <t>219K</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>213K</t>
+        </is>
+      </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>215.5K</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F397" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="398">
@@ -10390,12 +10390,12 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D401" t="inlineStr"/>
@@ -10412,12 +10412,12 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="D402" t="inlineStr"/>
@@ -10536,22 +10536,26 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Participation RateJAN</t>
+          <t>Average Weekly HoursJAN</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>62.6%</t>
-        </is>
-      </c>
-      <c r="D408" t="inlineStr"/>
+          <t>34.1</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F408" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="409">
@@ -10562,18 +10566,18 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Government PayrollsJAN</t>
+          <t>U-6 Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>32K</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="D409" t="inlineStr"/>
       <c r="E409" t="inlineStr">
         <is>
-          <t>25K</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="F409" t="n">
@@ -10588,26 +10592,26 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoYJAN</t>
+          <t>Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
           <t>4.1%</t>
         </is>
       </c>
-      <c r="D410" t="inlineStr">
-        <is>
-          <t>3.8%</t>
-        </is>
-      </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F410" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="411">
@@ -10618,26 +10622,26 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsJAN</t>
+          <t>Manufacturing PayrollsJAN</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>143K</t>
+          <t>3K</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>170K</t>
+          <t>-2K</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>205K</t>
+          <t>-5K</t>
         </is>
       </c>
       <c r="F411" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="412">
@@ -10648,26 +10652,26 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateJAN</t>
+          <t>Average Hourly Earnings MoMJAN</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>111K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>141K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>180K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F412" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="413">
@@ -10678,26 +10682,26 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMJAN</t>
+          <t>Nonfarm Payrolls PrivateJAN</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>111K</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>141K</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>180K</t>
         </is>
       </c>
       <c r="F413" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="414">
@@ -10708,26 +10712,26 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsJAN</t>
+          <t>Non Farm PayrollsJAN</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>3K</t>
+          <t>143K</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>-2K</t>
+          <t>170K</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>-5K</t>
+          <t>205K</t>
         </is>
       </c>
       <c r="F414" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="415">
@@ -10738,26 +10742,26 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Unemployment RateJAN</t>
+          <t>Average Hourly Earnings YoYJAN</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="F415" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="416">
@@ -10768,18 +10772,18 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>U-6 Unemployment RateJAN</t>
+          <t>Government PayrollsJAN</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>32K</t>
         </is>
       </c>
       <c r="D416" t="inlineStr"/>
       <c r="E416" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>25K</t>
         </is>
       </c>
       <c r="F416" t="n">
@@ -10794,26 +10798,22 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Average Weekly HoursJAN</t>
+          <t>Participation RateJAN</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>34.1</t>
-        </is>
-      </c>
-      <c r="D417" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
+          <t>62.6%</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr"/>
       <c r="E417" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="F417" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="418">
@@ -10904,22 +10904,22 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelFEB</t>
+          <t>Wholesale Inventories MoMDEC</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F422" t="n">
@@ -10934,18 +10934,22 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelFEB</t>
+          <t>Michigan Current Conditions PrelFEB</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D423" t="inlineStr"/>
+          <t>68.7</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="F423" t="n">
@@ -10960,22 +10964,26 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelFEB</t>
+          <t>Michigan Consumer Sentiment PrelFEB</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="D424" t="inlineStr"/>
+          <t>67.8</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>71.1</t>
+        </is>
+      </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F424" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="425">
@@ -10986,26 +10994,22 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelFEB</t>
+          <t>Michigan 5 Year Inflation Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>67.8</t>
-        </is>
-      </c>
-      <c r="D425" t="inlineStr">
-        <is>
-          <t>71.1</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr"/>
       <c r="E425" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F425" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="426">
@@ -11016,22 +11020,22 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelFEB</t>
+          <t>Michigan Consumer Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="F426" t="n">
@@ -11046,22 +11050,18 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoMDEC</t>
+          <t>Michigan Inflation Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
-      <c r="D427" t="inlineStr">
-        <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr"/>
       <c r="E427" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F427" t="n">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>4.225%</t>
+          <t>4.185%</t>
         </is>
       </c>
       <c r="D434" t="inlineStr"/>
@@ -11234,12 +11234,12 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>4.185%</t>
+          <t>4.225%</t>
         </is>
       </c>
       <c r="D435" t="inlineStr"/>
@@ -11474,7 +11474,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/07</t>
+          <t>MBA Mortgage ApplicationsFEB/07</t>
         </is>
       </c>
       <c r="C447" t="inlineStr"/>
@@ -11492,14 +11492,14 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/07</t>
+          <t>MBA Purchase IndexFEB/07</t>
         </is>
       </c>
       <c r="C448" t="inlineStr"/>
       <c r="D448" t="inlineStr"/>
       <c r="E448" t="inlineStr"/>
       <c r="F448" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="449">
@@ -11510,7 +11510,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/07</t>
+          <t>MBA Mortgage Market IndexFEB/07</t>
         </is>
       </c>
       <c r="C449" t="inlineStr"/>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/07</t>
+          <t>MBA Mortgage Refinance IndexFEB/07</t>
         </is>
       </c>
       <c r="C450" t="inlineStr"/>
@@ -11546,14 +11546,14 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/07</t>
+          <t>MBA 30-Year Mortgage RateFEB/07</t>
         </is>
       </c>
       <c r="C451" t="inlineStr"/>
       <c r="D451" t="inlineStr"/>
       <c r="E451" t="inlineStr"/>
       <c r="F451" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="452">
@@ -11716,7 +11716,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C458" t="inlineStr"/>
@@ -11734,14 +11734,14 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C459" t="inlineStr"/>
       <c r="D459" t="inlineStr"/>
       <c r="E459" t="inlineStr"/>
       <c r="F459" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="460">
@@ -11752,14 +11752,14 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C460" t="inlineStr"/>
       <c r="D460" t="inlineStr"/>
       <c r="E460" t="inlineStr"/>
       <c r="F460" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="461">
@@ -11770,7 +11770,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C461" t="inlineStr"/>
@@ -11788,7 +11788,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C462" t="inlineStr"/>
@@ -11806,14 +11806,14 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C463" t="inlineStr"/>
       <c r="D463" t="inlineStr"/>
       <c r="E463" t="inlineStr"/>
       <c r="F463" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="464">
@@ -11824,14 +11824,14 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C464" t="inlineStr"/>
       <c r="D464" t="inlineStr"/>
       <c r="E464" t="inlineStr"/>
       <c r="F464" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="465">
@@ -11842,7 +11842,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C465" t="inlineStr"/>
@@ -11860,7 +11860,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C466" t="inlineStr"/>
@@ -11976,18 +11976,22 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C472" t="inlineStr"/>
-      <c r="D472" t="inlineStr"/>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F472" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="473">
@@ -11998,14 +12002,18 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C473" t="inlineStr"/>
-      <c r="D473" t="inlineStr"/>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F473" t="n">
@@ -12020,22 +12028,18 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C474" t="inlineStr"/>
-      <c r="D474" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D474" t="inlineStr"/>
       <c r="E474" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="F474" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="475">
@@ -12046,18 +12050,14 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C475" t="inlineStr"/>
-      <c r="D475" t="inlineStr">
-        <is>
-          <t>3.2%</t>
-        </is>
-      </c>
+      <c r="D475" t="inlineStr"/>
       <c r="E475" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="F475" t="n">
@@ -12072,22 +12072,18 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C476" t="inlineStr"/>
-      <c r="D476" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D476" t="inlineStr"/>
       <c r="E476" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F476" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="477">
@@ -12098,14 +12094,18 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C477" t="inlineStr"/>
-      <c r="D477" t="inlineStr"/>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F477" t="n">
@@ -12120,18 +12120,22 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C478" t="inlineStr"/>
-      <c r="D478" t="inlineStr"/>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F478" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="479">
@@ -12142,14 +12146,14 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C479" t="inlineStr"/>
       <c r="D479" t="inlineStr"/>
       <c r="E479" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="F479" t="n">
@@ -12164,18 +12168,14 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C480" t="inlineStr"/>
-      <c r="D480" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+      <c r="D480" t="inlineStr"/>
       <c r="E480" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F480" t="n">
@@ -12190,22 +12190,22 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C481" t="inlineStr"/>
       <c r="D481" t="inlineStr">
         <is>
-          <t>216K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F481" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="482">
@@ -12574,18 +12574,22 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="C499" t="inlineStr"/>
-      <c r="D499" t="inlineStr"/>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F499" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="500">
@@ -12596,14 +12600,18 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="C500" t="inlineStr"/>
-      <c r="D500" t="inlineStr"/>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>77.7%</t>
+        </is>
+      </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="F500" t="n">
@@ -12618,18 +12626,14 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="C501" t="inlineStr"/>
-      <c r="D501" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+      <c r="D501" t="inlineStr"/>
       <c r="E501" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F501" t="n">
@@ -12644,18 +12648,14 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="C502" t="inlineStr"/>
-      <c r="D502" t="inlineStr">
-        <is>
-          <t>77.7%</t>
-        </is>
-      </c>
+      <c r="D502" t="inlineStr"/>
       <c r="E502" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F502" t="n">
@@ -12670,22 +12670,22 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Manufacturing Production MoMJAN</t>
         </is>
       </c>
       <c r="C503" t="inlineStr"/>
       <c r="D503" t="inlineStr">
         <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
           <t>0.2%</t>
         </is>
       </c>
-      <c r="E503" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
       <c r="F503" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="504">
@@ -13158,14 +13158,14 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C527" t="inlineStr"/>
       <c r="D527" t="inlineStr"/>
       <c r="E527" t="inlineStr"/>
       <c r="F527" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="528">
@@ -13212,14 +13212,14 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="C530" t="inlineStr"/>
       <c r="D530" t="inlineStr"/>
       <c r="E530" t="inlineStr"/>
       <c r="F530" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="531">
@@ -13622,18 +13622,22 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C551" t="inlineStr"/>
-      <c r="D551" t="inlineStr"/>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>1.4M</t>
+        </is>
+      </c>
       <c r="E551" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F551" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="552">
@@ -13670,22 +13674,18 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C553" t="inlineStr"/>
-      <c r="D553" t="inlineStr">
-        <is>
-          <t>1.4M</t>
-        </is>
-      </c>
+      <c r="D553" t="inlineStr"/>
       <c r="E553" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F553" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="554">
@@ -14572,7 +14572,7 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C598" t="inlineStr"/>
@@ -14590,14 +14590,14 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C599" t="inlineStr"/>
       <c r="D599" t="inlineStr"/>
       <c r="E599" t="inlineStr"/>
       <c r="F599" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="600">
@@ -14608,7 +14608,7 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C600" t="inlineStr"/>
@@ -14788,7 +14788,7 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C610" t="inlineStr"/>
@@ -14806,14 +14806,14 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>Fed Musalem Speech</t>
         </is>
       </c>
       <c r="C611" t="inlineStr"/>
       <c r="D611" t="inlineStr"/>
       <c r="E611" t="inlineStr"/>
       <c r="F611" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="612">
@@ -14842,7 +14842,7 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C613" t="inlineStr"/>
@@ -14860,14 +14860,14 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>Fed Musalem Speech</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C614" t="inlineStr"/>
       <c r="D614" t="inlineStr"/>
       <c r="E614" t="inlineStr"/>
       <c r="F614" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="615">
@@ -14878,14 +14878,14 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C615" t="inlineStr"/>
       <c r="D615" t="inlineStr"/>
       <c r="E615" t="inlineStr"/>
       <c r="F615" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="616">
@@ -14896,7 +14896,7 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C616" t="inlineStr"/>
@@ -14914,7 +14914,7 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C617" t="inlineStr"/>
@@ -14932,14 +14932,14 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C618" t="inlineStr"/>
       <c r="D618" t="inlineStr"/>
       <c r="E618" t="inlineStr"/>
       <c r="F618" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="619">
@@ -14950,14 +14950,14 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C619" t="inlineStr"/>
       <c r="D619" t="inlineStr"/>
       <c r="E619" t="inlineStr"/>
       <c r="F619" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="620">
@@ -16070,14 +16070,18 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C673" t="inlineStr"/>
       <c r="D673" t="inlineStr"/>
-      <c r="E673" t="inlineStr"/>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="F673" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="674">
@@ -16142,18 +16146,14 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C677" t="inlineStr"/>
       <c r="D677" t="inlineStr"/>
-      <c r="E677" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="E677" t="inlineStr"/>
       <c r="F677" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="678">
@@ -16164,7 +16164,7 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C678" t="inlineStr"/>
@@ -16200,7 +16200,7 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C680" t="inlineStr"/>
@@ -16290,7 +16290,7 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
       <c r="C685" t="inlineStr"/>
@@ -16416,7 +16416,7 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>Money SupplyJAN</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C692" t="inlineStr"/>
@@ -16434,7 +16434,7 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>Money SupplyJAN</t>
         </is>
       </c>
       <c r="C693" t="inlineStr"/>
@@ -16560,7 +16560,7 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C700" t="inlineStr"/>
@@ -16614,7 +16614,7 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C703" t="inlineStr"/>
@@ -16704,7 +16704,7 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>New Home Sales MoMJAN</t>
+          <t>New Home SalesJAN</t>
         </is>
       </c>
       <c r="C708" t="inlineStr"/>
@@ -16758,7 +16758,7 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>New Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C711" t="inlineStr"/>
@@ -16776,7 +16776,7 @@
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>New Home SalesJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C712" t="inlineStr"/>
@@ -16794,7 +16794,7 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C713" t="inlineStr"/>
@@ -17100,7 +17100,7 @@
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+          <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C730" t="inlineStr"/>
@@ -17118,7 +17118,7 @@
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/21</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
       <c r="C731" t="inlineStr"/>
@@ -17610,14 +17610,14 @@
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMJAN</t>
+          <t>Continuing Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C757" t="inlineStr"/>
       <c r="D757" t="inlineStr"/>
       <c r="E757" t="inlineStr"/>
       <c r="F757" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="758">
@@ -17672,22 +17672,22 @@
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ 2nd EstQ4</t>
+          <t>Core PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C760" t="inlineStr"/>
       <c r="D760" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="E760" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F760" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="761">
@@ -17720,22 +17720,22 @@
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ 2nd EstQ4</t>
+          <t>GDP Price Index QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C762" t="inlineStr"/>
       <c r="D762" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="E762" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="F762" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="763">
@@ -17746,14 +17746,14 @@
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/15</t>
+          <t>Durable Goods Orders Ex Transp MoMJAN</t>
         </is>
       </c>
       <c r="C763" t="inlineStr"/>
       <c r="D763" t="inlineStr"/>
       <c r="E763" t="inlineStr"/>
       <c r="F763" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="764">
@@ -17764,22 +17764,14 @@
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
+          <t>Initial Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C764" t="inlineStr"/>
-      <c r="D764" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
-      <c r="E764" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
+      <c r="D764" t="inlineStr"/>
+      <c r="E764" t="inlineStr"/>
       <c r="F764" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="765">
@@ -17790,14 +17782,22 @@
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/22</t>
+          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C765" t="inlineStr"/>
-      <c r="D765" t="inlineStr"/>
-      <c r="E765" t="inlineStr"/>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="E765" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
       <c r="F765" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="766">
@@ -17826,12 +17826,16 @@
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/22</t>
+          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C767" t="inlineStr"/>
       <c r="D767" t="inlineStr"/>
-      <c r="E767" t="inlineStr"/>
+      <c r="E767" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="F767" t="n">
         <v>3</v>
       </c>
@@ -17844,7 +17848,7 @@
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirJAN</t>
+          <t>Durable Goods Orders ex Defense MoMJAN</t>
         </is>
       </c>
       <c r="C768" t="inlineStr"/>
@@ -17862,14 +17866,18 @@
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ 2nd EstQ4</t>
+          <t>PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C769" t="inlineStr"/>
-      <c r="D769" t="inlineStr"/>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
       <c r="E769" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F769" t="n">
@@ -17906,18 +17914,14 @@
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ 2nd EstQ4</t>
+          <t>GDP Sales QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C771" t="inlineStr"/>
-      <c r="D771" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
+      <c r="D771" t="inlineStr"/>
       <c r="E771" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F771" t="n">
@@ -17932,7 +17936,7 @@
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMJAN</t>
+          <t>Non Defense Goods Orders Ex AirJAN</t>
         </is>
       </c>
       <c r="C772" t="inlineStr"/>
@@ -17950,16 +17954,12 @@
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
+          <t>Jobless Claims 4-week AverageFEB/22</t>
         </is>
       </c>
       <c r="C773" t="inlineStr"/>
       <c r="D773" t="inlineStr"/>
-      <c r="E773" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="E773" t="inlineStr"/>
       <c r="F773" t="n">
         <v>3</v>
       </c>

--- a/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-02-27.xlsx
+++ b/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-02-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F794"/>
+  <dimension ref="A1:F795"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -720,12 +720,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -742,12 +742,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.041M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -764,18 +764,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>7.717M</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0.7M</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -786,19 +790,15 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>6.406M</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>-0.1M</t>
-        </is>
-      </c>
+          <t>-0.416M</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
         <v>3</v>
@@ -812,22 +812,18 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.178M</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>-2.75M</t>
-        </is>
-      </c>
+          <t>0.041M</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -838,15 +834,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.416M</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>-0.1M</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
         <v>3</v>
@@ -860,22 +860,18 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -886,12 +882,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.142M</t>
+          <t>0.099M</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -908,18 +904,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.323M</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1582,22 +1582,18 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Balance of TradeNOV</t>
+          <t>ExportsNOV</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>$-78.2B</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>$-78B</t>
-        </is>
-      </c>
+          <t>$273.4B</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>$-70B</t>
+          <t>$264B</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -1612,18 +1608,18 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ExportsNOV</t>
+          <t>ImportsNOV</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>$273.4B</t>
+          <t>$351.6B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>$264B</t>
+          <t>$334B</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -1638,18 +1634,22 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ImportsNOV</t>
+          <t>Balance of TradeNOV</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>$351.6B</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
+          <t>$-78.2B</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>$-78B</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>$334B</t>
+          <t>$-70B</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Used Car Prices MoMDEC</t>
+          <t>Used Car Prices YoYDEC</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -2254,12 +2254,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Used Car Prices YoYDEC</t>
+          <t>Used Car Prices MoMDEC</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -3148,18 +3148,18 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelJAN</t>
+          <t>Michigan Consumer Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F112" t="n">
@@ -3174,22 +3174,26 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
+          <t>Michigan Consumer Sentiment PrelJAN</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr"/>
+          <t>73.2</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>73.8</t>
+        </is>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114">
@@ -3200,18 +3204,18 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelJAN</t>
+          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F114" t="n">
@@ -3226,26 +3230,22 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelJAN</t>
+          <t>Michigan Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>73.2</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>73.8</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="116">
@@ -3256,18 +3256,18 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelJAN</t>
+          <t>Michigan Current Conditions PrelJAN</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F116" t="n">
@@ -3458,12 +3458,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>4.180%</t>
+          <t>4.225%</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
@@ -3480,12 +3480,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>4.225%</t>
+          <t>4.180%</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
@@ -4010,22 +4010,22 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMDEC</t>
+          <t>Core Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F147" t="n">
@@ -4040,26 +4040,26 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexJAN</t>
+          <t>Core Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>-12.60</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="149">
@@ -4070,22 +4070,26 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>CPI s.aDEC</t>
+          <t>Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>317.685</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr"/>
+          <t>2.9%</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>2.9%</t>
+        </is>
+      </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>317.4</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150">
@@ -4096,26 +4100,26 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYDEC</t>
+          <t>CPIDEC</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>315.6</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="151">
@@ -4126,22 +4130,22 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>CPIDEC</t>
+          <t>NY Empire State Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>-12.60</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>315.6</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="F151" t="n">
@@ -4156,22 +4160,22 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMDEC</t>
+          <t>Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F152" t="n">
@@ -4186,26 +4190,22 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYDEC</t>
+          <t>CPI s.aDEC</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+          <t>317.685</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>317.4</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="154">
@@ -4252,19 +4252,15 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>3.077M</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>1.1M</t>
-        </is>
-      </c>
+          <t>0.765M</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="n">
         <v>3</v>
@@ -4278,12 +4274,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>-0.021M</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
@@ -4300,18 +4296,22 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>0.397M</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr"/>
+          <t>-1.961M</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>-1.6M</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="159">
@@ -4322,18 +4322,22 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>0.646M</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>2.60M</t>
+        </is>
+      </c>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="160">
@@ -4344,22 +4348,18 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>2.60M</t>
-        </is>
-      </c>
+          <t>-1.304M</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="161">
@@ -4370,12 +4370,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>-1.304M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
@@ -4392,22 +4392,18 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>-1.961M</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>-1.6M</t>
-        </is>
-      </c>
+          <t>-0.255M</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="163">
@@ -4418,15 +4414,19 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>-0.021M</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr"/>
+          <t>3.077M</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>1.1M</t>
+        </is>
+      </c>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="n">
         <v>3</v>
@@ -4440,12 +4440,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>0.765M</t>
+          <t>0.646M</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
@@ -4556,26 +4556,18 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
+          <t>46.3</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" t="inlineStr"/>
       <c r="F170" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="171">
@@ -4586,22 +4578,22 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F171" t="n">
@@ -4616,16 +4608,20 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
-      <c r="E172" t="inlineStr"/>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>4.0%</t>
+        </is>
+      </c>
       <c r="F172" t="n">
         <v>3</v>
       </c>
@@ -4638,18 +4634,26 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>39.00</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr"/>
-      <c r="E173" t="inlineStr"/>
+          <t>217K</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>210K</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>209.0K</t>
+        </is>
+      </c>
       <c r="F173" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="174">
@@ -4660,20 +4664,16 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>212.75K</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>215.0K</t>
-        </is>
-      </c>
+      <c r="E174" t="inlineStr"/>
       <c r="F174" t="n">
         <v>3</v>
       </c>
@@ -4686,26 +4686,26 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F175" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="176">
@@ -4716,22 +4716,22 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>217K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>210K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F176" t="n">
@@ -4746,18 +4746,22 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>1.8%</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="F177" t="n">
@@ -4772,16 +4776,24 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>11.9</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr"/>
-      <c r="E178" t="inlineStr"/>
+          <t>1859K</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>1870.0K</t>
+        </is>
+      </c>
       <c r="F178" t="n">
         <v>3</v>
       </c>
@@ -4794,22 +4806,22 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F179" t="n">
@@ -4824,26 +4836,22 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>1.8%</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F180" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="181">
@@ -4854,26 +4862,18 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr"/>
+      <c r="E181" t="inlineStr"/>
       <c r="F181" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="182">
@@ -4884,16 +4884,20 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>212.75K</t>
         </is>
       </c>
       <c r="D182" t="inlineStr"/>
-      <c r="E182" t="inlineStr"/>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>215.0K</t>
+        </is>
+      </c>
       <c r="F182" t="n">
         <v>3</v>
       </c>
@@ -4906,20 +4910,16 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>39.00</t>
         </is>
       </c>
       <c r="D183" t="inlineStr"/>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>4.0%</t>
-        </is>
-      </c>
+      <c r="E183" t="inlineStr"/>
       <c r="F183" t="n">
         <v>3</v>
       </c>
@@ -4932,24 +4932,16 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>1.6%</t>
-        </is>
-      </c>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
+      <c r="E184" t="inlineStr"/>
       <c r="F184" t="n">
         <v>3</v>
       </c>
@@ -4962,18 +4954,26 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr"/>
-      <c r="E185" t="inlineStr"/>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>-10</t>
+        </is>
+      </c>
       <c r="F185" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="186">
@@ -4984,26 +4984,26 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F186" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="187">
@@ -5014,26 +5014,26 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoMNOV</t>
+          <t>NAHB Housing Market IndexJAN</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F187" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="188">
@@ -5044,22 +5044,22 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>NAHB Housing Market IndexJAN</t>
+          <t>Business Inventories MoMNOV</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F188" t="n">
@@ -5074,17 +5074,17 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Business Inventories MoMNOV</t>
+          <t>Retail Inventories Ex Autos MoMNOV</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -5093,7 +5093,7 @@
         </is>
       </c>
       <c r="F189" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="190">
@@ -5240,22 +5240,26 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Housing Starts MoMDEC</t>
+          <t>Housing StartsDEC</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>15.8%</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr"/>
+          <t>1.499M</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>1.32M</t>
+        </is>
+      </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>1.32M</t>
         </is>
       </c>
       <c r="F196" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="197">
@@ -5266,18 +5270,18 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelDEC</t>
+          <t>Housing Starts MoMDEC</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>15.8%</t>
         </is>
       </c>
       <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="F197" t="n">
@@ -5292,26 +5296,22 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Housing StartsDEC</t>
+          <t>Building Permits MoM PrelDEC</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>1.499M</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>1.32M</t>
-        </is>
-      </c>
+          <t>-0.7%</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr">
         <is>
-          <t>1.32M</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="F198" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="199">
@@ -5352,18 +5352,18 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Industrial Production YoYDEC</t>
+          <t>Manufacturing Production YoYDEC</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F200" t="n">
@@ -5378,26 +5378,26 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Capacity UtilizationDEC</t>
+          <t>Industrial Production MoMDEC</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F201" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="202">
@@ -5438,26 +5438,26 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Industrial Production MoMDEC</t>
+          <t>Capacity UtilizationDEC</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="F203" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="204">
@@ -5468,18 +5468,18 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYDEC</t>
+          <t>Industrial Production YoYDEC</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D204" t="inlineStr"/>
       <c r="E204" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F204" t="n">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>42-Day Bill Auction</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>4.025%</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
@@ -5692,12 +5692,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>42-Day Bill Auction</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>4.025%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
@@ -5942,22 +5942,18 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/11</t>
+          <t>Jobless Claims 4-week AverageJAN/18</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>1899K</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>1860K</t>
-        </is>
-      </c>
+          <t>213.5K</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr"/>
       <c r="E225" t="inlineStr">
         <is>
-          <t>1861K</t>
+          <t>213.0K</t>
         </is>
       </c>
       <c r="F225" t="n">
@@ -5972,22 +5968,26 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/18</t>
+          <t>Initial Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>213.5K</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr"/>
+          <t>223K</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>220K</t>
+        </is>
+      </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>213.0K</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="F226" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="227">
@@ -5998,26 +5998,26 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/18</t>
+          <t>Continuing Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>1899K</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>220K</t>
+          <t>1860K</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>1861K</t>
         </is>
       </c>
       <c r="F227" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="228">
@@ -6150,18 +6150,22 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>6.96%</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E233" t="inlineStr"/>
       <c r="F233" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="234">
@@ -6172,12 +6176,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
@@ -6194,15 +6198,19 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>-1.125M</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="n">
         <v>3</v>
@@ -6216,12 +6224,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -6238,22 +6246,18 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>-0.148M</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr"/>
       <c r="E237" t="inlineStr"/>
       <c r="F237" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="238">
@@ -6264,18 +6268,22 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>0.184M</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="239">
@@ -6286,22 +6294,18 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>0.068M</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr"/>
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="240">
@@ -6312,12 +6316,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
@@ -6334,12 +6338,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D241" t="inlineStr"/>
@@ -6356,19 +6360,15 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>6.96%</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr"/>
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="n">
         <v>3</v>
@@ -6382,12 +6382,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
@@ -6448,22 +6448,22 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashJAN</t>
+          <t>S&amp;P Global Manufacturing PMI FlashJAN</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="F246" t="n">
@@ -6478,22 +6478,22 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashJAN</t>
+          <t>S&amp;P Global Services PMI FlashJAN</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="F247" t="n">
@@ -6534,26 +6534,26 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F249" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="250">
@@ -6564,22 +6564,26 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr"/>
+          <t>69.3</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>70.2</t>
+        </is>
+      </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F250" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="251">
@@ -6590,26 +6594,26 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>4.24M</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.19M</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="F251" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="252">
@@ -6620,12 +6624,12 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -6650,26 +6654,26 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>4.24M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>4.19M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F253" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="254">
@@ -6680,26 +6684,22 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="D254" t="inlineStr">
-        <is>
-          <t>77.9</t>
-        </is>
-      </c>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr"/>
       <c r="E254" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F254" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="255">
@@ -6710,26 +6710,26 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F255" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="256">
@@ -7178,18 +7178,22 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
+          <t>House Price Index MoMNOV</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="D273" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F273" t="n">
@@ -7204,18 +7208,18 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>House Price Index YoYNOV</t>
+          <t>House Price IndexNOV</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>433.4</t>
         </is>
       </c>
       <c r="D274" t="inlineStr"/>
       <c r="E274" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>433</t>
         </is>
       </c>
       <c r="F274" t="n">
@@ -7260,18 +7264,18 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>House Price IndexNOV</t>
+          <t>House Price Index YoYNOV</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>433.4</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="D276" t="inlineStr"/>
       <c r="E276" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F276" t="n">
@@ -7286,22 +7290,18 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>House Price Index MoMNOV</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D277" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>-0.1%</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr"/>
       <c r="E277" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F277" t="n">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>Money SupplyDEC</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>4.457%</t>
+          <t>$21.53T</t>
         </is>
       </c>
       <c r="D286" t="inlineStr"/>
@@ -7546,12 +7546,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Money SupplyDEC</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>$21.53T</t>
+          <t>4.457%</t>
         </is>
       </c>
       <c r="D287" t="inlineStr"/>
@@ -7790,19 +7790,15 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>-4.994M</t>
-        </is>
-      </c>
-      <c r="D297" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.128M</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr"/>
       <c r="E297" t="inlineStr"/>
       <c r="F297" t="n">
         <v>3</v>
@@ -7816,18 +7812,22 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>-0.333M</t>
-        </is>
-      </c>
-      <c r="D298" t="inlineStr"/>
+          <t>3.463M</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>3.2M</t>
+        </is>
+      </c>
       <c r="E298" t="inlineStr"/>
       <c r="F298" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="299">
@@ -7838,22 +7838,18 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>2.957M</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>0.532M</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr"/>
       <c r="E299" t="inlineStr"/>
       <c r="F299" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="300">
@@ -7864,12 +7860,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>0.028M</t>
+          <t>-0.044M</t>
         </is>
       </c>
       <c r="D300" t="inlineStr"/>
@@ -7886,12 +7882,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>-0.044M</t>
+          <t>0.326M</t>
         </is>
       </c>
       <c r="D301" t="inlineStr"/>
@@ -7908,17 +7904,17 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>3.463M</t>
+          <t>2.957M</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>3.2M</t>
+          <t>1.5M</t>
         </is>
       </c>
       <c r="E302" t="inlineStr"/>
@@ -7934,12 +7930,12 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>0.326M</t>
+          <t>0.028M</t>
         </is>
       </c>
       <c r="D303" t="inlineStr"/>
@@ -7956,12 +7952,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>0.128M</t>
+          <t>-0.333M</t>
         </is>
       </c>
       <c r="D304" t="inlineStr"/>
@@ -7978,15 +7974,19 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>0.532M</t>
-        </is>
-      </c>
-      <c r="D305" t="inlineStr"/>
+          <t>-4.994M</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E305" t="inlineStr"/>
       <c r="F305" t="n">
         <v>3</v>
@@ -8070,18 +8070,22 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ AdvQ4</t>
+          <t>Core PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="D309" t="inlineStr"/>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F309" t="n">
@@ -8096,22 +8100,26 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ AdvQ4</t>
+          <t>GDP Price Index QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D310" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F310" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="311">
@@ -8122,18 +8130,22 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ AdvQ4</t>
+          <t>Continuing Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>2.3%</t>
-        </is>
-      </c>
-      <c r="D311" t="inlineStr"/>
+          <t>1858K</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>1890K</t>
+        </is>
+      </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>1885.0K</t>
         </is>
       </c>
       <c r="F311" t="n">
@@ -8148,22 +8160,26 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/25</t>
+          <t>GDP Growth Rate QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>212.5K</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr"/>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>214.0K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F312" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="313">
@@ -8174,26 +8190,26 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ AdvQ4</t>
+          <t>Initial Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>207K</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>228.0K</t>
         </is>
       </c>
       <c r="F313" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="314">
@@ -8204,22 +8220,18 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/18</t>
+          <t>PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>1858K</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr">
-        <is>
-          <t>1890K</t>
-        </is>
-      </c>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr"/>
       <c r="E314" t="inlineStr">
         <is>
-          <t>1885.0K</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="F314" t="n">
@@ -8234,26 +8246,22 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ AdvQ4</t>
+          <t>GDP Sales QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr"/>
       <c r="E315" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F315" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="316">
@@ -8264,26 +8272,22 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/25</t>
+          <t>Jobless Claims 4-week AverageJAN/25</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>207K</t>
-        </is>
-      </c>
-      <c r="D316" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+          <t>212.5K</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr"/>
       <c r="E316" t="inlineStr">
         <is>
-          <t>228.0K</t>
+          <t>214.0K</t>
         </is>
       </c>
       <c r="F316" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="317">
@@ -8294,22 +8298,18 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ AdvQ4</t>
+          <t>Real Consumer Spending QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>2.5%</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr"/>
       <c r="E317" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F317" t="n">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D321" t="inlineStr"/>
@@ -8428,12 +8428,12 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="D322" t="inlineStr"/>
@@ -8516,18 +8516,22 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D326" t="inlineStr"/>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F326" t="n">
@@ -8542,22 +8546,26 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
+          <t>Core PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="D327" t="inlineStr"/>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F327" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="328">
@@ -8568,22 +8576,22 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F328" t="n">
@@ -8598,24 +8606,12 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
-        </is>
-      </c>
-      <c r="C329" t="inlineStr">
-        <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D329" t="inlineStr">
-        <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="E329" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr"/>
+      <c r="D329" t="inlineStr"/>
+      <c r="E329" t="inlineStr"/>
       <c r="F329" t="n">
         <v>2</v>
       </c>
@@ -8628,26 +8624,26 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F330" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="331">
@@ -8658,22 +8654,18 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
+          <t>Employment Cost - Wages QoQQ4</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D331" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr"/>
       <c r="E331" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F331" t="n">
@@ -8688,22 +8680,22 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F332" t="n">
@@ -8718,14 +8710,26 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C333" t="inlineStr"/>
-      <c r="D333" t="inlineStr"/>
-      <c r="E333" t="inlineStr"/>
+          <t>Personal Income MoMDEC</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F333" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="334">
@@ -8736,26 +8740,22 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
+          <t>Employment Cost - Benefits QoQQ4</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr"/>
       <c r="E334" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F334" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="335">
@@ -8766,26 +8766,26 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F335" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="336">
@@ -8904,26 +8904,26 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesJAN</t>
+          <t>ISM Manufacturing PMIJAN</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="F340" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="341">
@@ -8934,22 +8934,26 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentJAN</t>
+          <t>Construction Spending MoMDEC</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>50.3</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F341" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="342">
@@ -8960,22 +8964,22 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersJAN</t>
+          <t>ISM Manufacturing EmploymentJAN</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="D342" t="inlineStr"/>
       <c r="E342" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F342" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="343">
@@ -8986,22 +8990,22 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Construction Spending MoMDEC</t>
+          <t>ISM Manufacturing PricesJAN</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F343" t="n">
@@ -9016,26 +9020,22 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIJAN</t>
+          <t>ISM Manufacturing New OrdersJAN</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>50.9</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr">
-        <is>
-          <t>49.8</t>
-        </is>
-      </c>
+          <t>55.1</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr"/>
       <c r="E344" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F344" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="345">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/31</t>
+          <t>MBA Mortgage ApplicationsJAN/31</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>584.3</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D363" t="inlineStr"/>
@@ -9472,18 +9472,18 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/31</t>
+          <t>MBA 30-Year Mortgage RateJAN/31</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>224.8</t>
+          <t>6.97%</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
       <c r="E364" t="inlineStr"/>
       <c r="F364" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="365">
@@ -9516,18 +9516,18 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/31</t>
+          <t>MBA Mortgage Market IndexJAN/31</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>6.97%</t>
+          <t>224.8</t>
         </is>
       </c>
       <c r="D366" t="inlineStr"/>
       <c r="E366" t="inlineStr"/>
       <c r="F366" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="367">
@@ -9538,12 +9538,12 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/31</t>
+          <t>MBA Mortgage Refinance IndexJAN/31</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>584.3</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
@@ -9768,18 +9768,18 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersJAN</t>
+          <t>ISM Services Business ActivityJAN</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="D376" t="inlineStr"/>
       <c r="E376" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="F376" t="n">
@@ -9794,22 +9794,26 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>ISM Services PricesJAN</t>
+          <t>ISM Services PMIJAN</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>60.4</t>
-        </is>
-      </c>
-      <c r="D377" t="inlineStr"/>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>54.3</t>
+        </is>
+      </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F377" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="378">
@@ -9846,26 +9850,22 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>ISM Services PMIJAN</t>
+          <t>ISM Services PricesJAN</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>52.8</t>
-        </is>
-      </c>
-      <c r="D379" t="inlineStr">
-        <is>
-          <t>54.3</t>
-        </is>
-      </c>
+          <t>60.4</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr"/>
       <c r="E379" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="F379" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="380">
@@ -9876,18 +9876,18 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityJAN</t>
+          <t>ISM Services New OrdersJAN</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="D380" t="inlineStr"/>
       <c r="E380" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F380" t="n">
@@ -10434,12 +10434,12 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/06</t>
+          <t>30-Year Mortgage RateFEB/06</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>6.05%</t>
+          <t>6.89%</t>
         </is>
       </c>
       <c r="D403" t="inlineStr"/>
@@ -10456,12 +10456,12 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/06</t>
+          <t>15-Year Mortgage RateFEB/06</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>6.89%</t>
+          <t>6.05%</t>
         </is>
       </c>
       <c r="D404" t="inlineStr"/>
@@ -10536,22 +10536,26 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Participation RateJAN</t>
+          <t>Average Weekly HoursJAN</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>62.6%</t>
-        </is>
-      </c>
-      <c r="D408" t="inlineStr"/>
+          <t>34.1</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F408" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="409">
@@ -10562,22 +10566,26 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Government PayrollsJAN</t>
+          <t>Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>32K</t>
-        </is>
-      </c>
-      <c r="D409" t="inlineStr"/>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>4.1%</t>
+        </is>
+      </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>25K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F409" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="410">
@@ -10588,26 +10596,26 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoYJAN</t>
+          <t>Manufacturing PayrollsJAN</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>3K</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>-2K</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>-5K</t>
         </is>
       </c>
       <c r="F410" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="411">
@@ -10618,26 +10626,26 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsJAN</t>
+          <t>Average Hourly Earnings MoMJAN</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>143K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>170K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>205K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F411" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="412">
@@ -10648,22 +10656,18 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateJAN</t>
+          <t>U-6 Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>111K</t>
-        </is>
-      </c>
-      <c r="D412" t="inlineStr">
-        <is>
-          <t>141K</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr"/>
       <c r="E412" t="inlineStr">
         <is>
-          <t>180K</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="F412" t="n">
@@ -10678,26 +10682,26 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMJAN</t>
+          <t>Non Farm PayrollsJAN</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>143K</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>170K</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>205K</t>
         </is>
       </c>
       <c r="F413" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="414">
@@ -10708,26 +10712,26 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsJAN</t>
+          <t>Average Hourly Earnings YoYJAN</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>3K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>-2K</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>-5K</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="F414" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="415">
@@ -10738,26 +10742,22 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Unemployment RateJAN</t>
+          <t>Government PayrollsJAN</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>4%</t>
-        </is>
-      </c>
-      <c r="D415" t="inlineStr">
-        <is>
-          <t>4.1%</t>
-        </is>
-      </c>
+          <t>32K</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr"/>
       <c r="E415" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>25K</t>
         </is>
       </c>
       <c r="F415" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="416">
@@ -10768,22 +10768,22 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>U-6 Unemployment RateJAN</t>
+          <t>Participation RateJAN</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="D416" t="inlineStr"/>
       <c r="E416" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="F416" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="417">
@@ -10794,22 +10794,22 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Average Weekly HoursJAN</t>
+          <t>Nonfarm Payrolls PrivateJAN</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>111K</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>141K</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>180K</t>
         </is>
       </c>
       <c r="F417" t="n">
@@ -10904,22 +10904,26 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelFEB</t>
+          <t>Michigan Consumer Sentiment PrelFEB</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="D422" t="inlineStr"/>
+          <t>67.8</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>71.1</t>
+        </is>
+      </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F422" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="423">
@@ -10930,22 +10934,18 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelFEB</t>
+          <t>Michigan Inflation Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>67.3</t>
-        </is>
-      </c>
-      <c r="D423" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr"/>
       <c r="E423" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F423" t="n">
@@ -10960,18 +10960,22 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelFEB</t>
+          <t>Michigan Consumer Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D424" t="inlineStr"/>
+          <t>67.3</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="F424" t="n">
@@ -10986,22 +10990,18 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelFEB</t>
+          <t>Michigan 5 Year Inflation Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>68.7</t>
-        </is>
-      </c>
-      <c r="D425" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr"/>
       <c r="E425" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F425" t="n">
@@ -11016,22 +11016,22 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoMDEC</t>
+          <t>Michigan Current Conditions PrelFEB</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>73</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="F426" t="n">
@@ -11046,26 +11046,26 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelFEB</t>
+          <t>Wholesale Inventories MoMDEC</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F427" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="428">
@@ -11564,22 +11564,18 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>CPI s.aJAN</t>
         </is>
       </c>
       <c r="C452" t="inlineStr"/>
-      <c r="D452" t="inlineStr">
-        <is>
-          <t>2.9%</t>
-        </is>
-      </c>
+      <c r="D452" t="inlineStr"/>
       <c r="E452" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>318.2</t>
         </is>
       </c>
       <c r="F452" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="453">
@@ -11590,22 +11586,22 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>CPIJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C453" t="inlineStr"/>
       <c r="D453" t="inlineStr">
         <is>
-          <t>317.42</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>317.3</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F453" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="454">
@@ -11616,7 +11612,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C454" t="inlineStr"/>
@@ -11627,7 +11623,7 @@
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F454" t="n">
@@ -11642,22 +11638,22 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>CPIJAN</t>
         </is>
       </c>
       <c r="C455" t="inlineStr"/>
       <c r="D455" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>317.42</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>317.3</t>
         </is>
       </c>
       <c r="F455" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="456">
@@ -11668,18 +11664,18 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C456" t="inlineStr"/>
       <c r="D456" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F456" t="n">
@@ -11694,18 +11690,22 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>CPI s.aJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C457" t="inlineStr"/>
-      <c r="D457" t="inlineStr"/>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>318.2</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F457" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="458">
@@ -11716,7 +11716,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C458" t="inlineStr"/>
@@ -11734,7 +11734,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C459" t="inlineStr"/>
@@ -11752,14 +11752,14 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C460" t="inlineStr"/>
       <c r="D460" t="inlineStr"/>
       <c r="E460" t="inlineStr"/>
       <c r="F460" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="461">
@@ -11770,14 +11770,14 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C461" t="inlineStr"/>
       <c r="D461" t="inlineStr"/>
       <c r="E461" t="inlineStr"/>
       <c r="F461" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="462">
@@ -11788,14 +11788,14 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C462" t="inlineStr"/>
       <c r="D462" t="inlineStr"/>
       <c r="E462" t="inlineStr"/>
       <c r="F462" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="463">
@@ -11806,14 +11806,14 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C463" t="inlineStr"/>
       <c r="D463" t="inlineStr"/>
       <c r="E463" t="inlineStr"/>
       <c r="F463" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="464">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C464" t="inlineStr"/>
@@ -11842,7 +11842,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C465" t="inlineStr"/>
@@ -11860,7 +11860,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C466" t="inlineStr"/>
@@ -11976,22 +11976,22 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C472" t="inlineStr"/>
       <c r="D472" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F472" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="473">
@@ -12002,14 +12002,14 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C473" t="inlineStr"/>
       <c r="D473" t="inlineStr"/>
       <c r="E473" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="F473" t="n">
@@ -12024,14 +12024,14 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C474" t="inlineStr"/>
       <c r="D474" t="inlineStr"/>
       <c r="E474" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F474" t="n">
@@ -12046,22 +12046,18 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C475" t="inlineStr"/>
-      <c r="D475" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D475" t="inlineStr"/>
       <c r="E475" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="F475" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="476">
@@ -12072,18 +12068,18 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C476" t="inlineStr"/>
       <c r="D476" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F476" t="n">
@@ -12098,18 +12094,22 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C477" t="inlineStr"/>
-      <c r="D477" t="inlineStr"/>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F477" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="478">
@@ -12120,14 +12120,14 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C478" t="inlineStr"/>
       <c r="D478" t="inlineStr"/>
       <c r="E478" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="F478" t="n">
@@ -12142,18 +12142,18 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C479" t="inlineStr"/>
       <c r="D479" t="inlineStr">
         <is>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
           <t>3.3%</t>
-        </is>
-      </c>
-      <c r="E479" t="inlineStr">
-        <is>
-          <t>3.5%</t>
         </is>
       </c>
       <c r="F479" t="n">
@@ -12168,22 +12168,18 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C480" t="inlineStr"/>
-      <c r="D480" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
+      <c r="D480" t="inlineStr"/>
       <c r="E480" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F480" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="481">
@@ -12194,18 +12190,22 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C481" t="inlineStr"/>
-      <c r="D481" t="inlineStr"/>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F481" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="482">
@@ -12252,7 +12252,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C484" t="inlineStr"/>
@@ -12270,7 +12270,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C485" t="inlineStr"/>
@@ -12360,18 +12360,22 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="C490" t="inlineStr"/>
-      <c r="D490" t="inlineStr"/>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F490" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="491">
@@ -12382,18 +12386,22 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="C491" t="inlineStr"/>
-      <c r="D491" t="inlineStr"/>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F491" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="492">
@@ -12404,22 +12412,18 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="C492" t="inlineStr"/>
-      <c r="D492" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D492" t="inlineStr"/>
       <c r="E492" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F492" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="493">
@@ -12430,18 +12434,22 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="C493" t="inlineStr"/>
-      <c r="D493" t="inlineStr"/>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="F493" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="494">
@@ -12452,14 +12460,14 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="C494" t="inlineStr"/>
       <c r="D494" t="inlineStr"/>
       <c r="E494" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F494" t="n">
@@ -12474,22 +12482,18 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="C495" t="inlineStr"/>
-      <c r="D495" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
+      <c r="D495" t="inlineStr"/>
       <c r="E495" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F495" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="496">
@@ -12500,7 +12504,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="C496" t="inlineStr"/>
@@ -12526,14 +12530,14 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="C497" t="inlineStr"/>
       <c r="D497" t="inlineStr"/>
       <c r="E497" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F497" t="n">
@@ -12548,22 +12552,18 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="C498" t="inlineStr"/>
-      <c r="D498" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D498" t="inlineStr"/>
       <c r="E498" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F498" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="499">
@@ -12574,18 +12574,18 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="C499" t="inlineStr"/>
       <c r="D499" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>77.7%</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="F499" t="n">
@@ -12600,14 +12600,18 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Manufacturing Production MoMJAN</t>
         </is>
       </c>
       <c r="C500" t="inlineStr"/>
-      <c r="D500" t="inlineStr"/>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F500" t="n">
@@ -12622,22 +12626,18 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="C501" t="inlineStr"/>
-      <c r="D501" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="D501" t="inlineStr"/>
       <c r="E501" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F501" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="502">
@@ -12648,22 +12648,22 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="C502" t="inlineStr"/>
       <c r="D502" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F502" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="503">
@@ -12696,22 +12696,22 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>Business Inventories MoMDEC</t>
+          <t>Retail Inventories Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C504" t="inlineStr"/>
       <c r="D504" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F504" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="505">
@@ -12722,22 +12722,22 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoMDEC</t>
+          <t>Business Inventories MoMDEC</t>
         </is>
       </c>
       <c r="C505" t="inlineStr"/>
       <c r="D505" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F505" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="506">
@@ -12748,7 +12748,7 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/14</t>
+          <t>Baker Hughes Oil Rig CountFEB/14</t>
         </is>
       </c>
       <c r="C506" t="inlineStr"/>
@@ -12766,7 +12766,7 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/14</t>
+          <t>Baker Hughes Total Rigs CountFEB/14</t>
         </is>
       </c>
       <c r="C507" t="inlineStr"/>
@@ -13068,7 +13068,7 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C522" t="inlineStr"/>
@@ -13086,7 +13086,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C523" t="inlineStr"/>
@@ -13176,14 +13176,14 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C528" t="inlineStr"/>
       <c r="D528" t="inlineStr"/>
       <c r="E528" t="inlineStr"/>
       <c r="F528" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="529">
@@ -13194,14 +13194,14 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="C529" t="inlineStr"/>
       <c r="D529" t="inlineStr"/>
       <c r="E529" t="inlineStr"/>
       <c r="F529" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="530">
@@ -13230,14 +13230,18 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Net Long-term TIC FlowsDEC</t>
         </is>
       </c>
       <c r="C531" t="inlineStr"/>
-      <c r="D531" t="inlineStr"/>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>$149.1B</t>
+        </is>
+      </c>
       <c r="E531" t="inlineStr"/>
       <c r="F531" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="532">
@@ -13266,18 +13270,14 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsDEC</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C533" t="inlineStr"/>
-      <c r="D533" t="inlineStr">
-        <is>
-          <t>$149.1B</t>
-        </is>
-      </c>
+      <c r="D533" t="inlineStr"/>
       <c r="E533" t="inlineStr"/>
       <c r="F533" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="534">
@@ -13288,14 +13288,18 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Net Long-term TIC FlowsDEC</t>
         </is>
       </c>
       <c r="C534" t="inlineStr"/>
-      <c r="D534" t="inlineStr"/>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>$149.1B</t>
+        </is>
+      </c>
       <c r="E534" t="inlineStr"/>
       <c r="F534" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="535">
@@ -13306,7 +13310,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="C535" t="inlineStr"/>
@@ -13324,18 +13328,14 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsDEC</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C536" t="inlineStr"/>
-      <c r="D536" t="inlineStr">
-        <is>
-          <t>$149.1B</t>
-        </is>
-      </c>
+      <c r="D536" t="inlineStr"/>
       <c r="E536" t="inlineStr"/>
       <c r="F536" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="537">
@@ -13454,7 +13454,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C543" t="inlineStr"/>
@@ -13472,14 +13472,14 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C544" t="inlineStr"/>
       <c r="D544" t="inlineStr"/>
       <c r="E544" t="inlineStr"/>
       <c r="F544" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="545">
@@ -13490,14 +13490,14 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C545" t="inlineStr"/>
       <c r="D545" t="inlineStr"/>
       <c r="E545" t="inlineStr"/>
       <c r="F545" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="546">
@@ -13508,7 +13508,7 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C546" t="inlineStr"/>
@@ -13552,22 +13552,18 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C548" t="inlineStr"/>
-      <c r="D548" t="inlineStr">
-        <is>
-          <t>1.4M</t>
-        </is>
-      </c>
+      <c r="D548" t="inlineStr"/>
       <c r="E548" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F548" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="549">
@@ -13600,18 +13596,22 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C550" t="inlineStr"/>
-      <c r="D550" t="inlineStr"/>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>1.4M</t>
+        </is>
+      </c>
       <c r="E550" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F550" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="551">
@@ -13622,14 +13622,14 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C551" t="inlineStr"/>
       <c r="D551" t="inlineStr"/>
       <c r="E551" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F551" t="n">
@@ -13644,18 +13644,18 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C552" t="inlineStr"/>
       <c r="D552" t="inlineStr">
         <is>
-          <t>1.46M</t>
+          <t>1.4M</t>
         </is>
       </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F552" t="n">
@@ -13670,22 +13670,18 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C553" t="inlineStr"/>
-      <c r="D553" t="inlineStr">
-        <is>
-          <t>1.4M</t>
-        </is>
-      </c>
+      <c r="D553" t="inlineStr"/>
       <c r="E553" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F553" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="554">
@@ -13696,18 +13692,22 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C554" t="inlineStr"/>
-      <c r="D554" t="inlineStr"/>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>1.46M</t>
+        </is>
+      </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F554" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="555">
@@ -14142,22 +14142,22 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C577" t="inlineStr"/>
       <c r="D577" t="inlineStr">
         <is>
-          <t>16.3</t>
+          <t>1860K</t>
         </is>
       </c>
       <c r="E577" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>1879.0K</t>
         </is>
       </c>
       <c r="F577" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="578">
@@ -14168,22 +14168,22 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C578" t="inlineStr"/>
       <c r="D578" t="inlineStr">
         <is>
-          <t>1860K</t>
+          <t>16.3</t>
         </is>
       </c>
       <c r="E578" t="inlineStr">
         <is>
-          <t>1879.0K</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F578" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="579">
@@ -14194,12 +14194,16 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C579" t="inlineStr"/>
       <c r="D579" t="inlineStr"/>
-      <c r="E579" t="inlineStr"/>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="F579" t="n">
         <v>3</v>
       </c>
@@ -14212,7 +14216,7 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C580" t="inlineStr"/>
@@ -14230,7 +14234,7 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C581" t="inlineStr"/>
@@ -14248,7 +14252,7 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C582" t="inlineStr"/>
@@ -14266,7 +14270,7 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C583" t="inlineStr"/>
@@ -14284,16 +14288,12 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C584" t="inlineStr"/>
       <c r="D584" t="inlineStr"/>
-      <c r="E584" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="E584" t="inlineStr"/>
       <c r="F584" t="n">
         <v>3</v>
       </c>
@@ -14482,7 +14482,7 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C593" t="inlineStr"/>
@@ -14536,7 +14536,7 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C596" t="inlineStr"/>
@@ -14554,14 +14554,14 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C597" t="inlineStr"/>
       <c r="D597" t="inlineStr"/>
       <c r="E597" t="inlineStr"/>
       <c r="F597" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="598">
@@ -14572,14 +14572,14 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C598" t="inlineStr"/>
       <c r="D598" t="inlineStr"/>
       <c r="E598" t="inlineStr"/>
       <c r="F598" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="599">
@@ -14590,7 +14590,7 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C599" t="inlineStr"/>
@@ -14608,14 +14608,14 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C600" t="inlineStr"/>
       <c r="D600" t="inlineStr"/>
       <c r="E600" t="inlineStr"/>
       <c r="F600" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="601">
@@ -14626,14 +14626,14 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C601" t="inlineStr"/>
       <c r="D601" t="inlineStr"/>
       <c r="E601" t="inlineStr"/>
       <c r="F601" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="602">
@@ -14644,14 +14644,14 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C602" t="inlineStr"/>
       <c r="D602" t="inlineStr"/>
       <c r="E602" t="inlineStr"/>
       <c r="F602" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="603">
@@ -14662,7 +14662,7 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C603" t="inlineStr"/>
@@ -14680,7 +14680,7 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C604" t="inlineStr"/>
@@ -14698,7 +14698,7 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C605" t="inlineStr"/>
@@ -14716,7 +14716,7 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C606" t="inlineStr"/>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C607" t="inlineStr"/>
@@ -14752,7 +14752,7 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C608" t="inlineStr"/>
@@ -14770,7 +14770,7 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C609" t="inlineStr"/>
@@ -14788,14 +14788,14 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>Fed Musalem Speech</t>
         </is>
       </c>
       <c r="C610" t="inlineStr"/>
       <c r="D610" t="inlineStr"/>
       <c r="E610" t="inlineStr"/>
       <c r="F610" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="611">
@@ -14806,7 +14806,7 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C611" t="inlineStr"/>
@@ -14824,7 +14824,7 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C612" t="inlineStr"/>
@@ -14842,14 +14842,14 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C613" t="inlineStr"/>
       <c r="D613" t="inlineStr"/>
       <c r="E613" t="inlineStr"/>
       <c r="F613" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="614">
@@ -14860,14 +14860,14 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C614" t="inlineStr"/>
       <c r="D614" t="inlineStr"/>
       <c r="E614" t="inlineStr"/>
       <c r="F614" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="615">
@@ -14878,7 +14878,7 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C615" t="inlineStr"/>
@@ -14896,7 +14896,7 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C616" t="inlineStr"/>
@@ -14914,14 +14914,14 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>Fed Musalem Speech</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C617" t="inlineStr"/>
       <c r="D617" t="inlineStr"/>
       <c r="E617" t="inlineStr"/>
       <c r="F617" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="618">
@@ -14932,14 +14932,14 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C618" t="inlineStr"/>
       <c r="D618" t="inlineStr"/>
       <c r="E618" t="inlineStr"/>
       <c r="F618" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="619">
@@ -14950,7 +14950,7 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C619" t="inlineStr"/>
@@ -15148,14 +15148,18 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C630" t="inlineStr"/>
-      <c r="D630" t="inlineStr"/>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>51.3</t>
+        </is>
+      </c>
       <c r="E630" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F630" t="n">
@@ -15170,15 +15174,11 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C631" t="inlineStr"/>
-      <c r="D631" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
+      <c r="D631" t="inlineStr"/>
       <c r="E631" t="inlineStr">
         <is>
           <t>52.7</t>
@@ -15196,18 +15196,18 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="C632" t="inlineStr"/>
       <c r="D632" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>53</t>
         </is>
       </c>
       <c r="E632" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="F632" t="n">
@@ -15248,14 +15248,18 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C634" t="inlineStr"/>
-      <c r="D634" t="inlineStr"/>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>51.3</t>
+        </is>
+      </c>
       <c r="E634" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F634" t="n">
@@ -15270,18 +15274,14 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C635" t="inlineStr"/>
-      <c r="D635" t="inlineStr">
-        <is>
-          <t>51.3</t>
-        </is>
-      </c>
+      <c r="D635" t="inlineStr"/>
       <c r="E635" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="F635" t="n">
@@ -15296,22 +15296,22 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C636" t="inlineStr"/>
       <c r="D636" t="inlineStr">
         <is>
-          <t>4.13M</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F636" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="637">
@@ -15344,22 +15344,22 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C638" t="inlineStr"/>
       <c r="D638" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="E638" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F638" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="639">
@@ -15370,22 +15370,22 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C639" t="inlineStr"/>
       <c r="D639" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>4.13M</t>
         </is>
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F639" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="640">
@@ -15396,18 +15396,18 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C640" t="inlineStr"/>
       <c r="D640" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E640" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F640" t="n">
@@ -15422,18 +15422,18 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C641" t="inlineStr"/>
       <c r="D641" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E641" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F641" t="n">
@@ -15448,22 +15448,22 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C642" t="inlineStr"/>
       <c r="D642" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.13M</t>
         </is>
       </c>
       <c r="E642" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F642" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="643">
@@ -15474,22 +15474,22 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C643" t="inlineStr"/>
       <c r="D643" t="inlineStr">
         <is>
-          <t>4.13M</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F643" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="644">
@@ -15500,14 +15500,18 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C644" t="inlineStr"/>
-      <c r="D644" t="inlineStr"/>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>67.8</t>
+        </is>
+      </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F644" t="n">
@@ -15522,22 +15526,22 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C645" t="inlineStr"/>
       <c r="D645" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F645" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="646">
@@ -15574,18 +15578,18 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C647" t="inlineStr"/>
       <c r="D647" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F647" t="n">
@@ -15600,22 +15604,18 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C648" t="inlineStr"/>
-      <c r="D648" t="inlineStr">
-        <is>
-          <t>68.7</t>
-        </is>
-      </c>
+      <c r="D648" t="inlineStr"/>
       <c r="E648" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F648" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="649">
@@ -15626,22 +15626,22 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C649" t="inlineStr"/>
       <c r="D649" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F649" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="650">
@@ -15706,7 +15706,7 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/21</t>
+          <t>Baker Hughes Total Rigs CountFEB/21</t>
         </is>
       </c>
       <c r="C653" t="inlineStr"/>
@@ -15724,7 +15724,7 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/21</t>
+          <t>Baker Hughes Oil Rig CountFEB/21</t>
         </is>
       </c>
       <c r="C654" t="inlineStr"/>
@@ -15832,7 +15832,7 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C660" t="inlineStr"/>
@@ -15868,7 +15868,7 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C662" t="inlineStr"/>
@@ -15976,7 +15976,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C668" t="inlineStr"/>
@@ -15994,18 +15994,14 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C669" t="inlineStr"/>
       <c r="D669" t="inlineStr"/>
-      <c r="E669" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="E669" t="inlineStr"/>
       <c r="F669" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="670">
@@ -16016,7 +16012,7 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C670" t="inlineStr"/>
@@ -16052,7 +16048,7 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C672" t="inlineStr"/>
@@ -16070,14 +16066,18 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C673" t="inlineStr"/>
       <c r="D673" t="inlineStr"/>
-      <c r="E673" t="inlineStr"/>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="F673" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="674">
@@ -16088,14 +16088,18 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C674" t="inlineStr"/>
       <c r="D674" t="inlineStr"/>
-      <c r="E674" t="inlineStr"/>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="F674" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="675">
@@ -16106,7 +16110,7 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C675" t="inlineStr"/>
@@ -16124,7 +16128,7 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C676" t="inlineStr"/>
@@ -16142,18 +16146,14 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C677" t="inlineStr"/>
       <c r="D677" t="inlineStr"/>
-      <c r="E677" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="E677" t="inlineStr"/>
       <c r="F677" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="678">
@@ -16182,14 +16182,14 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C679" t="inlineStr"/>
       <c r="D679" t="inlineStr"/>
       <c r="E679" t="inlineStr"/>
       <c r="F679" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="680">
@@ -16200,7 +16200,7 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C680" t="inlineStr"/>
@@ -16218,7 +16218,7 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C681" t="inlineStr"/>
@@ -16236,7 +16236,7 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
       <c r="C682" t="inlineStr"/>
@@ -16254,14 +16254,14 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C683" t="inlineStr"/>
       <c r="D683" t="inlineStr"/>
       <c r="E683" t="inlineStr"/>
       <c r="F683" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="684">
@@ -16290,7 +16290,7 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
       <c r="C685" t="inlineStr"/>
@@ -16308,7 +16308,7 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexFEB</t>
+          <t>Dallas Fed Services IndexFEB</t>
         </is>
       </c>
       <c r="C686" t="inlineStr"/>
@@ -16362,7 +16362,7 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexFEB</t>
+          <t>Dallas Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C689" t="inlineStr"/>
@@ -16380,7 +16380,7 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>Money SupplyJAN</t>
         </is>
       </c>
       <c r="C690" t="inlineStr"/>
@@ -16398,7 +16398,7 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>Money SupplyJAN</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C691" t="inlineStr"/>
@@ -16416,7 +16416,7 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>Money SupplyJAN</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C692" t="inlineStr"/>
@@ -16434,7 +16434,7 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>Money SupplyJAN</t>
         </is>
       </c>
       <c r="C693" t="inlineStr"/>
@@ -16488,7 +16488,7 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/21</t>
+          <t>MBA Purchase IndexFEB/21</t>
         </is>
       </c>
       <c r="C696" t="inlineStr"/>
@@ -16506,7 +16506,7 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/21</t>
+          <t>MBA Mortgage Refinance IndexFEB/21</t>
         </is>
       </c>
       <c r="C697" t="inlineStr"/>
@@ -16524,7 +16524,7 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/21</t>
+          <t>MBA Mortgage Market IndexFEB/21</t>
         </is>
       </c>
       <c r="C698" t="inlineStr"/>
@@ -16542,7 +16542,7 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/21</t>
+          <t>MBA Mortgage ApplicationsFEB/21</t>
         </is>
       </c>
       <c r="C699" t="inlineStr"/>
@@ -16560,14 +16560,14 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
         </is>
       </c>
       <c r="C700" t="inlineStr"/>
       <c r="D700" t="inlineStr"/>
       <c r="E700" t="inlineStr"/>
       <c r="F700" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="701">
@@ -16596,14 +16596,14 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
+          <t>MBA Purchase IndexFEB/21</t>
         </is>
       </c>
       <c r="C702" t="inlineStr"/>
       <c r="D702" t="inlineStr"/>
       <c r="E702" t="inlineStr"/>
       <c r="F702" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="703">
@@ -16614,7 +16614,7 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C703" t="inlineStr"/>
@@ -16632,7 +16632,7 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C704" t="inlineStr"/>
@@ -16650,7 +16650,7 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/21</t>
+          <t>MBA Mortgage Market IndexFEB/21</t>
         </is>
       </c>
       <c r="C705" t="inlineStr"/>
@@ -16668,7 +16668,7 @@
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/21</t>
+          <t>MBA Mortgage Refinance IndexFEB/21</t>
         </is>
       </c>
       <c r="C706" t="inlineStr"/>
@@ -16704,7 +16704,7 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>New Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C708" t="inlineStr"/>
@@ -16740,7 +16740,7 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>New Home Sales MoMJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C710" t="inlineStr"/>
@@ -16758,7 +16758,7 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>New Home SalesJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C711" t="inlineStr"/>
@@ -16776,7 +16776,7 @@
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>New Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C712" t="inlineStr"/>
@@ -16794,7 +16794,7 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>New Home Sales MoMJAN</t>
+          <t>New Home SalesJAN</t>
         </is>
       </c>
       <c r="C713" t="inlineStr"/>
@@ -16812,7 +16812,7 @@
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/21</t>
+          <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C714" t="inlineStr"/>
@@ -16830,14 +16830,14 @@
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C715" t="inlineStr"/>
       <c r="D715" t="inlineStr"/>
       <c r="E715" t="inlineStr"/>
       <c r="F715" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="716">
@@ -16848,14 +16848,14 @@
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C716" t="inlineStr"/>
       <c r="D716" t="inlineStr"/>
       <c r="E716" t="inlineStr"/>
       <c r="F716" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="717">
@@ -16884,7 +16884,7 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/21</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C718" t="inlineStr"/>
@@ -16902,7 +16902,7 @@
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/21</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C719" t="inlineStr"/>
@@ -16920,7 +16920,7 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C720" t="inlineStr"/>
@@ -16956,14 +16956,14 @@
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C722" t="inlineStr"/>
       <c r="D722" t="inlineStr"/>
       <c r="E722" t="inlineStr"/>
       <c r="F722" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="723">
@@ -16974,7 +16974,7 @@
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C723" t="inlineStr"/>
@@ -16992,7 +16992,7 @@
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
+          <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C724" t="inlineStr"/>
@@ -17010,7 +17010,7 @@
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C725" t="inlineStr"/>
@@ -17046,14 +17046,14 @@
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C727" t="inlineStr"/>
       <c r="D727" t="inlineStr"/>
       <c r="E727" t="inlineStr"/>
       <c r="F727" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="728">
@@ -17064,14 +17064,14 @@
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C728" t="inlineStr"/>
       <c r="D728" t="inlineStr"/>
       <c r="E728" t="inlineStr"/>
       <c r="F728" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="729">
@@ -17082,14 +17082,14 @@
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
       <c r="C729" t="inlineStr"/>
       <c r="D729" t="inlineStr"/>
       <c r="E729" t="inlineStr"/>
       <c r="F729" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="730">
@@ -17100,14 +17100,14 @@
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C730" t="inlineStr"/>
       <c r="D730" t="inlineStr"/>
       <c r="E730" t="inlineStr"/>
       <c r="F730" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="731">
@@ -17118,14 +17118,14 @@
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/21</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C731" t="inlineStr"/>
       <c r="D731" t="inlineStr"/>
       <c r="E731" t="inlineStr"/>
       <c r="F731" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="732">
@@ -17136,7 +17136,7 @@
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>17-Week Bill Auction</t>
         </is>
       </c>
       <c r="C732" t="inlineStr"/>
@@ -17172,7 +17172,7 @@
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>17-Week Bill Auction</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C734" t="inlineStr"/>
@@ -17208,7 +17208,7 @@
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C736" t="inlineStr"/>
@@ -17226,7 +17226,7 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Fed Bostic Speech</t>
         </is>
       </c>
       <c r="C737" t="inlineStr"/>
@@ -17262,7 +17262,7 @@
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>Fed Bostic Speech</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C739" t="inlineStr"/>
@@ -17280,7 +17280,7 @@
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>2-Year FRN Auction</t>
         </is>
       </c>
       <c r="C740" t="inlineStr"/>
@@ -17316,7 +17316,7 @@
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C742" t="inlineStr"/>
@@ -17334,7 +17334,7 @@
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>2-Year FRN Auction</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C743" t="inlineStr"/>
@@ -17352,7 +17352,7 @@
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>2-Year FRN Auction</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C744" t="inlineStr"/>
@@ -17388,7 +17388,7 @@
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>2-Year FRN Auction</t>
         </is>
       </c>
       <c r="C746" t="inlineStr"/>
@@ -17406,7 +17406,7 @@
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C747" t="inlineStr"/>
@@ -17424,7 +17424,7 @@
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/22</t>
         </is>
       </c>
       <c r="C748" t="inlineStr"/>
@@ -17592,7 +17592,7 @@
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/22</t>
         </is>
       </c>
       <c r="C756" t="inlineStr"/>
@@ -17610,14 +17610,18 @@
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMJAN</t>
+          <t>GDP Sales QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C757" t="inlineStr"/>
       <c r="D757" t="inlineStr"/>
-      <c r="E757" t="inlineStr"/>
+      <c r="E757" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="F757" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="758">
@@ -17654,16 +17658,12 @@
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
+          <t>Non Defense Goods Orders Ex AirJAN</t>
         </is>
       </c>
       <c r="C759" t="inlineStr"/>
       <c r="D759" t="inlineStr"/>
-      <c r="E759" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="E759" t="inlineStr"/>
       <c r="F759" t="n">
         <v>3</v>
       </c>
@@ -17676,22 +17676,22 @@
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ 2nd EstQ4</t>
+          <t>PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C760" t="inlineStr"/>
       <c r="D760" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="E760" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F760" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="761">
@@ -17702,20 +17702,12 @@
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ 2nd EstQ4</t>
+          <t>Durable Goods Orders ex Defense MoMJAN</t>
         </is>
       </c>
       <c r="C761" t="inlineStr"/>
-      <c r="D761" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
-      <c r="E761" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+      <c r="D761" t="inlineStr"/>
+      <c r="E761" t="inlineStr"/>
       <c r="F761" t="n">
         <v>3</v>
       </c>
@@ -17728,12 +17720,16 @@
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/15</t>
+          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C762" t="inlineStr"/>
       <c r="D762" t="inlineStr"/>
-      <c r="E762" t="inlineStr"/>
+      <c r="E762" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="F762" t="n">
         <v>3</v>
       </c>
@@ -17746,20 +17742,12 @@
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
+          <t>Durable Goods Orders MoMJAN</t>
         </is>
       </c>
       <c r="C763" t="inlineStr"/>
-      <c r="D763" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
-      <c r="E763" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
+      <c r="D763" t="inlineStr"/>
+      <c r="E763" t="inlineStr"/>
       <c r="F763" t="n">
         <v>1</v>
       </c>
@@ -17772,12 +17760,20 @@
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMJAN</t>
+          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C764" t="inlineStr"/>
-      <c r="D764" t="inlineStr"/>
-      <c r="E764" t="inlineStr"/>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="E764" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
       <c r="F764" t="n">
         <v>1</v>
       </c>
@@ -17790,16 +17786,12 @@
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ 2nd EstQ4</t>
+          <t>Continuing Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C765" t="inlineStr"/>
       <c r="D765" t="inlineStr"/>
-      <c r="E765" t="inlineStr">
-        <is>
-          <t>3.2%</t>
-        </is>
-      </c>
+      <c r="E765" t="inlineStr"/>
       <c r="F765" t="n">
         <v>3</v>
       </c>
@@ -17812,14 +17804,18 @@
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
+          <t>Core PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C766" t="inlineStr"/>
-      <c r="D766" t="inlineStr"/>
+      <c r="D766" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="E766" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F766" t="n">
@@ -17834,14 +17830,22 @@
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMJAN</t>
+          <t>GDP Price Index QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C767" t="inlineStr"/>
-      <c r="D767" t="inlineStr"/>
-      <c r="E767" t="inlineStr"/>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="E767" t="inlineStr">
+        <is>
+          <t>2.2%</t>
+        </is>
+      </c>
       <c r="F767" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="768">
@@ -17852,22 +17856,14 @@
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ 2nd EstQ4</t>
+          <t>Durable Goods Orders Ex Transp MoMJAN</t>
         </is>
       </c>
       <c r="C768" t="inlineStr"/>
-      <c r="D768" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
-      <c r="E768" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
+      <c r="D768" t="inlineStr"/>
+      <c r="E768" t="inlineStr"/>
       <c r="F768" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="769">
@@ -17878,12 +17874,16 @@
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/22</t>
+          <t>GDP Sales QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C769" t="inlineStr"/>
       <c r="D769" t="inlineStr"/>
-      <c r="E769" t="inlineStr"/>
+      <c r="E769" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="F769" t="n">
         <v>3</v>
       </c>
@@ -17896,7 +17896,7 @@
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirJAN</t>
+          <t>Durable Goods Orders ex Defense MoMJAN</t>
         </is>
       </c>
       <c r="C770" t="inlineStr"/>
@@ -17914,14 +17914,14 @@
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/22</t>
+          <t>Initial Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C771" t="inlineStr"/>
       <c r="D771" t="inlineStr"/>
       <c r="E771" t="inlineStr"/>
       <c r="F771" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="772">
@@ -17932,14 +17932,18 @@
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/22</t>
+          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C772" t="inlineStr"/>
       <c r="D772" t="inlineStr"/>
-      <c r="E772" t="inlineStr"/>
+      <c r="E772" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="F772" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="773">
@@ -17950,16 +17954,12 @@
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ 2nd EstQ4</t>
+          <t>Non Defense Goods Orders Ex AirJAN</t>
         </is>
       </c>
       <c r="C773" t="inlineStr"/>
       <c r="D773" t="inlineStr"/>
-      <c r="E773" t="inlineStr">
-        <is>
-          <t>3.2%</t>
-        </is>
-      </c>
+      <c r="E773" t="inlineStr"/>
       <c r="F773" t="n">
         <v>3</v>
       </c>
@@ -17972,7 +17972,7 @@
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>Pending Home Sales YoYJAN</t>
+          <t>Pending Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C774" t="inlineStr"/>
@@ -17990,7 +17990,7 @@
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>Pending Home Sales MoMJAN</t>
+          <t>Pending Home Sales YoYJAN</t>
         </is>
       </c>
       <c r="C775" t="inlineStr"/>
@@ -18008,7 +18008,7 @@
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>Pending Home Sales MoMJAN</t>
+          <t>Pending Home Sales YoYJAN</t>
         </is>
       </c>
       <c r="C776" t="inlineStr"/>
@@ -18026,7 +18026,7 @@
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>Pending Home Sales YoYJAN</t>
+          <t>Pending Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C777" t="inlineStr"/>
@@ -18084,15 +18084,11 @@
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>NY Fed Treasury Purchases 4 to 6 yrs</t>
+          <t>EIA Natural Gas Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C780" t="inlineStr"/>
-      <c r="D780" t="inlineStr">
-        <is>
-          <t>$50 million</t>
-        </is>
-      </c>
+      <c r="D780" t="inlineStr"/>
       <c r="E780" t="inlineStr"/>
       <c r="F780" t="n">
         <v>3</v>
@@ -18106,11 +18102,15 @@
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>EIA Natural Gas Stocks ChangeFEB/21</t>
+          <t>NY Fed Treasury Purchases 4 to 6 yrs</t>
         </is>
       </c>
       <c r="C781" t="inlineStr"/>
-      <c r="D781" t="inlineStr"/>
+      <c r="D781" t="inlineStr">
+        <is>
+          <t>$50 million</t>
+        </is>
+      </c>
       <c r="E781" t="inlineStr"/>
       <c r="F781" t="n">
         <v>3</v>
@@ -18124,7 +18124,7 @@
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>Kansas Fed Manufacturing IndexFEB</t>
+          <t>Kansas Fed Composite IndexFEB</t>
         </is>
       </c>
       <c r="C782" t="inlineStr"/>
@@ -18142,7 +18142,7 @@
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>Kansas Fed Composite IndexFEB</t>
+          <t>Kansas Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C783" t="inlineStr"/>
@@ -18160,7 +18160,7 @@
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>Kansas Fed Composite IndexFEB</t>
+          <t>Kansas Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C784" t="inlineStr"/>
@@ -18178,7 +18178,7 @@
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>Kansas Fed Manufacturing IndexFEB</t>
+          <t>Kansas Fed Composite IndexFEB</t>
         </is>
       </c>
       <c r="C785" t="inlineStr"/>
@@ -18196,7 +18196,7 @@
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C786" t="inlineStr"/>
@@ -18214,7 +18214,7 @@
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C787" t="inlineStr"/>
@@ -18232,7 +18232,7 @@
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C788" t="inlineStr"/>
@@ -18250,7 +18250,7 @@
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C789" t="inlineStr"/>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/27</t>
+          <t>15-Year Mortgage RateFEB/27</t>
         </is>
       </c>
       <c r="C791" t="inlineStr"/>
@@ -18322,7 +18322,7 @@
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/27</t>
+          <t>30-Year Mortgage RateFEB/27</t>
         </is>
       </c>
       <c r="C793" t="inlineStr"/>
@@ -18350,6 +18350,24 @@
         <v>3</v>
       </c>
     </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>2025-02-27 16:30:00-05:00</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>Fed Balance SheetFEB/26</t>
+        </is>
+      </c>
+      <c r="C795" t="inlineStr"/>
+      <c r="D795" t="inlineStr"/>
+      <c r="E795" t="inlineStr"/>
+      <c r="F795" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-02-27.xlsx
+++ b/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-02-27.xlsx
@@ -720,22 +720,18 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.178M</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>-2.75M</t>
-        </is>
-      </c>
+          <t>0.041M</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -746,12 +742,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -768,18 +764,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>7.717M</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0.7M</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -790,19 +790,15 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>6.406M</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>-0.1M</t>
-        </is>
-      </c>
+          <t>-0.416M</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
         <v>3</v>
@@ -816,12 +812,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.142M</t>
+          <t>0.099M</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -838,15 +834,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.416M</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>-0.1M</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
         <v>3</v>
@@ -860,22 +860,18 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -886,18 +882,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.323M</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -908,12 +908,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.041M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1582,18 +1582,22 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ImportsNOV</t>
+          <t>Balance of TradeNOV</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>$351.6B</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr"/>
+          <t>$-78.2B</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>$-78B</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>$334B</t>
+          <t>$-70B</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -1608,22 +1612,18 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Balance of TradeNOV</t>
+          <t>ExportsNOV</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>$-78.2B</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>$-78B</t>
-        </is>
-      </c>
+          <t>$273.4B</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>$-70B</t>
+          <t>$264B</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -1638,18 +1638,18 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ExportsNOV</t>
+          <t>ImportsNOV</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>$273.4B</t>
+          <t>$351.6B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>$264B</t>
+          <t>$334B</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Used Car Prices MoMDEC</t>
+          <t>Used Car Prices YoYDEC</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -2254,12 +2254,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Used Car Prices YoYDEC</t>
+          <t>Used Car Prices MoMDEC</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -3148,18 +3148,18 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelJAN</t>
+          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F112" t="n">
@@ -3174,18 +3174,18 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelJAN</t>
+          <t>Michigan Consumer Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F113" t="n">
@@ -3200,26 +3200,22 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelJAN</t>
+          <t>Michigan Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>73.2</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>73.8</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="115">
@@ -3230,18 +3226,18 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelJAN</t>
+          <t>Michigan Current Conditions PrelJAN</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F115" t="n">
@@ -3256,22 +3252,26 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
+          <t>Michigan Consumer Sentiment PrelJAN</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr"/>
+          <t>73.2</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>73.8</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117">
@@ -3458,12 +3458,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>4.180%</t>
+          <t>4.225%</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
@@ -3480,12 +3480,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>4.225%</t>
+          <t>4.180%</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
@@ -4010,22 +4010,26 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>CPI s.aDEC</t>
+          <t>Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>317.685</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr"/>
+          <t>2.9%</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>2.9%</t>
+        </is>
+      </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>317.4</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148">
@@ -4036,22 +4040,22 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMDEC</t>
+          <t>Core Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -4066,22 +4070,22 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>CPIDEC</t>
+          <t>NY Empire State Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>-12.60</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>315.6</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="F149" t="n">
@@ -4096,26 +4100,26 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexJAN</t>
+          <t>Core Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>-12.60</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="151">
@@ -4126,22 +4130,22 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMDEC</t>
+          <t>Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F151" t="n">
@@ -4156,26 +4160,22 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYDEC</t>
+          <t>CPI s.aDEC</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+          <t>317.685</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>317.4</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="153">
@@ -4186,26 +4186,26 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYDEC</t>
+          <t>CPIDEC</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>315.6</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="154">
@@ -4252,18 +4252,22 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>0.646M</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>2.60M</t>
+        </is>
+      </c>
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="157">
@@ -4274,19 +4278,15 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>3.077M</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>1.1M</t>
-        </is>
-      </c>
+          <t>0.765M</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="n">
         <v>3</v>
@@ -4300,12 +4300,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>-0.021M</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>-1.304M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
@@ -4344,18 +4344,22 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>0.397M</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr"/>
+          <t>-1.961M</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>-1.6M</t>
+        </is>
+      </c>
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="161">
@@ -4366,22 +4370,18 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>-1.961M</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>-1.6M</t>
-        </is>
-      </c>
+          <t>-0.255M</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="162">
@@ -4392,15 +4392,19 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>-0.021M</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr"/>
+          <t>3.077M</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>1.1M</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="n">
         <v>3</v>
@@ -4414,12 +4418,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>0.765M</t>
+          <t>0.646M</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
@@ -4436,22 +4440,18 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>2.60M</t>
-        </is>
-      </c>
+          <t>-1.304M</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="165">
@@ -4556,20 +4556,16 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>212.75K</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="D170" t="inlineStr"/>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>215.0K</t>
-        </is>
-      </c>
+      <c r="E170" t="inlineStr"/>
       <c r="F170" t="n">
         <v>3</v>
       </c>
@@ -4582,16 +4578,24 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>11.9</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr"/>
-      <c r="E171" t="inlineStr"/>
+          <t>1859K</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>1870.0K</t>
+        </is>
+      </c>
       <c r="F171" t="n">
         <v>3</v>
       </c>
@@ -4604,18 +4608,26 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>39.00</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr"/>
-      <c r="E172" t="inlineStr"/>
+          <t>217K</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>210K</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>209.0K</t>
+        </is>
+      </c>
       <c r="F172" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="173">
@@ -4626,26 +4638,22 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>1.8%</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="174">
@@ -4656,22 +4664,22 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F174" t="n">
@@ -4686,26 +4694,18 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
+          <t>46.3</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr"/>
       <c r="F175" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="176">
@@ -4716,18 +4716,22 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>1.8%</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="F176" t="n">
@@ -4742,16 +4746,20 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
-      <c r="E177" t="inlineStr"/>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>4.0%</t>
+        </is>
+      </c>
       <c r="F177" t="n">
         <v>3</v>
       </c>
@@ -4764,26 +4772,26 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F178" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="179">
@@ -4794,26 +4802,26 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F179" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="180">
@@ -4824,24 +4832,16 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>1.6%</t>
-        </is>
-      </c>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr"/>
       <c r="F180" t="n">
         <v>3</v>
       </c>
@@ -4854,22 +4854,22 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F181" t="n">
@@ -4884,18 +4884,26 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr"/>
-      <c r="E182" t="inlineStr"/>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>-10</t>
+        </is>
+      </c>
       <c r="F182" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="183">
@@ -4906,22 +4914,22 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>217K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>210K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F183" t="n">
@@ -4936,20 +4944,16 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>39.00</t>
         </is>
       </c>
       <c r="D184" t="inlineStr"/>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>4.0%</t>
-        </is>
-      </c>
+      <c r="E184" t="inlineStr"/>
       <c r="F184" t="n">
         <v>3</v>
       </c>
@@ -4962,26 +4966,18 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr"/>
+      <c r="E185" t="inlineStr"/>
       <c r="F185" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="186">
@@ -4992,16 +4988,20 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>212.75K</t>
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
-      <c r="E186" t="inlineStr"/>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>215.0K</t>
+        </is>
+      </c>
       <c r="F186" t="n">
         <v>3</v>
       </c>
@@ -5014,17 +5014,17 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Business Inventories MoMNOV</t>
+          <t>Retail Inventories Ex Autos MoMNOV</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -5033,7 +5033,7 @@
         </is>
       </c>
       <c r="F187" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="188">
@@ -5044,26 +5044,26 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoMNOV</t>
+          <t>NAHB Housing Market IndexJAN</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F188" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="189">
@@ -5074,22 +5074,22 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>NAHB Housing Market IndexJAN</t>
+          <t>Business Inventories MoMNOV</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F189" t="n">
@@ -5240,18 +5240,18 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelDEC</t>
+          <t>Housing Starts MoMDEC</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>15.8%</t>
         </is>
       </c>
       <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="F196" t="n">
@@ -5266,26 +5266,22 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Housing StartsDEC</t>
+          <t>Building Permits MoM PrelDEC</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>1.499M</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>1.32M</t>
-        </is>
-      </c>
+          <t>-0.7%</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr">
         <is>
-          <t>1.32M</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="F197" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="198">
@@ -5296,22 +5292,26 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Housing Starts MoMDEC</t>
+          <t>Housing StartsDEC</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>15.8%</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr"/>
+          <t>1.499M</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>1.32M</t>
+        </is>
+      </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>1.32M</t>
         </is>
       </c>
       <c r="F198" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="199">
@@ -5352,18 +5352,18 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Industrial Production YoYDEC</t>
+          <t>Manufacturing Production YoYDEC</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F200" t="n">
@@ -5378,26 +5378,26 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Capacity UtilizationDEC</t>
+          <t>Industrial Production MoMDEC</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F201" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="202">
@@ -5438,26 +5438,26 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Industrial Production MoMDEC</t>
+          <t>Capacity UtilizationDEC</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="F203" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="204">
@@ -5468,18 +5468,18 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYDEC</t>
+          <t>Industrial Production YoYDEC</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D204" t="inlineStr"/>
       <c r="E204" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F204" t="n">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>42-Day Bill Auction</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>4.025%</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
@@ -5692,12 +5692,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>42-Day Bill Auction</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>4.025%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
@@ -5942,26 +5942,26 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/18</t>
+          <t>Continuing Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>1899K</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>220K</t>
+          <t>1860K</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>1861K</t>
         </is>
       </c>
       <c r="F225" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="226">
@@ -5972,22 +5972,18 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/11</t>
+          <t>Jobless Claims 4-week AverageJAN/18</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>1899K</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr">
-        <is>
-          <t>1860K</t>
-        </is>
-      </c>
+          <t>213.5K</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr"/>
       <c r="E226" t="inlineStr">
         <is>
-          <t>1861K</t>
+          <t>213.0K</t>
         </is>
       </c>
       <c r="F226" t="n">
@@ -6002,22 +5998,26 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/18</t>
+          <t>Initial Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>213.5K</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr"/>
+          <t>223K</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>220K</t>
+        </is>
+      </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>213.0K</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="F227" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="228">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D233" t="inlineStr"/>
@@ -6172,18 +6172,22 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>0.184M</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="235">
@@ -6194,18 +6198,22 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>6.96%</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="236">
@@ -6216,12 +6224,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -6238,15 +6246,19 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>-1.125M</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="E237" t="inlineStr"/>
       <c r="F237" t="n">
         <v>3</v>
@@ -6260,12 +6272,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -6282,12 +6294,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
@@ -6304,19 +6316,15 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>6.96%</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr"/>
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="n">
         <v>3</v>
@@ -6330,12 +6338,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D241" t="inlineStr"/>
@@ -6352,22 +6360,18 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>0.068M</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr"/>
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="243">
@@ -6378,22 +6382,18 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>-0.148M</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr"/>
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="244">
@@ -6448,22 +6448,22 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashJAN</t>
+          <t>S&amp;P Global Manufacturing PMI FlashJAN</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="F246" t="n">
@@ -6478,22 +6478,22 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashJAN</t>
+          <t>S&amp;P Global Services PMI FlashJAN</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="F247" t="n">
@@ -6534,22 +6534,26 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr"/>
+          <t>69.3</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>70.2</t>
+        </is>
+      </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F249" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="250">
@@ -6560,26 +6564,26 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F250" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="251">
@@ -6590,12 +6594,12 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -6620,26 +6624,26 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>4.24M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>4.19M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F252" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="253">
@@ -6650,26 +6654,26 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>4.24M</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.19M</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="F253" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="254">
@@ -6680,26 +6684,26 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F254" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="255">
@@ -6710,26 +6714,22 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr">
-        <is>
-          <t>77.9</t>
-        </is>
-      </c>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr"/>
       <c r="E255" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F255" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="256">
@@ -7178,18 +7178,22 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
+          <t>House Price Index MoMNOV</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="D273" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F273" t="n">
@@ -7204,18 +7208,18 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>House Price Index YoYNOV</t>
+          <t>House Price IndexNOV</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>433.4</t>
         </is>
       </c>
       <c r="D274" t="inlineStr"/>
       <c r="E274" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>433</t>
         </is>
       </c>
       <c r="F274" t="n">
@@ -7260,18 +7264,18 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>House Price IndexNOV</t>
+          <t>House Price Index YoYNOV</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>433.4</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="D276" t="inlineStr"/>
       <c r="E276" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F276" t="n">
@@ -7286,22 +7290,18 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>House Price Index MoMNOV</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D277" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>-0.1%</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr"/>
       <c r="E277" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F277" t="n">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>Money SupplyDEC</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>4.457%</t>
+          <t>$21.53T</t>
         </is>
       </c>
       <c r="D286" t="inlineStr"/>
@@ -7546,12 +7546,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Money SupplyDEC</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>$21.53T</t>
+          <t>4.457%</t>
         </is>
       </c>
       <c r="D287" t="inlineStr"/>
@@ -7790,18 +7790,22 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>-0.333M</t>
-        </is>
-      </c>
-      <c r="D297" t="inlineStr"/>
+          <t>3.463M</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>3.2M</t>
+        </is>
+      </c>
       <c r="E297" t="inlineStr"/>
       <c r="F297" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="298">
@@ -7812,22 +7816,18 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>2.957M</t>
-        </is>
-      </c>
-      <c r="D298" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>0.532M</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr"/>
       <c r="E298" t="inlineStr"/>
       <c r="F298" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="299">
@@ -7838,19 +7838,15 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>-4.994M</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.128M</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr"/>
       <c r="E299" t="inlineStr"/>
       <c r="F299" t="n">
         <v>3</v>
@@ -7864,12 +7860,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>0.326M</t>
+          <t>0.028M</t>
         </is>
       </c>
       <c r="D300" t="inlineStr"/>
@@ -7886,12 +7882,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>0.028M</t>
+          <t>-0.044M</t>
         </is>
       </c>
       <c r="D301" t="inlineStr"/>
@@ -7908,15 +7904,19 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>0.532M</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr"/>
+          <t>-4.994M</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E302" t="inlineStr"/>
       <c r="F302" t="n">
         <v>3</v>
@@ -7930,12 +7930,12 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>-0.044M</t>
+          <t>0.326M</t>
         </is>
       </c>
       <c r="D303" t="inlineStr"/>
@@ -7952,17 +7952,17 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>3.463M</t>
+          <t>2.957M</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>3.2M</t>
+          <t>1.5M</t>
         </is>
       </c>
       <c r="E304" t="inlineStr"/>
@@ -7978,12 +7978,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>0.128M</t>
+          <t>-0.333M</t>
         </is>
       </c>
       <c r="D305" t="inlineStr"/>
@@ -8070,18 +8070,22 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ AdvQ4</t>
+          <t>Core PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="D309" t="inlineStr"/>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F309" t="n">
@@ -8096,22 +8100,26 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ AdvQ4</t>
+          <t>GDP Price Index QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D310" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F310" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="311">
@@ -8122,18 +8130,22 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ AdvQ4</t>
+          <t>Continuing Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>2.3%</t>
-        </is>
-      </c>
-      <c r="D311" t="inlineStr"/>
+          <t>1858K</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>1890K</t>
+        </is>
+      </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>1885.0K</t>
         </is>
       </c>
       <c r="F311" t="n">
@@ -8148,26 +8160,22 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/25</t>
+          <t>Jobless Claims 4-week AverageJAN/25</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>207K</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+          <t>212.5K</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr"/>
       <c r="E312" t="inlineStr">
         <is>
-          <t>228.0K</t>
+          <t>214.0K</t>
         </is>
       </c>
       <c r="F312" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="313">
@@ -8178,22 +8186,26 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/25</t>
+          <t>GDP Growth Rate QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>212.5K</t>
-        </is>
-      </c>
-      <c r="D313" t="inlineStr"/>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>214.0K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F313" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="314">
@@ -8204,22 +8216,18 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/18</t>
+          <t>PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>1858K</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr">
-        <is>
-          <t>1890K</t>
-        </is>
-      </c>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr"/>
       <c r="E314" t="inlineStr">
         <is>
-          <t>1885.0K</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="F314" t="n">
@@ -8234,26 +8242,22 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ AdvQ4</t>
+          <t>GDP Sales QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr"/>
       <c r="E315" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F315" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="316">
@@ -8264,26 +8268,26 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ AdvQ4</t>
+          <t>Initial Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>207K</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>228.0K</t>
         </is>
       </c>
       <c r="F316" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="317">
@@ -8294,22 +8298,18 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ AdvQ4</t>
+          <t>Real Consumer Spending QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>2.5%</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr"/>
       <c r="E317" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F317" t="n">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D321" t="inlineStr"/>
@@ -8428,12 +8428,12 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="D322" t="inlineStr"/>
@@ -8516,24 +8516,12 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
-        </is>
-      </c>
-      <c r="C326" t="inlineStr">
-        <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D326" t="inlineStr">
-        <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="E326" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr"/>
+      <c r="D326" t="inlineStr"/>
+      <c r="E326" t="inlineStr"/>
       <c r="F326" t="n">
         <v>2</v>
       </c>
@@ -8546,26 +8534,26 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F327" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="328">
@@ -8576,22 +8564,26 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
+          <t>Core PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr"/>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F328" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="329">
@@ -8602,22 +8594,22 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F329" t="n">
@@ -8632,18 +8624,22 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D330" t="inlineStr"/>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F330" t="n">
@@ -8658,22 +8654,22 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F331" t="n">
@@ -8688,14 +8684,26 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C332" t="inlineStr"/>
-      <c r="D332" t="inlineStr"/>
-      <c r="E332" t="inlineStr"/>
+          <t>Personal Income MoMDEC</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F332" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="333">
@@ -8706,26 +8714,22 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
+          <t>Employment Cost - Benefits QoQQ4</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr"/>
       <c r="E333" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F333" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="334">
@@ -8736,26 +8740,26 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F334" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="335">
@@ -8766,22 +8770,18 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
+          <t>Employment Cost - Wages QoQQ4</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D335" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr"/>
       <c r="E335" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F335" t="n">
@@ -8904,22 +8904,22 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersJAN</t>
+          <t>ISM Manufacturing EmploymentJAN</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="D340" t="inlineStr"/>
       <c r="E340" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F340" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="341">
@@ -8930,26 +8930,26 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesJAN</t>
+          <t>ISM Manufacturing PMIJAN</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="F341" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="342">
@@ -8960,22 +8960,22 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Construction Spending MoMDEC</t>
+          <t>ISM Manufacturing PricesJAN</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F342" t="n">
@@ -8990,26 +8990,22 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIJAN</t>
+          <t>ISM Manufacturing New OrdersJAN</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>50.9</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr">
-        <is>
-          <t>49.8</t>
-        </is>
-      </c>
+          <t>55.1</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr"/>
       <c r="E343" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F343" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="344">
@@ -9020,22 +9016,26 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentJAN</t>
+          <t>Construction Spending MoMDEC</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>50.3</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F344" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="345">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/31</t>
+          <t>MBA Mortgage ApplicationsJAN/31</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>584.3</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D363" t="inlineStr"/>
@@ -9472,18 +9472,18 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/31</t>
+          <t>MBA 30-Year Mortgage RateJAN/31</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>224.8</t>
+          <t>6.97%</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
       <c r="E364" t="inlineStr"/>
       <c r="F364" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="365">
@@ -9516,18 +9516,18 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/31</t>
+          <t>MBA Mortgage Market IndexJAN/31</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>6.97%</t>
+          <t>224.8</t>
         </is>
       </c>
       <c r="D366" t="inlineStr"/>
       <c r="E366" t="inlineStr"/>
       <c r="F366" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="367">
@@ -9538,12 +9538,12 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/31</t>
+          <t>MBA Mortgage Refinance IndexJAN/31</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>584.3</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
@@ -9768,18 +9768,18 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersJAN</t>
+          <t>ISM Services Business ActivityJAN</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="D376" t="inlineStr"/>
       <c r="E376" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="F376" t="n">
@@ -9794,22 +9794,26 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>ISM Services PricesJAN</t>
+          <t>ISM Services PMIJAN</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>60.4</t>
-        </is>
-      </c>
-      <c r="D377" t="inlineStr"/>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>54.3</t>
+        </is>
+      </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F377" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="378">
@@ -9846,26 +9850,22 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>ISM Services PMIJAN</t>
+          <t>ISM Services PricesJAN</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>52.8</t>
-        </is>
-      </c>
-      <c r="D379" t="inlineStr">
-        <is>
-          <t>54.3</t>
-        </is>
-      </c>
+          <t>60.4</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr"/>
       <c r="E379" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="F379" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="380">
@@ -9876,18 +9876,18 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityJAN</t>
+          <t>ISM Services New OrdersJAN</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="D380" t="inlineStr"/>
       <c r="E380" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F380" t="n">
@@ -10434,12 +10434,12 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/06</t>
+          <t>30-Year Mortgage RateFEB/06</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>6.05%</t>
+          <t>6.89%</t>
         </is>
       </c>
       <c r="D403" t="inlineStr"/>
@@ -10456,12 +10456,12 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/06</t>
+          <t>15-Year Mortgage RateFEB/06</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>6.89%</t>
+          <t>6.05%</t>
         </is>
       </c>
       <c r="D404" t="inlineStr"/>
@@ -10536,22 +10536,18 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateJAN</t>
+          <t>U-6 Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>111K</t>
-        </is>
-      </c>
-      <c r="D408" t="inlineStr">
-        <is>
-          <t>141K</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr"/>
       <c r="E408" t="inlineStr">
         <is>
-          <t>180K</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="F408" t="n">
@@ -10566,22 +10562,26 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Government PayrollsJAN</t>
+          <t>Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>32K</t>
-        </is>
-      </c>
-      <c r="D409" t="inlineStr"/>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>4.1%</t>
+        </is>
+      </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>25K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F409" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="410">
@@ -10592,26 +10592,26 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoYJAN</t>
+          <t>Manufacturing PayrollsJAN</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>3K</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>-2K</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>-5K</t>
         </is>
       </c>
       <c r="F410" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="411">
@@ -10622,26 +10622,26 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsJAN</t>
+          <t>Average Hourly Earnings MoMJAN</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>143K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>170K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>205K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F411" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="412">
@@ -10652,22 +10652,26 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Participation RateJAN</t>
+          <t>Average Weekly HoursJAN</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>62.6%</t>
-        </is>
-      </c>
-      <c r="D412" t="inlineStr"/>
+          <t>34.1</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F412" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="413">
@@ -10678,26 +10682,26 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMJAN</t>
+          <t>Non Farm PayrollsJAN</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>143K</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>170K</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>205K</t>
         </is>
       </c>
       <c r="F413" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="414">
@@ -10708,26 +10712,26 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsJAN</t>
+          <t>Average Hourly Earnings YoYJAN</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>3K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>-2K</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>-5K</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="F414" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="415">
@@ -10738,26 +10742,22 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Unemployment RateJAN</t>
+          <t>Government PayrollsJAN</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>4%</t>
-        </is>
-      </c>
-      <c r="D415" t="inlineStr">
-        <is>
-          <t>4.1%</t>
-        </is>
-      </c>
+          <t>32K</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr"/>
       <c r="E415" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>25K</t>
         </is>
       </c>
       <c r="F415" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="416">
@@ -10768,22 +10768,22 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Average Weekly HoursJAN</t>
+          <t>Nonfarm Payrolls PrivateJAN</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>111K</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>141K</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>180K</t>
         </is>
       </c>
       <c r="F416" t="n">
@@ -10798,22 +10798,22 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>U-6 Unemployment RateJAN</t>
+          <t>Participation RateJAN</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="D417" t="inlineStr"/>
       <c r="E417" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="F417" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="418">
@@ -10904,22 +10904,22 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoMDEC</t>
+          <t>Michigan Current Conditions PrelFEB</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>73</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="F422" t="n">
@@ -10934,26 +10934,26 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelFEB</t>
+          <t>Wholesale Inventories MoMDEC</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F423" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="424">
@@ -10964,22 +10964,26 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelFEB</t>
+          <t>Michigan Consumer Sentiment PrelFEB</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="D424" t="inlineStr"/>
+          <t>67.8</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>71.1</t>
+        </is>
+      </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F424" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="425">
@@ -10990,22 +10994,18 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelFEB</t>
+          <t>Michigan Inflation Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>67.3</t>
-        </is>
-      </c>
-      <c r="D425" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr"/>
       <c r="E425" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F425" t="n">
@@ -11020,18 +11020,22 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelFEB</t>
+          <t>Michigan Consumer Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D426" t="inlineStr"/>
+          <t>67.3</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="F426" t="n">
@@ -11046,22 +11050,18 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelFEB</t>
+          <t>Michigan 5 Year Inflation Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>68.7</t>
-        </is>
-      </c>
-      <c r="D427" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr"/>
       <c r="E427" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F427" t="n">
@@ -11564,7 +11564,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C452" t="inlineStr"/>
@@ -11575,7 +11575,7 @@
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F452" t="n">
@@ -11590,22 +11590,18 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>CPI s.aJAN</t>
         </is>
       </c>
       <c r="C453" t="inlineStr"/>
-      <c r="D453" t="inlineStr">
-        <is>
-          <t>2.9%</t>
-        </is>
-      </c>
+      <c r="D453" t="inlineStr"/>
       <c r="E453" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>318.2</t>
         </is>
       </c>
       <c r="F453" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="454">
@@ -11616,22 +11612,22 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>CPIJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C454" t="inlineStr"/>
       <c r="D454" t="inlineStr">
         <is>
-          <t>317.42</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>317.3</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F454" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="455">
@@ -11642,18 +11638,18 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C455" t="inlineStr"/>
       <c r="D455" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F455" t="n">
@@ -11668,18 +11664,22 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>CPI s.aJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C456" t="inlineStr"/>
-      <c r="D456" t="inlineStr"/>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>318.2</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F456" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="457">
@@ -11690,22 +11690,22 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>CPIJAN</t>
         </is>
       </c>
       <c r="C457" t="inlineStr"/>
       <c r="D457" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>317.42</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>317.3</t>
         </is>
       </c>
       <c r="F457" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="458">
@@ -11716,7 +11716,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C458" t="inlineStr"/>
@@ -11734,14 +11734,14 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C459" t="inlineStr"/>
       <c r="D459" t="inlineStr"/>
       <c r="E459" t="inlineStr"/>
       <c r="F459" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="460">
@@ -11752,7 +11752,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C460" t="inlineStr"/>
@@ -11770,14 +11770,14 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C461" t="inlineStr"/>
       <c r="D461" t="inlineStr"/>
       <c r="E461" t="inlineStr"/>
       <c r="F461" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="462">
@@ -11788,14 +11788,14 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C462" t="inlineStr"/>
       <c r="D462" t="inlineStr"/>
       <c r="E462" t="inlineStr"/>
       <c r="F462" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="463">
@@ -11806,7 +11806,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C463" t="inlineStr"/>
@@ -11824,7 +11824,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C464" t="inlineStr"/>
@@ -11842,7 +11842,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C465" t="inlineStr"/>
@@ -11860,14 +11860,14 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C466" t="inlineStr"/>
       <c r="D466" t="inlineStr"/>
       <c r="E466" t="inlineStr"/>
       <c r="F466" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="467">
@@ -11976,14 +11976,14 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C472" t="inlineStr"/>
       <c r="D472" t="inlineStr"/>
       <c r="E472" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="F472" t="n">
@@ -11998,14 +11998,14 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C473" t="inlineStr"/>
       <c r="D473" t="inlineStr"/>
       <c r="E473" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F473" t="n">
@@ -12020,22 +12020,22 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C474" t="inlineStr"/>
       <c r="D474" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F474" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="475">
@@ -12046,22 +12046,18 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C475" t="inlineStr"/>
-      <c r="D475" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D475" t="inlineStr"/>
       <c r="E475" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="F475" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="476">
@@ -12072,18 +12068,18 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C476" t="inlineStr"/>
       <c r="D476" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F476" t="n">
@@ -12098,18 +12094,22 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C477" t="inlineStr"/>
-      <c r="D477" t="inlineStr"/>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F477" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="478">
@@ -12120,18 +12120,22 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C478" t="inlineStr"/>
-      <c r="D478" t="inlineStr"/>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F478" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="479">
@@ -12142,18 +12146,18 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C479" t="inlineStr"/>
       <c r="D479" t="inlineStr">
         <is>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
           <t>3.3%</t>
-        </is>
-      </c>
-      <c r="E479" t="inlineStr">
-        <is>
-          <t>3.5%</t>
         </is>
       </c>
       <c r="F479" t="n">
@@ -12168,14 +12172,14 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C480" t="inlineStr"/>
       <c r="D480" t="inlineStr"/>
       <c r="E480" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="F480" t="n">
@@ -12190,22 +12194,18 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C481" t="inlineStr"/>
-      <c r="D481" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
+      <c r="D481" t="inlineStr"/>
       <c r="E481" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F481" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="482">
@@ -12252,7 +12252,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C484" t="inlineStr"/>
@@ -12270,7 +12270,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C485" t="inlineStr"/>
@@ -12360,22 +12360,18 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="C490" t="inlineStr"/>
-      <c r="D490" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D490" t="inlineStr"/>
       <c r="E490" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F490" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="491">
@@ -12386,14 +12382,14 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="C491" t="inlineStr"/>
       <c r="D491" t="inlineStr"/>
       <c r="E491" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F491" t="n">
@@ -12408,18 +12404,22 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="C492" t="inlineStr"/>
-      <c r="D492" t="inlineStr"/>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F492" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="493">
@@ -12430,18 +12430,22 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="C493" t="inlineStr"/>
-      <c r="D493" t="inlineStr"/>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="F493" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="494">
@@ -12452,7 +12456,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="C494" t="inlineStr"/>
@@ -12478,22 +12482,18 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="C495" t="inlineStr"/>
-      <c r="D495" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
+      <c r="D495" t="inlineStr"/>
       <c r="E495" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F495" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="496">
@@ -12504,14 +12504,14 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="C496" t="inlineStr"/>
       <c r="D496" t="inlineStr"/>
       <c r="E496" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F496" t="n">
@@ -12526,22 +12526,18 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="C497" t="inlineStr"/>
-      <c r="D497" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D497" t="inlineStr"/>
       <c r="E497" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F497" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="498">
@@ -12552,18 +12548,22 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="C498" t="inlineStr"/>
-      <c r="D498" t="inlineStr"/>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F498" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="499">
@@ -12574,22 +12574,18 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="C499" t="inlineStr"/>
-      <c r="D499" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="D499" t="inlineStr"/>
       <c r="E499" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F499" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="500">
@@ -12600,22 +12596,22 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="C500" t="inlineStr"/>
       <c r="D500" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F500" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="501">
@@ -12626,18 +12622,18 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="C501" t="inlineStr"/>
       <c r="D501" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>77.7%</t>
         </is>
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="F501" t="n">
@@ -12652,14 +12648,18 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Manufacturing Production MoMJAN</t>
         </is>
       </c>
       <c r="C502" t="inlineStr"/>
-      <c r="D502" t="inlineStr"/>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F502" t="n">
@@ -12696,22 +12696,22 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>Business Inventories MoMDEC</t>
+          <t>Retail Inventories Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C504" t="inlineStr"/>
       <c r="D504" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F504" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="505">
@@ -12722,22 +12722,22 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoMDEC</t>
+          <t>Business Inventories MoMDEC</t>
         </is>
       </c>
       <c r="C505" t="inlineStr"/>
       <c r="D505" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F505" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="506">
@@ -12748,7 +12748,7 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/14</t>
+          <t>Baker Hughes Oil Rig CountFEB/14</t>
         </is>
       </c>
       <c r="C506" t="inlineStr"/>
@@ -12766,7 +12766,7 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/14</t>
+          <t>Baker Hughes Total Rigs CountFEB/14</t>
         </is>
       </c>
       <c r="C507" t="inlineStr"/>
@@ -13288,7 +13288,7 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="C534" t="inlineStr"/>
@@ -13306,18 +13306,14 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsDEC</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C535" t="inlineStr"/>
-      <c r="D535" t="inlineStr">
-        <is>
-          <t>$149.1B</t>
-        </is>
-      </c>
+      <c r="D535" t="inlineStr"/>
       <c r="E535" t="inlineStr"/>
       <c r="F535" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="536">
@@ -13328,14 +13324,18 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Net Long-term TIC FlowsDEC</t>
         </is>
       </c>
       <c r="C536" t="inlineStr"/>
-      <c r="D536" t="inlineStr"/>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>$149.1B</t>
+        </is>
+      </c>
       <c r="E536" t="inlineStr"/>
       <c r="F536" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="537">
@@ -13454,7 +13454,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C543" t="inlineStr"/>
@@ -13472,14 +13472,14 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C544" t="inlineStr"/>
       <c r="D544" t="inlineStr"/>
       <c r="E544" t="inlineStr"/>
       <c r="F544" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="545">
@@ -13490,14 +13490,14 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C545" t="inlineStr"/>
       <c r="D545" t="inlineStr"/>
       <c r="E545" t="inlineStr"/>
       <c r="F545" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="546">
@@ -13508,7 +13508,7 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C546" t="inlineStr"/>
@@ -13526,22 +13526,18 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C547" t="inlineStr"/>
-      <c r="D547" t="inlineStr">
-        <is>
-          <t>1.4M</t>
-        </is>
-      </c>
+      <c r="D547" t="inlineStr"/>
       <c r="E547" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F547" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="548">
@@ -13648,14 +13644,14 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C552" t="inlineStr"/>
       <c r="D552" t="inlineStr"/>
       <c r="E552" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F552" t="n">
@@ -13670,18 +13666,22 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C553" t="inlineStr"/>
-      <c r="D553" t="inlineStr"/>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>1.4M</t>
+        </is>
+      </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F553" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="554">
@@ -14518,7 +14518,7 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C595" t="inlineStr"/>
@@ -14536,7 +14536,7 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C596" t="inlineStr"/>
@@ -14716,7 +14716,7 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C606" t="inlineStr"/>
@@ -14752,7 +14752,7 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C608" t="inlineStr"/>
@@ -14770,14 +14770,14 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C609" t="inlineStr"/>
       <c r="D609" t="inlineStr"/>
       <c r="E609" t="inlineStr"/>
       <c r="F609" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="610">
@@ -14788,14 +14788,14 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>Fed Musalem Speech</t>
         </is>
       </c>
       <c r="C610" t="inlineStr"/>
       <c r="D610" t="inlineStr"/>
       <c r="E610" t="inlineStr"/>
       <c r="F610" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="611">
@@ -14806,7 +14806,7 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C611" t="inlineStr"/>
@@ -14842,14 +14842,14 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C613" t="inlineStr"/>
       <c r="D613" t="inlineStr"/>
       <c r="E613" t="inlineStr"/>
       <c r="F613" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="614">
@@ -14860,14 +14860,14 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C614" t="inlineStr"/>
       <c r="D614" t="inlineStr"/>
       <c r="E614" t="inlineStr"/>
       <c r="F614" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="615">
@@ -14896,7 +14896,7 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C616" t="inlineStr"/>
@@ -14914,7 +14914,7 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>Fed Musalem Speech</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C617" t="inlineStr"/>
@@ -14932,7 +14932,7 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C618" t="inlineStr"/>
@@ -14950,7 +14950,7 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C619" t="inlineStr"/>
@@ -16110,7 +16110,7 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C675" t="inlineStr"/>
@@ -16128,7 +16128,7 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C676" t="inlineStr"/>
@@ -16200,7 +16200,7 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C680" t="inlineStr"/>
@@ -16290,7 +16290,7 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
       <c r="C685" t="inlineStr"/>
@@ -16308,7 +16308,7 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexFEB</t>
+          <t>Dallas Fed Services IndexFEB</t>
         </is>
       </c>
       <c r="C686" t="inlineStr"/>
@@ -16362,7 +16362,7 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexFEB</t>
+          <t>Dallas Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C689" t="inlineStr"/>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/21</t>
+          <t>MBA Mortgage Refinance IndexFEB/21</t>
         </is>
       </c>
       <c r="C701" t="inlineStr"/>
@@ -16596,7 +16596,7 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/21</t>
+          <t>MBA Mortgage Market IndexFEB/21</t>
         </is>
       </c>
       <c r="C702" t="inlineStr"/>
@@ -16614,14 +16614,14 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
+          <t>MBA Purchase IndexFEB/21</t>
         </is>
       </c>
       <c r="C703" t="inlineStr"/>
       <c r="D703" t="inlineStr"/>
       <c r="E703" t="inlineStr"/>
       <c r="F703" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="704">
@@ -16632,14 +16632,14 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
         </is>
       </c>
       <c r="C704" t="inlineStr"/>
       <c r="D704" t="inlineStr"/>
       <c r="E704" t="inlineStr"/>
       <c r="F704" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="705">
@@ -16650,7 +16650,7 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C705" t="inlineStr"/>
@@ -16668,7 +16668,7 @@
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C706" t="inlineStr"/>
@@ -16758,7 +16758,7 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>New Home Sales MoMJAN</t>
+          <t>New Home SalesJAN</t>
         </is>
       </c>
       <c r="C711" t="inlineStr"/>
@@ -16776,7 +16776,7 @@
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>New Home SalesJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C712" t="inlineStr"/>
@@ -16794,7 +16794,7 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>New Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C713" t="inlineStr"/>
@@ -17154,7 +17154,7 @@
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C733" t="inlineStr"/>
@@ -17172,7 +17172,7 @@
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C734" t="inlineStr"/>
@@ -17226,7 +17226,7 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C737" t="inlineStr"/>
@@ -17262,7 +17262,7 @@
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C739" t="inlineStr"/>
@@ -17352,7 +17352,7 @@
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>2-Year FRN Auction</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C744" t="inlineStr"/>
@@ -17388,7 +17388,7 @@
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>2-Year FRN Auction</t>
         </is>
       </c>
       <c r="C746" t="inlineStr"/>
@@ -17592,14 +17592,14 @@
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/22</t>
+          <t>Durable Goods Orders ex Defense MoMJAN</t>
         </is>
       </c>
       <c r="C756" t="inlineStr"/>
       <c r="D756" t="inlineStr"/>
       <c r="E756" t="inlineStr"/>
       <c r="F756" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="757">
@@ -17658,7 +17658,7 @@
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/22</t>
         </is>
       </c>
       <c r="C759" t="inlineStr"/>
@@ -17676,14 +17676,18 @@
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ 2nd EstQ4</t>
+          <t>PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C760" t="inlineStr"/>
-      <c r="D760" t="inlineStr"/>
+      <c r="D760" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
       <c r="E760" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F760" t="n">
@@ -17698,14 +17702,14 @@
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMJAN</t>
+          <t>Durable Goods Orders MoMJAN</t>
         </is>
       </c>
       <c r="C761" t="inlineStr"/>
       <c r="D761" t="inlineStr"/>
       <c r="E761" t="inlineStr"/>
       <c r="F761" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="762">
@@ -17716,22 +17720,22 @@
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ 2nd EstQ4</t>
+          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C762" t="inlineStr"/>
       <c r="D762" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="E762" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F762" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="763">
@@ -17742,20 +17746,12 @@
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ 2nd EstQ4</t>
+          <t>Continuing Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C763" t="inlineStr"/>
-      <c r="D763" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
-      <c r="E763" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+      <c r="D763" t="inlineStr"/>
+      <c r="E763" t="inlineStr"/>
       <c r="F763" t="n">
         <v>3</v>
       </c>
@@ -17768,12 +17764,20 @@
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/15</t>
+          <t>Core PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C764" t="inlineStr"/>
-      <c r="D764" t="inlineStr"/>
-      <c r="E764" t="inlineStr"/>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="E764" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="F764" t="n">
         <v>3</v>
       </c>
@@ -17786,22 +17790,22 @@
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
+          <t>GDP Price Index QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C765" t="inlineStr"/>
       <c r="D765" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="E765" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="F765" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="766">
@@ -17812,14 +17816,14 @@
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMJAN</t>
+          <t>Durable Goods Orders Ex Transp MoMJAN</t>
         </is>
       </c>
       <c r="C766" t="inlineStr"/>
       <c r="D766" t="inlineStr"/>
       <c r="E766" t="inlineStr"/>
       <c r="F766" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="767">
@@ -17830,18 +17834,14 @@
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ 2nd EstQ4</t>
+          <t>GDP Sales QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C767" t="inlineStr"/>
-      <c r="D767" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
+      <c r="D767" t="inlineStr"/>
       <c r="E767" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F767" t="n">
@@ -17856,14 +17856,14 @@
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/22</t>
+          <t>Initial Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C768" t="inlineStr"/>
       <c r="D768" t="inlineStr"/>
       <c r="E768" t="inlineStr"/>
       <c r="F768" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="769">
@@ -18084,15 +18084,11 @@
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>NY Fed Treasury Purchases 4 to 6 yrs</t>
+          <t>EIA Natural Gas Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C780" t="inlineStr"/>
-      <c r="D780" t="inlineStr">
-        <is>
-          <t>$50 million</t>
-        </is>
-      </c>
+      <c r="D780" t="inlineStr"/>
       <c r="E780" t="inlineStr"/>
       <c r="F780" t="n">
         <v>3</v>
@@ -18106,11 +18102,15 @@
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>EIA Natural Gas Stocks ChangeFEB/21</t>
+          <t>NY Fed Treasury Purchases 4 to 6 yrs</t>
         </is>
       </c>
       <c r="C781" t="inlineStr"/>
-      <c r="D781" t="inlineStr"/>
+      <c r="D781" t="inlineStr">
+        <is>
+          <t>$50 million</t>
+        </is>
+      </c>
       <c r="E781" t="inlineStr"/>
       <c r="F781" t="n">
         <v>3</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/27</t>
+          <t>15-Year Mortgage RateFEB/27</t>
         </is>
       </c>
       <c r="C791" t="inlineStr"/>
@@ -18322,7 +18322,7 @@
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/27</t>
+          <t>30-Year Mortgage RateFEB/27</t>
         </is>
       </c>
       <c r="C793" t="inlineStr"/>

--- a/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-02-27.xlsx
+++ b/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-02-27.xlsx
@@ -720,12 +720,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.041M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -742,18 +742,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.323M</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -764,22 +768,18 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -790,15 +790,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.416M</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>-0.1M</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
         <v>3</v>
@@ -812,12 +816,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -834,19 +838,15 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>6.406M</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>-0.1M</t>
-        </is>
-      </c>
+          <t>-0.416M</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
         <v>3</v>
@@ -860,18 +860,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>7.717M</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>0.7M</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -882,22 +886,18 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-1.178M</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>-2.75M</t>
-        </is>
-      </c>
+          <t>0.041M</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -908,12 +908,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.142M</t>
+          <t>0.099M</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1582,22 +1582,18 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Balance of TradeNOV</t>
+          <t>ExportsNOV</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>$-78.2B</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>$-78B</t>
-        </is>
-      </c>
+          <t>$273.4B</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>$-70B</t>
+          <t>$264B</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -1612,18 +1608,18 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ExportsNOV</t>
+          <t>ImportsNOV</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>$273.4B</t>
+          <t>$351.6B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>$264B</t>
+          <t>$334B</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -1638,18 +1634,22 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ImportsNOV</t>
+          <t>Balance of TradeNOV</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>$351.6B</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
+          <t>$-78.2B</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>$-78B</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>$334B</t>
+          <t>$-70B</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Used Car Prices YoYDEC</t>
+          <t>Used Car Prices MoMDEC</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -2254,12 +2254,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Used Car Prices MoMDEC</t>
+          <t>Used Car Prices YoYDEC</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -3148,22 +3148,26 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
+          <t>Michigan Consumer Sentiment PrelJAN</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr"/>
+          <t>73.2</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>73.8</t>
+        </is>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
@@ -3174,18 +3178,18 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelJAN</t>
+          <t>Michigan Current Conditions PrelJAN</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F113" t="n">
@@ -3200,18 +3204,18 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelJAN</t>
+          <t>Michigan Consumer Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F114" t="n">
@@ -3226,18 +3230,18 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelJAN</t>
+          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F115" t="n">
@@ -3252,26 +3256,22 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelJAN</t>
+          <t>Michigan Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>73.2</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>73.8</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="117">
@@ -3458,12 +3458,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>4.225%</t>
+          <t>4.180%</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
@@ -3480,12 +3480,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>4.180%</t>
+          <t>4.225%</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
@@ -4010,26 +4010,26 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYDEC</t>
+          <t>CPIDEC</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>315.6</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="148">
@@ -4040,26 +4040,22 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYDEC</t>
+          <t>CPI s.aDEC</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+          <t>317.685</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>317.4</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="149">
@@ -4070,26 +4066,26 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexJAN</t>
+          <t>Core Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>-12.60</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150">
@@ -4100,22 +4096,22 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMDEC</t>
+          <t>Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F150" t="n">
@@ -4130,22 +4126,22 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMDEC</t>
+          <t>Core Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F151" t="n">
@@ -4160,22 +4156,26 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>CPI s.aDEC</t>
+          <t>Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>317.685</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr"/>
+          <t>2.9%</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>2.9%</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>317.4</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153">
@@ -4186,22 +4186,22 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>CPIDEC</t>
+          <t>NY Empire State Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>-12.60</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>315.6</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="F153" t="n">
@@ -4252,22 +4252,18 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>2.60M</t>
-        </is>
-      </c>
+          <t>-1.304M</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="157">
@@ -4278,12 +4274,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>0.765M</t>
+          <t>0.646M</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
@@ -4300,15 +4296,19 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>-0.021M</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr"/>
+          <t>3.077M</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>1.1M</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="n">
         <v>3</v>
@@ -4322,18 +4322,22 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>0.397M</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr"/>
+          <t>-1.961M</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>-1.6M</t>
+        </is>
+      </c>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="160">
@@ -4344,22 +4348,18 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>-1.961M</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>-1.6M</t>
-        </is>
-      </c>
+          <t>-0.255M</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="161">
@@ -4370,12 +4370,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>-0.021M</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
@@ -4392,19 +4392,15 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>3.077M</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>1.1M</t>
-        </is>
-      </c>
+          <t>0.765M</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="n">
         <v>3</v>
@@ -4418,18 +4414,22 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>0.646M</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>2.60M</t>
+        </is>
+      </c>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="164">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>-1.304M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
@@ -4556,18 +4556,26 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr"/>
-      <c r="E170" t="inlineStr"/>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>-10</t>
+        </is>
+      </c>
       <c r="F170" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="171">
@@ -4578,22 +4586,22 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F171" t="n">
@@ -4608,22 +4616,22 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>217K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>210K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F172" t="n">
@@ -4638,18 +4646,22 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>1.8%</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="F173" t="n">
@@ -4664,26 +4676,18 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="inlineStr"/>
       <c r="F174" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="175">
@@ -4694,16 +4698,20 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>212.75K</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
-      <c r="E175" t="inlineStr"/>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>215.0K</t>
+        </is>
+      </c>
       <c r="F175" t="n">
         <v>3</v>
       </c>
@@ -4716,24 +4724,16 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>1.6%</t>
-        </is>
-      </c>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr"/>
       <c r="F176" t="n">
         <v>3</v>
       </c>
@@ -4746,20 +4746,16 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>39.00</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>4.0%</t>
-        </is>
-      </c>
+      <c r="E177" t="inlineStr"/>
       <c r="F177" t="n">
         <v>3</v>
       </c>
@@ -4772,26 +4768,26 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F178" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="179">
@@ -4802,26 +4798,18 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
+          <t>46.3</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr"/>
       <c r="F179" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="180">
@@ -4832,16 +4820,20 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
-      <c r="E180" t="inlineStr"/>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>4.0%</t>
+        </is>
+      </c>
       <c r="F180" t="n">
         <v>3</v>
       </c>
@@ -4854,26 +4846,26 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F181" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="182">
@@ -4884,22 +4876,22 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F182" t="n">
@@ -4914,26 +4906,22 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>1.8%</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="184">
@@ -4944,18 +4932,26 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>39.00</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr"/>
-      <c r="E184" t="inlineStr"/>
+          <t>217K</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>210K</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>209.0K</t>
+        </is>
+      </c>
       <c r="F184" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="185">
@@ -4966,16 +4962,24 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>11.9</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr"/>
-      <c r="E185" t="inlineStr"/>
+          <t>1859K</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>1870.0K</t>
+        </is>
+      </c>
       <c r="F185" t="n">
         <v>3</v>
       </c>
@@ -4988,20 +4992,16 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>212.75K</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>215.0K</t>
-        </is>
-      </c>
+      <c r="E186" t="inlineStr"/>
       <c r="F186" t="n">
         <v>3</v>
       </c>
@@ -5014,26 +5014,26 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoMNOV</t>
+          <t>NAHB Housing Market IndexJAN</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F187" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="188">
@@ -5044,22 +5044,22 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>NAHB Housing Market IndexJAN</t>
+          <t>Business Inventories MoMNOV</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F188" t="n">
@@ -5074,17 +5074,17 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Business Inventories MoMNOV</t>
+          <t>Retail Inventories Ex Autos MoMNOV</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -5093,7 +5093,7 @@
         </is>
       </c>
       <c r="F189" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="190">
@@ -5240,22 +5240,26 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Housing Starts MoMDEC</t>
+          <t>Housing StartsDEC</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>15.8%</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr"/>
+          <t>1.499M</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>1.32M</t>
+        </is>
+      </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>1.32M</t>
         </is>
       </c>
       <c r="F196" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="197">
@@ -5266,18 +5270,18 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelDEC</t>
+          <t>Housing Starts MoMDEC</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>15.8%</t>
         </is>
       </c>
       <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="F197" t="n">
@@ -5292,26 +5296,22 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Housing StartsDEC</t>
+          <t>Building Permits MoM PrelDEC</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>1.499M</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>1.32M</t>
-        </is>
-      </c>
+          <t>-0.7%</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr">
         <is>
-          <t>1.32M</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="F198" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="199">
@@ -5352,18 +5352,18 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYDEC</t>
+          <t>Industrial Production YoYDEC</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F200" t="n">
@@ -5378,26 +5378,26 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Industrial Production MoMDEC</t>
+          <t>Capacity UtilizationDEC</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="F201" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="202">
@@ -5438,26 +5438,26 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Capacity UtilizationDEC</t>
+          <t>Industrial Production MoMDEC</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F203" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="204">
@@ -5468,18 +5468,18 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Industrial Production YoYDEC</t>
+          <t>Manufacturing Production YoYDEC</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D204" t="inlineStr"/>
       <c r="E204" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F204" t="n">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>42-Day Bill Auction</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>4.025%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
@@ -5692,12 +5692,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>42-Day Bill Auction</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>4.025%</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
@@ -5942,22 +5942,18 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/11</t>
+          <t>Jobless Claims 4-week AverageJAN/18</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>1899K</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>1860K</t>
-        </is>
-      </c>
+          <t>213.5K</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr"/>
       <c r="E225" t="inlineStr">
         <is>
-          <t>1861K</t>
+          <t>213.0K</t>
         </is>
       </c>
       <c r="F225" t="n">
@@ -5972,22 +5968,26 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/18</t>
+          <t>Initial Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>213.5K</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr"/>
+          <t>223K</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>220K</t>
+        </is>
+      </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>213.0K</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="F226" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="227">
@@ -5998,26 +5998,26 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/18</t>
+          <t>Continuing Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>1899K</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>220K</t>
+          <t>1860K</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>1861K</t>
         </is>
       </c>
       <c r="F227" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="228">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D233" t="inlineStr"/>
@@ -6172,22 +6172,18 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>-0.148M</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr"/>
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="235">
@@ -6198,22 +6194,18 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>0.068M</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr"/>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="236">
@@ -6224,12 +6216,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -6246,19 +6238,15 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>6.96%</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr"/>
       <c r="E237" t="inlineStr"/>
       <c r="F237" t="n">
         <v>3</v>
@@ -6272,15 +6260,19 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>-1.125M</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="n">
         <v>3</v>
@@ -6294,12 +6286,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
@@ -6316,18 +6308,22 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>6.96%</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="241">
@@ -6338,18 +6334,22 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>0.184M</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="242">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -6382,12 +6382,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
@@ -6448,22 +6448,22 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashJAN</t>
+          <t>S&amp;P Global Services PMI FlashJAN</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="F246" t="n">
@@ -6478,22 +6478,22 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashJAN</t>
+          <t>S&amp;P Global Manufacturing PMI FlashJAN</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="F247" t="n">
@@ -6534,26 +6534,26 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F249" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="250">
@@ -6564,26 +6564,22 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr">
-        <is>
-          <t>77.9</t>
-        </is>
-      </c>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr"/>
       <c r="E250" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F250" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="251">
@@ -6594,26 +6590,26 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>4.24M</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.19M</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="F251" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="252">
@@ -6624,12 +6620,12 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -6654,26 +6650,26 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>4.24M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>4.19M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F253" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="254">
@@ -6684,26 +6680,26 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F254" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="255">
@@ -6714,22 +6710,26 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr"/>
+          <t>69.3</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>70.2</t>
+        </is>
+      </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F255" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="256">
@@ -7178,22 +7178,18 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>House Price Index MoMNOV</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D273" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>-0.1%</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr"/>
       <c r="E273" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F273" t="n">
@@ -7208,18 +7204,18 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>House Price IndexNOV</t>
+          <t>House Price Index YoYNOV</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>433.4</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="D274" t="inlineStr"/>
       <c r="E274" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F274" t="n">
@@ -7264,18 +7260,18 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>House Price Index YoYNOV</t>
+          <t>House Price IndexNOV</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>433.4</t>
         </is>
       </c>
       <c r="D276" t="inlineStr"/>
       <c r="E276" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>433</t>
         </is>
       </c>
       <c r="F276" t="n">
@@ -7290,18 +7286,22 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
+          <t>House Price Index MoMNOV</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="D277" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F277" t="n">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Money SupplyDEC</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>$21.53T</t>
+          <t>4.457%</t>
         </is>
       </c>
       <c r="D286" t="inlineStr"/>
@@ -7546,12 +7546,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>Money SupplyDEC</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>4.457%</t>
+          <t>$21.53T</t>
         </is>
       </c>
       <c r="D287" t="inlineStr"/>
@@ -7790,17 +7790,17 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>3.463M</t>
+          <t>2.957M</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>3.2M</t>
+          <t>1.5M</t>
         </is>
       </c>
       <c r="E297" t="inlineStr"/>
@@ -7816,15 +7816,19 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>0.532M</t>
-        </is>
-      </c>
-      <c r="D298" t="inlineStr"/>
+          <t>-4.994M</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E298" t="inlineStr"/>
       <c r="F298" t="n">
         <v>3</v>
@@ -7838,12 +7842,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>0.128M</t>
+          <t>-0.333M</t>
         </is>
       </c>
       <c r="D299" t="inlineStr"/>
@@ -7860,12 +7864,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>0.028M</t>
+          <t>-0.044M</t>
         </is>
       </c>
       <c r="D300" t="inlineStr"/>
@@ -7882,12 +7886,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>-0.044M</t>
+          <t>0.326M</t>
         </is>
       </c>
       <c r="D301" t="inlineStr"/>
@@ -7904,19 +7908,15 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>-4.994M</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.128M</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr"/>
       <c r="E302" t="inlineStr"/>
       <c r="F302" t="n">
         <v>3</v>
@@ -7930,12 +7930,12 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>0.326M</t>
+          <t>0.028M</t>
         </is>
       </c>
       <c r="D303" t="inlineStr"/>
@@ -7952,22 +7952,18 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>2.957M</t>
-        </is>
-      </c>
-      <c r="D304" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>0.532M</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr"/>
       <c r="E304" t="inlineStr"/>
       <c r="F304" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="305">
@@ -7978,18 +7974,22 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>-0.333M</t>
-        </is>
-      </c>
-      <c r="D305" t="inlineStr"/>
+          <t>3.463M</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>3.2M</t>
+        </is>
+      </c>
       <c r="E305" t="inlineStr"/>
       <c r="F305" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="306">
@@ -8070,22 +8070,18 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ AdvQ4</t>
+          <t>Real Consumer Spending QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>2.5%</t>
-        </is>
-      </c>
-      <c r="D309" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr"/>
       <c r="E309" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F309" t="n">
@@ -8100,26 +8096,22 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ AdvQ4</t>
+          <t>GDP Sales QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D310" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr"/>
       <c r="E310" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F310" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="311">
@@ -8130,22 +8122,18 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/18</t>
+          <t>PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>1858K</t>
-        </is>
-      </c>
-      <c r="D311" t="inlineStr">
-        <is>
-          <t>1890K</t>
-        </is>
-      </c>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr"/>
       <c r="E311" t="inlineStr">
         <is>
-          <t>1885.0K</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="F311" t="n">
@@ -8160,22 +8148,26 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/25</t>
+          <t>GDP Growth Rate QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>212.5K</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr"/>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>214.0K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F312" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="313">
@@ -8186,26 +8178,26 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ AdvQ4</t>
+          <t>Initial Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>207K</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>228.0K</t>
         </is>
       </c>
       <c r="F313" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="314">
@@ -8216,18 +8208,22 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ AdvQ4</t>
+          <t>Continuing Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>2.3%</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr"/>
+          <t>1858K</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>1890K</t>
+        </is>
+      </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>1885.0K</t>
         </is>
       </c>
       <c r="F314" t="n">
@@ -8242,22 +8238,26 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ AdvQ4</t>
+          <t>GDP Price Index QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F315" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="316">
@@ -8268,26 +8268,22 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/25</t>
+          <t>Jobless Claims 4-week AverageJAN/25</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>207K</t>
-        </is>
-      </c>
-      <c r="D316" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+          <t>212.5K</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr"/>
       <c r="E316" t="inlineStr">
         <is>
-          <t>228.0K</t>
+          <t>214.0K</t>
         </is>
       </c>
       <c r="F316" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="317">
@@ -8298,18 +8294,22 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ AdvQ4</t>
+          <t>Core PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr"/>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F317" t="n">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="D321" t="inlineStr"/>
@@ -8428,12 +8428,12 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D322" t="inlineStr"/>
@@ -8516,14 +8516,26 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C326" t="inlineStr"/>
-      <c r="D326" t="inlineStr"/>
-      <c r="E326" t="inlineStr"/>
+          <t>Personal Income MoMDEC</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F326" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="327">
@@ -8534,22 +8546,18 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
+          <t>Employment Cost - Wages QoQQ4</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D327" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr"/>
       <c r="E327" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F327" t="n">
@@ -8564,26 +8572,26 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F328" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="329">
@@ -8594,26 +8602,22 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
+          <t>Employment Cost - Benefits QoQQ4</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D329" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr"/>
       <c r="E329" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F329" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="330">
@@ -8624,22 +8628,22 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F330" t="n">
@@ -8654,24 +8658,12 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
-        </is>
-      </c>
-      <c r="C331" t="inlineStr">
-        <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D331" t="inlineStr">
-        <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="E331" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr"/>
+      <c r="D331" t="inlineStr"/>
+      <c r="E331" t="inlineStr"/>
       <c r="F331" t="n">
         <v>2</v>
       </c>
@@ -8684,22 +8676,22 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F332" t="n">
@@ -8714,22 +8706,26 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
+          <t>Core PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr"/>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F333" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="334">
@@ -8740,26 +8736,26 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F334" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="335">
@@ -8770,18 +8766,22 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D335" t="inlineStr"/>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F335" t="n">
@@ -8904,22 +8904,26 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentJAN</t>
+          <t>Construction Spending MoMDEC</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>50.3</t>
-        </is>
-      </c>
-      <c r="D340" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F340" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="341">
@@ -8930,26 +8934,22 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIJAN</t>
+          <t>ISM Manufacturing New OrdersJAN</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>50.9</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr">
-        <is>
-          <t>49.8</t>
-        </is>
-      </c>
+          <t>55.1</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr"/>
       <c r="E341" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F341" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="342">
@@ -8960,26 +8960,26 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesJAN</t>
+          <t>ISM Manufacturing PMIJAN</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="F342" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="343">
@@ -8990,22 +8990,22 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersJAN</t>
+          <t>ISM Manufacturing EmploymentJAN</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="D343" t="inlineStr"/>
       <c r="E343" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F343" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="344">
@@ -9016,22 +9016,22 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Construction Spending MoMDEC</t>
+          <t>ISM Manufacturing PricesJAN</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F344" t="n">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/31</t>
+          <t>MBA Mortgage Refinance IndexJAN/31</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>584.3</t>
         </is>
       </c>
       <c r="D363" t="inlineStr"/>
@@ -9472,18 +9472,18 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/31</t>
+          <t>MBA Mortgage Market IndexJAN/31</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>6.97%</t>
+          <t>224.8</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
       <c r="E364" t="inlineStr"/>
       <c r="F364" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="365">
@@ -9516,18 +9516,18 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/31</t>
+          <t>MBA 30-Year Mortgage RateJAN/31</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>224.8</t>
+          <t>6.97%</t>
         </is>
       </c>
       <c r="D366" t="inlineStr"/>
       <c r="E366" t="inlineStr"/>
       <c r="F366" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="367">
@@ -9538,12 +9538,12 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/31</t>
+          <t>MBA Mortgage ApplicationsJAN/31</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>584.3</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
@@ -9768,18 +9768,18 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityJAN</t>
+          <t>ISM Services New OrdersJAN</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="D376" t="inlineStr"/>
       <c r="E376" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F376" t="n">
@@ -9794,26 +9794,22 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>ISM Services PMIJAN</t>
+          <t>ISM Services PricesJAN</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>52.8</t>
-        </is>
-      </c>
-      <c r="D377" t="inlineStr">
-        <is>
-          <t>54.3</t>
-        </is>
-      </c>
+          <t>60.4</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr"/>
       <c r="E377" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="F377" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="378">
@@ -9850,22 +9846,26 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>ISM Services PricesJAN</t>
+          <t>ISM Services PMIJAN</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>60.4</t>
-        </is>
-      </c>
-      <c r="D379" t="inlineStr"/>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>54.3</t>
+        </is>
+      </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F379" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="380">
@@ -9876,18 +9876,18 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersJAN</t>
+          <t>ISM Services Business ActivityJAN</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="D380" t="inlineStr"/>
       <c r="E380" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="F380" t="n">
@@ -10434,12 +10434,12 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/06</t>
+          <t>15-Year Mortgage RateFEB/06</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>6.89%</t>
+          <t>6.05%</t>
         </is>
       </c>
       <c r="D403" t="inlineStr"/>
@@ -10456,12 +10456,12 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/06</t>
+          <t>30-Year Mortgage RateFEB/06</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>6.05%</t>
+          <t>6.89%</t>
         </is>
       </c>
       <c r="D404" t="inlineStr"/>
@@ -10536,22 +10536,22 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>U-6 Unemployment RateJAN</t>
+          <t>Participation RateJAN</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="D408" t="inlineStr"/>
       <c r="E408" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="F408" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="409">
@@ -10562,26 +10562,22 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Unemployment RateJAN</t>
+          <t>Government PayrollsJAN</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>4%</t>
-        </is>
-      </c>
-      <c r="D409" t="inlineStr">
-        <is>
-          <t>4.1%</t>
-        </is>
-      </c>
+          <t>32K</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr"/>
       <c r="E409" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>25K</t>
         </is>
       </c>
       <c r="F409" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="410">
@@ -10592,26 +10588,26 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsJAN</t>
+          <t>Average Hourly Earnings YoYJAN</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>3K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>-2K</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>-5K</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="F410" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="411">
@@ -10622,26 +10618,26 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMJAN</t>
+          <t>Non Farm PayrollsJAN</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>143K</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>170K</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>205K</t>
         </is>
       </c>
       <c r="F411" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="412">
@@ -10652,22 +10648,22 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Average Weekly HoursJAN</t>
+          <t>Nonfarm Payrolls PrivateJAN</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>111K</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>141K</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>180K</t>
         </is>
       </c>
       <c r="F412" t="n">
@@ -10682,26 +10678,26 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsJAN</t>
+          <t>Average Hourly Earnings MoMJAN</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>143K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>170K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>205K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F413" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="414">
@@ -10712,26 +10708,26 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoYJAN</t>
+          <t>Manufacturing PayrollsJAN</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>3K</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>-2K</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>-5K</t>
         </is>
       </c>
       <c r="F414" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="415">
@@ -10742,22 +10738,26 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Government PayrollsJAN</t>
+          <t>Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>32K</t>
-        </is>
-      </c>
-      <c r="D415" t="inlineStr"/>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>4.1%</t>
+        </is>
+      </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>25K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F415" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="416">
@@ -10768,22 +10768,18 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateJAN</t>
+          <t>U-6 Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>111K</t>
-        </is>
-      </c>
-      <c r="D416" t="inlineStr">
-        <is>
-          <t>141K</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr"/>
       <c r="E416" t="inlineStr">
         <is>
-          <t>180K</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="F416" t="n">
@@ -10798,22 +10794,26 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Participation RateJAN</t>
+          <t>Average Weekly HoursJAN</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>62.6%</t>
-        </is>
-      </c>
-      <c r="D417" t="inlineStr"/>
+          <t>34.1</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F417" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="418">
@@ -10904,22 +10904,18 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelFEB</t>
+          <t>Michigan 5 Year Inflation Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>68.7</t>
-        </is>
-      </c>
-      <c r="D422" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr"/>
       <c r="E422" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F422" t="n">
@@ -10934,22 +10930,22 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoMDEC</t>
+          <t>Michigan Current Conditions PrelFEB</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>73</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="F423" t="n">
@@ -10964,26 +10960,26 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelFEB</t>
+          <t>Wholesale Inventories MoMDEC</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F424" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="425">
@@ -10994,22 +10990,26 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelFEB</t>
+          <t>Michigan Consumer Sentiment PrelFEB</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="D425" t="inlineStr"/>
+          <t>67.8</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>71.1</t>
+        </is>
+      </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F425" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="426">
@@ -11020,22 +11020,18 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelFEB</t>
+          <t>Michigan Inflation Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>67.3</t>
-        </is>
-      </c>
-      <c r="D426" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr"/>
       <c r="E426" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F426" t="n">
@@ -11050,18 +11046,22 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelFEB</t>
+          <t>Michigan Consumer Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D427" t="inlineStr"/>
+          <t>67.3</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="F427" t="n">
@@ -11564,22 +11564,22 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>CPIJAN</t>
         </is>
       </c>
       <c r="C452" t="inlineStr"/>
       <c r="D452" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>317.42</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>317.3</t>
         </is>
       </c>
       <c r="F452" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="453">
@@ -11590,18 +11590,22 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>CPI s.aJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C453" t="inlineStr"/>
-      <c r="D453" t="inlineStr"/>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>318.2</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F453" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="454">
@@ -11612,18 +11616,18 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C454" t="inlineStr"/>
       <c r="D454" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F454" t="n">
@@ -11638,22 +11642,18 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>CPI s.aJAN</t>
         </is>
       </c>
       <c r="C455" t="inlineStr"/>
-      <c r="D455" t="inlineStr">
-        <is>
-          <t>2.9%</t>
-        </is>
-      </c>
+      <c r="D455" t="inlineStr"/>
       <c r="E455" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>318.2</t>
         </is>
       </c>
       <c r="F455" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="456">
@@ -11664,7 +11664,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C456" t="inlineStr"/>
@@ -11675,7 +11675,7 @@
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F456" t="n">
@@ -11690,22 +11690,22 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>CPIJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C457" t="inlineStr"/>
       <c r="D457" t="inlineStr">
         <is>
-          <t>317.42</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>317.3</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F457" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="458">
@@ -11716,7 +11716,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C458" t="inlineStr"/>
@@ -11734,14 +11734,14 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C459" t="inlineStr"/>
       <c r="D459" t="inlineStr"/>
       <c r="E459" t="inlineStr"/>
       <c r="F459" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="460">
@@ -11752,7 +11752,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C460" t="inlineStr"/>
@@ -11770,14 +11770,14 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C461" t="inlineStr"/>
       <c r="D461" t="inlineStr"/>
       <c r="E461" t="inlineStr"/>
       <c r="F461" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="462">
@@ -11788,7 +11788,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C462" t="inlineStr"/>
@@ -11806,7 +11806,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C463" t="inlineStr"/>
@@ -11824,14 +11824,14 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C464" t="inlineStr"/>
       <c r="D464" t="inlineStr"/>
       <c r="E464" t="inlineStr"/>
       <c r="F464" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="465">
@@ -11842,7 +11842,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C465" t="inlineStr"/>
@@ -11860,14 +11860,14 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C466" t="inlineStr"/>
       <c r="D466" t="inlineStr"/>
       <c r="E466" t="inlineStr"/>
       <c r="F466" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="467">
@@ -11976,14 +11976,14 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C472" t="inlineStr"/>
       <c r="D472" t="inlineStr"/>
       <c r="E472" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="F472" t="n">
@@ -11998,18 +11998,22 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C473" t="inlineStr"/>
-      <c r="D473" t="inlineStr"/>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F473" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="474">
@@ -12020,22 +12024,18 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C474" t="inlineStr"/>
-      <c r="D474" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
+      <c r="D474" t="inlineStr"/>
       <c r="E474" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F474" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="475">
@@ -12046,18 +12046,22 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C475" t="inlineStr"/>
-      <c r="D475" t="inlineStr"/>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F475" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="476">
@@ -12068,18 +12072,18 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C476" t="inlineStr"/>
       <c r="D476" t="inlineStr">
         <is>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
           <t>3.3%</t>
-        </is>
-      </c>
-      <c r="E476" t="inlineStr">
-        <is>
-          <t>3.5%</t>
         </is>
       </c>
       <c r="F476" t="n">
@@ -12094,22 +12098,18 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C477" t="inlineStr"/>
-      <c r="D477" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D477" t="inlineStr"/>
       <c r="E477" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="F477" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="478">
@@ -12120,22 +12120,22 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C478" t="inlineStr"/>
       <c r="D478" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F478" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="479">
@@ -12146,18 +12146,18 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C479" t="inlineStr"/>
       <c r="D479" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F479" t="n">
@@ -12172,14 +12172,14 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C480" t="inlineStr"/>
       <c r="D480" t="inlineStr"/>
       <c r="E480" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F480" t="n">
@@ -12194,14 +12194,14 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C481" t="inlineStr"/>
       <c r="D481" t="inlineStr"/>
       <c r="E481" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="F481" t="n">
@@ -12252,7 +12252,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C484" t="inlineStr"/>
@@ -12270,7 +12270,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C485" t="inlineStr"/>
@@ -12360,14 +12360,14 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="C490" t="inlineStr"/>
       <c r="D490" t="inlineStr"/>
       <c r="E490" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F490" t="n">
@@ -12382,18 +12382,22 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="C491" t="inlineStr"/>
-      <c r="D491" t="inlineStr"/>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F491" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="492">
@@ -12404,22 +12408,18 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="C492" t="inlineStr"/>
-      <c r="D492" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D492" t="inlineStr"/>
       <c r="E492" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F492" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="493">
@@ -12430,22 +12430,18 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="C493" t="inlineStr"/>
-      <c r="D493" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
+      <c r="D493" t="inlineStr"/>
       <c r="E493" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F493" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="494">
@@ -12456,22 +12452,18 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="C494" t="inlineStr"/>
-      <c r="D494" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D494" t="inlineStr"/>
       <c r="E494" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F494" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="495">
@@ -12482,18 +12474,22 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="C495" t="inlineStr"/>
-      <c r="D495" t="inlineStr"/>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="F495" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="496">
@@ -12504,18 +12500,22 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="C496" t="inlineStr"/>
-      <c r="D496" t="inlineStr"/>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F496" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="497">
@@ -12526,14 +12526,14 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="C497" t="inlineStr"/>
       <c r="D497" t="inlineStr"/>
       <c r="E497" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F497" t="n">
@@ -12548,7 +12548,7 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="C498" t="inlineStr"/>
@@ -12574,14 +12574,18 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Manufacturing Production MoMJAN</t>
         </is>
       </c>
       <c r="C499" t="inlineStr"/>
-      <c r="D499" t="inlineStr"/>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F499" t="n">
@@ -12596,22 +12600,18 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="C500" t="inlineStr"/>
-      <c r="D500" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="D500" t="inlineStr"/>
       <c r="E500" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F500" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="501">
@@ -12622,22 +12622,22 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="C501" t="inlineStr"/>
       <c r="D501" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F501" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="502">
@@ -12648,18 +12648,18 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="C502" t="inlineStr"/>
       <c r="D502" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>77.7%</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="F502" t="n">
@@ -12696,22 +12696,22 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoMDEC</t>
+          <t>Business Inventories MoMDEC</t>
         </is>
       </c>
       <c r="C504" t="inlineStr"/>
       <c r="D504" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F504" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="505">
@@ -12722,22 +12722,22 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Business Inventories MoMDEC</t>
+          <t>Retail Inventories Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C505" t="inlineStr"/>
       <c r="D505" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F505" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="506">
@@ -12748,7 +12748,7 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/14</t>
+          <t>Baker Hughes Total Rigs CountFEB/14</t>
         </is>
       </c>
       <c r="C506" t="inlineStr"/>
@@ -12766,7 +12766,7 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/14</t>
+          <t>Baker Hughes Oil Rig CountFEB/14</t>
         </is>
       </c>
       <c r="C507" t="inlineStr"/>
@@ -13288,14 +13288,18 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Net Long-term TIC FlowsDEC</t>
         </is>
       </c>
       <c r="C534" t="inlineStr"/>
-      <c r="D534" t="inlineStr"/>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>$149.1B</t>
+        </is>
+      </c>
       <c r="E534" t="inlineStr"/>
       <c r="F534" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="535">
@@ -13306,7 +13310,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="C535" t="inlineStr"/>
@@ -13324,18 +13328,14 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsDEC</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C536" t="inlineStr"/>
-      <c r="D536" t="inlineStr">
-        <is>
-          <t>$149.1B</t>
-        </is>
-      </c>
+      <c r="D536" t="inlineStr"/>
       <c r="E536" t="inlineStr"/>
       <c r="F536" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="537">
@@ -13454,7 +13454,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C543" t="inlineStr"/>
@@ -13472,14 +13472,14 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C544" t="inlineStr"/>
       <c r="D544" t="inlineStr"/>
       <c r="E544" t="inlineStr"/>
       <c r="F544" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="545">
@@ -13490,14 +13490,14 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C545" t="inlineStr"/>
       <c r="D545" t="inlineStr"/>
       <c r="E545" t="inlineStr"/>
       <c r="F545" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="546">
@@ -13508,7 +13508,7 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C546" t="inlineStr"/>
@@ -13526,14 +13526,14 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C547" t="inlineStr"/>
       <c r="D547" t="inlineStr"/>
       <c r="E547" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F547" t="n">
@@ -13644,18 +13644,22 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C552" t="inlineStr"/>
-      <c r="D552" t="inlineStr"/>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>1.4M</t>
+        </is>
+      </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F552" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="553">
@@ -13666,22 +13670,18 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C553" t="inlineStr"/>
-      <c r="D553" t="inlineStr">
-        <is>
-          <t>1.4M</t>
-        </is>
-      </c>
+      <c r="D553" t="inlineStr"/>
       <c r="E553" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F553" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="554">
@@ -14518,7 +14518,7 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C595" t="inlineStr"/>
@@ -14536,7 +14536,7 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C596" t="inlineStr"/>
@@ -14716,14 +14716,14 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>Fed Musalem Speech</t>
         </is>
       </c>
       <c r="C606" t="inlineStr"/>
       <c r="D606" t="inlineStr"/>
       <c r="E606" t="inlineStr"/>
       <c r="F606" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="607">
@@ -14752,7 +14752,7 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C608" t="inlineStr"/>
@@ -14770,7 +14770,7 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C609" t="inlineStr"/>
@@ -14788,7 +14788,7 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>Fed Musalem Speech</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C610" t="inlineStr"/>
@@ -14806,7 +14806,7 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C611" t="inlineStr"/>
@@ -14842,14 +14842,14 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C613" t="inlineStr"/>
       <c r="D613" t="inlineStr"/>
       <c r="E613" t="inlineStr"/>
       <c r="F613" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="614">
@@ -14860,14 +14860,14 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C614" t="inlineStr"/>
       <c r="D614" t="inlineStr"/>
       <c r="E614" t="inlineStr"/>
       <c r="F614" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="615">
@@ -14896,7 +14896,7 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C616" t="inlineStr"/>
@@ -14914,14 +14914,14 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C617" t="inlineStr"/>
       <c r="D617" t="inlineStr"/>
       <c r="E617" t="inlineStr"/>
       <c r="F617" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="618">
@@ -14932,7 +14932,7 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C618" t="inlineStr"/>
@@ -14950,7 +14950,7 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C619" t="inlineStr"/>
@@ -16110,7 +16110,7 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C675" t="inlineStr"/>
@@ -16128,7 +16128,7 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C676" t="inlineStr"/>
@@ -16200,7 +16200,7 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
       <c r="C680" t="inlineStr"/>
@@ -16290,7 +16290,7 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C685" t="inlineStr"/>
@@ -16308,7 +16308,7 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexFEB</t>
+          <t>Dallas Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C686" t="inlineStr"/>
@@ -16362,7 +16362,7 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexFEB</t>
+          <t>Dallas Fed Services IndexFEB</t>
         </is>
       </c>
       <c r="C689" t="inlineStr"/>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/21</t>
+          <t>MBA Mortgage Market IndexFEB/21</t>
         </is>
       </c>
       <c r="C701" t="inlineStr"/>
@@ -16596,7 +16596,7 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C702" t="inlineStr"/>
@@ -16614,7 +16614,7 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/21</t>
+          <t>MBA Mortgage Refinance IndexFEB/21</t>
         </is>
       </c>
       <c r="C703" t="inlineStr"/>
@@ -16632,14 +16632,14 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
+          <t>MBA Purchase IndexFEB/21</t>
         </is>
       </c>
       <c r="C704" t="inlineStr"/>
       <c r="D704" t="inlineStr"/>
       <c r="E704" t="inlineStr"/>
       <c r="F704" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="705">
@@ -16650,14 +16650,14 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
         </is>
       </c>
       <c r="C705" t="inlineStr"/>
       <c r="D705" t="inlineStr"/>
       <c r="E705" t="inlineStr"/>
       <c r="F705" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="706">
@@ -16668,7 +16668,7 @@
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C706" t="inlineStr"/>
@@ -16758,7 +16758,7 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>New Home SalesJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C711" t="inlineStr"/>
@@ -16776,7 +16776,7 @@
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>New Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C712" t="inlineStr"/>
@@ -16794,7 +16794,7 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>New Home Sales MoMJAN</t>
+          <t>New Home SalesJAN</t>
         </is>
       </c>
       <c r="C713" t="inlineStr"/>
@@ -17154,7 +17154,7 @@
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C733" t="inlineStr"/>
@@ -17172,7 +17172,7 @@
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C734" t="inlineStr"/>
@@ -17226,7 +17226,7 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C737" t="inlineStr"/>
@@ -17262,7 +17262,7 @@
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C739" t="inlineStr"/>
@@ -17352,7 +17352,7 @@
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>2-Year FRN Auction</t>
         </is>
       </c>
       <c r="C744" t="inlineStr"/>
@@ -17388,7 +17388,7 @@
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>2-Year FRN Auction</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C746" t="inlineStr"/>
@@ -17658,14 +17658,14 @@
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/22</t>
+          <t>Initial Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C759" t="inlineStr"/>
       <c r="D759" t="inlineStr"/>
       <c r="E759" t="inlineStr"/>
       <c r="F759" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="760">
@@ -17676,18 +17676,14 @@
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ 2nd EstQ4</t>
+          <t>GDP Sales QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C760" t="inlineStr"/>
-      <c r="D760" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
+      <c r="D760" t="inlineStr"/>
       <c r="E760" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F760" t="n">
@@ -17702,14 +17698,14 @@
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMJAN</t>
+          <t>Durable Goods Orders Ex Transp MoMJAN</t>
         </is>
       </c>
       <c r="C761" t="inlineStr"/>
       <c r="D761" t="inlineStr"/>
       <c r="E761" t="inlineStr"/>
       <c r="F761" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="762">
@@ -17720,22 +17716,22 @@
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
+          <t>GDP Price Index QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C762" t="inlineStr"/>
       <c r="D762" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="E762" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="F762" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="763">
@@ -17746,12 +17742,20 @@
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/15</t>
+          <t>Core PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C763" t="inlineStr"/>
-      <c r="D763" t="inlineStr"/>
-      <c r="E763" t="inlineStr"/>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="E763" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="F763" t="n">
         <v>3</v>
       </c>
@@ -17764,20 +17768,12 @@
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ 2nd EstQ4</t>
+          <t>Continuing Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C764" t="inlineStr"/>
-      <c r="D764" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
-      <c r="E764" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+      <c r="D764" t="inlineStr"/>
+      <c r="E764" t="inlineStr"/>
       <c r="F764" t="n">
         <v>3</v>
       </c>
@@ -17790,22 +17786,22 @@
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ 2nd EstQ4</t>
+          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C765" t="inlineStr"/>
       <c r="D765" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="E765" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F765" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="766">
@@ -17816,14 +17812,14 @@
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMJAN</t>
+          <t>Durable Goods Orders MoMJAN</t>
         </is>
       </c>
       <c r="C766" t="inlineStr"/>
       <c r="D766" t="inlineStr"/>
       <c r="E766" t="inlineStr"/>
       <c r="F766" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="767">
@@ -17834,14 +17830,18 @@
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ 2nd EstQ4</t>
+          <t>PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C767" t="inlineStr"/>
-      <c r="D767" t="inlineStr"/>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
       <c r="E767" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F767" t="n">
@@ -17856,14 +17856,14 @@
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/22</t>
+          <t>Jobless Claims 4-week AverageFEB/22</t>
         </is>
       </c>
       <c r="C768" t="inlineStr"/>
       <c r="D768" t="inlineStr"/>
       <c r="E768" t="inlineStr"/>
       <c r="F768" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="769">
@@ -18084,11 +18084,15 @@
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>EIA Natural Gas Stocks ChangeFEB/21</t>
+          <t>NY Fed Treasury Purchases 4 to 6 yrs</t>
         </is>
       </c>
       <c r="C780" t="inlineStr"/>
-      <c r="D780" t="inlineStr"/>
+      <c r="D780" t="inlineStr">
+        <is>
+          <t>$50 million</t>
+        </is>
+      </c>
       <c r="E780" t="inlineStr"/>
       <c r="F780" t="n">
         <v>3</v>
@@ -18102,15 +18106,11 @@
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>NY Fed Treasury Purchases 4 to 6 yrs</t>
+          <t>EIA Natural Gas Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C781" t="inlineStr"/>
-      <c r="D781" t="inlineStr">
-        <is>
-          <t>$50 million</t>
-        </is>
-      </c>
+      <c r="D781" t="inlineStr"/>
       <c r="E781" t="inlineStr"/>
       <c r="F781" t="n">
         <v>3</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/27</t>
+          <t>30-Year Mortgage RateFEB/27</t>
         </is>
       </c>
       <c r="C791" t="inlineStr"/>
@@ -18322,7 +18322,7 @@
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/27</t>
+          <t>15-Year Mortgage RateFEB/27</t>
         </is>
       </c>
       <c r="C793" t="inlineStr"/>
